--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5194,31 +5194,107 @@
       <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="13" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="C58" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="D58" t="n">
+        <v>100.53</v>
+      </c>
+      <c r="E58" t="n">
+        <v>101.89</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="I58" t="n">
+        <v>77.28</v>
+      </c>
+      <c r="J58" t="n">
+        <v>87.65000000000001</v>
+      </c>
+      <c r="K58" t="n">
+        <v>93.26000000000001</v>
+      </c>
+      <c r="L58" t="n">
+        <v>98.86</v>
+      </c>
+      <c r="M58" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="N58" t="n">
+        <v>114.83</v>
+      </c>
+      <c r="O58" t="n">
+        <v>118.05</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr"/>
+      <c r="Q58" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="8" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="10" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I58" s="14" t="n">
-        <v>77.28</v>
-      </c>
-      <c r="J58" s="14" t="n">
-        <v>87.65000000000001</v>
-      </c>
-      <c r="K58" s="14" t="n">
-        <v>93.26000000000001</v>
-      </c>
-      <c r="L58" s="14" t="n">
-        <v>98.86</v>
-      </c>
-      <c r="M58" s="14" t="n">
-        <v>106.85</v>
-      </c>
-      <c r="N58" s="14" t="n">
-        <v>114.83</v>
-      </c>
-      <c r="O58" s="14" t="n">
-        <v>118.05</v>
+      <c r="I59" s="14" t="n">
+        <v>96.11</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v>97.05</v>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v>102.31</v>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v>105.88</v>
+      </c>
+      <c r="O59" s="14" t="n">
+        <v>109.37</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -106,9 +106,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -123,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -669,50 +669,52 @@
         <v>1.75</v>
       </c>
       <c r="I2" t="n">
-        <v>59.44</v>
+        <v>59.54</v>
       </c>
       <c r="J2" t="n">
-        <v>60.1</v>
+        <v>60.23</v>
       </c>
       <c r="K2" t="n">
-        <v>61.55</v>
+        <v>61.6</v>
       </c>
       <c r="L2" t="n">
-        <v>62.99</v>
+        <v>62.97</v>
       </c>
       <c r="M2" t="n">
-        <v>64.05</v>
+        <v>64</v>
       </c>
       <c r="N2" t="n">
-        <v>65.11</v>
+        <v>65.03</v>
       </c>
       <c r="O2" t="n">
-        <v>66.94</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S2" s="8" t="inlineStr">
+        <v>66.73999999999999</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T2" s="9" t="inlineStr">
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W2" s="10" t="inlineStr">
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -771,30 +773,32 @@
       <c r="O3" t="n">
         <v>65.68000000000001</v>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T3" s="9" t="inlineStr">
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -849,34 +853,36 @@
       <c r="O4" t="n">
         <v>67.25</v>
       </c>
-      <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="7" t="inlineStr">
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="7" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T4" s="9" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -935,28 +941,30 @@
       <c r="O5" t="n">
         <v>70.61</v>
       </c>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T5" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W5" s="10" t="inlineStr">
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1015,30 +1023,32 @@
       <c r="O6" t="n">
         <v>66.47</v>
       </c>
-      <c r="P6" s="6" t="inlineStr"/>
-      <c r="Q6" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="11" t="inlineStr">
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T6" s="9" t="inlineStr">
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W6" s="10" t="inlineStr">
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1097,32 +1107,34 @@
       <c r="O7" t="n">
         <v>67</v>
       </c>
-      <c r="P7" s="6" t="inlineStr"/>
-      <c r="Q7" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T7" s="9" t="inlineStr">
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U7" s="9" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V7" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W7" s="10" t="inlineStr">
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1181,32 +1193,34 @@
       <c r="O8" t="n">
         <v>70.98999999999999</v>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="7" t="inlineStr">
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="7" t="inlineStr">
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="11" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T8" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W8" s="12" t="inlineStr">
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1261,30 +1275,32 @@
       <c r="O9" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="7" t="inlineStr">
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="11" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T9" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W9" s="12" t="inlineStr">
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1339,30 +1355,32 @@
       <c r="O10" t="n">
         <v>67.62</v>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
-      <c r="Q10" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="7" t="inlineStr">
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="11" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T10" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W10" s="12" t="inlineStr">
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1417,32 +1435,34 @@
       <c r="O11" t="n">
         <v>63.74</v>
       </c>
-      <c r="P11" s="6" t="inlineStr"/>
-      <c r="Q11" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T11" s="9" t="inlineStr">
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U11" s="9" t="inlineStr">
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V11" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W11" s="10" t="inlineStr">
+      <c r="V11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1501,28 +1521,30 @@
       <c r="O12" t="n">
         <v>68.83</v>
       </c>
-      <c r="P12" s="6" t="inlineStr"/>
-      <c r="Q12" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="8" t="inlineStr">
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T12" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W12" s="10" t="inlineStr">
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1581,30 +1603,32 @@
       <c r="O13" t="n">
         <v>64.7</v>
       </c>
-      <c r="P13" s="6" t="inlineStr"/>
-      <c r="Q13" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="7" t="inlineStr">
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="11" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T13" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W13" s="10" t="inlineStr">
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1663,32 +1687,34 @@
       <c r="O14" t="n">
         <v>64.17</v>
       </c>
-      <c r="P14" s="6" t="inlineStr"/>
-      <c r="Q14" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="7" t="inlineStr">
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="8" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T14" s="9" t="inlineStr">
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U14" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W14" s="10" t="inlineStr">
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1747,30 +1773,32 @@
       <c r="O15" t="n">
         <v>64.44</v>
       </c>
-      <c r="P15" s="6" t="inlineStr"/>
-      <c r="Q15" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="7" t="inlineStr">
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="11" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T15" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="10" t="inlineStr">
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1829,28 +1857,30 @@
       <c r="O16" t="n">
         <v>64.48</v>
       </c>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="11" t="inlineStr">
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T16" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="10" t="inlineStr">
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1909,30 +1939,32 @@
       <c r="O17" t="n">
         <v>62.18</v>
       </c>
-      <c r="P17" s="6" t="inlineStr"/>
-      <c r="Q17" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="8" t="inlineStr">
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T17" s="9" t="inlineStr">
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U17" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="10" t="inlineStr">
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1987,32 +2019,34 @@
       <c r="O18" t="n">
         <v>62.72</v>
       </c>
-      <c r="P18" s="6" t="inlineStr"/>
-      <c r="Q18" s="7" t="inlineStr">
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="7" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="11" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T18" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="12" t="inlineStr">
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2067,30 +2101,32 @@
       <c r="O19" t="n">
         <v>63.59</v>
       </c>
-      <c r="P19" s="6" t="inlineStr"/>
-      <c r="Q19" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="7" t="inlineStr">
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="11" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T19" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="12" t="inlineStr">
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2145,30 +2181,32 @@
       <c r="O20" t="n">
         <v>60.62</v>
       </c>
-      <c r="P20" s="6" t="inlineStr"/>
-      <c r="Q20" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="8" t="inlineStr">
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T20" s="9" t="inlineStr">
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="12" t="inlineStr">
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2227,32 +2265,34 @@
       <c r="O21" t="n">
         <v>61.16</v>
       </c>
-      <c r="P21" s="6" t="inlineStr"/>
-      <c r="Q21" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="8" t="inlineStr">
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T21" s="9" t="inlineStr">
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="9" t="inlineStr">
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V21" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="12" t="inlineStr">
+      <c r="V21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2311,34 +2351,36 @@
       <c r="O22" t="n">
         <v>60.5</v>
       </c>
-      <c r="P22" s="6" t="inlineStr"/>
-      <c r="Q22" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="7" t="inlineStr">
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="8" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T22" s="9" t="inlineStr">
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="9" t="inlineStr">
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V22" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="12" t="inlineStr">
+      <c r="V22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2397,30 +2439,32 @@
       <c r="O23" t="n">
         <v>63.78</v>
       </c>
-      <c r="P23" s="6" t="inlineStr"/>
-      <c r="Q23" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="8" t="inlineStr">
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T23" s="9" t="inlineStr">
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="12" t="inlineStr">
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2479,30 +2523,32 @@
       <c r="O24" t="n">
         <v>66.27</v>
       </c>
-      <c r="P24" s="6" t="inlineStr"/>
-      <c r="Q24" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="8" t="inlineStr">
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T24" s="9" t="inlineStr">
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U24" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="12" t="inlineStr">
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2561,34 +2607,36 @@
       <c r="O25" t="n">
         <v>64.02</v>
       </c>
-      <c r="P25" s="6" t="inlineStr"/>
-      <c r="Q25" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="8" t="inlineStr">
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T25" s="9" t="inlineStr">
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="9" t="inlineStr">
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V25" s="9" t="inlineStr">
+      <c r="V25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W25" s="10" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2643,30 +2691,32 @@
       <c r="O26" t="n">
         <v>72.81999999999999</v>
       </c>
-      <c r="P26" s="6" t="inlineStr"/>
-      <c r="Q26" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="7" t="inlineStr">
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="11" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T26" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="10" t="inlineStr">
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2725,30 +2775,32 @@
       <c r="O27" t="n">
         <v>69.94</v>
       </c>
-      <c r="P27" s="6" t="inlineStr"/>
-      <c r="Q27" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="11" t="inlineStr">
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T27" s="9" t="inlineStr">
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="10" t="inlineStr">
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2807,32 +2859,34 @@
       <c r="O28" t="n">
         <v>69.52</v>
       </c>
-      <c r="P28" s="6" t="inlineStr"/>
-      <c r="Q28" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="8" t="inlineStr">
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T28" s="9" t="inlineStr">
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="9" t="inlineStr">
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V28" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="10" t="inlineStr">
+      <c r="V28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2891,30 +2945,32 @@
       <c r="O29" t="n">
         <v>72.23</v>
       </c>
-      <c r="P29" s="6" t="inlineStr"/>
-      <c r="Q29" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="7" t="inlineStr">
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="8" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T29" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="10" t="inlineStr">
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2969,34 +3025,36 @@
       <c r="O30" t="n">
         <v>72.06</v>
       </c>
-      <c r="P30" s="6" t="inlineStr"/>
-      <c r="Q30" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="8" t="inlineStr">
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T30" s="9" t="inlineStr">
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="9" t="inlineStr">
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V30" s="9" t="inlineStr">
+      <c r="V30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W30" s="10" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3051,36 +3109,38 @@
       <c r="O31" t="n">
         <v>116.02</v>
       </c>
-      <c r="P31" s="6" t="inlineStr"/>
-      <c r="Q31" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="7" t="inlineStr">
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="8" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T31" s="9" t="inlineStr">
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="9" t="inlineStr">
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V31" s="9" t="inlineStr">
+      <c r="V31" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W31" s="10" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3135,28 +3195,30 @@
       <c r="O32" t="n">
         <v>162.23</v>
       </c>
-      <c r="P32" s="6" t="inlineStr"/>
-      <c r="Q32" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="11" t="inlineStr">
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T32" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="10" t="inlineStr">
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3215,32 +3277,34 @@
       <c r="O33" t="n">
         <v>112.92</v>
       </c>
-      <c r="P33" s="6" t="inlineStr"/>
-      <c r="Q33" s="7" t="inlineStr">
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R33" s="7" t="inlineStr">
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="8" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T33" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="10" t="inlineStr">
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3299,30 +3363,32 @@
       <c r="O34" t="n">
         <v>118.97</v>
       </c>
-      <c r="P34" s="6" t="inlineStr"/>
-      <c r="Q34" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="8" t="inlineStr">
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T34" s="9" t="inlineStr">
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="10" t="inlineStr">
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3377,32 +3443,34 @@
       <c r="O35" t="n">
         <v>131.44</v>
       </c>
-      <c r="P35" s="6" t="inlineStr"/>
-      <c r="Q35" s="7" t="inlineStr">
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="7" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="11" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T35" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="12" t="inlineStr">
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3461,30 +3529,32 @@
       <c r="O36" t="n">
         <v>144.21</v>
       </c>
-      <c r="P36" s="6" t="inlineStr"/>
-      <c r="Q36" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="7" t="inlineStr">
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="11" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T36" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W36" s="12" t="inlineStr">
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3539,30 +3609,32 @@
       <c r="O37" t="n">
         <v>130.7</v>
       </c>
-      <c r="P37" s="6" t="inlineStr"/>
-      <c r="Q37" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="8" t="inlineStr">
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T37" s="9" t="inlineStr">
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="12" t="inlineStr">
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3621,34 +3693,36 @@
       <c r="O38" t="n">
         <v>109.76</v>
       </c>
-      <c r="P38" s="6" t="inlineStr"/>
-      <c r="Q38" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="8" t="inlineStr">
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T38" s="9" t="inlineStr">
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U38" s="9" t="inlineStr">
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V38" s="9" t="inlineStr">
+      <c r="V38" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W38" s="12" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3707,30 +3781,32 @@
       <c r="O39" t="n">
         <v>127.27</v>
       </c>
-      <c r="P39" s="6" t="inlineStr"/>
-      <c r="Q39" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="7" t="inlineStr">
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="11" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T39" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W39" s="12" t="inlineStr">
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3785,30 +3861,32 @@
       <c r="O40" t="n">
         <v>126.26</v>
       </c>
-      <c r="P40" s="6" t="inlineStr"/>
-      <c r="Q40" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="8" t="inlineStr">
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T40" s="9" t="inlineStr">
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U40" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W40" s="12" t="inlineStr">
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3867,32 +3945,34 @@
       <c r="O41" t="n">
         <v>115.87</v>
       </c>
-      <c r="P41" s="6" t="inlineStr"/>
-      <c r="Q41" s="7" t="inlineStr">
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="7" t="inlineStr">
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="11" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T41" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W41" s="12" t="inlineStr">
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3951,30 +4031,32 @@
       <c r="O42" t="n">
         <v>124.21</v>
       </c>
-      <c r="P42" s="6" t="inlineStr"/>
-      <c r="Q42" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="7" t="inlineStr">
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="11" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T42" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="12" t="inlineStr">
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4029,32 +4111,34 @@
       <c r="O43" t="n">
         <v>103.05</v>
       </c>
-      <c r="P43" s="6" t="inlineStr"/>
-      <c r="Q43" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="8" t="inlineStr">
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T43" s="9" t="inlineStr">
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U43" s="9" t="inlineStr">
+      <c r="U43" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V43" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W43" s="12" t="inlineStr">
+      <c r="V43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4113,32 +4197,34 @@
       <c r="O44" t="n">
         <v>105.55</v>
       </c>
-      <c r="P44" s="6" t="inlineStr"/>
-      <c r="Q44" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="7" t="inlineStr">
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="11" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T44" s="9" t="inlineStr">
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U44" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="12" t="inlineStr">
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4193,30 +4279,32 @@
       <c r="O45" t="n">
         <v>107.74</v>
       </c>
-      <c r="P45" s="6" t="inlineStr"/>
-      <c r="Q45" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="7" t="inlineStr">
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="11" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T45" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="12" t="inlineStr">
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4271,32 +4359,34 @@
       <c r="O46" t="n">
         <v>91.26000000000001</v>
       </c>
-      <c r="P46" s="6" t="inlineStr"/>
-      <c r="Q46" s="7" t="inlineStr">
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="7" t="inlineStr">
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="11" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T46" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="12" t="inlineStr">
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4351,28 +4441,30 @@
       <c r="O47" t="n">
         <v>89.36</v>
       </c>
-      <c r="P47" s="6" t="inlineStr"/>
-      <c r="Q47" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="11" t="inlineStr">
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T47" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W47" s="12" t="inlineStr">
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4427,32 +4519,34 @@
       <c r="O48" t="n">
         <v>76.16</v>
       </c>
-      <c r="P48" s="6" t="inlineStr"/>
-      <c r="Q48" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="8" t="inlineStr">
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T48" s="9" t="inlineStr">
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U48" s="9" t="inlineStr">
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V48" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W48" s="12" t="inlineStr">
+      <c r="V48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4511,34 +4605,36 @@
       <c r="O49" t="n">
         <v>84.34</v>
       </c>
-      <c r="P49" s="6" t="inlineStr"/>
-      <c r="Q49" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="8" t="inlineStr">
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T49" s="9" t="inlineStr">
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U49" s="9" t="inlineStr">
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V49" s="9" t="inlineStr">
+      <c r="V49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W49" s="10" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4593,32 +4689,34 @@
       <c r="O50" t="n">
         <v>92.91</v>
       </c>
-      <c r="P50" s="6" t="inlineStr"/>
-      <c r="Q50" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="8" t="inlineStr">
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T50" s="9" t="inlineStr">
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U50" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="9" t="inlineStr">
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W50" s="10" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4673,30 +4771,32 @@
       <c r="O51" t="n">
         <v>106.73</v>
       </c>
-      <c r="P51" s="6" t="inlineStr"/>
-      <c r="Q51" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="7" t="inlineStr">
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="11" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T51" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W51" s="10" t="inlineStr">
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4755,32 +4855,34 @@
       <c r="O52" t="n">
         <v>95.95999999999999</v>
       </c>
-      <c r="P52" s="6" t="inlineStr"/>
-      <c r="Q52" s="7" t="inlineStr">
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="7" t="inlineStr">
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="11" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T52" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W52" s="10" t="inlineStr">
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4839,30 +4941,32 @@
       <c r="O53" t="n">
         <v>90.42</v>
       </c>
-      <c r="P53" s="6" t="inlineStr"/>
-      <c r="Q53" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="8" t="inlineStr">
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T53" s="9" t="inlineStr">
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U53" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W53" s="10" t="inlineStr">
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4917,30 +5021,32 @@
       <c r="O54" t="n">
         <v>91.43000000000001</v>
       </c>
-      <c r="P54" s="6" t="inlineStr"/>
-      <c r="Q54" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="8" t="inlineStr">
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T54" s="9" t="inlineStr">
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U54" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="10" t="inlineStr">
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4995,32 +5101,34 @@
       <c r="O55" t="n">
         <v>96.5</v>
       </c>
-      <c r="P55" s="6" t="inlineStr"/>
-      <c r="Q55" s="7" t="inlineStr">
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R55" s="7" t="inlineStr">
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="11" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T55" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="10" t="inlineStr">
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5079,32 +5187,34 @@
       <c r="O56" t="n">
         <v>93.52</v>
       </c>
-      <c r="P56" s="6" t="inlineStr"/>
-      <c r="Q56" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="8" t="inlineStr">
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T56" s="9" t="inlineStr">
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U56" s="9" t="inlineStr">
+      <c r="U56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V56" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="10" t="inlineStr">
+      <c r="V56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5159,34 +5269,36 @@
       <c r="O57" t="n">
         <v>102.17</v>
       </c>
-      <c r="P57" s="6" t="inlineStr"/>
-      <c r="Q57" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="8" t="inlineStr">
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T57" s="9" t="inlineStr">
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U57" s="9" t="inlineStr">
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V57" s="9" t="inlineStr">
+      <c r="V57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W57" s="10" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5200,25 +5312,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>102.25</v>
+        <v>102.01</v>
       </c>
       <c r="C58" t="n">
-        <v>104.95</v>
+        <v>102.85</v>
       </c>
       <c r="D58" t="n">
-        <v>100.53</v>
+        <v>101.83</v>
       </c>
       <c r="E58" t="n">
-        <v>101.89</v>
+        <v/>
       </c>
       <c r="F58" t="n">
-        <v>1.84</v>
+        <v/>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0184</v>
+        <v/>
       </c>
       <c r="H58" t="n">
-        <v>4.42</v>
+        <v>1.02</v>
       </c>
       <c r="I58" t="n">
         <v>77.28</v>
@@ -5241,33 +5353,41 @@
       <c r="O58" t="n">
         <v>118.05</v>
       </c>
-      <c r="P58" s="6" t="inlineStr"/>
-      <c r="Q58" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="8" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="10" t="inlineStr">
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
@@ -5276,25 +5396,25 @@
         </is>
       </c>
       <c r="I59" s="14" t="n">
-        <v>96.11</v>
+        <v>100.81</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>97.05</v>
+        <v/>
       </c>
       <c r="K59" s="14" t="n">
-        <v>99.68000000000001</v>
+        <v/>
       </c>
       <c r="L59" s="14" t="n">
-        <v>102.31</v>
+        <v/>
       </c>
       <c r="M59" s="14" t="n">
-        <v>104.1</v>
+        <v/>
       </c>
       <c r="N59" s="14" t="n">
-        <v>105.88</v>
+        <v/>
       </c>
       <c r="O59" s="14" t="n">
-        <v>109.37</v>
+        <v>103.87</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5315,7 +5315,7 @@
         <v>102.01</v>
       </c>
       <c r="C58" t="n">
-        <v>102.85</v>
+        <v>102.98</v>
       </c>
       <c r="D58" t="n">
         <v>101.83</v>
@@ -5330,7 +5330,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="I58" t="n">
         <v>77.28</v>
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="I59" s="14" t="n">
-        <v>100.81</v>
+        <v>100.68</v>
       </c>
       <c r="J59" s="14" t="n">
         <v/>
@@ -5414,7 +5414,7 @@
         <v/>
       </c>
       <c r="O59" s="14" t="n">
-        <v>103.87</v>
+        <v>104.13</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -106,6 +106,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -120,9 +123,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -689,32 +689,30 @@
       <c r="O2" t="n">
         <v>66.73999999999999</v>
       </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
+      <c r="P2" s="6" t="inlineStr"/>
+      <c r="Q2" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
+      <c r="T2" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W2" s="9" t="inlineStr">
+      <c r="U2" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W2" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -773,32 +771,30 @@
       <c r="O3" t="n">
         <v>65.68000000000001</v>
       </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
+      <c r="P3" s="6" t="inlineStr"/>
+      <c r="Q3" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T3" s="8" t="inlineStr">
+      <c r="T3" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W3" s="9" t="inlineStr">
+      <c r="U3" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W3" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -853,36 +849,34 @@
       <c r="O4" t="n">
         <v>67.25</v>
       </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr"/>
+      <c r="Q4" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="T4" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="U4" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W4" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -941,30 +935,28 @@
       <c r="O5" t="n">
         <v>70.61</v>
       </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="P5" s="6" t="inlineStr"/>
+      <c r="Q5" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="11" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="T5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1023,32 +1015,30 @@
       <c r="O6" t="n">
         <v>66.47</v>
       </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="P6" s="6" t="inlineStr"/>
+      <c r="Q6" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="11" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="T6" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="U6" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W6" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1107,34 +1097,32 @@
       <c r="O7" t="n">
         <v>67</v>
       </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="P7" s="6" t="inlineStr"/>
+      <c r="Q7" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="T7" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="U7" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="V7" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1193,34 +1181,32 @@
       <c r="O8" t="n">
         <v>70.98999999999999</v>
       </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="P8" s="6" t="inlineStr"/>
+      <c r="Q8" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="T8" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1275,32 +1261,30 @@
       <c r="O9" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="P9" s="6" t="inlineStr"/>
+      <c r="Q9" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="T9" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W9" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1355,32 +1339,30 @@
       <c r="O10" t="n">
         <v>67.62</v>
       </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="T10" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1435,34 +1417,32 @@
       <c r="O11" t="n">
         <v>63.74</v>
       </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="P11" s="6" t="inlineStr"/>
+      <c r="Q11" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T11" s="8" t="inlineStr">
+      <c r="T11" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
+      <c r="U11" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="V11" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1521,30 +1501,28 @@
       <c r="O12" t="n">
         <v>68.83</v>
       </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="P12" s="6" t="inlineStr"/>
+      <c r="Q12" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="8" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="T12" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1603,32 +1581,30 @@
       <c r="O13" t="n">
         <v>64.7</v>
       </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="P13" s="6" t="inlineStr"/>
+      <c r="Q13" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="T13" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W13" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1687,34 +1663,32 @@
       <c r="O14" t="n">
         <v>64.17</v>
       </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="P14" s="6" t="inlineStr"/>
+      <c r="Q14" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="8" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T14" s="8" t="inlineStr">
+      <c r="T14" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="U14" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W14" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1773,32 +1747,30 @@
       <c r="O15" t="n">
         <v>64.44</v>
       </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="P15" s="6" t="inlineStr"/>
+      <c r="Q15" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="T15" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W15" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1857,30 +1829,28 @@
       <c r="O16" t="n">
         <v>64.48</v>
       </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="P16" s="6" t="inlineStr"/>
+      <c r="Q16" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="11" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="T16" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1939,32 +1909,30 @@
       <c r="O17" t="n">
         <v>62.18</v>
       </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="P17" s="6" t="inlineStr"/>
+      <c r="Q17" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T17" s="8" t="inlineStr">
+      <c r="T17" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="U17" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W17" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2019,34 +1987,32 @@
       <c r="O18" t="n">
         <v>62.72</v>
       </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="P18" s="6" t="inlineStr"/>
+      <c r="Q18" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="T18" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2101,32 +2067,30 @@
       <c r="O19" t="n">
         <v>63.59</v>
       </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="P19" s="6" t="inlineStr"/>
+      <c r="Q19" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="T19" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W19" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2181,32 +2145,30 @@
       <c r="O20" t="n">
         <v>60.62</v>
       </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="P20" s="6" t="inlineStr"/>
+      <c r="Q20" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="8" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="T20" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="U20" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2265,34 +2227,32 @@
       <c r="O21" t="n">
         <v>61.16</v>
       </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="P21" s="6" t="inlineStr"/>
+      <c r="Q21" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="8" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T21" s="8" t="inlineStr">
+      <c r="T21" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
+      <c r="U21" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="V21" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W21" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2351,36 +2311,34 @@
       <c r="O22" t="n">
         <v>60.5</v>
       </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="P22" s="6" t="inlineStr"/>
+      <c r="Q22" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T22" s="8" t="inlineStr">
+      <c r="T22" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
+      <c r="U22" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="V22" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W22" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2439,32 +2397,30 @@
       <c r="O23" t="n">
         <v>63.78</v>
       </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="P23" s="6" t="inlineStr"/>
+      <c r="Q23" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="8" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T23" s="8" t="inlineStr">
+      <c r="T23" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="U23" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2523,32 +2479,30 @@
       <c r="O24" t="n">
         <v>66.27</v>
       </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="P24" s="6" t="inlineStr"/>
+      <c r="Q24" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T24" s="8" t="inlineStr">
+      <c r="T24" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="U24" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2607,36 +2561,34 @@
       <c r="O25" t="n">
         <v>64.02</v>
       </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="P25" s="6" t="inlineStr"/>
+      <c r="Q25" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T25" s="8" t="inlineStr">
+      <c r="T25" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
+      <c r="U25" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V25" s="8" t="inlineStr">
+      <c r="V25" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2691,32 +2643,30 @@
       <c r="O26" t="n">
         <v>72.81999999999999</v>
       </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="P26" s="6" t="inlineStr"/>
+      <c r="Q26" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="11" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="T26" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2775,32 +2725,30 @@
       <c r="O27" t="n">
         <v>69.94</v>
       </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="P27" s="6" t="inlineStr"/>
+      <c r="Q27" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="11" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T27" s="8" t="inlineStr">
+      <c r="T27" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="U27" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2859,34 +2807,32 @@
       <c r="O28" t="n">
         <v>69.52</v>
       </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="P28" s="6" t="inlineStr"/>
+      <c r="Q28" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T28" s="8" t="inlineStr">
+      <c r="T28" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
+      <c r="U28" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="V28" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W28" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2945,32 +2891,30 @@
       <c r="O29" t="n">
         <v>72.23</v>
       </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="P29" s="6" t="inlineStr"/>
+      <c r="Q29" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="8" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="T29" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W29" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3025,36 +2969,34 @@
       <c r="O30" t="n">
         <v>72.06</v>
       </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="P30" s="6" t="inlineStr"/>
+      <c r="Q30" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T30" s="8" t="inlineStr">
+      <c r="T30" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="inlineStr">
+      <c r="U30" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V30" s="8" t="inlineStr">
+      <c r="V30" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3109,38 +3051,36 @@
       <c r="O31" t="n">
         <v>116.02</v>
       </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="P31" s="6" t="inlineStr"/>
+      <c r="Q31" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T31" s="8" t="inlineStr">
+      <c r="T31" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="inlineStr">
+      <c r="U31" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V31" s="8" t="inlineStr">
+      <c r="V31" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3195,30 +3135,28 @@
       <c r="O32" t="n">
         <v>162.23</v>
       </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="P32" s="6" t="inlineStr"/>
+      <c r="Q32" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="11" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="T32" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3277,34 +3215,32 @@
       <c r="O33" t="n">
         <v>112.92</v>
       </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="P33" s="6" t="inlineStr"/>
+      <c r="Q33" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="8" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="T33" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W33" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3363,32 +3299,30 @@
       <c r="O34" t="n">
         <v>118.97</v>
       </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="P34" s="6" t="inlineStr"/>
+      <c r="Q34" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T34" s="8" t="inlineStr">
+      <c r="T34" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="U34" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3443,34 +3377,32 @@
       <c r="O35" t="n">
         <v>131.44</v>
       </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="P35" s="6" t="inlineStr"/>
+      <c r="Q35" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="T35" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3529,32 +3461,30 @@
       <c r="O36" t="n">
         <v>144.21</v>
       </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="P36" s="6" t="inlineStr"/>
+      <c r="Q36" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="T36" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W36" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3609,32 +3539,30 @@
       <c r="O37" t="n">
         <v>130.7</v>
       </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="P37" s="6" t="inlineStr"/>
+      <c r="Q37" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T37" s="8" t="inlineStr">
+      <c r="T37" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="U37" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W37" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3693,36 +3621,34 @@
       <c r="O38" t="n">
         <v>109.76</v>
       </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="P38" s="6" t="inlineStr"/>
+      <c r="Q38" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="T38" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U38" s="8" t="inlineStr">
+      <c r="U38" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V38" s="8" t="inlineStr">
+      <c r="V38" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3781,32 +3707,30 @@
       <c r="O39" t="n">
         <v>127.27</v>
       </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="P39" s="6" t="inlineStr"/>
+      <c r="Q39" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="T39" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W39" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3861,32 +3785,30 @@
       <c r="O40" t="n">
         <v>126.26</v>
       </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="P40" s="6" t="inlineStr"/>
+      <c r="Q40" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="T40" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="U40" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W40" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3945,34 +3867,32 @@
       <c r="O41" t="n">
         <v>115.87</v>
       </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="P41" s="6" t="inlineStr"/>
+      <c r="Q41" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="T41" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W41" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4031,32 +3951,30 @@
       <c r="O42" t="n">
         <v>124.21</v>
       </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="P42" s="6" t="inlineStr"/>
+      <c r="Q42" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="T42" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W42" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4111,34 +4029,32 @@
       <c r="O43" t="n">
         <v>103.05</v>
       </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="P43" s="6" t="inlineStr"/>
+      <c r="Q43" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T43" s="8" t="inlineStr">
+      <c r="T43" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U43" s="8" t="inlineStr">
+      <c r="U43" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="V43" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W43" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4197,34 +4113,32 @@
       <c r="O44" t="n">
         <v>105.55</v>
       </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="P44" s="6" t="inlineStr"/>
+      <c r="Q44" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T44" s="8" t="inlineStr">
+      <c r="T44" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="U44" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4279,32 +4193,30 @@
       <c r="O45" t="n">
         <v>107.74</v>
       </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="P45" s="6" t="inlineStr"/>
+      <c r="Q45" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="T45" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W45" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4359,34 +4271,32 @@
       <c r="O46" t="n">
         <v>91.26000000000001</v>
       </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="P46" s="6" t="inlineStr"/>
+      <c r="Q46" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="T46" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W46" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4441,30 +4351,28 @@
       <c r="O47" t="n">
         <v>89.36</v>
       </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="P47" s="6" t="inlineStr"/>
+      <c r="Q47" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="11" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="T47" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W47" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4519,34 +4427,32 @@
       <c r="O48" t="n">
         <v>76.16</v>
       </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="P48" s="6" t="inlineStr"/>
+      <c r="Q48" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T48" s="8" t="inlineStr">
+      <c r="T48" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U48" s="8" t="inlineStr">
+      <c r="U48" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="V48" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W48" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4605,36 +4511,34 @@
       <c r="O49" t="n">
         <v>84.34</v>
       </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="P49" s="6" t="inlineStr"/>
+      <c r="Q49" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T49" s="8" t="inlineStr">
+      <c r="T49" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U49" s="8" t="inlineStr">
+      <c r="U49" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V49" s="8" t="inlineStr">
+      <c r="V49" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4689,34 +4593,32 @@
       <c r="O50" t="n">
         <v>92.91</v>
       </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="P50" s="6" t="inlineStr"/>
+      <c r="Q50" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T50" s="8" t="inlineStr">
+      <c r="T50" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
+      <c r="U50" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4771,32 +4673,30 @@
       <c r="O51" t="n">
         <v>106.73</v>
       </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="P51" s="6" t="inlineStr"/>
+      <c r="Q51" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="T51" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W51" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4855,34 +4755,32 @@
       <c r="O52" t="n">
         <v>95.95999999999999</v>
       </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="P52" s="6" t="inlineStr"/>
+      <c r="Q52" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="T52" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W52" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4941,32 +4839,30 @@
       <c r="O53" t="n">
         <v>90.42</v>
       </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="P53" s="6" t="inlineStr"/>
+      <c r="Q53" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T53" s="8" t="inlineStr">
+      <c r="T53" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="U53" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W53" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5021,32 +4917,30 @@
       <c r="O54" t="n">
         <v>91.43000000000001</v>
       </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="P54" s="6" t="inlineStr"/>
+      <c r="Q54" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="T54" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="U54" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W54" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5101,34 +4995,32 @@
       <c r="O55" t="n">
         <v>96.5</v>
       </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="P55" s="6" t="inlineStr"/>
+      <c r="Q55" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="11" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="T55" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W55" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5187,34 +5079,32 @@
       <c r="O56" t="n">
         <v>93.52</v>
       </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="P56" s="6" t="inlineStr"/>
+      <c r="Q56" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T56" s="8" t="inlineStr">
+      <c r="T56" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U56" s="8" t="inlineStr">
+      <c r="U56" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="V56" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W56" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5269,36 +5159,34 @@
       <c r="O57" t="n">
         <v>102.17</v>
       </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="P57" s="6" t="inlineStr"/>
+      <c r="Q57" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="8" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T57" s="8" t="inlineStr">
+      <c r="T57" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U57" s="8" t="inlineStr">
+      <c r="U57" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V57" s="8" t="inlineStr">
+      <c r="V57" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5312,25 +5200,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>102.01</v>
+        <v>102.25</v>
       </c>
       <c r="C58" t="n">
-        <v>102.98</v>
+        <v>104.95</v>
       </c>
       <c r="D58" t="n">
-        <v>101.83</v>
+        <v>100.53</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>101.39</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>1.34</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0134</v>
       </c>
       <c r="H58" t="n">
-        <v>1.15</v>
+        <v>4.42</v>
       </c>
       <c r="I58" t="n">
         <v>77.28</v>
@@ -5353,41 +5241,33 @@
       <c r="O58" t="n">
         <v>118.05</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="P58" s="6" t="inlineStr"/>
+      <c r="Q58" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="8" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="13" t="inlineStr">
@@ -5396,25 +5276,25 @@
         </is>
       </c>
       <c r="I59" s="14" t="n">
-        <v>100.68</v>
+        <v>96.11</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v/>
+        <v>96.3</v>
       </c>
       <c r="K59" s="14" t="n">
-        <v/>
+        <v>99.18000000000001</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v/>
+        <v>102.06</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v/>
+        <v>103.6</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v/>
+        <v>105.13</v>
       </c>
       <c r="O59" s="14" t="n">
-        <v>104.13</v>
+        <v>109.37</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5209,13 +5209,13 @@
         <v>100.53</v>
       </c>
       <c r="E58" t="n">
-        <v>101.39</v>
+        <v>102.98</v>
       </c>
       <c r="F58" t="n">
-        <v>1.34</v>
+        <v>2.93</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0293</v>
       </c>
       <c r="H58" t="n">
         <v>4.42</v>
@@ -5250,11 +5250,13 @@
       </c>
       <c r="S58" s="8" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="9" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="9" t="n">
         <v/>
@@ -5279,19 +5281,19 @@
         <v>96.11</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>96.3</v>
+        <v>98.68000000000001</v>
       </c>
       <c r="K59" s="14" t="n">
-        <v>99.18000000000001</v>
+        <v>100.77</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>102.06</v>
+        <v>102.86</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>103.6</v>
+        <v>105.19</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>105.13</v>
+        <v>107.52</v>
       </c>
       <c r="O59" s="14" t="n">
         <v>109.37</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5203,22 +5203,22 @@
         <v>102.25</v>
       </c>
       <c r="C58" t="n">
-        <v>104.95</v>
+        <v>106.75</v>
       </c>
       <c r="D58" t="n">
         <v>100.53</v>
       </c>
       <c r="E58" t="n">
-        <v>102.98</v>
+        <v>105.48</v>
       </c>
       <c r="F58" t="n">
-        <v>2.93</v>
+        <v>5.43</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0293</v>
+        <v>0.0543</v>
       </c>
       <c r="H58" t="n">
-        <v>4.42</v>
+        <v>6.22</v>
       </c>
       <c r="I58" t="n">
         <v>77.28</v>
@@ -5278,25 +5278,25 @@
         </is>
       </c>
       <c r="I59" s="14" t="n">
-        <v>96.11</v>
+        <v>94.31</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>98.68000000000001</v>
+        <v>100.18</v>
       </c>
       <c r="K59" s="14" t="n">
-        <v>100.77</v>
+        <v>102.37</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>102.86</v>
+        <v>104.56</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>105.19</v>
+        <v>108.59</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>107.52</v>
+        <v>112.62</v>
       </c>
       <c r="O59" s="14" t="n">
-        <v>109.37</v>
+        <v>112.97</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -669,25 +669,25 @@
         <v>1.75</v>
       </c>
       <c r="I2" t="n">
-        <v>59.54</v>
+        <v>59.73</v>
       </c>
       <c r="J2" t="n">
-        <v>60.23</v>
+        <v>60.47</v>
       </c>
       <c r="K2" t="n">
-        <v>61.6</v>
+        <v>61.69</v>
       </c>
       <c r="L2" t="n">
-        <v>62.97</v>
+        <v>62.92</v>
       </c>
       <c r="M2" t="n">
-        <v>64</v>
+        <v>63.91</v>
       </c>
       <c r="N2" t="n">
-        <v>65.03</v>
+        <v>64.89</v>
       </c>
       <c r="O2" t="n">
-        <v>66.73999999999999</v>
+        <v>66.36</v>
       </c>
       <c r="P2" s="6" t="inlineStr"/>
       <c r="Q2" s="7" t="n">
@@ -5203,22 +5203,22 @@
         <v>102.25</v>
       </c>
       <c r="C58" t="n">
-        <v>106.75</v>
+        <v>105.63</v>
       </c>
       <c r="D58" t="n">
         <v>100.53</v>
       </c>
       <c r="E58" t="n">
-        <v>105.48</v>
+        <v>105.28</v>
       </c>
       <c r="F58" t="n">
-        <v>5.43</v>
+        <v>5.23</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0543</v>
+        <v>0.0523</v>
       </c>
       <c r="H58" t="n">
-        <v>6.22</v>
+        <v>5.1</v>
       </c>
       <c r="I58" t="n">
         <v>77.28</v>
@@ -5278,25 +5278,25 @@
         </is>
       </c>
       <c r="I59" s="14" t="n">
-        <v>94.31</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>100.18</v>
+        <v>101.28</v>
       </c>
       <c r="K59" s="14" t="n">
-        <v>102.37</v>
+        <v>102.73</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>104.56</v>
+        <v>104.18</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>108.59</v>
+        <v>107.83</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>112.62</v>
+        <v>111.48</v>
       </c>
       <c r="O59" s="14" t="n">
-        <v>112.97</v>
+        <v>110.73</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5203,22 +5203,22 @@
         <v>102.25</v>
       </c>
       <c r="C58" t="n">
-        <v>105.63</v>
+        <v>106.75</v>
       </c>
       <c r="D58" t="n">
         <v>100.53</v>
       </c>
       <c r="E58" t="n">
-        <v>105.28</v>
+        <v>104.81</v>
       </c>
       <c r="F58" t="n">
-        <v>5.23</v>
+        <v>4.76</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0523</v>
+        <v>0.0476</v>
       </c>
       <c r="H58" t="n">
-        <v>5.1</v>
+        <v>6.22</v>
       </c>
       <c r="I58" t="n">
         <v>77.28</v>
@@ -5278,25 +5278,25 @@
         </is>
       </c>
       <c r="I59" s="14" t="n">
-        <v>95.43000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>101.28</v>
+        <v>99.17</v>
       </c>
       <c r="K59" s="14" t="n">
-        <v>102.73</v>
+        <v>101.7</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>104.18</v>
+        <v>104.22</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>107.83</v>
+        <v>107.92</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>111.48</v>
+        <v>111.61</v>
       </c>
       <c r="O59" s="14" t="n">
-        <v>110.73</v>
+        <v>112.97</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5209,13 +5209,13 @@
         <v>100.53</v>
       </c>
       <c r="E58" t="n">
-        <v>104.81</v>
+        <v>103.27</v>
       </c>
       <c r="F58" t="n">
-        <v>4.76</v>
+        <v>3.22</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0476</v>
+        <v>0.0322</v>
       </c>
       <c r="H58" t="n">
         <v>6.22</v>
@@ -5281,19 +5281,19 @@
         <v>94.31</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>99.17</v>
+        <v>96.86</v>
       </c>
       <c r="K59" s="14" t="n">
-        <v>101.7</v>
+        <v>100.16</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>104.22</v>
+        <v>103.45</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>107.92</v>
+        <v>106.38</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>111.61</v>
+        <v>109.3</v>
       </c>
       <c r="O59" s="14" t="n">
         <v>112.97</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5209,13 +5209,13 @@
         <v>100.53</v>
       </c>
       <c r="E58" t="n">
-        <v>103.27</v>
+        <v>103.22</v>
       </c>
       <c r="F58" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0322</v>
+        <v>0.0317</v>
       </c>
       <c r="H58" t="n">
         <v>6.22</v>
@@ -5281,19 +5281,19 @@
         <v>94.31</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>96.86</v>
+        <v>96.79000000000001</v>
       </c>
       <c r="K59" s="14" t="n">
-        <v>100.16</v>
+        <v>100.11</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>103.45</v>
+        <v>103.43</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>106.38</v>
+        <v>106.33</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>109.3</v>
+        <v>109.23</v>
       </c>
       <c r="O59" s="14" t="n">
         <v>112.97</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5209,13 +5209,13 @@
         <v>100.53</v>
       </c>
       <c r="E58" t="n">
-        <v>103.22</v>
+        <v>103.54</v>
       </c>
       <c r="F58" t="n">
-        <v>3.17</v>
+        <v>3.49</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0317</v>
+        <v>0.0349</v>
       </c>
       <c r="H58" t="n">
         <v>6.22</v>
@@ -5281,19 +5281,19 @@
         <v>94.31</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>96.79000000000001</v>
+        <v>97.27</v>
       </c>
       <c r="K59" s="14" t="n">
-        <v>100.11</v>
+        <v>100.43</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>103.43</v>
+        <v>103.59</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>106.33</v>
+        <v>106.65</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>109.23</v>
+        <v>109.71</v>
       </c>
       <c r="O59" s="14" t="n">
         <v>112.97</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5209,13 +5209,13 @@
         <v>100.53</v>
       </c>
       <c r="E58" t="n">
-        <v>103.54</v>
+        <v>102.13</v>
       </c>
       <c r="F58" t="n">
-        <v>3.49</v>
+        <v>2.08</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0349</v>
+        <v>0.0208</v>
       </c>
       <c r="H58" t="n">
         <v>6.22</v>
@@ -5250,13 +5250,11 @@
       </c>
       <c r="S58" s="8" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="9" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="9" t="n">
+        <v/>
       </c>
       <c r="U58" s="9" t="n">
         <v/>
@@ -5281,19 +5279,19 @@
         <v>94.31</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>97.27</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="K59" s="14" t="n">
-        <v>100.43</v>
+        <v>99.02</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>103.59</v>
+        <v>102.88</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>106.65</v>
+        <v>105.24</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>109.71</v>
+        <v>107.59</v>
       </c>
       <c r="O59" s="14" t="n">
         <v>112.97</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -669,25 +669,25 @@
         <v>1.75</v>
       </c>
       <c r="I2" t="n">
-        <v>59.73</v>
+        <v>61.01</v>
       </c>
       <c r="J2" t="n">
-        <v>60.47</v>
+        <v>60.95</v>
       </c>
       <c r="K2" t="n">
-        <v>61.69</v>
+        <v>62.01</v>
       </c>
       <c r="L2" t="n">
-        <v>62.92</v>
+        <v>63.08</v>
       </c>
       <c r="M2" t="n">
-        <v>63.91</v>
+        <v>63.58</v>
       </c>
       <c r="N2" t="n">
-        <v>64.89</v>
+        <v>64.09</v>
       </c>
       <c r="O2" t="n">
-        <v>66.36</v>
+        <v>65.72</v>
       </c>
       <c r="P2" s="6" t="inlineStr"/>
       <c r="Q2" s="7" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5209,13 +5209,13 @@
         <v>100.53</v>
       </c>
       <c r="E58" t="n">
-        <v>102.13</v>
+        <v>101.18</v>
       </c>
       <c r="F58" t="n">
-        <v>2.08</v>
+        <v>1.13</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0208</v>
+        <v>0.0113</v>
       </c>
       <c r="H58" t="n">
         <v>6.22</v>
@@ -5279,19 +5279,19 @@
         <v>94.31</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>95.15000000000001</v>
+        <v>93.73</v>
       </c>
       <c r="K59" s="14" t="n">
-        <v>99.02</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>102.88</v>
+        <v>102.41</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>105.24</v>
+        <v>104.29</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>107.59</v>
+        <v>106.17</v>
       </c>
       <c r="O59" s="14" t="n">
         <v>112.97</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5209,13 +5209,13 @@
         <v>100.53</v>
       </c>
       <c r="E58" t="n">
-        <v>101.18</v>
+        <v>100.98</v>
       </c>
       <c r="F58" t="n">
-        <v>1.13</v>
+        <v>0.93</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0113</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H58" t="n">
         <v>6.22</v>
@@ -5279,19 +5279,19 @@
         <v>94.31</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>93.73</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="K59" s="14" t="n">
-        <v>98.06999999999999</v>
+        <v>97.87</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>102.41</v>
+        <v>102.31</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>104.29</v>
+        <v>104.09</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>106.17</v>
+        <v>105.87</v>
       </c>
       <c r="O59" s="14" t="n">
         <v>112.97</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5209,13 +5209,13 @@
         <v>100.53</v>
       </c>
       <c r="E58" t="n">
-        <v>100.98</v>
+        <v>101.09</v>
       </c>
       <c r="F58" t="n">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0104</v>
       </c>
       <c r="H58" t="n">
         <v>6.22</v>
@@ -5279,19 +5279,19 @@
         <v>94.31</v>
       </c>
       <c r="J59" s="14" t="n">
-        <v>93.43000000000001</v>
+        <v>93.59</v>
       </c>
       <c r="K59" s="14" t="n">
-        <v>97.87</v>
+        <v>97.98</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>102.31</v>
+        <v>102.36</v>
       </c>
       <c r="M59" s="14" t="n">
-        <v>104.09</v>
+        <v>104.2</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>105.87</v>
+        <v>106.03</v>
       </c>
       <c r="O59" s="14" t="n">
         <v>112.97</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -123,8 +118,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -669,25 +662,25 @@
         <v>1.75</v>
       </c>
       <c r="I2" t="n">
-        <v>61.01</v>
+        <v>61.21</v>
       </c>
       <c r="J2" t="n">
-        <v>60.95</v>
+        <v>61.02</v>
       </c>
       <c r="K2" t="n">
-        <v>62.01</v>
+        <v>62.06</v>
       </c>
       <c r="L2" t="n">
-        <v>63.08</v>
+        <v>63.11</v>
       </c>
       <c r="M2" t="n">
-        <v>63.58</v>
+        <v>63.53</v>
       </c>
       <c r="N2" t="n">
-        <v>64.09</v>
+        <v>63.96</v>
       </c>
       <c r="O2" t="n">
-        <v>65.72</v>
+        <v>65.62</v>
       </c>
       <c r="P2" s="6" t="inlineStr"/>
       <c r="Q2" s="7" t="n">
@@ -5209,13 +5202,13 @@
         <v>100.53</v>
       </c>
       <c r="E58" t="n">
-        <v>101.09</v>
+        <v>100.9</v>
       </c>
       <c r="F58" t="n">
-        <v>1.04</v>
+        <v>0.85</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0104</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H58" t="n">
         <v>6.22</v>
@@ -5268,34 +5261,6 @@
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="13" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I59" s="14" t="n">
-        <v>94.31</v>
-      </c>
-      <c r="J59" s="14" t="n">
-        <v>93.59</v>
-      </c>
-      <c r="K59" s="14" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="L59" s="14" t="n">
-        <v>102.36</v>
-      </c>
-      <c r="M59" s="14" t="n">
-        <v>104.2</v>
-      </c>
-      <c r="N59" s="14" t="n">
-        <v>106.03</v>
-      </c>
-      <c r="O59" s="14" t="n">
-        <v>112.97</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5202,13 +5202,13 @@
         <v>100.53</v>
       </c>
       <c r="E58" t="n">
-        <v>100.9</v>
+        <v>100.89</v>
       </c>
       <c r="F58" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H58" t="n">
         <v>6.22</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -637,50 +637,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63</v>
+        <v>63.88</v>
       </c>
       <c r="C2" t="n">
-        <v>63.93</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>62.18</v>
+        <v>62.95</v>
       </c>
       <c r="E2" t="n">
-        <v>63.66</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.86</v>
+        <v>0.35</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0137</v>
+        <v>0.0055</v>
       </c>
       <c r="H2" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="I2" t="n">
-        <v>61.21</v>
+        <v>60.43</v>
       </c>
       <c r="J2" t="n">
-        <v>61.02</v>
+        <v>62.21</v>
       </c>
       <c r="K2" t="n">
-        <v>62.06</v>
+        <v>62.78</v>
       </c>
       <c r="L2" t="n">
-        <v>63.11</v>
+        <v>63.36</v>
       </c>
       <c r="M2" t="n">
-        <v>63.53</v>
+        <v>64.53</v>
       </c>
       <c r="N2" t="n">
-        <v>63.96</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>65.62</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="P2" s="6" t="inlineStr"/>
       <c r="Q2" s="7" t="n">
@@ -710,75 +710,75 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63.88</v>
+        <v>63.95</v>
       </c>
       <c r="C3" t="n">
-        <v>65.09999999999999</v>
+        <v>66.03</v>
       </c>
       <c r="D3" t="n">
-        <v>62.95</v>
+        <v>61.45</v>
       </c>
       <c r="E3" t="n">
-        <v>64.01000000000001</v>
+        <v>61.87</v>
       </c>
       <c r="F3" t="n">
-        <v>0.35</v>
+        <v>-2.14</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.0334</v>
       </c>
       <c r="H3" t="n">
-        <v>2.15</v>
+        <v>4.58</v>
       </c>
       <c r="I3" t="n">
-        <v>60.43</v>
+        <v>60.8</v>
       </c>
       <c r="J3" t="n">
-        <v>62.21</v>
+        <v>61.85</v>
       </c>
       <c r="K3" t="n">
-        <v>62.78</v>
+        <v>62.94</v>
       </c>
       <c r="L3" t="n">
-        <v>63.36</v>
+        <v>64.02</v>
       </c>
       <c r="M3" t="n">
-        <v>64.53</v>
+        <v>65.09</v>
       </c>
       <c r="N3" t="n">
-        <v>65.70999999999999</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>65.68000000000001</v>
+        <v>67.25</v>
       </c>
       <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="8" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q3" s="7" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="11" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="9" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U3" s="9" t="n">
@@ -792,76 +792,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63.95</v>
+        <v>62</v>
       </c>
       <c r="C4" t="n">
-        <v>66.03</v>
+        <v>64.08</v>
       </c>
       <c r="D4" t="n">
-        <v>61.45</v>
+        <v>61.69</v>
       </c>
       <c r="E4" t="n">
-        <v>61.87</v>
+        <v>62.69</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.14</v>
+        <v>0.82</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0334</v>
+        <v>0.0133</v>
       </c>
       <c r="H4" t="n">
-        <v>4.58</v>
+        <v>2.39</v>
       </c>
       <c r="I4" t="n">
-        <v>60.8</v>
+        <v>56.87</v>
       </c>
       <c r="J4" t="n">
-        <v>61.85</v>
+        <v>56.36</v>
       </c>
       <c r="K4" t="n">
-        <v>62.94</v>
+        <v>59.58</v>
       </c>
       <c r="L4" t="n">
-        <v>64.02</v>
+        <v>62.8</v>
       </c>
       <c r="M4" t="n">
-        <v>65.09</v>
+        <v>64.16</v>
       </c>
       <c r="N4" t="n">
-        <v>66.15000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>67.25</v>
+        <v>70.61</v>
       </c>
       <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="7" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R4" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q4" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="7" t="n">
+        <v/>
       </c>
       <c r="S4" s="11" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="9" t="n">
+        <v/>
       </c>
       <c r="U4" s="9" t="n">
         <v/>
@@ -876,57 +874,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62</v>
+        <v>62.97</v>
       </c>
       <c r="C5" t="n">
-        <v>64.08</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>61.69</v>
+        <v>62.52</v>
       </c>
       <c r="E5" t="n">
-        <v>62.69</v>
+        <v>62.68</v>
       </c>
       <c r="F5" t="n">
-        <v>0.82</v>
+        <v>-0.01</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0002</v>
       </c>
       <c r="H5" t="n">
-        <v>2.39</v>
+        <v>2.24</v>
       </c>
       <c r="I5" t="n">
-        <v>56.87</v>
+        <v>59.3</v>
       </c>
       <c r="J5" t="n">
-        <v>56.36</v>
+        <v>60.2</v>
       </c>
       <c r="K5" t="n">
-        <v>59.58</v>
+        <v>61.49</v>
       </c>
       <c r="L5" t="n">
-        <v>62.8</v>
+        <v>62.79</v>
       </c>
       <c r="M5" t="n">
-        <v>64.16</v>
+        <v>63.89</v>
       </c>
       <c r="N5" t="n">
-        <v>65.51000000000001</v>
+        <v>64.98</v>
       </c>
       <c r="O5" t="n">
-        <v>70.61</v>
+        <v>66.47</v>
       </c>
       <c r="P5" s="6" t="inlineStr"/>
       <c r="Q5" s="7" t="n">
@@ -940,8 +938,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T5" s="9" t="n">
-        <v/>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U5" s="9" t="n">
         <v/>
@@ -963,50 +963,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62.97</v>
+        <v>62.74</v>
       </c>
       <c r="C6" t="n">
-        <v>64.76000000000001</v>
+        <v>66.42</v>
       </c>
       <c r="D6" t="n">
-        <v>62.52</v>
+        <v>61.85</v>
       </c>
       <c r="E6" t="n">
-        <v>62.68</v>
+        <v>65.72</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.01</v>
+        <v>3.04</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0485</v>
       </c>
       <c r="H6" t="n">
-        <v>2.24</v>
+        <v>4.57</v>
       </c>
       <c r="I6" t="n">
-        <v>59.3</v>
+        <v>60.28</v>
       </c>
       <c r="J6" t="n">
-        <v>60.2</v>
+        <v>59.96</v>
       </c>
       <c r="K6" t="n">
-        <v>61.49</v>
+        <v>61.56</v>
       </c>
       <c r="L6" t="n">
-        <v>62.79</v>
+        <v>63.16</v>
       </c>
       <c r="M6" t="n">
-        <v>63.89</v>
+        <v>63.8</v>
       </c>
       <c r="N6" t="n">
-        <v>64.98</v>
+        <v>64.44</v>
       </c>
       <c r="O6" t="n">
-        <v>66.47</v>
+        <v>67</v>
       </c>
       <c r="P6" s="6" t="inlineStr"/>
       <c r="Q6" s="7" t="n">
@@ -1015,9 +1015,9 @@
       <c r="R6" s="7" t="n">
         <v/>
       </c>
-      <c r="S6" s="11" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S6" s="8" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T6" s="9" t="inlineStr">
@@ -1025,8 +1025,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="9" t="n">
-        <v/>
+      <c r="U6" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V6" s="9" t="n">
         <v/>
@@ -1045,144 +1047,138 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62.74</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>66.42</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>61.85</v>
+        <v>60.4</v>
       </c>
       <c r="E7" t="n">
-        <v>65.72</v>
+        <v>60.88</v>
       </c>
       <c r="F7" t="n">
-        <v>3.04</v>
+        <v>-4.84</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0485</v>
+        <v>-0.0736</v>
       </c>
       <c r="H7" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>60.28</v>
+        <v>57.28</v>
       </c>
       <c r="J7" t="n">
-        <v>59.96</v>
+        <v>61.94</v>
       </c>
       <c r="K7" t="n">
-        <v>61.56</v>
+        <v>63.44</v>
       </c>
       <c r="L7" t="n">
-        <v>63.16</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>63.8</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>64.44</v>
+        <v>71.08</v>
       </c>
       <c r="O7" t="n">
-        <v>67</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="P7" s="6" t="inlineStr"/>
-      <c r="Q7" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="8" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="9" t="inlineStr">
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U7" s="9" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S7" s="11" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="9" t="n">
+        <v/>
       </c>
       <c r="V7" s="9" t="n">
         <v/>
       </c>
-      <c r="W7" s="10" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W7" s="12" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>65.06999999999999</v>
+        <v>61.14</v>
       </c>
       <c r="C8" t="n">
-        <v>65.40000000000001</v>
+        <v>62.92</v>
       </c>
       <c r="D8" t="n">
-        <v>60.4</v>
+        <v>58.22</v>
       </c>
       <c r="E8" t="n">
-        <v>60.88</v>
+        <v>58.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.84</v>
+        <v>-1.98</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0736</v>
+        <v>-0.0325</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
-        <v>57.28</v>
+        <v>55.4</v>
       </c>
       <c r="J8" t="n">
-        <v>61.94</v>
+        <v>54.87</v>
       </c>
       <c r="K8" t="n">
-        <v>63.44</v>
+        <v>58.38</v>
       </c>
       <c r="L8" t="n">
-        <v>64.93000000000001</v>
+        <v>61.89</v>
       </c>
       <c r="M8" t="n">
-        <v>68.01000000000001</v>
+        <v>63.38</v>
       </c>
       <c r="N8" t="n">
-        <v>71.08</v>
+        <v>64.87</v>
       </c>
       <c r="O8" t="n">
-        <v>70.98999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="7" t="inlineStr">
+      <c r="Q8" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S8" s="11" t="inlineStr">
@@ -1209,50 +1205,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61.14</v>
+        <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>62.92</v>
+        <v>60.17</v>
       </c>
       <c r="D9" t="n">
-        <v>58.22</v>
+        <v>56.6</v>
       </c>
       <c r="E9" t="n">
-        <v>58.9</v>
+        <v>57.54</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.98</v>
+        <v>-1.36</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0325</v>
+        <v>-0.0231</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7</v>
+        <v>3.57</v>
       </c>
       <c r="I9" t="n">
-        <v>55.4</v>
+        <v>53.52</v>
       </c>
       <c r="J9" t="n">
-        <v>54.87</v>
+        <v>53.37</v>
       </c>
       <c r="K9" t="n">
-        <v>58.38</v>
+        <v>56.55</v>
       </c>
       <c r="L9" t="n">
-        <v>61.89</v>
+        <v>59.74</v>
       </c>
       <c r="M9" t="n">
-        <v>63.38</v>
+        <v>61.25</v>
       </c>
       <c r="N9" t="n">
-        <v>64.87</v>
+        <v>62.76</v>
       </c>
       <c r="O9" t="n">
-        <v>70.40000000000001</v>
+        <v>67.62</v>
       </c>
       <c r="P9" s="6" t="inlineStr"/>
       <c r="Q9" s="7" t="n">
@@ -1287,128 +1283,134 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>57.73</v>
       </c>
       <c r="C10" t="n">
-        <v>60.17</v>
+        <v>62.59</v>
       </c>
       <c r="D10" t="n">
-        <v>56.6</v>
+        <v>56.35</v>
       </c>
       <c r="E10" t="n">
-        <v>57.54</v>
+        <v>61.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.36</v>
+        <v>3.96</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0231</v>
+        <v>0.0688</v>
       </c>
       <c r="H10" t="n">
-        <v>3.57</v>
+        <v>6.24</v>
       </c>
       <c r="I10" t="n">
-        <v>53.52</v>
+        <v>53.03</v>
       </c>
       <c r="J10" t="n">
-        <v>53.37</v>
+        <v>53.55</v>
       </c>
       <c r="K10" t="n">
-        <v>56.55</v>
+        <v>55.76</v>
       </c>
       <c r="L10" t="n">
-        <v>59.74</v>
+        <v>57.96</v>
       </c>
       <c r="M10" t="n">
-        <v>61.25</v>
+        <v>59.33</v>
       </c>
       <c r="N10" t="n">
-        <v>62.76</v>
+        <v>60.69</v>
       </c>
       <c r="O10" t="n">
-        <v>67.62</v>
+        <v>63.74</v>
       </c>
       <c r="P10" s="6" t="inlineStr"/>
       <c r="Q10" s="7" t="n">
         <v/>
       </c>
-      <c r="R10" s="7" t="inlineStr">
+      <c r="R10" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="11" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="9" t="n">
-        <v/>
-      </c>
       <c r="V10" s="9" t="n">
         <v/>
       </c>
-      <c r="W10" s="12" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="W10" s="10" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57.73</v>
+        <v>61.82</v>
       </c>
       <c r="C11" t="n">
-        <v>62.59</v>
+        <v>62.17</v>
       </c>
       <c r="D11" t="n">
-        <v>56.35</v>
+        <v>59.64</v>
       </c>
       <c r="E11" t="n">
-        <v>61.5</v>
+        <v>60.98</v>
       </c>
       <c r="F11" t="n">
-        <v>3.96</v>
+        <v>-0.52</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0688</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>6.24</v>
+        <v>2.53</v>
       </c>
       <c r="I11" t="n">
-        <v>53.03</v>
+        <v>50.11</v>
       </c>
       <c r="J11" t="n">
-        <v>53.55</v>
+        <v>56.27</v>
       </c>
       <c r="K11" t="n">
-        <v>55.76</v>
+        <v>58.38</v>
       </c>
       <c r="L11" t="n">
-        <v>57.96</v>
+        <v>60.48</v>
       </c>
       <c r="M11" t="n">
-        <v>59.33</v>
+        <v>64.62</v>
       </c>
       <c r="N11" t="n">
-        <v>60.69</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>63.74</v>
+        <v>68.83</v>
       </c>
       <c r="P11" s="6" t="inlineStr"/>
       <c r="Q11" s="7" t="n">
@@ -1419,18 +1421,14 @@
       </c>
       <c r="S11" s="8" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="9" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="9" t="n">
+        <v/>
       </c>
       <c r="V11" s="9" t="n">
         <v/>
@@ -1442,68 +1440,70 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61.82</v>
+        <v>61.4</v>
       </c>
       <c r="C12" t="n">
-        <v>62.17</v>
+        <v>61.5</v>
       </c>
       <c r="D12" t="n">
-        <v>59.64</v>
+        <v>58.83</v>
       </c>
       <c r="E12" t="n">
-        <v>60.98</v>
+        <v>59.75</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.52</v>
+        <v>-1.23</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0202</v>
       </c>
       <c r="H12" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="I12" t="n">
-        <v>50.11</v>
+        <v>57.11</v>
       </c>
       <c r="J12" t="n">
-        <v>56.27</v>
+        <v>58.49</v>
       </c>
       <c r="K12" t="n">
-        <v>58.38</v>
+        <v>59.72</v>
       </c>
       <c r="L12" t="n">
-        <v>60.48</v>
+        <v>60.94</v>
       </c>
       <c r="M12" t="n">
-        <v>64.62</v>
+        <v>62.24</v>
       </c>
       <c r="N12" t="n">
-        <v>68.76000000000001</v>
+        <v>63.55</v>
       </c>
       <c r="O12" t="n">
-        <v>68.83</v>
+        <v>64.7</v>
       </c>
       <c r="P12" s="6" t="inlineStr"/>
       <c r="Q12" s="7" t="n">
         <v/>
       </c>
-      <c r="R12" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R12" s="7" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="9" t="n">
@@ -1522,57 +1522,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61.4</v>
+        <v>59.87</v>
       </c>
       <c r="C13" t="n">
-        <v>61.5</v>
+        <v>61.28</v>
       </c>
       <c r="D13" t="n">
-        <v>58.83</v>
+        <v>58.12</v>
       </c>
       <c r="E13" t="n">
-        <v>59.75</v>
+        <v>60.09</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.23</v>
+        <v>0.34</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0202</v>
+        <v>0.0057</v>
       </c>
       <c r="H13" t="n">
-        <v>2.67</v>
+        <v>3.16</v>
       </c>
       <c r="I13" t="n">
-        <v>57.11</v>
+        <v>56.16</v>
       </c>
       <c r="J13" t="n">
-        <v>58.49</v>
+        <v>56.87</v>
       </c>
       <c r="K13" t="n">
-        <v>59.72</v>
+        <v>58.42</v>
       </c>
       <c r="L13" t="n">
-        <v>60.94</v>
+        <v>59.96</v>
       </c>
       <c r="M13" t="n">
-        <v>62.24</v>
+        <v>61.08</v>
       </c>
       <c r="N13" t="n">
-        <v>63.55</v>
+        <v>62.21</v>
       </c>
       <c r="O13" t="n">
-        <v>64.7</v>
+        <v>64.17</v>
       </c>
       <c r="P13" s="6" t="inlineStr"/>
       <c r="Q13" s="7" t="n">
@@ -1580,16 +1580,18 @@
       </c>
       <c r="R13" s="7" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S13" s="11" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="9" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="8" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U13" s="9" t="n">
         <v/>
@@ -1604,57 +1606,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59.87</v>
+        <v>59.8</v>
       </c>
       <c r="C14" t="n">
-        <v>61.28</v>
+        <v>60.93</v>
       </c>
       <c r="D14" t="n">
-        <v>58.12</v>
+        <v>57.38</v>
       </c>
       <c r="E14" t="n">
-        <v>60.09</v>
+        <v>58.06</v>
       </c>
       <c r="F14" t="n">
-        <v>0.34</v>
+        <v>-2.03</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.0338</v>
       </c>
       <c r="H14" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="I14" t="n">
-        <v>56.16</v>
+        <v>54.96</v>
       </c>
       <c r="J14" t="n">
-        <v>56.87</v>
+        <v>57.13</v>
       </c>
       <c r="K14" t="n">
-        <v>58.42</v>
+        <v>58.51</v>
       </c>
       <c r="L14" t="n">
-        <v>59.96</v>
+        <v>59.89</v>
       </c>
       <c r="M14" t="n">
-        <v>61.08</v>
+        <v>61.67</v>
       </c>
       <c r="N14" t="n">
-        <v>62.21</v>
+        <v>63.45</v>
       </c>
       <c r="O14" t="n">
-        <v>64.17</v>
+        <v>64.44</v>
       </c>
       <c r="P14" s="6" t="inlineStr"/>
       <c r="Q14" s="7" t="n">
@@ -1662,18 +1664,16 @@
       </c>
       <c r="R14" s="7" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="8" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S14" s="11" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="9" t="n">
+        <v/>
       </c>
       <c r="U14" s="9" t="n">
         <v/>
@@ -1688,70 +1688,68 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>59.8</v>
+        <v>58.05</v>
       </c>
       <c r="C15" t="n">
-        <v>60.93</v>
+        <v>59.64</v>
       </c>
       <c r="D15" t="n">
-        <v>57.38</v>
+        <v>57.1</v>
       </c>
       <c r="E15" t="n">
-        <v>58.06</v>
+        <v>58.55</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.03</v>
+        <v>0.49</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>3.55</v>
+        <v>2.54</v>
       </c>
       <c r="I15" t="n">
-        <v>54.96</v>
+        <v>53.83</v>
       </c>
       <c r="J15" t="n">
-        <v>57.13</v>
+        <v>53.96</v>
       </c>
       <c r="K15" t="n">
-        <v>58.51</v>
+        <v>56.29</v>
       </c>
       <c r="L15" t="n">
-        <v>59.89</v>
+        <v>58.61</v>
       </c>
       <c r="M15" t="n">
-        <v>61.67</v>
+        <v>59.84</v>
       </c>
       <c r="N15" t="n">
-        <v>63.45</v>
+        <v>61.06</v>
       </c>
       <c r="O15" t="n">
-        <v>64.44</v>
+        <v>64.48</v>
       </c>
       <c r="P15" s="6" t="inlineStr"/>
       <c r="Q15" s="7" t="n">
         <v/>
       </c>
-      <c r="R15" s="7" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R15" s="7" t="n">
+        <v/>
       </c>
       <c r="S15" s="11" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="9" t="n">
@@ -1770,57 +1768,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>58.05</v>
+        <v>58.96</v>
       </c>
       <c r="C16" t="n">
-        <v>59.64</v>
+        <v>60.5</v>
       </c>
       <c r="D16" t="n">
-        <v>57.1</v>
+        <v>58.28</v>
       </c>
       <c r="E16" t="n">
-        <v>58.55</v>
+        <v>60.08</v>
       </c>
       <c r="F16" t="n">
-        <v>0.49</v>
+        <v>1.53</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0261</v>
       </c>
       <c r="H16" t="n">
-        <v>2.54</v>
+        <v>2.22</v>
       </c>
       <c r="I16" t="n">
-        <v>53.83</v>
+        <v>54.56</v>
       </c>
       <c r="J16" t="n">
-        <v>53.96</v>
+        <v>56.1</v>
       </c>
       <c r="K16" t="n">
-        <v>56.29</v>
+        <v>57.28</v>
       </c>
       <c r="L16" t="n">
-        <v>58.61</v>
+        <v>58.46</v>
       </c>
       <c r="M16" t="n">
-        <v>59.84</v>
+        <v>59.82</v>
       </c>
       <c r="N16" t="n">
-        <v>61.06</v>
+        <v>61.18</v>
       </c>
       <c r="O16" t="n">
-        <v>64.48</v>
+        <v>62.18</v>
       </c>
       <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="7" t="n">
@@ -1829,13 +1827,15 @@
       <c r="R16" s="7" t="n">
         <v/>
       </c>
-      <c r="S16" s="11" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="9" t="n">
-        <v/>
+      <c r="S16" s="8" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U16" s="9" t="n">
         <v/>
@@ -1848,86 +1848,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>58.96</v>
+        <v>60.15</v>
       </c>
       <c r="C17" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="D17" t="n">
-        <v>58.28</v>
+        <v>57.01</v>
       </c>
       <c r="E17" t="n">
-        <v>60.08</v>
+        <v>57.44</v>
       </c>
       <c r="F17" t="n">
-        <v>1.53</v>
+        <v>-2.64</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0261</v>
+        <v>-0.0439</v>
       </c>
       <c r="H17" t="n">
-        <v>2.22</v>
+        <v>3.29</v>
       </c>
       <c r="I17" t="n">
-        <v>54.56</v>
+        <v>56.06</v>
       </c>
       <c r="J17" t="n">
-        <v>56.1</v>
+        <v>58.21</v>
       </c>
       <c r="K17" t="n">
-        <v>57.28</v>
+        <v>58.97</v>
       </c>
       <c r="L17" t="n">
-        <v>58.46</v>
+        <v>59.74</v>
       </c>
       <c r="M17" t="n">
-        <v>59.82</v>
+        <v>61.19</v>
       </c>
       <c r="N17" t="n">
-        <v>61.18</v>
+        <v>62.65</v>
       </c>
       <c r="O17" t="n">
-        <v>62.18</v>
+        <v>62.72</v>
       </c>
       <c r="P17" s="6" t="inlineStr"/>
-      <c r="Q17" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="8" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="9" t="inlineStr">
+      <c r="Q17" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="11" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="9" t="n">
+        <v/>
+      </c>
       <c r="U17" s="9" t="n">
         <v/>
       </c>
       <c r="V17" s="9" t="n">
         <v/>
       </c>
-      <c r="W17" s="10" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W17" s="12" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1935,60 +1933,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>60.15</v>
+        <v>57.5</v>
       </c>
       <c r="C18" t="n">
-        <v>60.3</v>
+        <v>57.8</v>
       </c>
       <c r="D18" t="n">
-        <v>57.01</v>
+        <v>54.98</v>
       </c>
       <c r="E18" t="n">
-        <v>57.44</v>
+        <v>56.66</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.64</v>
+        <v>-0.78</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0439</v>
+        <v>-0.0136</v>
       </c>
       <c r="H18" t="n">
-        <v>3.29</v>
+        <v>2.82</v>
       </c>
       <c r="I18" t="n">
-        <v>56.06</v>
+        <v>53.72</v>
       </c>
       <c r="J18" t="n">
-        <v>58.21</v>
+        <v>53.54</v>
       </c>
       <c r="K18" t="n">
-        <v>58.97</v>
+        <v>55.79</v>
       </c>
       <c r="L18" t="n">
-        <v>59.74</v>
+        <v>58.05</v>
       </c>
       <c r="M18" t="n">
-        <v>61.19</v>
+        <v>59.08</v>
       </c>
       <c r="N18" t="n">
-        <v>62.65</v>
+        <v>60.12</v>
       </c>
       <c r="O18" t="n">
-        <v>62.72</v>
+        <v>63.59</v>
       </c>
       <c r="P18" s="6" t="inlineStr"/>
-      <c r="Q18" s="7" t="inlineStr">
+      <c r="Q18" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="7" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R18" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S18" s="11" t="inlineStr">
@@ -2015,67 +2011,67 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>57.5</v>
+        <v>56.63</v>
       </c>
       <c r="C19" t="n">
-        <v>57.8</v>
+        <v>58.88</v>
       </c>
       <c r="D19" t="n">
-        <v>54.98</v>
+        <v>56.6</v>
       </c>
       <c r="E19" t="n">
-        <v>56.66</v>
+        <v>56.74</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.78</v>
+        <v>0.08</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0136</v>
+        <v>0.0014</v>
       </c>
       <c r="H19" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="I19" t="n">
-        <v>53.72</v>
+        <v>52.16</v>
       </c>
       <c r="J19" t="n">
-        <v>53.54</v>
+        <v>53.98</v>
       </c>
       <c r="K19" t="n">
-        <v>55.79</v>
+        <v>55.25</v>
       </c>
       <c r="L19" t="n">
-        <v>58.05</v>
+        <v>56.52</v>
       </c>
       <c r="M19" t="n">
-        <v>59.08</v>
+        <v>58.07</v>
       </c>
       <c r="N19" t="n">
-        <v>60.12</v>
+        <v>59.61</v>
       </c>
       <c r="O19" t="n">
-        <v>63.59</v>
+        <v>60.62</v>
       </c>
       <c r="P19" s="6" t="inlineStr"/>
       <c r="Q19" s="7" t="n">
         <v/>
       </c>
-      <c r="R19" s="7" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S19" s="11" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="9" t="n">
-        <v/>
+      <c r="R19" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="8" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U19" s="9" t="n">
         <v/>
@@ -2088,55 +2084,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>56.63</v>
+        <v>57.04</v>
       </c>
       <c r="C20" t="n">
-        <v>58.88</v>
+        <v>58.55</v>
       </c>
       <c r="D20" t="n">
         <v>56.6</v>
       </c>
       <c r="E20" t="n">
-        <v>56.74</v>
+        <v>57.32</v>
       </c>
       <c r="F20" t="n">
-        <v>0.08</v>
+        <v>0.58</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0102</v>
       </c>
       <c r="H20" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="I20" t="n">
-        <v>52.16</v>
+        <v>54.32</v>
       </c>
       <c r="J20" t="n">
-        <v>53.98</v>
+        <v>53.96</v>
       </c>
       <c r="K20" t="n">
-        <v>55.25</v>
+        <v>55.6</v>
       </c>
       <c r="L20" t="n">
-        <v>56.52</v>
+        <v>57.24</v>
       </c>
       <c r="M20" t="n">
-        <v>58.07</v>
+        <v>57.88</v>
       </c>
       <c r="N20" t="n">
-        <v>59.61</v>
+        <v>58.52</v>
       </c>
       <c r="O20" t="n">
-        <v>60.62</v>
+        <v>61.16</v>
       </c>
       <c r="P20" s="6" t="inlineStr"/>
       <c r="Q20" s="7" t="n">
@@ -2155,8 +2155,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="9" t="n">
-        <v/>
+      <c r="U20" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V20" s="9" t="n">
         <v/>
@@ -2168,68 +2170,70 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>57.04</v>
+        <v>57.47</v>
       </c>
       <c r="C21" t="n">
-        <v>58.55</v>
+        <v>59.77</v>
       </c>
       <c r="D21" t="n">
-        <v>56.6</v>
+        <v>55.76</v>
       </c>
       <c r="E21" t="n">
-        <v>57.32</v>
+        <v>59.12</v>
       </c>
       <c r="F21" t="n">
-        <v>0.58</v>
+        <v>1.8</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0314</v>
       </c>
       <c r="H21" t="n">
-        <v>1.95</v>
+        <v>4.01</v>
       </c>
       <c r="I21" t="n">
-        <v>54.32</v>
+        <v>54.65</v>
       </c>
       <c r="J21" t="n">
-        <v>53.96</v>
+        <v>55.24</v>
       </c>
       <c r="K21" t="n">
-        <v>55.6</v>
+        <v>56.34</v>
       </c>
       <c r="L21" t="n">
-        <v>57.24</v>
+        <v>57.45</v>
       </c>
       <c r="M21" t="n">
-        <v>57.88</v>
+        <v>58.3</v>
       </c>
       <c r="N21" t="n">
-        <v>58.52</v>
+        <v>59.14</v>
       </c>
       <c r="O21" t="n">
-        <v>61.16</v>
+        <v>60.5</v>
       </c>
       <c r="P21" s="6" t="inlineStr"/>
       <c r="Q21" s="7" t="n">
         <v/>
       </c>
-      <c r="R21" s="7" t="n">
-        <v/>
+      <c r="R21" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="8" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="9" t="inlineStr">
@@ -2239,7 +2243,7 @@
       </c>
       <c r="U21" s="9" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V21" s="9" t="n">
@@ -2252,81 +2256,77 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>57.47</v>
+        <v>59</v>
       </c>
       <c r="C22" t="n">
-        <v>59.77</v>
+        <v>62.36</v>
       </c>
       <c r="D22" t="n">
-        <v>55.76</v>
+        <v>58.45</v>
       </c>
       <c r="E22" t="n">
-        <v>59.12</v>
+        <v>59.44</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8</v>
+        <v>0.32</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0314</v>
+        <v>0.0054</v>
       </c>
       <c r="H22" t="n">
-        <v>4.01</v>
+        <v>3.91</v>
       </c>
       <c r="I22" t="n">
-        <v>54.65</v>
+        <v>51.75</v>
       </c>
       <c r="J22" t="n">
-        <v>55.24</v>
+        <v>55.79</v>
       </c>
       <c r="K22" t="n">
-        <v>56.34</v>
+        <v>57.11</v>
       </c>
       <c r="L22" t="n">
-        <v>57.45</v>
+        <v>58.44</v>
       </c>
       <c r="M22" t="n">
-        <v>58.3</v>
+        <v>61.12</v>
       </c>
       <c r="N22" t="n">
-        <v>59.14</v>
+        <v>63.81</v>
       </c>
       <c r="O22" t="n">
-        <v>60.5</v>
+        <v>63.78</v>
       </c>
       <c r="P22" s="6" t="inlineStr"/>
       <c r="Q22" s="7" t="n">
         <v/>
       </c>
-      <c r="R22" s="7" t="inlineStr">
+      <c r="R22" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="8" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="8" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="9" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U22" s="9" t="n">
+        <v/>
       </c>
       <c r="V22" s="9" t="n">
         <v/>
@@ -2338,57 +2338,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>59</v>
+        <v>59.01</v>
       </c>
       <c r="C23" t="n">
-        <v>62.36</v>
+        <v>61.36</v>
       </c>
       <c r="D23" t="n">
-        <v>58.45</v>
+        <v>58.7</v>
       </c>
       <c r="E23" t="n">
-        <v>59.44</v>
+        <v>61.07</v>
       </c>
       <c r="F23" t="n">
-        <v>0.32</v>
+        <v>1.63</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0274</v>
       </c>
       <c r="H23" t="n">
-        <v>3.91</v>
+        <v>2.66</v>
       </c>
       <c r="I23" t="n">
-        <v>51.75</v>
+        <v>54.54</v>
       </c>
       <c r="J23" t="n">
-        <v>55.79</v>
+        <v>55.05</v>
       </c>
       <c r="K23" t="n">
-        <v>57.11</v>
+        <v>57.48</v>
       </c>
       <c r="L23" t="n">
-        <v>58.44</v>
+        <v>59.92</v>
       </c>
       <c r="M23" t="n">
-        <v>61.12</v>
+        <v>61.39</v>
       </c>
       <c r="N23" t="n">
-        <v>63.81</v>
+        <v>62.87</v>
       </c>
       <c r="O23" t="n">
-        <v>63.78</v>
+        <v>66.27</v>
       </c>
       <c r="P23" s="6" t="inlineStr"/>
       <c r="Q23" s="7" t="n">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="S23" s="8" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="9" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U23" s="9" t="n">
@@ -2420,57 +2420,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>59.01</v>
+        <v>61.22</v>
       </c>
       <c r="C24" t="n">
-        <v>61.36</v>
+        <v>66.48</v>
       </c>
       <c r="D24" t="n">
-        <v>58.7</v>
+        <v>60.14</v>
       </c>
       <c r="E24" t="n">
-        <v>61.07</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>1.63</v>
+        <v>4.14</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0678</v>
       </c>
       <c r="H24" t="n">
-        <v>2.66</v>
+        <v>6.34</v>
       </c>
       <c r="I24" t="n">
-        <v>54.54</v>
+        <v>56.04</v>
       </c>
       <c r="J24" t="n">
-        <v>55.05</v>
+        <v>58.93</v>
       </c>
       <c r="K24" t="n">
-        <v>57.48</v>
+        <v>59.74</v>
       </c>
       <c r="L24" t="n">
-        <v>59.92</v>
+        <v>60.55</v>
       </c>
       <c r="M24" t="n">
-        <v>61.39</v>
+        <v>62.4</v>
       </c>
       <c r="N24" t="n">
-        <v>62.87</v>
+        <v>64.25</v>
       </c>
       <c r="O24" t="n">
-        <v>66.27</v>
+        <v>64.02</v>
       </c>
       <c r="P24" s="6" t="inlineStr"/>
       <c r="Q24" s="7" t="n">
@@ -2486,173 +2486,173 @@
       </c>
       <c r="T24" s="9" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="9" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U24" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="12" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="V24" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W24" s="10" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>61.22</v>
+        <v>64.72</v>
       </c>
       <c r="C25" t="n">
-        <v>66.48</v>
+        <v>65.53</v>
       </c>
       <c r="D25" t="n">
-        <v>60.14</v>
+        <v>61.12</v>
       </c>
       <c r="E25" t="n">
-        <v>65.20999999999999</v>
+        <v>63.55</v>
       </c>
       <c r="F25" t="n">
-        <v>4.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0678</v>
+        <v>-0.0255</v>
       </c>
       <c r="H25" t="n">
-        <v>6.34</v>
+        <v>4.41</v>
       </c>
       <c r="I25" t="n">
-        <v>56.04</v>
+        <v>53.8</v>
       </c>
       <c r="J25" t="n">
-        <v>58.93</v>
+        <v>59.82</v>
       </c>
       <c r="K25" t="n">
-        <v>59.74</v>
+        <v>62.04</v>
       </c>
       <c r="L25" t="n">
-        <v>60.55</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>62.4</v>
+        <v>68.38</v>
       </c>
       <c r="N25" t="n">
-        <v>64.25</v>
+        <v>72.5</v>
       </c>
       <c r="O25" t="n">
-        <v>64.02</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="P25" s="6" t="inlineStr"/>
       <c r="Q25" s="7" t="n">
         <v/>
       </c>
-      <c r="R25" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="8" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="9" t="inlineStr">
+      <c r="R25" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="9" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V25" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S25" s="11" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="9" t="n">
+        <v/>
       </c>
       <c r="W25" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>64.72</v>
+        <v>62.99</v>
       </c>
       <c r="C26" t="n">
-        <v>65.53</v>
+        <v>65.83</v>
       </c>
       <c r="D26" t="n">
-        <v>61.12</v>
+        <v>62.14</v>
       </c>
       <c r="E26" t="n">
-        <v>63.55</v>
+        <v>62.89</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.66</v>
+        <v>-0.66</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0255</v>
+        <v>-0.0104</v>
       </c>
       <c r="H26" t="n">
-        <v>4.41</v>
+        <v>3.69</v>
       </c>
       <c r="I26" t="n">
-        <v>53.8</v>
+        <v>56.71</v>
       </c>
       <c r="J26" t="n">
-        <v>59.82</v>
+        <v>59.25</v>
       </c>
       <c r="K26" t="n">
-        <v>62.04</v>
+        <v>61.34</v>
       </c>
       <c r="L26" t="n">
-        <v>64.26000000000001</v>
+        <v>63.44</v>
       </c>
       <c r="M26" t="n">
-        <v>68.38</v>
+        <v>65.75</v>
       </c>
       <c r="N26" t="n">
-        <v>72.5</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>72.81999999999999</v>
+        <v>69.94</v>
       </c>
       <c r="P26" s="6" t="inlineStr"/>
       <c r="Q26" s="7" t="n">
         <v/>
       </c>
-      <c r="R26" s="7" t="inlineStr">
+      <c r="R26" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="11" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="9" t="n">
-        <v/>
-      </c>
       <c r="U26" s="9" t="n">
         <v/>
       </c>
@@ -2666,57 +2666,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>62.99</v>
+        <v>63.3</v>
       </c>
       <c r="C27" t="n">
-        <v>65.83</v>
+        <v>67.05</v>
       </c>
       <c r="D27" t="n">
-        <v>62.14</v>
+        <v>61.87</v>
       </c>
       <c r="E27" t="n">
-        <v>62.89</v>
+        <v>66.39</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.66</v>
+        <v>3.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0557</v>
       </c>
       <c r="H27" t="n">
-        <v>3.69</v>
+        <v>5.18</v>
       </c>
       <c r="I27" t="n">
-        <v>56.71</v>
+        <v>58.45</v>
       </c>
       <c r="J27" t="n">
-        <v>59.25</v>
+        <v>58.65</v>
       </c>
       <c r="K27" t="n">
-        <v>61.34</v>
+        <v>61.04</v>
       </c>
       <c r="L27" t="n">
         <v>63.44</v>
       </c>
       <c r="M27" t="n">
-        <v>65.75</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>68.06999999999999</v>
+        <v>66.03</v>
       </c>
       <c r="O27" t="n">
-        <v>69.94</v>
+        <v>69.52</v>
       </c>
       <c r="P27" s="6" t="inlineStr"/>
       <c r="Q27" s="7" t="n">
@@ -2725,9 +2725,9 @@
       <c r="R27" s="7" t="n">
         <v/>
       </c>
-      <c r="S27" s="11" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T27" s="9" t="inlineStr">
@@ -2735,8 +2735,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="9" t="n">
-        <v/>
+      <c r="U27" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V27" s="9" t="n">
         <v/>
@@ -2755,72 +2757,70 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>63.3</v>
+        <v>65.89</v>
       </c>
       <c r="C28" t="n">
-        <v>67.05</v>
+        <v>67.83</v>
       </c>
       <c r="D28" t="n">
-        <v>61.87</v>
+        <v>63.6</v>
       </c>
       <c r="E28" t="n">
-        <v>66.39</v>
+        <v>67.02</v>
       </c>
       <c r="F28" t="n">
-        <v>3.5</v>
+        <v>0.63</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0557</v>
+        <v>0.0095</v>
       </c>
       <c r="H28" t="n">
-        <v>5.18</v>
+        <v>4.23</v>
       </c>
       <c r="I28" t="n">
-        <v>58.45</v>
+        <v>56.69</v>
       </c>
       <c r="J28" t="n">
-        <v>58.65</v>
+        <v>62.17</v>
       </c>
       <c r="K28" t="n">
-        <v>61.04</v>
+        <v>63.8</v>
       </c>
       <c r="L28" t="n">
-        <v>63.44</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>64.73999999999999</v>
+        <v>68.98</v>
       </c>
       <c r="N28" t="n">
-        <v>66.03</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>69.52</v>
+        <v>72.23</v>
       </c>
       <c r="P28" s="6" t="inlineStr"/>
       <c r="Q28" s="7" t="n">
         <v/>
       </c>
-      <c r="R28" s="7" t="n">
-        <v/>
+      <c r="R28" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="9" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="9" t="n">
+        <v/>
       </c>
       <c r="V28" s="9" t="n">
         <v/>
@@ -2830,82 +2830,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>65.89</v>
+        <v>75</v>
       </c>
       <c r="C29" t="n">
-        <v>67.83</v>
+        <v>92.61</v>
       </c>
       <c r="D29" t="n">
-        <v>63.6</v>
+        <v>69.2</v>
       </c>
       <c r="E29" t="n">
-        <v>67.02</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.63</v>
+        <v>23.88</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.3563</v>
       </c>
       <c r="H29" t="n">
-        <v>4.23</v>
+        <v>23.41</v>
       </c>
       <c r="I29" t="n">
-        <v>56.69</v>
+        <v>59.37</v>
       </c>
       <c r="J29" t="n">
-        <v>62.17</v>
+        <v>63.44</v>
       </c>
       <c r="K29" t="n">
-        <v>63.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>65.43000000000001</v>
+        <v>66.37</v>
       </c>
       <c r="M29" t="n">
-        <v>68.98</v>
+        <v>69.13</v>
       </c>
       <c r="N29" t="n">
-        <v>72.54000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>72.23</v>
+        <v>72.06</v>
       </c>
       <c r="P29" s="6" t="inlineStr"/>
       <c r="Q29" s="7" t="n">
         <v/>
       </c>
-      <c r="R29" s="7" t="inlineStr">
+      <c r="R29" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="8" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="8" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="9" t="n">
-        <v/>
+      <c r="U29" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W29" s="10" t="inlineStr">
         <is>
@@ -2917,57 +2917,59 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C30" t="n">
-        <v>92.61</v>
+        <v>119.48</v>
       </c>
       <c r="D30" t="n">
-        <v>69.2</v>
+        <v>76.73</v>
       </c>
       <c r="E30" t="n">
-        <v>90.90000000000001</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>23.88</v>
+        <v>7.81</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.3563</v>
+        <v>0.0859</v>
       </c>
       <c r="H30" t="n">
-        <v>23.41</v>
+        <v>42.75</v>
       </c>
       <c r="I30" t="n">
-        <v>59.37</v>
+        <v>45.79</v>
       </c>
       <c r="J30" t="n">
-        <v>63.44</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>64.90000000000001</v>
+        <v>79.19</v>
       </c>
       <c r="L30" t="n">
-        <v>66.37</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>69.13</v>
+        <v>102.61</v>
       </c>
       <c r="N30" t="n">
-        <v>71.90000000000001</v>
+        <v>119.31</v>
       </c>
       <c r="O30" t="n">
-        <v>72.06</v>
+        <v>116.02</v>
       </c>
       <c r="P30" s="6" t="inlineStr"/>
       <c r="Q30" s="7" t="n">
         <v/>
       </c>
-      <c r="R30" s="7" t="n">
-        <v/>
+      <c r="R30" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
         <is>
@@ -2976,17 +2978,17 @@
       </c>
       <c r="T30" s="9" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U30" s="9" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="9" t="inlineStr">
+      <c r="V30" s="9" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="V30" s="9" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W30" s="10" t="inlineStr">
@@ -2999,145 +3001,145 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>98</v>
+        <v>100.93</v>
       </c>
       <c r="C31" t="n">
-        <v>119.48</v>
+        <v>102.44</v>
       </c>
       <c r="D31" t="n">
-        <v>76.73</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>98.70999999999999</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>7.81</v>
+        <v>-0.39</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0859</v>
+        <v>-0.004</v>
       </c>
       <c r="H31" t="n">
-        <v>42.75</v>
+        <v>10.48</v>
       </c>
       <c r="I31" t="n">
-        <v>45.79</v>
+        <v>33.98</v>
       </c>
       <c r="J31" t="n">
-        <v>72.48999999999999</v>
+        <v>56.26</v>
       </c>
       <c r="K31" t="n">
-        <v>79.19</v>
+        <v>77.33</v>
       </c>
       <c r="L31" t="n">
-        <v>85.90000000000001</v>
+        <v>98.41</v>
       </c>
       <c r="M31" t="n">
-        <v>102.61</v>
+        <v>120.08</v>
       </c>
       <c r="N31" t="n">
-        <v>119.31</v>
+        <v>141.76</v>
       </c>
       <c r="O31" t="n">
-        <v>116.02</v>
+        <v>162.23</v>
       </c>
       <c r="P31" s="6" t="inlineStr"/>
       <c r="Q31" s="7" t="n">
         <v/>
       </c>
-      <c r="R31" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="8" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="9" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U31" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R31" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="11" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="9" t="n">
+        <v/>
       </c>
       <c r="W31" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>100.93</v>
+        <v>100.51</v>
       </c>
       <c r="C32" t="n">
-        <v>102.44</v>
+        <v>101.67</v>
       </c>
       <c r="D32" t="n">
-        <v>91.95999999999999</v>
+        <v>84.37</v>
       </c>
       <c r="E32" t="n">
-        <v>98.31999999999999</v>
+        <v>99.64</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.39</v>
+        <v>1.32</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0134</v>
       </c>
       <c r="H32" t="n">
-        <v>10.48</v>
+        <v>17.3</v>
       </c>
       <c r="I32" t="n">
-        <v>33.98</v>
+        <v>81.48</v>
       </c>
       <c r="J32" t="n">
-        <v>56.26</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>77.33</v>
+        <v>93.08</v>
       </c>
       <c r="L32" t="n">
-        <v>98.41</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>120.08</v>
+        <v>103.56</v>
       </c>
       <c r="N32" t="n">
-        <v>141.76</v>
+        <v>109.36</v>
       </c>
       <c r="O32" t="n">
-        <v>162.23</v>
+        <v>112.92</v>
       </c>
       <c r="P32" s="6" t="inlineStr"/>
-      <c r="Q32" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="11" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="8" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T32" s="9" t="n">
@@ -3163,69 +3165,67 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>100.51</v>
+        <v>102.6</v>
       </c>
       <c r="C33" t="n">
-        <v>101.67</v>
+        <v>113.97</v>
       </c>
       <c r="D33" t="n">
-        <v>84.37</v>
+        <v>96.5</v>
       </c>
       <c r="E33" t="n">
-        <v>99.64</v>
+        <v>111.54</v>
       </c>
       <c r="F33" t="n">
-        <v>1.32</v>
+        <v>11.9</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.1194</v>
       </c>
       <c r="H33" t="n">
-        <v>17.3</v>
+        <v>17.47</v>
       </c>
       <c r="I33" t="n">
-        <v>81.48</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>88.40000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>93.08</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>97.76000000000001</v>
+        <v>96.33</v>
       </c>
       <c r="M33" t="n">
-        <v>103.56</v>
+        <v>108.29</v>
       </c>
       <c r="N33" t="n">
-        <v>109.36</v>
+        <v>120.25</v>
       </c>
       <c r="O33" t="n">
-        <v>112.92</v>
+        <v>118.97</v>
       </c>
       <c r="P33" s="6" t="inlineStr"/>
-      <c r="Q33" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q33" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="7" t="n">
+        <v/>
       </c>
       <c r="S33" s="8" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="9" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="9" t="n">
         <v/>
@@ -3238,149 +3238,149 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>102.6</v>
+        <v>112.96</v>
       </c>
       <c r="C34" t="n">
-        <v>113.97</v>
+        <v>117.63</v>
       </c>
       <c r="D34" t="n">
-        <v>96.5</v>
+        <v>91.05</v>
       </c>
       <c r="E34" t="n">
-        <v>111.54</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>11.9</v>
+        <v>-14.97</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.1194</v>
+        <v>-0.1342</v>
       </c>
       <c r="H34" t="n">
-        <v>17.47</v>
+        <v>26.58</v>
       </c>
       <c r="I34" t="n">
-        <v>67.06999999999999</v>
+        <v>79.03</v>
       </c>
       <c r="J34" t="n">
-        <v>85.65000000000001</v>
+        <v>97.22</v>
       </c>
       <c r="K34" t="n">
-        <v>90.98999999999999</v>
+        <v>102.81</v>
       </c>
       <c r="L34" t="n">
-        <v>96.33</v>
+        <v>108.39</v>
       </c>
       <c r="M34" t="n">
-        <v>108.29</v>
+        <v>120.28</v>
       </c>
       <c r="N34" t="n">
-        <v>120.25</v>
+        <v>132.16</v>
       </c>
       <c r="O34" t="n">
-        <v>118.97</v>
+        <v>131.44</v>
       </c>
       <c r="P34" s="6" t="inlineStr"/>
-      <c r="Q34" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="8" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="9" t="inlineStr">
+      <c r="Q34" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R34" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="11" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="9" t="n">
+        <v/>
+      </c>
       <c r="U34" s="9" t="n">
         <v/>
       </c>
       <c r="V34" s="9" t="n">
         <v/>
       </c>
-      <c r="W34" s="10" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="W34" s="12" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>112.96</v>
+        <v>102</v>
       </c>
       <c r="C35" t="n">
-        <v>117.63</v>
+        <v>105.63</v>
       </c>
       <c r="D35" t="n">
-        <v>91.05</v>
+        <v>80.56</v>
       </c>
       <c r="E35" t="n">
-        <v>96.56999999999999</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>-14.97</v>
+        <v>-12.72</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.1342</v>
+        <v>-0.1317</v>
       </c>
       <c r="H35" t="n">
-        <v>26.58</v>
+        <v>25.07</v>
       </c>
       <c r="I35" t="n">
-        <v>79.03</v>
+        <v>64.47</v>
       </c>
       <c r="J35" t="n">
-        <v>97.22</v>
+        <v>66.11</v>
       </c>
       <c r="K35" t="n">
-        <v>102.81</v>
+        <v>83.28</v>
       </c>
       <c r="L35" t="n">
-        <v>108.39</v>
+        <v>100.45</v>
       </c>
       <c r="M35" t="n">
-        <v>120.28</v>
+        <v>109.86</v>
       </c>
       <c r="N35" t="n">
-        <v>132.16</v>
+        <v>119.26</v>
       </c>
       <c r="O35" t="n">
-        <v>131.44</v>
+        <v>144.21</v>
       </c>
       <c r="P35" s="6" t="inlineStr"/>
-      <c r="Q35" s="7" t="inlineStr">
+      <c r="Q35" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S35" s="11" t="inlineStr">
         <is>
           <t>↓</t>
@@ -3400,77 +3400,73 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C36" t="n">
-        <v>105.63</v>
+        <v>98.39</v>
       </c>
       <c r="D36" t="n">
-        <v>80.56</v>
+        <v>87.02</v>
       </c>
       <c r="E36" t="n">
-        <v>83.84999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-12.72</v>
+        <v>10.55</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.1317</v>
+        <v>0.1258</v>
       </c>
       <c r="H36" t="n">
-        <v>25.07</v>
+        <v>11.37</v>
       </c>
       <c r="I36" t="n">
-        <v>64.47</v>
+        <v>55.49</v>
       </c>
       <c r="J36" t="n">
-        <v>66.11</v>
+        <v>54.16</v>
       </c>
       <c r="K36" t="n">
-        <v>83.28</v>
+        <v>71.31</v>
       </c>
       <c r="L36" t="n">
-        <v>100.45</v>
+        <v>88.47</v>
       </c>
       <c r="M36" t="n">
-        <v>109.86</v>
+        <v>96.38</v>
       </c>
       <c r="N36" t="n">
-        <v>119.26</v>
+        <v>104.3</v>
       </c>
       <c r="O36" t="n">
-        <v>144.21</v>
+        <v>130.7</v>
       </c>
       <c r="P36" s="6" t="inlineStr"/>
       <c r="Q36" s="7" t="n">
         <v/>
       </c>
-      <c r="R36" s="7" t="inlineStr">
+      <c r="R36" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="8" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="11" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="9" t="n">
-        <v/>
-      </c>
       <c r="U36" s="9" t="n">
         <v/>
       </c>
@@ -3482,55 +3478,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>89</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>98.39</v>
+        <v>110.93</v>
       </c>
       <c r="D37" t="n">
-        <v>87.02</v>
+        <v>94.59</v>
       </c>
       <c r="E37" t="n">
-        <v>94.40000000000001</v>
+        <v>101.94</v>
       </c>
       <c r="F37" t="n">
-        <v>10.55</v>
+        <v>7.54</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.1258</v>
+        <v>0.0799</v>
       </c>
       <c r="H37" t="n">
-        <v>11.37</v>
+        <v>16.34</v>
       </c>
       <c r="I37" t="n">
-        <v>55.49</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>54.16</v>
+        <v>83.88</v>
       </c>
       <c r="K37" t="n">
-        <v>71.31</v>
+        <v>88.72</v>
       </c>
       <c r="L37" t="n">
-        <v>88.47</v>
+        <v>93.55</v>
       </c>
       <c r="M37" t="n">
-        <v>96.38</v>
+        <v>100.09</v>
       </c>
       <c r="N37" t="n">
-        <v>104.3</v>
+        <v>106.62</v>
       </c>
       <c r="O37" t="n">
-        <v>130.7</v>
+        <v>109.76</v>
       </c>
       <c r="P37" s="6" t="inlineStr"/>
       <c r="Q37" s="7" t="n">
@@ -3549,11 +3549,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="9" t="n">
-        <v/>
+      <c r="U37" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W37" s="12" t="inlineStr">
         <is>
@@ -3562,161 +3566,153 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>95.59999999999999</v>
+        <v>99.73</v>
       </c>
       <c r="C38" t="n">
-        <v>110.93</v>
+        <v>107.46</v>
       </c>
       <c r="D38" t="n">
-        <v>94.59</v>
+        <v>88.66</v>
       </c>
       <c r="E38" t="n">
-        <v>101.94</v>
+        <v>95.42</v>
       </c>
       <c r="F38" t="n">
-        <v>7.54</v>
+        <v>-6.52</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0799</v>
+        <v>-0.064</v>
       </c>
       <c r="H38" t="n">
-        <v>16.34</v>
+        <v>18.8</v>
       </c>
       <c r="I38" t="n">
-        <v>75.65000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="J38" t="n">
-        <v>83.88</v>
+        <v>85.19</v>
       </c>
       <c r="K38" t="n">
-        <v>88.72</v>
+        <v>93.77</v>
       </c>
       <c r="L38" t="n">
-        <v>93.55</v>
+        <v>102.35</v>
       </c>
       <c r="M38" t="n">
-        <v>100.09</v>
+        <v>110.11</v>
       </c>
       <c r="N38" t="n">
-        <v>106.62</v>
+        <v>117.87</v>
       </c>
       <c r="O38" t="n">
-        <v>109.76</v>
+        <v>127.27</v>
       </c>
       <c r="P38" s="6" t="inlineStr"/>
       <c r="Q38" s="7" t="n">
         <v/>
       </c>
-      <c r="R38" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="8" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="9" t="inlineStr">
+      <c r="R38" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U38" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S38" s="11" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="9" t="n">
+        <v/>
       </c>
       <c r="W38" s="12" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>99.73</v>
+        <v>98.19</v>
       </c>
       <c r="C39" t="n">
-        <v>107.46</v>
+        <v>106</v>
       </c>
       <c r="D39" t="n">
-        <v>88.66</v>
+        <v>96.13</v>
       </c>
       <c r="E39" t="n">
-        <v>95.42</v>
+        <v>105.42</v>
       </c>
       <c r="F39" t="n">
-        <v>-6.52</v>
+        <v>10</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.064</v>
+        <v>0.1048</v>
       </c>
       <c r="H39" t="n">
-        <v>18.8</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>78.25</v>
+        <v>69.86</v>
       </c>
       <c r="J39" t="n">
-        <v>85.19</v>
+        <v>75.3</v>
       </c>
       <c r="K39" t="n">
-        <v>93.77</v>
+        <v>86.02</v>
       </c>
       <c r="L39" t="n">
-        <v>102.35</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>110.11</v>
+        <v>104.82</v>
       </c>
       <c r="N39" t="n">
-        <v>117.87</v>
+        <v>112.9</v>
       </c>
       <c r="O39" t="n">
-        <v>127.27</v>
+        <v>126.26</v>
       </c>
       <c r="P39" s="6" t="inlineStr"/>
       <c r="Q39" s="7" t="n">
         <v/>
       </c>
-      <c r="R39" s="7" t="inlineStr">
+      <c r="R39" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="8" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="11" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="9" t="n">
-        <v/>
-      </c>
       <c r="U39" s="9" t="n">
         <v/>
       </c>
@@ -3728,73 +3724,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>98.19</v>
+        <v>106</v>
       </c>
       <c r="C40" t="n">
-        <v>106</v>
+        <v>109.47</v>
       </c>
       <c r="D40" t="n">
-        <v>96.13</v>
+        <v>94.73</v>
       </c>
       <c r="E40" t="n">
-        <v>105.42</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>10</v>
+        <v>-8.82</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.1048</v>
+        <v>-0.0837</v>
       </c>
       <c r="H40" t="n">
-        <v>9.869999999999999</v>
+        <v>14.74</v>
       </c>
       <c r="I40" t="n">
-        <v>69.86</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>75.3</v>
+        <v>97.73</v>
       </c>
       <c r="K40" t="n">
-        <v>86.02</v>
+        <v>100.48</v>
       </c>
       <c r="L40" t="n">
-        <v>96.73999999999999</v>
+        <v>103.24</v>
       </c>
       <c r="M40" t="n">
-        <v>104.82</v>
+        <v>110.35</v>
       </c>
       <c r="N40" t="n">
-        <v>112.9</v>
+        <v>117.47</v>
       </c>
       <c r="O40" t="n">
-        <v>126.26</v>
+        <v>115.87</v>
       </c>
       <c r="P40" s="6" t="inlineStr"/>
-      <c r="Q40" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="8" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="9" t="inlineStr">
+      <c r="Q40" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R40" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="11" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="9" t="n">
+        <v/>
+      </c>
       <c r="U40" s="9" t="n">
         <v/>
       </c>
@@ -3808,69 +3810,67 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>106</v>
+        <v>93.88</v>
       </c>
       <c r="C41" t="n">
-        <v>109.47</v>
+        <v>94.7</v>
       </c>
       <c r="D41" t="n">
-        <v>94.73</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>96.59999999999999</v>
+        <v>87.36</v>
       </c>
       <c r="F41" t="n">
-        <v>-8.82</v>
+        <v>-9.24</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0837</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>14.74</v>
+        <v>8.35</v>
       </c>
       <c r="I41" t="n">
-        <v>86.26000000000001</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>97.73</v>
+        <v>79.11</v>
       </c>
       <c r="K41" t="n">
-        <v>100.48</v>
+        <v>89.23</v>
       </c>
       <c r="L41" t="n">
-        <v>103.24</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>110.35</v>
+        <v>103.97</v>
       </c>
       <c r="N41" t="n">
-        <v>117.47</v>
+        <v>108.59</v>
       </c>
       <c r="O41" t="n">
-        <v>115.87</v>
+        <v>124.21</v>
       </c>
       <c r="P41" s="6" t="inlineStr"/>
-      <c r="Q41" s="7" t="inlineStr">
+      <c r="Q41" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S41" s="11" t="inlineStr">
         <is>
           <t>↓</t>
@@ -3890,79 +3890,77 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>93.88</v>
+        <v>88.5</v>
       </c>
       <c r="C42" t="n">
-        <v>94.7</v>
+        <v>97</v>
       </c>
       <c r="D42" t="n">
-        <v>86.34999999999999</v>
+        <v>88.45</v>
       </c>
       <c r="E42" t="n">
-        <v>87.36</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>-9.24</v>
+        <v>3.18</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.0364</v>
       </c>
       <c r="H42" t="n">
-        <v>8.35</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>79.98999999999999</v>
+        <v>78</v>
       </c>
       <c r="J42" t="n">
-        <v>79.11</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>89.23</v>
+        <v>83.19</v>
       </c>
       <c r="L42" t="n">
-        <v>99.34999999999999</v>
+        <v>88.94</v>
       </c>
       <c r="M42" t="n">
-        <v>103.97</v>
+        <v>91.53</v>
       </c>
       <c r="N42" t="n">
-        <v>108.59</v>
+        <v>94.13</v>
       </c>
       <c r="O42" t="n">
-        <v>124.21</v>
+        <v>103.05</v>
       </c>
       <c r="P42" s="6" t="inlineStr"/>
       <c r="Q42" s="7" t="n">
         <v/>
       </c>
-      <c r="R42" s="7" t="inlineStr">
+      <c r="R42" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="8" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="11" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="9" t="n">
-        <v/>
+      <c r="U42" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V42" s="9" t="n">
         <v/>
@@ -3972,78 +3970,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>88.5</v>
+        <v>93</v>
       </c>
       <c r="C43" t="n">
-        <v>97</v>
+        <v>95.47</v>
       </c>
       <c r="D43" t="n">
-        <v>88.45</v>
+        <v>83.2</v>
       </c>
       <c r="E43" t="n">
-        <v>90.54000000000001</v>
+        <v>84.88</v>
       </c>
       <c r="F43" t="n">
-        <v>3.18</v>
+        <v>-5.66</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0364</v>
+        <v>-0.0625</v>
       </c>
       <c r="H43" t="n">
-        <v>8.550000000000001</v>
+        <v>12.27</v>
       </c>
       <c r="I43" t="n">
-        <v>78</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>77.43000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>83.19</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>88.94</v>
+        <v>91.63</v>
       </c>
       <c r="M43" t="n">
-        <v>91.53</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="N43" t="n">
-        <v>94.13</v>
+        <v>98</v>
       </c>
       <c r="O43" t="n">
-        <v>103.05</v>
+        <v>105.55</v>
       </c>
       <c r="P43" s="6" t="inlineStr"/>
       <c r="Q43" s="7" t="n">
         <v/>
       </c>
-      <c r="R43" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="8" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R43" s="7" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S43" s="11" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="9" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U43" s="9" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U43" s="9" t="n">
+        <v/>
+      </c>
       <c r="V43" s="9" t="n">
         <v/>
       </c>
@@ -4052,59 +4054,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>93</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>95.47</v>
+        <v>82.42</v>
       </c>
       <c r="D44" t="n">
-        <v>83.2</v>
+        <v>73.58</v>
       </c>
       <c r="E44" t="n">
-        <v>84.88</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>-5.66</v>
+        <v>-7.34</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0625</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>12.27</v>
+        <v>8.84</v>
       </c>
       <c r="I44" t="n">
-        <v>79.90000000000001</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>80.90000000000001</v>
+        <v>70.38</v>
       </c>
       <c r="K44" t="n">
-        <v>86.26000000000001</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>91.63</v>
+        <v>87.11</v>
       </c>
       <c r="M44" t="n">
-        <v>94.81999999999999</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>98</v>
+        <v>94.92</v>
       </c>
       <c r="O44" t="n">
-        <v>105.55</v>
+        <v>107.74</v>
       </c>
       <c r="P44" s="6" t="inlineStr"/>
       <c r="Q44" s="7" t="n">
@@ -4120,10 +4118,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T44" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T44" s="9" t="n">
+        <v/>
       </c>
       <c r="U44" s="9" t="n">
         <v/>
@@ -4141,58 +4137,60 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>81.40000000000001</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>82.42</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>73.58</v>
+        <v>68.56</v>
       </c>
       <c r="E45" t="n">
-        <v>77.54000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="F45" t="n">
-        <v>-7.34</v>
+        <v>-8.31</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.1072</v>
       </c>
       <c r="H45" t="n">
-        <v>8.84</v>
+        <v>10.4</v>
       </c>
       <c r="I45" t="n">
-        <v>70.93000000000001</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="J45" t="n">
-        <v>70.38</v>
+        <v>68.47</v>
       </c>
       <c r="K45" t="n">
-        <v>78.73999999999999</v>
+        <v>73.12</v>
       </c>
       <c r="L45" t="n">
-        <v>87.11</v>
+        <v>77.77</v>
       </c>
       <c r="M45" t="n">
-        <v>91.01000000000001</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>94.92</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>107.74</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="P45" s="6" t="inlineStr"/>
-      <c r="Q45" s="7" t="n">
-        <v/>
+      <c r="Q45" s="7" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R45" s="7" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S45" s="11" t="inlineStr">
@@ -4219,65 +4217,61 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>78.93000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="C46" t="n">
-        <v>78.95999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>68.56</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>69.23</v>
+        <v>68.78</v>
       </c>
       <c r="F46" t="n">
-        <v>-8.31</v>
+        <v>-0.45</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.1072</v>
+        <v>-0.0065</v>
       </c>
       <c r="H46" t="n">
-        <v>10.4</v>
+        <v>4.56</v>
       </c>
       <c r="I46" t="n">
-        <v>64.73999999999999</v>
+        <v>58.16</v>
       </c>
       <c r="J46" t="n">
-        <v>68.47</v>
+        <v>56.57</v>
       </c>
       <c r="K46" t="n">
-        <v>73.12</v>
+        <v>64.03</v>
       </c>
       <c r="L46" t="n">
-        <v>77.77</v>
+        <v>71.5</v>
       </c>
       <c r="M46" t="n">
-        <v>81.95999999999999</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>86.15000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="O46" t="n">
-        <v>91.26000000000001</v>
+        <v>89.36</v>
       </c>
       <c r="P46" s="6" t="inlineStr"/>
-      <c r="Q46" s="7" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R46" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q46" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="7" t="n">
+        <v/>
       </c>
       <c r="S46" s="11" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="9" t="n">
@@ -4299,50 +4293,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>70.5</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>71.59999999999999</v>
+        <v>76.08</v>
       </c>
       <c r="D47" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>68.78</v>
+        <v>71.41</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.45</v>
+        <v>2.63</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0382</v>
       </c>
       <c r="H47" t="n">
-        <v>4.56</v>
+        <v>8.26</v>
       </c>
       <c r="I47" t="n">
-        <v>58.16</v>
+        <v>62.48</v>
       </c>
       <c r="J47" t="n">
-        <v>56.57</v>
+        <v>63.95</v>
       </c>
       <c r="K47" t="n">
-        <v>64.03</v>
+        <v>66.5</v>
       </c>
       <c r="L47" t="n">
-        <v>71.5</v>
+        <v>69.05</v>
       </c>
       <c r="M47" t="n">
-        <v>74.43000000000001</v>
+        <v>71.06</v>
       </c>
       <c r="N47" t="n">
-        <v>77.37</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O47" t="n">
-        <v>89.36</v>
+        <v>76.16</v>
       </c>
       <c r="P47" s="6" t="inlineStr"/>
       <c r="Q47" s="7" t="n">
@@ -4351,16 +4345,20 @@
       <c r="R47" s="7" t="n">
         <v/>
       </c>
-      <c r="S47" s="11" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="9" t="n">
-        <v/>
+      <c r="S47" s="8" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U47" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V47" s="9" t="n">
         <v/>
@@ -4370,55 +4368,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>68.68000000000001</v>
+        <v>73.69</v>
       </c>
       <c r="C48" t="n">
-        <v>76.08</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>67.81999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="E48" t="n">
-        <v>71.41</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>2.63</v>
+        <v>11.08</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0382</v>
+        <v>0.1552</v>
       </c>
       <c r="H48" t="n">
-        <v>8.26</v>
+        <v>10.15</v>
       </c>
       <c r="I48" t="n">
-        <v>62.48</v>
+        <v>59.56</v>
       </c>
       <c r="J48" t="n">
-        <v>63.95</v>
+        <v>62.88</v>
       </c>
       <c r="K48" t="n">
-        <v>66.5</v>
+        <v>67.28</v>
       </c>
       <c r="L48" t="n">
-        <v>69.05</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>71.06</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="N48" t="n">
-        <v>73.06999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>76.16</v>
+        <v>84.34</v>
       </c>
       <c r="P48" s="6" t="inlineStr"/>
       <c r="Q48" s="7" t="n">
@@ -4434,75 +4436,73 @@
       </c>
       <c r="T48" s="9" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="9" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U48" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W48" s="12" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W48" s="10" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>73.69</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>82.76000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="D49" t="n">
-        <v>72.61</v>
+        <v>80.27</v>
       </c>
       <c r="E49" t="n">
-        <v>82.48999999999999</v>
+        <v>89.31</v>
       </c>
       <c r="F49" t="n">
-        <v>11.08</v>
+        <v>6.82</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.1552</v>
+        <v>0.0827</v>
       </c>
       <c r="H49" t="n">
-        <v>10.15</v>
+        <v>13.23</v>
       </c>
       <c r="I49" t="n">
-        <v>59.56</v>
+        <v>62.46</v>
       </c>
       <c r="J49" t="n">
-        <v>62.88</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>67.28</v>
+        <v>77.41</v>
       </c>
       <c r="L49" t="n">
-        <v>71.68000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="M49" t="n">
-        <v>75.54000000000001</v>
+        <v>87.56</v>
       </c>
       <c r="N49" t="n">
-        <v>79.40000000000001</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>84.34</v>
+        <v>92.91</v>
       </c>
       <c r="P49" s="6" t="inlineStr"/>
       <c r="Q49" s="7" t="n">
@@ -4518,17 +4518,15 @@
       </c>
       <c r="T49" s="9" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U49" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="9" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="9" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W49" s="10" t="inlineStr">
@@ -4541,138 +4539,142 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>83.76000000000001</v>
+        <v>86.12</v>
       </c>
       <c r="C50" t="n">
-        <v>93.5</v>
+        <v>86.87</v>
       </c>
       <c r="D50" t="n">
-        <v>80.27</v>
+        <v>77.78</v>
       </c>
       <c r="E50" t="n">
-        <v>89.31</v>
+        <v>84.67</v>
       </c>
       <c r="F50" t="n">
-        <v>6.82</v>
+        <v>-4.64</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0827</v>
+        <v>-0.052</v>
       </c>
       <c r="H50" t="n">
-        <v>13.23</v>
+        <v>9.09</v>
       </c>
       <c r="I50" t="n">
-        <v>62.46</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>74.73999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>77.41</v>
+        <v>82.69</v>
       </c>
       <c r="L50" t="n">
-        <v>80.09</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>87.56</v>
+        <v>95.92</v>
       </c>
       <c r="N50" t="n">
-        <v>95.04000000000001</v>
+        <v>103.75</v>
       </c>
       <c r="O50" t="n">
-        <v>92.91</v>
+        <v>106.73</v>
       </c>
       <c r="P50" s="6" t="inlineStr"/>
       <c r="Q50" s="7" t="n">
         <v/>
       </c>
-      <c r="R50" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="8" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="9" t="inlineStr">
+      <c r="R50" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S50" s="11" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="9" t="n">
+        <v/>
+      </c>
       <c r="U50" s="9" t="n">
         <v/>
       </c>
-      <c r="V50" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V50" s="9" t="n">
+        <v/>
       </c>
       <c r="W50" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>86.12</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C51" t="n">
-        <v>86.87</v>
+        <v>82.33</v>
       </c>
       <c r="D51" t="n">
-        <v>77.78</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>84.67</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>-4.64</v>
+        <v>-6.49</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.0767</v>
       </c>
       <c r="H51" t="n">
-        <v>9.09</v>
+        <v>8.09</v>
       </c>
       <c r="I51" t="n">
-        <v>67.04000000000001</v>
+        <v>68.69</v>
       </c>
       <c r="J51" t="n">
-        <v>77.29000000000001</v>
+        <v>76.75</v>
       </c>
       <c r="K51" t="n">
-        <v>82.69</v>
+        <v>80.12</v>
       </c>
       <c r="L51" t="n">
-        <v>88.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="M51" t="n">
-        <v>95.92</v>
+        <v>89.22</v>
       </c>
       <c r="N51" t="n">
-        <v>103.75</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>106.73</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="P51" s="6" t="inlineStr"/>
-      <c r="Q51" s="7" t="n">
-        <v/>
+      <c r="Q51" s="7" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R51" s="7" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S51" s="11" t="inlineStr">
@@ -4703,70 +4705,68 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>80.09999999999999</v>
+        <v>78.42</v>
       </c>
       <c r="C52" t="n">
-        <v>82.33</v>
+        <v>84.61</v>
       </c>
       <c r="D52" t="n">
-        <v>74.23999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>78.18000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>-6.49</v>
+        <v>4.22</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0767</v>
+        <v>0.054</v>
       </c>
       <c r="H52" t="n">
-        <v>8.09</v>
+        <v>6.82</v>
       </c>
       <c r="I52" t="n">
-        <v>68.69</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>76.75</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>80.12</v>
+        <v>74.13</v>
       </c>
       <c r="L52" t="n">
-        <v>83.5</v>
+        <v>78.23</v>
       </c>
       <c r="M52" t="n">
-        <v>89.22</v>
+        <v>82.23</v>
       </c>
       <c r="N52" t="n">
-        <v>94.93000000000001</v>
+        <v>86.22</v>
       </c>
       <c r="O52" t="n">
-        <v>95.95999999999999</v>
+        <v>90.42</v>
       </c>
       <c r="P52" s="6" t="inlineStr"/>
-      <c r="Q52" s="7" t="inlineStr">
+      <c r="Q52" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="8" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="11" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="9" t="n">
-        <v/>
-      </c>
       <c r="U52" s="9" t="n">
         <v/>
       </c>
@@ -4778,59 +4778,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>78.42</v>
+        <v>82.53</v>
       </c>
       <c r="C53" t="n">
-        <v>84.61</v>
+        <v>89</v>
       </c>
       <c r="D53" t="n">
-        <v>77.79000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="E53" t="n">
-        <v>82.40000000000001</v>
+        <v>87.06</v>
       </c>
       <c r="F53" t="n">
-        <v>4.22</v>
+        <v>4.66</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.054</v>
+        <v>0.0566</v>
       </c>
       <c r="H53" t="n">
-        <v>6.82</v>
+        <v>7.5</v>
       </c>
       <c r="I53" t="n">
-        <v>66.15000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="J53" t="n">
-        <v>70.04000000000001</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>74.13</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>78.23</v>
+        <v>81.8</v>
       </c>
       <c r="M53" t="n">
-        <v>82.23</v>
+        <v>85.81</v>
       </c>
       <c r="N53" t="n">
-        <v>86.22</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="O53" t="n">
-        <v>90.42</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="P53" s="6" t="inlineStr"/>
       <c r="Q53" s="7" t="n">
@@ -4865,68 +4861,70 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>82.53</v>
+        <v>86.5</v>
       </c>
       <c r="C54" t="n">
-        <v>89</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>81.5</v>
+        <v>79.62</v>
       </c>
       <c r="E54" t="n">
-        <v>87.06</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>4.66</v>
+        <v>-3.66</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0566</v>
+        <v>-0.042</v>
       </c>
       <c r="H54" t="n">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="I54" t="n">
-        <v>70.97</v>
+        <v>74</v>
       </c>
       <c r="J54" t="n">
-        <v>76.18000000000001</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>78.98999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="L54" t="n">
-        <v>81.8</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>85.81</v>
+        <v>90.81</v>
       </c>
       <c r="N54" t="n">
-        <v>89.81999999999999</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="O54" t="n">
-        <v>91.43000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="P54" s="6" t="inlineStr"/>
-      <c r="Q54" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="8" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="9" t="inlineStr">
+      <c r="Q54" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="7" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S54" s="11" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="9" t="n">
+        <v/>
+      </c>
       <c r="U54" s="9" t="n">
         <v/>
       </c>
@@ -4938,78 +4936,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>86.5</v>
+        <v>84.69</v>
       </c>
       <c r="C55" t="n">
-        <v>86.56999999999999</v>
+        <v>93.14</v>
       </c>
       <c r="D55" t="n">
-        <v>79.62</v>
+        <v>84.11</v>
       </c>
       <c r="E55" t="n">
-        <v>83.40000000000001</v>
+        <v>91.48</v>
       </c>
       <c r="F55" t="n">
-        <v>-3.66</v>
+        <v>8.08</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.042</v>
+        <v>0.0969</v>
       </c>
       <c r="H55" t="n">
-        <v>6.95</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>74</v>
+        <v>72.67</v>
       </c>
       <c r="J55" t="n">
-        <v>80.45999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>83.31</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>86.15000000000001</v>
+        <v>83.25</v>
       </c>
       <c r="M55" t="n">
-        <v>90.81</v>
+        <v>86.88</v>
       </c>
       <c r="N55" t="n">
-        <v>95.45999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="O55" t="n">
-        <v>96.5</v>
+        <v>93.52</v>
       </c>
       <c r="P55" s="6" t="inlineStr"/>
-      <c r="Q55" s="7" t="inlineStr">
+      <c r="Q55" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="8" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="9" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R55" s="7" t="inlineStr">
+      <c r="U55" s="9" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="11" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="9" t="n">
-        <v/>
-      </c>
       <c r="V55" s="9" t="n">
         <v/>
       </c>
@@ -5018,59 +5020,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>84.69</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C56" t="n">
-        <v>93.14</v>
+        <v>104.46</v>
       </c>
       <c r="D56" t="n">
-        <v>84.11</v>
+        <v>90.87</v>
       </c>
       <c r="E56" t="n">
-        <v>91.48</v>
+        <v>100.05</v>
       </c>
       <c r="F56" t="n">
-        <v>8.08</v>
+        <v>8.57</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0969</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>9.029999999999999</v>
+        <v>13.59</v>
       </c>
       <c r="I56" t="n">
-        <v>72.67</v>
+        <v>75.08</v>
       </c>
       <c r="J56" t="n">
-        <v>76.59999999999999</v>
+        <v>83.88</v>
       </c>
       <c r="K56" t="n">
-        <v>79.93000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="L56" t="n">
-        <v>83.25</v>
+        <v>90.05</v>
       </c>
       <c r="M56" t="n">
-        <v>86.88</v>
+        <v>96</v>
       </c>
       <c r="N56" t="n">
-        <v>90.5</v>
+        <v>101.94</v>
       </c>
       <c r="O56" t="n">
-        <v>93.52</v>
+        <v>102.17</v>
       </c>
       <c r="P56" s="6" t="inlineStr"/>
       <c r="Q56" s="7" t="n">
@@ -5094,8 +5092,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V56" s="9" t="n">
-        <v/>
+      <c r="V56" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W56" s="10" t="inlineStr">
         <is>
@@ -5107,50 +5107,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>92.26000000000001</v>
+        <v>102.25</v>
       </c>
       <c r="C57" t="n">
-        <v>104.46</v>
+        <v>106.75</v>
       </c>
       <c r="D57" t="n">
-        <v>90.87</v>
+        <v>96.67</v>
       </c>
       <c r="E57" t="n">
-        <v>100.05</v>
+        <v>96.08</v>
       </c>
       <c r="F57" t="n">
-        <v>8.57</v>
+        <v>-3.97</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.0397</v>
       </c>
       <c r="H57" t="n">
-        <v>13.59</v>
+        <v>10.08</v>
       </c>
       <c r="I57" t="n">
-        <v>75.08</v>
+        <v>77.28</v>
       </c>
       <c r="J57" t="n">
-        <v>83.88</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="K57" t="n">
-        <v>86.97</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>90.05</v>
+        <v>98.86</v>
       </c>
       <c r="M57" t="n">
-        <v>96</v>
+        <v>106.85</v>
       </c>
       <c r="N57" t="n">
-        <v>101.94</v>
+        <v>114.83</v>
       </c>
       <c r="O57" t="n">
-        <v>102.17</v>
+        <v>118.05</v>
       </c>
       <c r="P57" s="6" t="inlineStr"/>
       <c r="Q57" s="7" t="n">
@@ -5159,108 +5159,30 @@
       <c r="R57" s="7" t="n">
         <v/>
       </c>
-      <c r="S57" s="8" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="9" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V57" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S57" s="11" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="9" t="n">
+        <v/>
       </c>
       <c r="W57" s="10" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>102.25</v>
-      </c>
-      <c r="C58" t="n">
-        <v>106.75</v>
-      </c>
-      <c r="D58" t="n">
-        <v>100.53</v>
-      </c>
-      <c r="E58" t="n">
-        <v>100.89</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.008399999999999999</v>
-      </c>
-      <c r="H58" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="I58" t="n">
-        <v>77.28</v>
-      </c>
-      <c r="J58" t="n">
-        <v>87.65000000000001</v>
-      </c>
-      <c r="K58" t="n">
-        <v>93.26000000000001</v>
-      </c>
-      <c r="L58" t="n">
-        <v>98.86</v>
-      </c>
-      <c r="M58" t="n">
-        <v>106.85</v>
-      </c>
-      <c r="N58" t="n">
-        <v>114.83</v>
-      </c>
-      <c r="O58" t="n">
-        <v>118.05</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr"/>
-      <c r="Q58" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="8" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="10" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -101,9 +101,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -483,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -682,30 +679,32 @@
       <c r="O2" t="n">
         <v>65.68000000000001</v>
       </c>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S2" s="8" t="inlineStr">
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T2" s="9" t="inlineStr">
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W2" s="10" t="inlineStr">
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -760,34 +759,36 @@
       <c r="O3" t="n">
         <v>67.25</v>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="7" t="inlineStr">
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="7" t="inlineStr">
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="11" t="inlineStr">
+      <c r="S3" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T3" s="9" t="inlineStr">
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -846,28 +847,30 @@
       <c r="O4" t="n">
         <v>70.61</v>
       </c>
-      <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T4" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -926,30 +929,32 @@
       <c r="O5" t="n">
         <v>66.47</v>
       </c>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T5" s="9" t="inlineStr">
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W5" s="10" t="inlineStr">
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1008,32 +1013,34 @@
       <c r="O6" t="n">
         <v>67</v>
       </c>
-      <c r="P6" s="6" t="inlineStr"/>
-      <c r="Q6" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T6" s="9" t="inlineStr">
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="9" t="inlineStr">
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V6" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W6" s="10" t="inlineStr">
+      <c r="V6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1092,32 +1099,34 @@
       <c r="O7" t="n">
         <v>70.98999999999999</v>
       </c>
-      <c r="P7" s="6" t="inlineStr"/>
-      <c r="Q7" s="7" t="inlineStr">
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="7" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="11" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T7" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W7" s="12" t="inlineStr">
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1172,30 +1181,32 @@
       <c r="O8" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="11" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T8" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W8" s="12" t="inlineStr">
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1250,30 +1261,32 @@
       <c r="O9" t="n">
         <v>67.62</v>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="7" t="inlineStr">
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="11" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T9" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W9" s="12" t="inlineStr">
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1328,32 +1341,34 @@
       <c r="O10" t="n">
         <v>63.74</v>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
-      <c r="Q10" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="8" t="inlineStr">
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T10" s="9" t="inlineStr">
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U10" s="9" t="inlineStr">
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V10" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W10" s="10" t="inlineStr">
+      <c r="V10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1412,28 +1427,30 @@
       <c r="O11" t="n">
         <v>68.83</v>
       </c>
-      <c r="P11" s="6" t="inlineStr"/>
-      <c r="Q11" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T11" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W11" s="10" t="inlineStr">
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1492,30 +1509,32 @@
       <c r="O12" t="n">
         <v>64.7</v>
       </c>
-      <c r="P12" s="6" t="inlineStr"/>
-      <c r="Q12" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="7" t="inlineStr">
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="11" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T12" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W12" s="10" t="inlineStr">
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1574,32 +1593,34 @@
       <c r="O13" t="n">
         <v>64.17</v>
       </c>
-      <c r="P13" s="6" t="inlineStr"/>
-      <c r="Q13" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="7" t="inlineStr">
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="8" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T13" s="9" t="inlineStr">
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U13" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W13" s="10" t="inlineStr">
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1658,30 +1679,32 @@
       <c r="O14" t="n">
         <v>64.44</v>
       </c>
-      <c r="P14" s="6" t="inlineStr"/>
-      <c r="Q14" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="7" t="inlineStr">
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="11" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T14" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W14" s="10" t="inlineStr">
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1740,28 +1763,30 @@
       <c r="O15" t="n">
         <v>64.48</v>
       </c>
-      <c r="P15" s="6" t="inlineStr"/>
-      <c r="Q15" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="11" t="inlineStr">
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T15" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="10" t="inlineStr">
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1820,30 +1845,32 @@
       <c r="O16" t="n">
         <v>62.18</v>
       </c>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="8" t="inlineStr">
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T16" s="9" t="inlineStr">
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U16" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="10" t="inlineStr">
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1898,32 +1925,34 @@
       <c r="O17" t="n">
         <v>62.72</v>
       </c>
-      <c r="P17" s="6" t="inlineStr"/>
-      <c r="Q17" s="7" t="inlineStr">
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="7" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="11" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T17" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="12" t="inlineStr">
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1978,30 +2007,32 @@
       <c r="O18" t="n">
         <v>63.59</v>
       </c>
-      <c r="P18" s="6" t="inlineStr"/>
-      <c r="Q18" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="7" t="inlineStr">
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="11" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T18" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="12" t="inlineStr">
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2056,30 +2087,32 @@
       <c r="O19" t="n">
         <v>60.62</v>
       </c>
-      <c r="P19" s="6" t="inlineStr"/>
-      <c r="Q19" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="8" t="inlineStr">
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T19" s="9" t="inlineStr">
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="12" t="inlineStr">
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2138,32 +2171,34 @@
       <c r="O20" t="n">
         <v>61.16</v>
       </c>
-      <c r="P20" s="6" t="inlineStr"/>
-      <c r="Q20" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="8" t="inlineStr">
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T20" s="9" t="inlineStr">
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="9" t="inlineStr">
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V20" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="12" t="inlineStr">
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2222,34 +2257,36 @@
       <c r="O21" t="n">
         <v>60.5</v>
       </c>
-      <c r="P21" s="6" t="inlineStr"/>
-      <c r="Q21" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="7" t="inlineStr">
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="8" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T21" s="9" t="inlineStr">
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="9" t="inlineStr">
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V21" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="12" t="inlineStr">
+      <c r="V21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2308,30 +2345,32 @@
       <c r="O22" t="n">
         <v>63.78</v>
       </c>
-      <c r="P22" s="6" t="inlineStr"/>
-      <c r="Q22" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="8" t="inlineStr">
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T22" s="9" t="inlineStr">
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="12" t="inlineStr">
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2390,30 +2429,32 @@
       <c r="O23" t="n">
         <v>66.27</v>
       </c>
-      <c r="P23" s="6" t="inlineStr"/>
-      <c r="Q23" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="8" t="inlineStr">
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T23" s="9" t="inlineStr">
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U23" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="12" t="inlineStr">
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2472,34 +2513,36 @@
       <c r="O24" t="n">
         <v>64.02</v>
       </c>
-      <c r="P24" s="6" t="inlineStr"/>
-      <c r="Q24" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="8" t="inlineStr">
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T24" s="9" t="inlineStr">
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="9" t="inlineStr">
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V24" s="9" t="inlineStr">
+      <c r="V24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W24" s="10" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2554,30 +2597,32 @@
       <c r="O25" t="n">
         <v>72.81999999999999</v>
       </c>
-      <c r="P25" s="6" t="inlineStr"/>
-      <c r="Q25" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="7" t="inlineStr">
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="11" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T25" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W25" s="10" t="inlineStr">
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2636,30 +2681,32 @@
       <c r="O26" t="n">
         <v>69.94</v>
       </c>
-      <c r="P26" s="6" t="inlineStr"/>
-      <c r="Q26" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="11" t="inlineStr">
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T26" s="9" t="inlineStr">
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="10" t="inlineStr">
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2718,32 +2765,34 @@
       <c r="O27" t="n">
         <v>69.52</v>
       </c>
-      <c r="P27" s="6" t="inlineStr"/>
-      <c r="Q27" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="8" t="inlineStr">
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T27" s="9" t="inlineStr">
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="9" t="inlineStr">
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V27" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="10" t="inlineStr">
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2802,30 +2851,32 @@
       <c r="O28" t="n">
         <v>72.23</v>
       </c>
-      <c r="P28" s="6" t="inlineStr"/>
-      <c r="Q28" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="7" t="inlineStr">
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="8" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T28" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="10" t="inlineStr">
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2880,34 +2931,36 @@
       <c r="O29" t="n">
         <v>72.06</v>
       </c>
-      <c r="P29" s="6" t="inlineStr"/>
-      <c r="Q29" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="8" t="inlineStr">
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T29" s="9" t="inlineStr">
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="9" t="inlineStr">
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V29" s="9" t="inlineStr">
+      <c r="V29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W29" s="10" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2962,36 +3015,38 @@
       <c r="O30" t="n">
         <v>116.02</v>
       </c>
-      <c r="P30" s="6" t="inlineStr"/>
-      <c r="Q30" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="7" t="inlineStr">
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="8" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T30" s="9" t="inlineStr">
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="9" t="inlineStr">
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V30" s="9" t="inlineStr">
+      <c r="V30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W30" s="10" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3046,28 +3101,30 @@
       <c r="O31" t="n">
         <v>162.23</v>
       </c>
-      <c r="P31" s="6" t="inlineStr"/>
-      <c r="Q31" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="11" t="inlineStr">
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T31" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="10" t="inlineStr">
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3126,32 +3183,34 @@
       <c r="O32" t="n">
         <v>112.92</v>
       </c>
-      <c r="P32" s="6" t="inlineStr"/>
-      <c r="Q32" s="7" t="inlineStr">
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R32" s="7" t="inlineStr">
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="8" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T32" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="10" t="inlineStr">
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3210,30 +3269,32 @@
       <c r="O33" t="n">
         <v>118.97</v>
       </c>
-      <c r="P33" s="6" t="inlineStr"/>
-      <c r="Q33" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="8" t="inlineStr">
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T33" s="9" t="inlineStr">
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="10" t="inlineStr">
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3288,32 +3349,34 @@
       <c r="O34" t="n">
         <v>131.44</v>
       </c>
-      <c r="P34" s="6" t="inlineStr"/>
-      <c r="Q34" s="7" t="inlineStr">
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="7" t="inlineStr">
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="11" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T34" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="12" t="inlineStr">
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3372,30 +3435,32 @@
       <c r="O35" t="n">
         <v>144.21</v>
       </c>
-      <c r="P35" s="6" t="inlineStr"/>
-      <c r="Q35" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="7" t="inlineStr">
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="11" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T35" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="12" t="inlineStr">
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3450,30 +3515,32 @@
       <c r="O36" t="n">
         <v>130.7</v>
       </c>
-      <c r="P36" s="6" t="inlineStr"/>
-      <c r="Q36" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="8" t="inlineStr">
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T36" s="9" t="inlineStr">
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U36" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W36" s="12" t="inlineStr">
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3532,34 +3599,36 @@
       <c r="O37" t="n">
         <v>109.76</v>
       </c>
-      <c r="P37" s="6" t="inlineStr"/>
-      <c r="Q37" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="8" t="inlineStr">
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T37" s="9" t="inlineStr">
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="9" t="inlineStr">
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V37" s="9" t="inlineStr">
+      <c r="V37" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W37" s="12" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3618,30 +3687,32 @@
       <c r="O38" t="n">
         <v>127.27</v>
       </c>
-      <c r="P38" s="6" t="inlineStr"/>
-      <c r="Q38" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="7" t="inlineStr">
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="11" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T38" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W38" s="12" t="inlineStr">
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3696,30 +3767,32 @@
       <c r="O39" t="n">
         <v>126.26</v>
       </c>
-      <c r="P39" s="6" t="inlineStr"/>
-      <c r="Q39" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="8" t="inlineStr">
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T39" s="9" t="inlineStr">
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U39" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W39" s="12" t="inlineStr">
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3778,32 +3851,34 @@
       <c r="O40" t="n">
         <v>115.87</v>
       </c>
-      <c r="P40" s="6" t="inlineStr"/>
-      <c r="Q40" s="7" t="inlineStr">
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="7" t="inlineStr">
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="11" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T40" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W40" s="12" t="inlineStr">
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3862,30 +3937,32 @@
       <c r="O41" t="n">
         <v>124.21</v>
       </c>
-      <c r="P41" s="6" t="inlineStr"/>
-      <c r="Q41" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="7" t="inlineStr">
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="11" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T41" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W41" s="12" t="inlineStr">
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3940,32 +4017,34 @@
       <c r="O42" t="n">
         <v>103.05</v>
       </c>
-      <c r="P42" s="6" t="inlineStr"/>
-      <c r="Q42" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="8" t="inlineStr">
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T42" s="9" t="inlineStr">
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U42" s="9" t="inlineStr">
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V42" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="12" t="inlineStr">
+      <c r="V42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4024,32 +4103,34 @@
       <c r="O43" t="n">
         <v>105.55</v>
       </c>
-      <c r="P43" s="6" t="inlineStr"/>
-      <c r="Q43" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="7" t="inlineStr">
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="11" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T43" s="9" t="inlineStr">
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U43" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W43" s="12" t="inlineStr">
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4104,30 +4185,32 @@
       <c r="O44" t="n">
         <v>107.74</v>
       </c>
-      <c r="P44" s="6" t="inlineStr"/>
-      <c r="Q44" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="7" t="inlineStr">
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="11" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T44" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="12" t="inlineStr">
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4182,32 +4265,34 @@
       <c r="O45" t="n">
         <v>91.26000000000001</v>
       </c>
-      <c r="P45" s="6" t="inlineStr"/>
-      <c r="Q45" s="7" t="inlineStr">
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="7" t="inlineStr">
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="11" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T45" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="12" t="inlineStr">
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4262,28 +4347,30 @@
       <c r="O46" t="n">
         <v>89.36</v>
       </c>
-      <c r="P46" s="6" t="inlineStr"/>
-      <c r="Q46" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="11" t="inlineStr">
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T46" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="12" t="inlineStr">
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4338,32 +4425,34 @@
       <c r="O47" t="n">
         <v>76.16</v>
       </c>
-      <c r="P47" s="6" t="inlineStr"/>
-      <c r="Q47" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="8" t="inlineStr">
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T47" s="9" t="inlineStr">
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U47" s="9" t="inlineStr">
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V47" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W47" s="12" t="inlineStr">
+      <c r="V47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4422,34 +4511,36 @@
       <c r="O48" t="n">
         <v>84.34</v>
       </c>
-      <c r="P48" s="6" t="inlineStr"/>
-      <c r="Q48" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="8" t="inlineStr">
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T48" s="9" t="inlineStr">
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U48" s="9" t="inlineStr">
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V48" s="9" t="inlineStr">
+      <c r="V48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W48" s="10" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4504,32 +4595,34 @@
       <c r="O49" t="n">
         <v>92.91</v>
       </c>
-      <c r="P49" s="6" t="inlineStr"/>
-      <c r="Q49" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="8" t="inlineStr">
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T49" s="9" t="inlineStr">
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U49" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="9" t="inlineStr">
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W49" s="10" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4584,30 +4677,32 @@
       <c r="O50" t="n">
         <v>106.73</v>
       </c>
-      <c r="P50" s="6" t="inlineStr"/>
-      <c r="Q50" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="7" t="inlineStr">
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="11" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T50" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="10" t="inlineStr">
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4666,32 +4761,34 @@
       <c r="O51" t="n">
         <v>95.95999999999999</v>
       </c>
-      <c r="P51" s="6" t="inlineStr"/>
-      <c r="Q51" s="7" t="inlineStr">
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="7" t="inlineStr">
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="11" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T51" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W51" s="10" t="inlineStr">
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4750,30 +4847,32 @@
       <c r="O52" t="n">
         <v>90.42</v>
       </c>
-      <c r="P52" s="6" t="inlineStr"/>
-      <c r="Q52" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="8" t="inlineStr">
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T52" s="9" t="inlineStr">
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U52" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W52" s="10" t="inlineStr">
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4828,30 +4927,32 @@
       <c r="O53" t="n">
         <v>91.43000000000001</v>
       </c>
-      <c r="P53" s="6" t="inlineStr"/>
-      <c r="Q53" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="8" t="inlineStr">
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T53" s="9" t="inlineStr">
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U53" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W53" s="10" t="inlineStr">
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4906,32 +5007,34 @@
       <c r="O54" t="n">
         <v>96.5</v>
       </c>
-      <c r="P54" s="6" t="inlineStr"/>
-      <c r="Q54" s="7" t="inlineStr">
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R54" s="7" t="inlineStr">
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="11" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T54" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="10" t="inlineStr">
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4990,32 +5093,34 @@
       <c r="O55" t="n">
         <v>93.52</v>
       </c>
-      <c r="P55" s="6" t="inlineStr"/>
-      <c r="Q55" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="8" t="inlineStr">
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T55" s="9" t="inlineStr">
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U55" s="9" t="inlineStr">
+      <c r="U55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V55" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="10" t="inlineStr">
+      <c r="V55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5070,34 +5175,36 @@
       <c r="O56" t="n">
         <v>102.17</v>
       </c>
-      <c r="P56" s="6" t="inlineStr"/>
-      <c r="Q56" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="8" t="inlineStr">
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T56" s="9" t="inlineStr">
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U56" s="9" t="inlineStr">
+      <c r="U56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V56" s="9" t="inlineStr">
+      <c r="V56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W56" s="10" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5117,19 +5224,19 @@
         <v>106.75</v>
       </c>
       <c r="D57" t="n">
-        <v>96.67</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>96.08</v>
+        <v>100.3</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.97</v>
+        <v>0.25</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0397</v>
+        <v>0.0025</v>
       </c>
       <c r="H57" t="n">
-        <v>10.08</v>
+        <v>7.65</v>
       </c>
       <c r="I57" t="n">
         <v>77.28</v>
@@ -5152,35 +5259,119 @@
       <c r="O57" t="n">
         <v>118.05</v>
       </c>
-      <c r="P57" s="6" t="inlineStr"/>
-      <c r="Q57" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="11" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="10" t="inlineStr">
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
+      <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="C58" t="n">
+        <v>92.04000000000001</v>
+      </c>
+      <c r="D58" t="n">
+        <v>91.79000000000001</v>
+      </c>
+      <c r="E58" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0847</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I58" t="n">
+        <v>91.45</v>
+      </c>
+      <c r="J58" t="n">
+        <v>91.34</v>
+      </c>
+      <c r="K58" t="n">
+        <v>96.48</v>
+      </c>
+      <c r="L58" t="n">
+        <v>101.61</v>
+      </c>
+      <c r="M58" t="n">
+        <v>104.13</v>
+      </c>
+      <c r="N58" t="n">
+        <v>106.64</v>
+      </c>
+      <c r="O58" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>2.15</v>
       </c>
       <c r="I2" t="n">
-        <v>60.43</v>
+        <v>60.57</v>
       </c>
       <c r="J2" t="n">
-        <v>62.21</v>
+        <v>62.26</v>
       </c>
       <c r="K2" t="n">
-        <v>62.78</v>
+        <v>62.82</v>
       </c>
       <c r="L2" t="n">
-        <v>63.36</v>
+        <v>63.38</v>
       </c>
       <c r="M2" t="n">
-        <v>64.53</v>
+        <v>64.5</v>
       </c>
       <c r="N2" t="n">
-        <v>65.70999999999999</v>
+        <v>65.62</v>
       </c>
       <c r="O2" t="n">
-        <v>65.68000000000001</v>
+        <v>65.61</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5296,25 +5296,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>91.95</v>
+        <v>101</v>
       </c>
       <c r="C58" t="n">
-        <v>92.04000000000001</v>
+        <v>101.08</v>
       </c>
       <c r="D58" t="n">
-        <v>91.79000000000001</v>
+        <v>89.16</v>
       </c>
       <c r="E58" t="n">
-        <v>91.8</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-8.5</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0847</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>0.25</v>
+        <v>11.92</v>
       </c>
       <c r="I58" t="n">
         <v>91.45</v>
@@ -5339,12 +5339,14 @@
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
@@ -5364,16 +5366,12 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5305,13 +5305,13 @@
         <v>89.16</v>
       </c>
       <c r="E58" t="n">
-        <v>90.51000000000001</v>
+        <v>91.27</v>
       </c>
       <c r="F58" t="n">
-        <v>-9.789999999999999</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="H58" t="n">
         <v>11.92</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5302,19 +5302,19 @@
         <v>101.08</v>
       </c>
       <c r="D58" t="n">
-        <v>89.16</v>
+        <v>89.84</v>
       </c>
       <c r="E58" t="n">
-        <v>91.27</v>
+        <v>89.88</v>
       </c>
       <c r="F58" t="n">
-        <v>-9.029999999999999</v>
+        <v>-10.42</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.09</v>
+        <v>-0.1039</v>
       </c>
       <c r="H58" t="n">
-        <v>11.92</v>
+        <v>11.24</v>
       </c>
       <c r="I58" t="n">
         <v>91.45</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>2.15</v>
       </c>
       <c r="I2" t="n">
-        <v>60.57</v>
+        <v>60.85</v>
       </c>
       <c r="J2" t="n">
-        <v>62.26</v>
+        <v>62.37</v>
       </c>
       <c r="K2" t="n">
-        <v>62.82</v>
+        <v>62.89</v>
       </c>
       <c r="L2" t="n">
-        <v>63.38</v>
+        <v>63.41</v>
       </c>
       <c r="M2" t="n">
-        <v>64.5</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>65.62</v>
+        <v>65.45</v>
       </c>
       <c r="O2" t="n">
-        <v>65.61</v>
+        <v>65.47</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5302,19 +5302,19 @@
         <v>101.08</v>
       </c>
       <c r="D58" t="n">
-        <v>89.84</v>
+        <v>89.47</v>
       </c>
       <c r="E58" t="n">
-        <v>89.88</v>
+        <v>90.2</v>
       </c>
       <c r="F58" t="n">
-        <v>-10.42</v>
+        <v>-10.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.1039</v>
+        <v>-0.1007</v>
       </c>
       <c r="H58" t="n">
-        <v>11.24</v>
+        <v>11.61</v>
       </c>
       <c r="I58" t="n">
         <v>91.45</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5305,13 +5305,13 @@
         <v>89.47</v>
       </c>
       <c r="E58" t="n">
-        <v>90.2</v>
+        <v>90.22</v>
       </c>
       <c r="F58" t="n">
-        <v>-10.1</v>
+        <v>-10.08</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.1007</v>
+        <v>-0.1005</v>
       </c>
       <c r="H58" t="n">
         <v>11.61</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5305,13 +5305,13 @@
         <v>89.47</v>
       </c>
       <c r="E58" t="n">
-        <v>90.22</v>
+        <v>89.92</v>
       </c>
       <c r="F58" t="n">
-        <v>-10.08</v>
+        <v>-10.38</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.1005</v>
+        <v>-0.1035</v>
       </c>
       <c r="H58" t="n">
         <v>11.61</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5305,13 +5305,13 @@
         <v>89.47</v>
       </c>
       <c r="E58" t="n">
-        <v>89.92</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>-10.38</v>
+        <v>-10.59</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.1035</v>
+        <v>-0.1056</v>
       </c>
       <c r="H58" t="n">
         <v>11.61</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5302,19 +5302,19 @@
         <v>101.08</v>
       </c>
       <c r="D58" t="n">
-        <v>89.47</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>89.70999999999999</v>
+        <v>91.08</v>
       </c>
       <c r="F58" t="n">
-        <v>-10.59</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.1056</v>
+        <v>-0.0919</v>
       </c>
       <c r="H58" t="n">
-        <v>11.61</v>
+        <v>12.37</v>
       </c>
       <c r="I58" t="n">
         <v>91.45</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5302,19 +5302,19 @@
         <v>101.08</v>
       </c>
       <c r="D58" t="n">
-        <v>88.70999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>91.08</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-9.220000000000001</v>
+        <v>-7.62</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0919</v>
+        <v>-0.076</v>
       </c>
       <c r="H58" t="n">
-        <v>12.37</v>
+        <v>8.68</v>
       </c>
       <c r="I58" t="n">
         <v>91.45</v>
@@ -5339,19 +5339,17 @@
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5366,12 +5364,16 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>2.15</v>
       </c>
       <c r="I2" t="n">
-        <v>60.85</v>
+        <v>61.11</v>
       </c>
       <c r="J2" t="n">
-        <v>62.37</v>
+        <v>62.47</v>
       </c>
       <c r="K2" t="n">
-        <v>62.89</v>
+        <v>62.95</v>
       </c>
       <c r="L2" t="n">
-        <v>63.41</v>
+        <v>63.44</v>
       </c>
       <c r="M2" t="n">
-        <v>64.43000000000001</v>
+        <v>64.36</v>
       </c>
       <c r="N2" t="n">
-        <v>65.45</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>65.47</v>
+        <v>65.34</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -5302,19 +5304,19 @@
         <v>101.08</v>
       </c>
       <c r="D58" t="n">
-        <v>92.40000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>92.68000000000001</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>-7.62</v>
+        <v>-5.73</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.076</v>
+        <v>-0.0571</v>
       </c>
       <c r="H58" t="n">
-        <v>8.68</v>
+        <v>12.37</v>
       </c>
       <c r="I58" t="n">
         <v>91.45</v>
@@ -5339,15 +5341,17 @@
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,56 +634,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63.88</v>
+        <v>63.95</v>
       </c>
       <c r="C2" t="n">
-        <v>65.09999999999999</v>
+        <v>66.03</v>
       </c>
       <c r="D2" t="n">
-        <v>62.95</v>
+        <v>61.45</v>
       </c>
       <c r="E2" t="n">
-        <v>64.01000000000001</v>
+        <v>61.87</v>
       </c>
       <c r="F2" t="n">
-        <v>0.35</v>
+        <v>-2.14</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0055</v>
+        <v>-0.0334</v>
       </c>
       <c r="H2" t="n">
-        <v>2.15</v>
+        <v>4.58</v>
       </c>
       <c r="I2" t="n">
-        <v>61.11</v>
+        <v>60.8</v>
       </c>
       <c r="J2" t="n">
-        <v>62.47</v>
+        <v>61.85</v>
       </c>
       <c r="K2" t="n">
-        <v>62.95</v>
+        <v>62.94</v>
       </c>
       <c r="L2" t="n">
-        <v>63.44</v>
+        <v>64.02</v>
       </c>
       <c r="M2" t="n">
-        <v>64.36</v>
+        <v>65.09</v>
       </c>
       <c r="N2" t="n">
-        <v>65.29000000000001</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>65.34</v>
+        <v>67.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -692,12 +694,12 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U2" s="8" t="n">
@@ -711,78 +713,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63.95</v>
+        <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>66.03</v>
+        <v>64.08</v>
       </c>
       <c r="D3" t="n">
-        <v>61.45</v>
+        <v>61.69</v>
       </c>
       <c r="E3" t="n">
-        <v>61.87</v>
+        <v>62.69</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.14</v>
+        <v>0.82</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0334</v>
+        <v>0.0133</v>
       </c>
       <c r="H3" t="n">
-        <v>4.58</v>
+        <v>2.39</v>
       </c>
       <c r="I3" t="n">
-        <v>60.8</v>
+        <v>56.87</v>
       </c>
       <c r="J3" t="n">
-        <v>61.85</v>
+        <v>56.36</v>
       </c>
       <c r="K3" t="n">
-        <v>62.94</v>
+        <v>59.58</v>
       </c>
       <c r="L3" t="n">
-        <v>64.02</v>
+        <v>62.8</v>
       </c>
       <c r="M3" t="n">
-        <v>65.09</v>
+        <v>64.16</v>
       </c>
       <c r="N3" t="n">
-        <v>66.15000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>67.25</v>
+        <v>70.61</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -797,57 +797,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62</v>
+        <v>62.97</v>
       </c>
       <c r="C4" t="n">
-        <v>64.08</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>61.69</v>
+        <v>62.52</v>
       </c>
       <c r="E4" t="n">
-        <v>62.69</v>
+        <v>62.68</v>
       </c>
       <c r="F4" t="n">
-        <v>0.82</v>
+        <v>-0.01</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0002</v>
       </c>
       <c r="H4" t="n">
-        <v>2.39</v>
+        <v>2.24</v>
       </c>
       <c r="I4" t="n">
-        <v>56.87</v>
+        <v>59.3</v>
       </c>
       <c r="J4" t="n">
-        <v>56.36</v>
+        <v>60.2</v>
       </c>
       <c r="K4" t="n">
-        <v>59.58</v>
+        <v>61.49</v>
       </c>
       <c r="L4" t="n">
-        <v>62.8</v>
+        <v>62.79</v>
       </c>
       <c r="M4" t="n">
-        <v>64.16</v>
+        <v>63.89</v>
       </c>
       <c r="N4" t="n">
-        <v>65.51000000000001</v>
+        <v>64.98</v>
       </c>
       <c r="O4" t="n">
-        <v>70.61</v>
+        <v>66.47</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,13 +858,15 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -886,50 +888,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.97</v>
+        <v>62.74</v>
       </c>
       <c r="C5" t="n">
-        <v>64.76000000000001</v>
+        <v>66.42</v>
       </c>
       <c r="D5" t="n">
-        <v>62.52</v>
+        <v>61.85</v>
       </c>
       <c r="E5" t="n">
-        <v>62.68</v>
+        <v>65.72</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01</v>
+        <v>3.04</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0485</v>
       </c>
       <c r="H5" t="n">
-        <v>2.24</v>
+        <v>4.57</v>
       </c>
       <c r="I5" t="n">
-        <v>59.3</v>
+        <v>60.28</v>
       </c>
       <c r="J5" t="n">
-        <v>60.2</v>
+        <v>59.96</v>
       </c>
       <c r="K5" t="n">
-        <v>61.49</v>
+        <v>61.56</v>
       </c>
       <c r="L5" t="n">
-        <v>62.79</v>
+        <v>63.16</v>
       </c>
       <c r="M5" t="n">
-        <v>63.89</v>
+        <v>63.8</v>
       </c>
       <c r="N5" t="n">
-        <v>64.98</v>
+        <v>64.44</v>
       </c>
       <c r="O5" t="n">
-        <v>66.47</v>
+        <v>67</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -942,7 +944,7 @@
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -950,8 +952,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="n">
-        <v/>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -970,151 +974,145 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62.74</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>66.42</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>61.85</v>
+        <v>60.4</v>
       </c>
       <c r="E6" t="n">
-        <v>65.72</v>
+        <v>60.88</v>
       </c>
       <c r="F6" t="n">
-        <v>3.04</v>
+        <v>-4.84</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0485</v>
+        <v>-0.0736</v>
       </c>
       <c r="H6" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>60.28</v>
+        <v>57.28</v>
       </c>
       <c r="J6" t="n">
-        <v>59.96</v>
+        <v>61.94</v>
       </c>
       <c r="K6" t="n">
-        <v>61.56</v>
+        <v>63.44</v>
       </c>
       <c r="L6" t="n">
-        <v>63.16</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>63.8</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>64.44</v>
+        <v>71.08</v>
       </c>
       <c r="O6" t="n">
-        <v>67</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>65.06999999999999</v>
+        <v>61.14</v>
       </c>
       <c r="C7" t="n">
-        <v>65.40000000000001</v>
+        <v>62.92</v>
       </c>
       <c r="D7" t="n">
-        <v>60.4</v>
+        <v>58.22</v>
       </c>
       <c r="E7" t="n">
-        <v>60.88</v>
+        <v>58.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.84</v>
+        <v>-1.98</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0736</v>
+        <v>-0.0325</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I7" t="n">
-        <v>57.28</v>
+        <v>55.4</v>
       </c>
       <c r="J7" t="n">
-        <v>61.94</v>
+        <v>54.87</v>
       </c>
       <c r="K7" t="n">
-        <v>63.44</v>
+        <v>58.38</v>
       </c>
       <c r="L7" t="n">
-        <v>64.93000000000001</v>
+        <v>61.89</v>
       </c>
       <c r="M7" t="n">
-        <v>68.01000000000001</v>
+        <v>63.38</v>
       </c>
       <c r="N7" t="n">
-        <v>71.08</v>
+        <v>64.87</v>
       </c>
       <c r="O7" t="n">
-        <v>70.98999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1138,50 +1136,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61.14</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>62.92</v>
+        <v>60.17</v>
       </c>
       <c r="D8" t="n">
-        <v>58.22</v>
+        <v>56.6</v>
       </c>
       <c r="E8" t="n">
-        <v>58.9</v>
+        <v>57.54</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.98</v>
+        <v>-1.36</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0325</v>
+        <v>-0.0231</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>3.57</v>
       </c>
       <c r="I8" t="n">
-        <v>55.4</v>
+        <v>53.52</v>
       </c>
       <c r="J8" t="n">
-        <v>54.87</v>
+        <v>53.37</v>
       </c>
       <c r="K8" t="n">
-        <v>58.38</v>
+        <v>56.55</v>
       </c>
       <c r="L8" t="n">
-        <v>61.89</v>
+        <v>59.74</v>
       </c>
       <c r="M8" t="n">
-        <v>63.38</v>
+        <v>61.25</v>
       </c>
       <c r="N8" t="n">
-        <v>64.87</v>
+        <v>62.76</v>
       </c>
       <c r="O8" t="n">
-        <v>70.40000000000001</v>
+        <v>67.62</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1194,7 +1192,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1218,50 +1216,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>57.73</v>
       </c>
       <c r="C9" t="n">
-        <v>60.17</v>
+        <v>62.59</v>
       </c>
       <c r="D9" t="n">
-        <v>56.6</v>
+        <v>56.35</v>
       </c>
       <c r="E9" t="n">
-        <v>57.54</v>
+        <v>61.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.36</v>
+        <v>3.96</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0231</v>
+        <v>0.0688</v>
       </c>
       <c r="H9" t="n">
-        <v>3.57</v>
+        <v>6.24</v>
       </c>
       <c r="I9" t="n">
-        <v>53.52</v>
+        <v>53.03</v>
       </c>
       <c r="J9" t="n">
-        <v>53.37</v>
+        <v>53.55</v>
       </c>
       <c r="K9" t="n">
-        <v>56.55</v>
+        <v>55.76</v>
       </c>
       <c r="L9" t="n">
-        <v>59.74</v>
+        <v>57.96</v>
       </c>
       <c r="M9" t="n">
-        <v>61.25</v>
+        <v>59.33</v>
       </c>
       <c r="N9" t="n">
-        <v>62.76</v>
+        <v>60.69</v>
       </c>
       <c r="O9" t="n">
-        <v>67.62</v>
+        <v>63.74</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1269,79 +1267,85 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="W9" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57.73</v>
+        <v>61.82</v>
       </c>
       <c r="C10" t="n">
-        <v>62.59</v>
+        <v>62.17</v>
       </c>
       <c r="D10" t="n">
-        <v>56.35</v>
+        <v>59.64</v>
       </c>
       <c r="E10" t="n">
-        <v>61.5</v>
+        <v>60.98</v>
       </c>
       <c r="F10" t="n">
-        <v>3.96</v>
+        <v>-0.52</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0688</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>6.24</v>
+        <v>2.53</v>
       </c>
       <c r="I10" t="n">
-        <v>53.03</v>
+        <v>50.11</v>
       </c>
       <c r="J10" t="n">
-        <v>53.55</v>
+        <v>56.27</v>
       </c>
       <c r="K10" t="n">
-        <v>55.76</v>
+        <v>58.38</v>
       </c>
       <c r="L10" t="n">
-        <v>57.96</v>
+        <v>60.48</v>
       </c>
       <c r="M10" t="n">
-        <v>59.33</v>
+        <v>64.62</v>
       </c>
       <c r="N10" t="n">
-        <v>60.69</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>63.74</v>
+        <v>68.83</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1352,20 +1356,16 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1377,57 +1377,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>61.82</v>
+        <v>61.4</v>
       </c>
       <c r="C11" t="n">
-        <v>62.17</v>
+        <v>61.5</v>
       </c>
       <c r="D11" t="n">
-        <v>59.64</v>
+        <v>58.83</v>
       </c>
       <c r="E11" t="n">
-        <v>60.98</v>
+        <v>59.75</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.52</v>
+        <v>-1.23</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0202</v>
       </c>
       <c r="H11" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="I11" t="n">
-        <v>50.11</v>
+        <v>57.11</v>
       </c>
       <c r="J11" t="n">
-        <v>56.27</v>
+        <v>58.49</v>
       </c>
       <c r="K11" t="n">
-        <v>58.38</v>
+        <v>59.72</v>
       </c>
       <c r="L11" t="n">
-        <v>60.48</v>
+        <v>60.94</v>
       </c>
       <c r="M11" t="n">
-        <v>64.62</v>
+        <v>62.24</v>
       </c>
       <c r="N11" t="n">
-        <v>68.76000000000001</v>
+        <v>63.55</v>
       </c>
       <c r="O11" t="n">
-        <v>68.83</v>
+        <v>64.7</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1435,12 +1435,14 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1459,57 +1461,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61.4</v>
+        <v>59.87</v>
       </c>
       <c r="C12" t="n">
-        <v>61.5</v>
+        <v>61.28</v>
       </c>
       <c r="D12" t="n">
-        <v>58.83</v>
+        <v>58.12</v>
       </c>
       <c r="E12" t="n">
-        <v>59.75</v>
+        <v>60.09</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.23</v>
+        <v>0.34</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0202</v>
+        <v>0.0057</v>
       </c>
       <c r="H12" t="n">
-        <v>2.67</v>
+        <v>3.16</v>
       </c>
       <c r="I12" t="n">
-        <v>57.11</v>
+        <v>56.16</v>
       </c>
       <c r="J12" t="n">
-        <v>58.49</v>
+        <v>56.87</v>
       </c>
       <c r="K12" t="n">
-        <v>59.72</v>
+        <v>58.42</v>
       </c>
       <c r="L12" t="n">
-        <v>60.94</v>
+        <v>59.96</v>
       </c>
       <c r="M12" t="n">
-        <v>62.24</v>
+        <v>61.08</v>
       </c>
       <c r="N12" t="n">
-        <v>63.55</v>
+        <v>62.21</v>
       </c>
       <c r="O12" t="n">
-        <v>64.7</v>
+        <v>64.17</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1519,16 +1521,18 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1543,57 +1547,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59.87</v>
+        <v>59.8</v>
       </c>
       <c r="C13" t="n">
-        <v>61.28</v>
+        <v>60.93</v>
       </c>
       <c r="D13" t="n">
-        <v>58.12</v>
+        <v>57.38</v>
       </c>
       <c r="E13" t="n">
-        <v>60.09</v>
+        <v>58.06</v>
       </c>
       <c r="F13" t="n">
-        <v>0.34</v>
+        <v>-2.03</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.0338</v>
       </c>
       <c r="H13" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>56.16</v>
+        <v>54.96</v>
       </c>
       <c r="J13" t="n">
-        <v>56.87</v>
+        <v>57.13</v>
       </c>
       <c r="K13" t="n">
-        <v>58.42</v>
+        <v>58.51</v>
       </c>
       <c r="L13" t="n">
-        <v>59.96</v>
+        <v>59.89</v>
       </c>
       <c r="M13" t="n">
-        <v>61.08</v>
+        <v>61.67</v>
       </c>
       <c r="N13" t="n">
-        <v>62.21</v>
+        <v>63.45</v>
       </c>
       <c r="O13" t="n">
-        <v>64.17</v>
+        <v>64.44</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1603,18 +1607,16 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1629,57 +1631,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>59.8</v>
+        <v>58.05</v>
       </c>
       <c r="C14" t="n">
-        <v>60.93</v>
+        <v>59.64</v>
       </c>
       <c r="D14" t="n">
-        <v>57.38</v>
+        <v>57.1</v>
       </c>
       <c r="E14" t="n">
-        <v>58.06</v>
+        <v>58.55</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.03</v>
+        <v>0.49</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>3.55</v>
+        <v>2.54</v>
       </c>
       <c r="I14" t="n">
-        <v>54.96</v>
+        <v>53.83</v>
       </c>
       <c r="J14" t="n">
-        <v>57.13</v>
+        <v>53.96</v>
       </c>
       <c r="K14" t="n">
-        <v>58.51</v>
+        <v>56.29</v>
       </c>
       <c r="L14" t="n">
-        <v>59.89</v>
+        <v>58.61</v>
       </c>
       <c r="M14" t="n">
-        <v>61.67</v>
+        <v>59.84</v>
       </c>
       <c r="N14" t="n">
-        <v>63.45</v>
+        <v>61.06</v>
       </c>
       <c r="O14" t="n">
-        <v>64.44</v>
+        <v>64.48</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1687,14 +1689,12 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1713,57 +1713,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58.05</v>
+        <v>58.96</v>
       </c>
       <c r="C15" t="n">
-        <v>59.64</v>
+        <v>60.5</v>
       </c>
       <c r="D15" t="n">
-        <v>57.1</v>
+        <v>58.28</v>
       </c>
       <c r="E15" t="n">
-        <v>58.55</v>
+        <v>60.08</v>
       </c>
       <c r="F15" t="n">
-        <v>0.49</v>
+        <v>1.53</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0261</v>
       </c>
       <c r="H15" t="n">
-        <v>2.54</v>
+        <v>2.22</v>
       </c>
       <c r="I15" t="n">
-        <v>53.83</v>
+        <v>54.56</v>
       </c>
       <c r="J15" t="n">
-        <v>53.96</v>
+        <v>56.1</v>
       </c>
       <c r="K15" t="n">
-        <v>56.29</v>
+        <v>57.28</v>
       </c>
       <c r="L15" t="n">
-        <v>58.61</v>
+        <v>58.46</v>
       </c>
       <c r="M15" t="n">
-        <v>59.84</v>
+        <v>59.82</v>
       </c>
       <c r="N15" t="n">
-        <v>61.06</v>
+        <v>61.18</v>
       </c>
       <c r="O15" t="n">
-        <v>64.48</v>
+        <v>62.18</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1776,11 +1776,13 @@
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1793,78 +1795,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>58.96</v>
+        <v>60.15</v>
       </c>
       <c r="C16" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="D16" t="n">
-        <v>58.28</v>
+        <v>57.01</v>
       </c>
       <c r="E16" t="n">
-        <v>60.08</v>
+        <v>57.44</v>
       </c>
       <c r="F16" t="n">
-        <v>1.53</v>
+        <v>-2.64</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0261</v>
+        <v>-0.0439</v>
       </c>
       <c r="H16" t="n">
-        <v>2.22</v>
+        <v>3.29</v>
       </c>
       <c r="I16" t="n">
-        <v>54.56</v>
+        <v>56.06</v>
       </c>
       <c r="J16" t="n">
-        <v>56.1</v>
+        <v>58.21</v>
       </c>
       <c r="K16" t="n">
-        <v>57.28</v>
+        <v>58.97</v>
       </c>
       <c r="L16" t="n">
-        <v>58.46</v>
+        <v>59.74</v>
       </c>
       <c r="M16" t="n">
-        <v>59.82</v>
+        <v>61.19</v>
       </c>
       <c r="N16" t="n">
-        <v>61.18</v>
+        <v>62.65</v>
       </c>
       <c r="O16" t="n">
-        <v>62.18</v>
+        <v>62.72</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1872,9 +1872,9 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1882,65 +1882,63 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>60.15</v>
+        <v>57.5</v>
       </c>
       <c r="C17" t="n">
-        <v>60.3</v>
+        <v>57.8</v>
       </c>
       <c r="D17" t="n">
-        <v>57.01</v>
+        <v>54.98</v>
       </c>
       <c r="E17" t="n">
-        <v>57.44</v>
+        <v>56.66</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.64</v>
+        <v>-0.78</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0439</v>
+        <v>-0.0136</v>
       </c>
       <c r="H17" t="n">
-        <v>3.29</v>
+        <v>2.82</v>
       </c>
       <c r="I17" t="n">
-        <v>56.06</v>
+        <v>53.72</v>
       </c>
       <c r="J17" t="n">
-        <v>58.21</v>
+        <v>53.54</v>
       </c>
       <c r="K17" t="n">
-        <v>58.97</v>
+        <v>55.79</v>
       </c>
       <c r="L17" t="n">
-        <v>59.74</v>
+        <v>58.05</v>
       </c>
       <c r="M17" t="n">
-        <v>61.19</v>
+        <v>59.08</v>
       </c>
       <c r="N17" t="n">
-        <v>62.65</v>
+        <v>60.12</v>
       </c>
       <c r="O17" t="n">
-        <v>62.72</v>
+        <v>63.59</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1964,50 +1962,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57.5</v>
+        <v>56.63</v>
       </c>
       <c r="C18" t="n">
-        <v>57.8</v>
+        <v>58.88</v>
       </c>
       <c r="D18" t="n">
-        <v>54.98</v>
+        <v>56.6</v>
       </c>
       <c r="E18" t="n">
-        <v>56.66</v>
+        <v>56.74</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.78</v>
+        <v>0.08</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0136</v>
+        <v>0.0014</v>
       </c>
       <c r="H18" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="I18" t="n">
-        <v>53.72</v>
+        <v>52.16</v>
       </c>
       <c r="J18" t="n">
-        <v>53.54</v>
+        <v>53.98</v>
       </c>
       <c r="K18" t="n">
-        <v>55.79</v>
+        <v>55.25</v>
       </c>
       <c r="L18" t="n">
-        <v>58.05</v>
+        <v>56.52</v>
       </c>
       <c r="M18" t="n">
-        <v>59.08</v>
+        <v>58.07</v>
       </c>
       <c r="N18" t="n">
-        <v>60.12</v>
+        <v>59.61</v>
       </c>
       <c r="O18" t="n">
-        <v>63.59</v>
+        <v>60.62</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2015,18 +2013,18 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2039,55 +2037,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>56.63</v>
+        <v>57.04</v>
       </c>
       <c r="C19" t="n">
-        <v>58.88</v>
+        <v>58.55</v>
       </c>
       <c r="D19" t="n">
         <v>56.6</v>
       </c>
       <c r="E19" t="n">
-        <v>56.74</v>
+        <v>57.32</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08</v>
+        <v>0.58</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0102</v>
       </c>
       <c r="H19" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="I19" t="n">
-        <v>52.16</v>
+        <v>54.32</v>
       </c>
       <c r="J19" t="n">
-        <v>53.98</v>
+        <v>53.96</v>
       </c>
       <c r="K19" t="n">
-        <v>55.25</v>
+        <v>55.6</v>
       </c>
       <c r="L19" t="n">
-        <v>56.52</v>
+        <v>57.24</v>
       </c>
       <c r="M19" t="n">
-        <v>58.07</v>
+        <v>57.88</v>
       </c>
       <c r="N19" t="n">
-        <v>59.61</v>
+        <v>58.52</v>
       </c>
       <c r="O19" t="n">
-        <v>60.62</v>
+        <v>61.16</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2098,7 +2100,7 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2108,8 +2110,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2121,57 +2125,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>57.04</v>
+        <v>57.47</v>
       </c>
       <c r="C20" t="n">
-        <v>58.55</v>
+        <v>59.77</v>
       </c>
       <c r="D20" t="n">
-        <v>56.6</v>
+        <v>55.76</v>
       </c>
       <c r="E20" t="n">
-        <v>57.32</v>
+        <v>59.12</v>
       </c>
       <c r="F20" t="n">
-        <v>0.58</v>
+        <v>1.8</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0314</v>
       </c>
       <c r="H20" t="n">
-        <v>1.95</v>
+        <v>4.01</v>
       </c>
       <c r="I20" t="n">
-        <v>54.32</v>
+        <v>54.65</v>
       </c>
       <c r="J20" t="n">
-        <v>53.96</v>
+        <v>55.24</v>
       </c>
       <c r="K20" t="n">
-        <v>55.6</v>
+        <v>56.34</v>
       </c>
       <c r="L20" t="n">
-        <v>57.24</v>
+        <v>57.45</v>
       </c>
       <c r="M20" t="n">
-        <v>57.88</v>
+        <v>58.3</v>
       </c>
       <c r="N20" t="n">
-        <v>58.52</v>
+        <v>59.14</v>
       </c>
       <c r="O20" t="n">
-        <v>61.16</v>
+        <v>60.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2179,12 +2183,14 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2194,7 +2200,7 @@
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V20" s="8" t="n">
@@ -2207,57 +2213,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>57.47</v>
+        <v>59</v>
       </c>
       <c r="C21" t="n">
-        <v>59.77</v>
+        <v>62.36</v>
       </c>
       <c r="D21" t="n">
-        <v>55.76</v>
+        <v>58.45</v>
       </c>
       <c r="E21" t="n">
-        <v>59.12</v>
+        <v>59.44</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8</v>
+        <v>0.32</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0314</v>
+        <v>0.0054</v>
       </c>
       <c r="H21" t="n">
-        <v>4.01</v>
+        <v>3.91</v>
       </c>
       <c r="I21" t="n">
-        <v>54.65</v>
+        <v>51.75</v>
       </c>
       <c r="J21" t="n">
-        <v>55.24</v>
+        <v>55.79</v>
       </c>
       <c r="K21" t="n">
-        <v>56.34</v>
+        <v>57.11</v>
       </c>
       <c r="L21" t="n">
-        <v>57.45</v>
+        <v>58.44</v>
       </c>
       <c r="M21" t="n">
-        <v>58.3</v>
+        <v>61.12</v>
       </c>
       <c r="N21" t="n">
-        <v>59.14</v>
+        <v>63.81</v>
       </c>
       <c r="O21" t="n">
-        <v>60.5</v>
+        <v>63.78</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2265,25 +2271,21 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2295,57 +2297,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>59</v>
+        <v>59.01</v>
       </c>
       <c r="C22" t="n">
-        <v>62.36</v>
+        <v>61.36</v>
       </c>
       <c r="D22" t="n">
-        <v>58.45</v>
+        <v>58.7</v>
       </c>
       <c r="E22" t="n">
-        <v>59.44</v>
+        <v>61.07</v>
       </c>
       <c r="F22" t="n">
-        <v>0.32</v>
+        <v>1.63</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0274</v>
       </c>
       <c r="H22" t="n">
-        <v>3.91</v>
+        <v>2.66</v>
       </c>
       <c r="I22" t="n">
-        <v>51.75</v>
+        <v>54.54</v>
       </c>
       <c r="J22" t="n">
-        <v>55.79</v>
+        <v>55.05</v>
       </c>
       <c r="K22" t="n">
-        <v>57.11</v>
+        <v>57.48</v>
       </c>
       <c r="L22" t="n">
-        <v>58.44</v>
+        <v>59.92</v>
       </c>
       <c r="M22" t="n">
-        <v>61.12</v>
+        <v>61.39</v>
       </c>
       <c r="N22" t="n">
-        <v>63.81</v>
+        <v>62.87</v>
       </c>
       <c r="O22" t="n">
-        <v>63.78</v>
+        <v>66.27</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2356,14 +2358,14 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U22" s="8" t="n">
@@ -2379,57 +2381,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>59.01</v>
+        <v>61.22</v>
       </c>
       <c r="C23" t="n">
-        <v>61.36</v>
+        <v>66.48</v>
       </c>
       <c r="D23" t="n">
-        <v>58.7</v>
+        <v>60.14</v>
       </c>
       <c r="E23" t="n">
-        <v>61.07</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>1.63</v>
+        <v>4.14</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0678</v>
       </c>
       <c r="H23" t="n">
-        <v>2.66</v>
+        <v>6.34</v>
       </c>
       <c r="I23" t="n">
-        <v>54.54</v>
+        <v>56.04</v>
       </c>
       <c r="J23" t="n">
-        <v>55.05</v>
+        <v>58.93</v>
       </c>
       <c r="K23" t="n">
-        <v>57.48</v>
+        <v>59.74</v>
       </c>
       <c r="L23" t="n">
-        <v>59.92</v>
+        <v>60.55</v>
       </c>
       <c r="M23" t="n">
-        <v>61.39</v>
+        <v>62.4</v>
       </c>
       <c r="N23" t="n">
-        <v>62.87</v>
+        <v>64.25</v>
       </c>
       <c r="O23" t="n">
-        <v>66.27</v>
+        <v>64.02</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2440,80 +2442,80 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>61.22</v>
+        <v>64.72</v>
       </c>
       <c r="C24" t="n">
-        <v>66.48</v>
+        <v>65.53</v>
       </c>
       <c r="D24" t="n">
-        <v>60.14</v>
+        <v>61.12</v>
       </c>
       <c r="E24" t="n">
-        <v>65.20999999999999</v>
+        <v>63.55</v>
       </c>
       <c r="F24" t="n">
-        <v>4.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0678</v>
+        <v>-0.0255</v>
       </c>
       <c r="H24" t="n">
-        <v>6.34</v>
+        <v>4.41</v>
       </c>
       <c r="I24" t="n">
-        <v>56.04</v>
+        <v>53.8</v>
       </c>
       <c r="J24" t="n">
-        <v>58.93</v>
+        <v>59.82</v>
       </c>
       <c r="K24" t="n">
-        <v>59.74</v>
+        <v>62.04</v>
       </c>
       <c r="L24" t="n">
-        <v>60.55</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>62.4</v>
+        <v>68.38</v>
       </c>
       <c r="N24" t="n">
-        <v>64.25</v>
+        <v>72.5</v>
       </c>
       <c r="O24" t="n">
-        <v>64.02</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2521,83 +2523,83 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>64.72</v>
+        <v>62.99</v>
       </c>
       <c r="C25" t="n">
-        <v>65.53</v>
+        <v>65.83</v>
       </c>
       <c r="D25" t="n">
-        <v>61.12</v>
+        <v>62.14</v>
       </c>
       <c r="E25" t="n">
-        <v>63.55</v>
+        <v>62.89</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.66</v>
+        <v>-0.66</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0255</v>
+        <v>-0.0104</v>
       </c>
       <c r="H25" t="n">
-        <v>4.41</v>
+        <v>3.69</v>
       </c>
       <c r="I25" t="n">
-        <v>53.8</v>
+        <v>56.71</v>
       </c>
       <c r="J25" t="n">
-        <v>59.82</v>
+        <v>59.25</v>
       </c>
       <c r="K25" t="n">
-        <v>62.04</v>
+        <v>61.34</v>
       </c>
       <c r="L25" t="n">
-        <v>64.26000000000001</v>
+        <v>63.44</v>
       </c>
       <c r="M25" t="n">
-        <v>68.38</v>
+        <v>65.75</v>
       </c>
       <c r="N25" t="n">
-        <v>72.5</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>72.81999999999999</v>
+        <v>69.94</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2605,19 +2607,19 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2631,57 +2633,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>62.99</v>
+        <v>63.3</v>
       </c>
       <c r="C26" t="n">
-        <v>65.83</v>
+        <v>67.05</v>
       </c>
       <c r="D26" t="n">
-        <v>62.14</v>
+        <v>61.87</v>
       </c>
       <c r="E26" t="n">
-        <v>62.89</v>
+        <v>66.39</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.66</v>
+        <v>3.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0557</v>
       </c>
       <c r="H26" t="n">
-        <v>3.69</v>
+        <v>5.18</v>
       </c>
       <c r="I26" t="n">
-        <v>56.71</v>
+        <v>58.45</v>
       </c>
       <c r="J26" t="n">
-        <v>59.25</v>
+        <v>58.65</v>
       </c>
       <c r="K26" t="n">
-        <v>61.34</v>
+        <v>61.04</v>
       </c>
       <c r="L26" t="n">
         <v>63.44</v>
       </c>
       <c r="M26" t="n">
-        <v>65.75</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>68.06999999999999</v>
+        <v>66.03</v>
       </c>
       <c r="O26" t="n">
-        <v>69.94</v>
+        <v>69.52</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2694,7 +2696,7 @@
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
@@ -2702,8 +2704,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2722,50 +2726,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>63.3</v>
+        <v>65.89</v>
       </c>
       <c r="C27" t="n">
-        <v>67.05</v>
+        <v>67.83</v>
       </c>
       <c r="D27" t="n">
-        <v>61.87</v>
+        <v>63.6</v>
       </c>
       <c r="E27" t="n">
-        <v>66.39</v>
+        <v>67.02</v>
       </c>
       <c r="F27" t="n">
-        <v>3.5</v>
+        <v>0.63</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0557</v>
+        <v>0.0095</v>
       </c>
       <c r="H27" t="n">
-        <v>5.18</v>
+        <v>4.23</v>
       </c>
       <c r="I27" t="n">
-        <v>58.45</v>
+        <v>56.69</v>
       </c>
       <c r="J27" t="n">
-        <v>58.65</v>
+        <v>62.17</v>
       </c>
       <c r="K27" t="n">
-        <v>61.04</v>
+        <v>63.8</v>
       </c>
       <c r="L27" t="n">
-        <v>63.44</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>64.73999999999999</v>
+        <v>68.98</v>
       </c>
       <c r="N27" t="n">
-        <v>66.03</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>69.52</v>
+        <v>72.23</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2773,23 +2777,21 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2799,59 +2801,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>65.89</v>
+        <v>75</v>
       </c>
       <c r="C28" t="n">
-        <v>67.83</v>
+        <v>92.61</v>
       </c>
       <c r="D28" t="n">
-        <v>63.6</v>
+        <v>69.2</v>
       </c>
       <c r="E28" t="n">
-        <v>67.02</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>0.63</v>
+        <v>23.88</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.3563</v>
       </c>
       <c r="H28" t="n">
-        <v>4.23</v>
+        <v>23.41</v>
       </c>
       <c r="I28" t="n">
-        <v>56.69</v>
+        <v>59.37</v>
       </c>
       <c r="J28" t="n">
-        <v>62.17</v>
+        <v>63.44</v>
       </c>
       <c r="K28" t="n">
-        <v>63.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>65.43000000000001</v>
+        <v>66.37</v>
       </c>
       <c r="M28" t="n">
-        <v>68.98</v>
+        <v>69.13</v>
       </c>
       <c r="N28" t="n">
-        <v>72.54000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>72.23</v>
+        <v>72.06</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2859,24 +2857,28 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
@@ -2888,50 +2890,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C29" t="n">
-        <v>92.61</v>
+        <v>119.48</v>
       </c>
       <c r="D29" t="n">
-        <v>69.2</v>
+        <v>76.73</v>
       </c>
       <c r="E29" t="n">
-        <v>90.90000000000001</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>23.88</v>
+        <v>7.81</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.3563</v>
+        <v>0.0859</v>
       </c>
       <c r="H29" t="n">
-        <v>23.41</v>
+        <v>42.75</v>
       </c>
       <c r="I29" t="n">
-        <v>59.37</v>
+        <v>45.79</v>
       </c>
       <c r="J29" t="n">
-        <v>63.44</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>64.90000000000001</v>
+        <v>79.19</v>
       </c>
       <c r="L29" t="n">
-        <v>66.37</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>69.13</v>
+        <v>102.61</v>
       </c>
       <c r="N29" t="n">
-        <v>71.90000000000001</v>
+        <v>119.31</v>
       </c>
       <c r="O29" t="n">
-        <v>72.06</v>
+        <v>116.02</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2939,27 +2941,29 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
+      <c r="V29" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W29" s="9" t="inlineStr">
@@ -2972,50 +2976,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>98</v>
+        <v>100.93</v>
       </c>
       <c r="C30" t="n">
-        <v>119.48</v>
+        <v>102.44</v>
       </c>
       <c r="D30" t="n">
-        <v>76.73</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>98.70999999999999</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>7.81</v>
+        <v>-0.39</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0859</v>
+        <v>-0.004</v>
       </c>
       <c r="H30" t="n">
-        <v>42.75</v>
+        <v>10.48</v>
       </c>
       <c r="I30" t="n">
-        <v>45.79</v>
+        <v>33.98</v>
       </c>
       <c r="J30" t="n">
-        <v>72.48999999999999</v>
+        <v>56.26</v>
       </c>
       <c r="K30" t="n">
-        <v>79.19</v>
+        <v>77.33</v>
       </c>
       <c r="L30" t="n">
-        <v>85.90000000000001</v>
+        <v>98.41</v>
       </c>
       <c r="M30" t="n">
-        <v>102.61</v>
+        <v>120.08</v>
       </c>
       <c r="N30" t="n">
-        <v>119.31</v>
+        <v>141.76</v>
       </c>
       <c r="O30" t="n">
-        <v>116.02</v>
+        <v>162.23</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3023,98 +3027,98 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>100.93</v>
+        <v>100.51</v>
       </c>
       <c r="C31" t="n">
-        <v>102.44</v>
+        <v>101.67</v>
       </c>
       <c r="D31" t="n">
-        <v>91.95999999999999</v>
+        <v>84.37</v>
       </c>
       <c r="E31" t="n">
-        <v>98.31999999999999</v>
+        <v>99.64</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.39</v>
+        <v>1.32</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0134</v>
       </c>
       <c r="H31" t="n">
-        <v>10.48</v>
+        <v>17.3</v>
       </c>
       <c r="I31" t="n">
-        <v>33.98</v>
+        <v>81.48</v>
       </c>
       <c r="J31" t="n">
-        <v>56.26</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>77.33</v>
+        <v>93.08</v>
       </c>
       <c r="L31" t="n">
-        <v>98.41</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>120.08</v>
+        <v>103.56</v>
       </c>
       <c r="N31" t="n">
-        <v>141.76</v>
+        <v>109.36</v>
       </c>
       <c r="O31" t="n">
-        <v>162.23</v>
+        <v>112.92</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3140,71 +3144,69 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>100.51</v>
+        <v>102.6</v>
       </c>
       <c r="C32" t="n">
-        <v>101.67</v>
+        <v>113.97</v>
       </c>
       <c r="D32" t="n">
-        <v>84.37</v>
+        <v>96.5</v>
       </c>
       <c r="E32" t="n">
-        <v>99.64</v>
+        <v>111.54</v>
       </c>
       <c r="F32" t="n">
-        <v>1.32</v>
+        <v>11.9</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.1194</v>
       </c>
       <c r="H32" t="n">
-        <v>17.3</v>
+        <v>17.47</v>
       </c>
       <c r="I32" t="n">
-        <v>81.48</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>88.40000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>93.08</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>97.76000000000001</v>
+        <v>96.33</v>
       </c>
       <c r="M32" t="n">
-        <v>103.56</v>
+        <v>108.29</v>
       </c>
       <c r="N32" t="n">
-        <v>109.36</v>
+        <v>120.25</v>
       </c>
       <c r="O32" t="n">
-        <v>112.92</v>
+        <v>118.97</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3217,78 +3219,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>102.6</v>
+        <v>112.96</v>
       </c>
       <c r="C33" t="n">
-        <v>113.97</v>
+        <v>117.63</v>
       </c>
       <c r="D33" t="n">
-        <v>96.5</v>
+        <v>91.05</v>
       </c>
       <c r="E33" t="n">
-        <v>111.54</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>11.9</v>
+        <v>-14.97</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.1194</v>
+        <v>-0.1342</v>
       </c>
       <c r="H33" t="n">
-        <v>17.47</v>
+        <v>26.58</v>
       </c>
       <c r="I33" t="n">
-        <v>67.06999999999999</v>
+        <v>79.03</v>
       </c>
       <c r="J33" t="n">
-        <v>85.65000000000001</v>
+        <v>97.22</v>
       </c>
       <c r="K33" t="n">
-        <v>90.98999999999999</v>
+        <v>102.81</v>
       </c>
       <c r="L33" t="n">
-        <v>96.33</v>
+        <v>108.39</v>
       </c>
       <c r="M33" t="n">
-        <v>108.29</v>
+        <v>120.28</v>
       </c>
       <c r="N33" t="n">
-        <v>120.25</v>
+        <v>132.16</v>
       </c>
       <c r="O33" t="n">
-        <v>118.97</v>
+        <v>131.44</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3296,75 +3296,77 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>112.96</v>
+        <v>102</v>
       </c>
       <c r="C34" t="n">
-        <v>117.63</v>
+        <v>105.63</v>
       </c>
       <c r="D34" t="n">
-        <v>91.05</v>
+        <v>80.56</v>
       </c>
       <c r="E34" t="n">
-        <v>96.56999999999999</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>-14.97</v>
+        <v>-12.72</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.1342</v>
+        <v>-0.1317</v>
       </c>
       <c r="H34" t="n">
-        <v>26.58</v>
+        <v>25.07</v>
       </c>
       <c r="I34" t="n">
-        <v>79.03</v>
+        <v>64.47</v>
       </c>
       <c r="J34" t="n">
-        <v>97.22</v>
+        <v>66.11</v>
       </c>
       <c r="K34" t="n">
-        <v>102.81</v>
+        <v>83.28</v>
       </c>
       <c r="L34" t="n">
-        <v>108.39</v>
+        <v>100.45</v>
       </c>
       <c r="M34" t="n">
-        <v>120.28</v>
+        <v>109.86</v>
       </c>
       <c r="N34" t="n">
-        <v>132.16</v>
+        <v>119.26</v>
       </c>
       <c r="O34" t="n">
-        <v>131.44</v>
+        <v>144.21</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3383,59 +3385,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C35" t="n">
-        <v>105.63</v>
+        <v>98.39</v>
       </c>
       <c r="D35" t="n">
-        <v>80.56</v>
+        <v>87.02</v>
       </c>
       <c r="E35" t="n">
-        <v>83.84999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-12.72</v>
+        <v>10.55</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.1317</v>
+        <v>0.1258</v>
       </c>
       <c r="H35" t="n">
-        <v>25.07</v>
+        <v>11.37</v>
       </c>
       <c r="I35" t="n">
-        <v>64.47</v>
+        <v>55.49</v>
       </c>
       <c r="J35" t="n">
-        <v>66.11</v>
+        <v>54.16</v>
       </c>
       <c r="K35" t="n">
-        <v>83.28</v>
+        <v>71.31</v>
       </c>
       <c r="L35" t="n">
-        <v>100.45</v>
+        <v>88.47</v>
       </c>
       <c r="M35" t="n">
-        <v>109.86</v>
+        <v>96.38</v>
       </c>
       <c r="N35" t="n">
-        <v>119.26</v>
+        <v>104.3</v>
       </c>
       <c r="O35" t="n">
-        <v>144.21</v>
+        <v>130.7</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3443,19 +3441,19 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3467,55 +3465,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>89</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>98.39</v>
+        <v>110.93</v>
       </c>
       <c r="D36" t="n">
-        <v>87.02</v>
+        <v>94.59</v>
       </c>
       <c r="E36" t="n">
-        <v>94.40000000000001</v>
+        <v>101.94</v>
       </c>
       <c r="F36" t="n">
-        <v>10.55</v>
+        <v>7.54</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.1258</v>
+        <v>0.0799</v>
       </c>
       <c r="H36" t="n">
-        <v>11.37</v>
+        <v>16.34</v>
       </c>
       <c r="I36" t="n">
-        <v>55.49</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>54.16</v>
+        <v>83.88</v>
       </c>
       <c r="K36" t="n">
-        <v>71.31</v>
+        <v>88.72</v>
       </c>
       <c r="L36" t="n">
-        <v>88.47</v>
+        <v>93.55</v>
       </c>
       <c r="M36" t="n">
-        <v>96.38</v>
+        <v>100.09</v>
       </c>
       <c r="N36" t="n">
-        <v>104.3</v>
+        <v>106.62</v>
       </c>
       <c r="O36" t="n">
-        <v>130.7</v>
+        <v>109.76</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3526,7 +3528,7 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3536,11 +3538,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
@@ -3549,57 +3555,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>95.59999999999999</v>
+        <v>99.73</v>
       </c>
       <c r="C37" t="n">
-        <v>110.93</v>
+        <v>107.46</v>
       </c>
       <c r="D37" t="n">
-        <v>94.59</v>
+        <v>88.66</v>
       </c>
       <c r="E37" t="n">
-        <v>101.94</v>
+        <v>95.42</v>
       </c>
       <c r="F37" t="n">
-        <v>7.54</v>
+        <v>-6.52</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0799</v>
+        <v>-0.064</v>
       </c>
       <c r="H37" t="n">
-        <v>16.34</v>
+        <v>18.8</v>
       </c>
       <c r="I37" t="n">
-        <v>75.65000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="J37" t="n">
-        <v>83.88</v>
+        <v>85.19</v>
       </c>
       <c r="K37" t="n">
-        <v>88.72</v>
+        <v>93.77</v>
       </c>
       <c r="L37" t="n">
-        <v>93.55</v>
+        <v>102.35</v>
       </c>
       <c r="M37" t="n">
-        <v>100.09</v>
+        <v>110.11</v>
       </c>
       <c r="N37" t="n">
-        <v>106.62</v>
+        <v>117.87</v>
       </c>
       <c r="O37" t="n">
-        <v>109.76</v>
+        <v>127.27</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3607,87 +3613,79 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>99.73</v>
+        <v>98.19</v>
       </c>
       <c r="C38" t="n">
-        <v>107.46</v>
+        <v>106</v>
       </c>
       <c r="D38" t="n">
-        <v>88.66</v>
+        <v>96.13</v>
       </c>
       <c r="E38" t="n">
-        <v>95.42</v>
+        <v>105.42</v>
       </c>
       <c r="F38" t="n">
-        <v>-6.52</v>
+        <v>10</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.064</v>
+        <v>0.1048</v>
       </c>
       <c r="H38" t="n">
-        <v>18.8</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>78.25</v>
+        <v>69.86</v>
       </c>
       <c r="J38" t="n">
-        <v>85.19</v>
+        <v>75.3</v>
       </c>
       <c r="K38" t="n">
-        <v>93.77</v>
+        <v>86.02</v>
       </c>
       <c r="L38" t="n">
-        <v>102.35</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>110.11</v>
+        <v>104.82</v>
       </c>
       <c r="N38" t="n">
-        <v>117.87</v>
+        <v>112.9</v>
       </c>
       <c r="O38" t="n">
-        <v>127.27</v>
+        <v>126.26</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3695,19 +3693,19 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3719,74 +3717,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>98.19</v>
+        <v>106</v>
       </c>
       <c r="C39" t="n">
-        <v>106</v>
+        <v>109.47</v>
       </c>
       <c r="D39" t="n">
-        <v>96.13</v>
+        <v>94.73</v>
       </c>
       <c r="E39" t="n">
-        <v>105.42</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>10</v>
+        <v>-8.82</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.1048</v>
+        <v>-0.0837</v>
       </c>
       <c r="H39" t="n">
-        <v>9.869999999999999</v>
+        <v>14.74</v>
       </c>
       <c r="I39" t="n">
-        <v>69.86</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>75.3</v>
+        <v>97.73</v>
       </c>
       <c r="K39" t="n">
-        <v>86.02</v>
+        <v>100.48</v>
       </c>
       <c r="L39" t="n">
-        <v>96.73999999999999</v>
+        <v>103.24</v>
       </c>
       <c r="M39" t="n">
-        <v>104.82</v>
+        <v>110.35</v>
       </c>
       <c r="N39" t="n">
-        <v>112.9</v>
+        <v>117.47</v>
       </c>
       <c r="O39" t="n">
-        <v>126.26</v>
+        <v>115.87</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3801,72 +3805,70 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>106</v>
+        <v>93.88</v>
       </c>
       <c r="C40" t="n">
-        <v>109.47</v>
+        <v>94.7</v>
       </c>
       <c r="D40" t="n">
-        <v>94.73</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>96.59999999999999</v>
+        <v>87.36</v>
       </c>
       <c r="F40" t="n">
-        <v>-8.82</v>
+        <v>-9.24</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0837</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>14.74</v>
+        <v>8.35</v>
       </c>
       <c r="I40" t="n">
-        <v>86.26000000000001</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>97.73</v>
+        <v>79.11</v>
       </c>
       <c r="K40" t="n">
-        <v>100.48</v>
+        <v>89.23</v>
       </c>
       <c r="L40" t="n">
-        <v>103.24</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>110.35</v>
+        <v>103.97</v>
       </c>
       <c r="N40" t="n">
-        <v>117.47</v>
+        <v>108.59</v>
       </c>
       <c r="O40" t="n">
-        <v>115.87</v>
+        <v>124.21</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3885,59 +3887,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>93.88</v>
+        <v>88.5</v>
       </c>
       <c r="C41" t="n">
-        <v>94.7</v>
+        <v>97</v>
       </c>
       <c r="D41" t="n">
-        <v>86.34999999999999</v>
+        <v>88.45</v>
       </c>
       <c r="E41" t="n">
-        <v>87.36</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>-9.24</v>
+        <v>3.18</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.0364</v>
       </c>
       <c r="H41" t="n">
-        <v>8.35</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>79.98999999999999</v>
+        <v>78</v>
       </c>
       <c r="J41" t="n">
-        <v>79.11</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>89.23</v>
+        <v>83.19</v>
       </c>
       <c r="L41" t="n">
-        <v>99.34999999999999</v>
+        <v>88.94</v>
       </c>
       <c r="M41" t="n">
-        <v>103.97</v>
+        <v>91.53</v>
       </c>
       <c r="N41" t="n">
-        <v>108.59</v>
+        <v>94.13</v>
       </c>
       <c r="O41" t="n">
-        <v>124.21</v>
+        <v>103.05</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3945,21 +3943,23 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3969,55 +3969,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>88.5</v>
+        <v>93</v>
       </c>
       <c r="C42" t="n">
-        <v>97</v>
+        <v>95.47</v>
       </c>
       <c r="D42" t="n">
-        <v>88.45</v>
+        <v>83.2</v>
       </c>
       <c r="E42" t="n">
-        <v>90.54000000000001</v>
+        <v>84.88</v>
       </c>
       <c r="F42" t="n">
-        <v>3.18</v>
+        <v>-5.66</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0364</v>
+        <v>-0.0625</v>
       </c>
       <c r="H42" t="n">
-        <v>8.550000000000001</v>
+        <v>12.27</v>
       </c>
       <c r="I42" t="n">
-        <v>78</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>77.43000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>83.19</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>88.94</v>
+        <v>91.63</v>
       </c>
       <c r="M42" t="n">
-        <v>91.53</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>94.13</v>
+        <v>98</v>
       </c>
       <c r="O42" t="n">
-        <v>103.05</v>
+        <v>105.55</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4025,24 +4029,24 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4051,59 +4055,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>93</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>95.47</v>
+        <v>82.42</v>
       </c>
       <c r="D43" t="n">
-        <v>83.2</v>
+        <v>73.58</v>
       </c>
       <c r="E43" t="n">
-        <v>84.88</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>-5.66</v>
+        <v>-7.34</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0625</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>12.27</v>
+        <v>8.84</v>
       </c>
       <c r="I43" t="n">
-        <v>79.90000000000001</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>80.90000000000001</v>
+        <v>70.38</v>
       </c>
       <c r="K43" t="n">
-        <v>86.26000000000001</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>91.63</v>
+        <v>87.11</v>
       </c>
       <c r="M43" t="n">
-        <v>94.81999999999999</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>98</v>
+        <v>94.92</v>
       </c>
       <c r="O43" t="n">
-        <v>105.55</v>
+        <v>107.74</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4116,15 +4116,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4142,63 +4140,65 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>81.40000000000001</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>82.42</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>73.58</v>
+        <v>68.56</v>
       </c>
       <c r="E44" t="n">
-        <v>77.54000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="F44" t="n">
-        <v>-7.34</v>
+        <v>-8.31</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.1072</v>
       </c>
       <c r="H44" t="n">
-        <v>8.84</v>
+        <v>10.4</v>
       </c>
       <c r="I44" t="n">
-        <v>70.93000000000001</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>70.38</v>
+        <v>68.47</v>
       </c>
       <c r="K44" t="n">
-        <v>78.73999999999999</v>
+        <v>73.12</v>
       </c>
       <c r="L44" t="n">
-        <v>87.11</v>
+        <v>77.77</v>
       </c>
       <c r="M44" t="n">
-        <v>91.01000000000001</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>94.92</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>107.74</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4222,67 +4222,63 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>78.93000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="C45" t="n">
-        <v>78.95999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>68.56</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>69.23</v>
+        <v>68.78</v>
       </c>
       <c r="F45" t="n">
-        <v>-8.31</v>
+        <v>-0.45</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.1072</v>
+        <v>-0.0065</v>
       </c>
       <c r="H45" t="n">
-        <v>10.4</v>
+        <v>4.56</v>
       </c>
       <c r="I45" t="n">
-        <v>64.73999999999999</v>
+        <v>58.16</v>
       </c>
       <c r="J45" t="n">
-        <v>68.47</v>
+        <v>56.57</v>
       </c>
       <c r="K45" t="n">
-        <v>73.12</v>
+        <v>64.03</v>
       </c>
       <c r="L45" t="n">
-        <v>77.77</v>
+        <v>71.5</v>
       </c>
       <c r="M45" t="n">
-        <v>81.95999999999999</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>86.15000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="O45" t="n">
-        <v>91.26000000000001</v>
+        <v>89.36</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4304,50 +4300,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>70.5</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C46" t="n">
-        <v>71.59999999999999</v>
+        <v>76.08</v>
       </c>
       <c r="D46" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>68.78</v>
+        <v>71.41</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.45</v>
+        <v>2.63</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0382</v>
       </c>
       <c r="H46" t="n">
-        <v>4.56</v>
+        <v>8.26</v>
       </c>
       <c r="I46" t="n">
-        <v>58.16</v>
+        <v>62.48</v>
       </c>
       <c r="J46" t="n">
-        <v>56.57</v>
+        <v>63.95</v>
       </c>
       <c r="K46" t="n">
-        <v>64.03</v>
+        <v>66.5</v>
       </c>
       <c r="L46" t="n">
-        <v>71.5</v>
+        <v>69.05</v>
       </c>
       <c r="M46" t="n">
-        <v>74.43000000000001</v>
+        <v>71.06</v>
       </c>
       <c r="N46" t="n">
-        <v>77.37</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O46" t="n">
-        <v>89.36</v>
+        <v>76.16</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4360,14 +4356,18 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4377,55 +4377,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>68.68000000000001</v>
+        <v>73.69</v>
       </c>
       <c r="C47" t="n">
-        <v>76.08</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>67.81999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="E47" t="n">
-        <v>71.41</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>2.63</v>
+        <v>11.08</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0382</v>
+        <v>0.1552</v>
       </c>
       <c r="H47" t="n">
-        <v>8.26</v>
+        <v>10.15</v>
       </c>
       <c r="I47" t="n">
-        <v>62.48</v>
+        <v>59.56</v>
       </c>
       <c r="J47" t="n">
-        <v>63.95</v>
+        <v>62.88</v>
       </c>
       <c r="K47" t="n">
-        <v>66.5</v>
+        <v>67.28</v>
       </c>
       <c r="L47" t="n">
-        <v>69.05</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M47" t="n">
-        <v>71.06</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>73.06999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>76.16</v>
+        <v>84.34</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4436,82 +4440,80 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W47" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W47" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>73.69</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>82.76000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="D48" t="n">
-        <v>72.61</v>
+        <v>80.27</v>
       </c>
       <c r="E48" t="n">
-        <v>82.48999999999999</v>
+        <v>89.31</v>
       </c>
       <c r="F48" t="n">
-        <v>11.08</v>
+        <v>6.82</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.1552</v>
+        <v>0.0827</v>
       </c>
       <c r="H48" t="n">
-        <v>10.15</v>
+        <v>13.23</v>
       </c>
       <c r="I48" t="n">
-        <v>59.56</v>
+        <v>62.46</v>
       </c>
       <c r="J48" t="n">
-        <v>62.88</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>67.28</v>
+        <v>77.41</v>
       </c>
       <c r="L48" t="n">
-        <v>71.68000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="M48" t="n">
-        <v>75.54000000000001</v>
+        <v>87.56</v>
       </c>
       <c r="N48" t="n">
-        <v>79.40000000000001</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>84.34</v>
+        <v>92.91</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4522,24 +4524,22 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W48" s="9" t="inlineStr">
@@ -4552,50 +4552,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>83.76000000000001</v>
+        <v>86.12</v>
       </c>
       <c r="C49" t="n">
-        <v>93.5</v>
+        <v>86.87</v>
       </c>
       <c r="D49" t="n">
-        <v>80.27</v>
+        <v>77.78</v>
       </c>
       <c r="E49" t="n">
-        <v>89.31</v>
+        <v>84.67</v>
       </c>
       <c r="F49" t="n">
-        <v>6.82</v>
+        <v>-4.64</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0827</v>
+        <v>-0.052</v>
       </c>
       <c r="H49" t="n">
-        <v>13.23</v>
+        <v>9.09</v>
       </c>
       <c r="I49" t="n">
-        <v>62.46</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>74.73999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>77.41</v>
+        <v>82.69</v>
       </c>
       <c r="L49" t="n">
-        <v>80.09</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>87.56</v>
+        <v>95.92</v>
       </c>
       <c r="N49" t="n">
-        <v>95.04000000000001</v>
+        <v>103.75</v>
       </c>
       <c r="O49" t="n">
-        <v>92.91</v>
+        <v>106.73</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4603,94 +4603,98 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>86.12</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C50" t="n">
-        <v>86.87</v>
+        <v>82.33</v>
       </c>
       <c r="D50" t="n">
-        <v>77.78</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>84.67</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>-4.64</v>
+        <v>-6.49</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.0767</v>
       </c>
       <c r="H50" t="n">
-        <v>9.09</v>
+        <v>8.09</v>
       </c>
       <c r="I50" t="n">
-        <v>67.04000000000001</v>
+        <v>68.69</v>
       </c>
       <c r="J50" t="n">
-        <v>77.29000000000001</v>
+        <v>76.75</v>
       </c>
       <c r="K50" t="n">
-        <v>82.69</v>
+        <v>80.12</v>
       </c>
       <c r="L50" t="n">
-        <v>88.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="M50" t="n">
-        <v>95.92</v>
+        <v>89.22</v>
       </c>
       <c r="N50" t="n">
-        <v>103.75</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>106.73</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4718,72 +4722,70 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>80.09999999999999</v>
+        <v>78.42</v>
       </c>
       <c r="C51" t="n">
-        <v>82.33</v>
+        <v>84.61</v>
       </c>
       <c r="D51" t="n">
-        <v>74.23999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>78.18000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>-6.49</v>
+        <v>4.22</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0767</v>
+        <v>0.054</v>
       </c>
       <c r="H51" t="n">
-        <v>8.09</v>
+        <v>6.82</v>
       </c>
       <c r="I51" t="n">
-        <v>68.69</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>76.75</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>80.12</v>
+        <v>74.13</v>
       </c>
       <c r="L51" t="n">
-        <v>83.5</v>
+        <v>78.23</v>
       </c>
       <c r="M51" t="n">
-        <v>89.22</v>
+        <v>82.23</v>
       </c>
       <c r="N51" t="n">
-        <v>94.93000000000001</v>
+        <v>86.22</v>
       </c>
       <c r="O51" t="n">
-        <v>95.95999999999999</v>
+        <v>90.42</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4795,59 +4797,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>78.42</v>
+        <v>82.53</v>
       </c>
       <c r="C52" t="n">
-        <v>84.61</v>
+        <v>89</v>
       </c>
       <c r="D52" t="n">
-        <v>77.79000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="E52" t="n">
-        <v>82.40000000000001</v>
+        <v>87.06</v>
       </c>
       <c r="F52" t="n">
-        <v>4.22</v>
+        <v>4.66</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.054</v>
+        <v>0.0566</v>
       </c>
       <c r="H52" t="n">
-        <v>6.82</v>
+        <v>7.5</v>
       </c>
       <c r="I52" t="n">
-        <v>66.15000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="J52" t="n">
-        <v>70.04000000000001</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>74.13</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>78.23</v>
+        <v>81.8</v>
       </c>
       <c r="M52" t="n">
-        <v>82.23</v>
+        <v>85.81</v>
       </c>
       <c r="N52" t="n">
-        <v>86.22</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="O52" t="n">
-        <v>90.42</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4858,7 +4856,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4884,69 +4882,71 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>82.53</v>
+        <v>86.5</v>
       </c>
       <c r="C53" t="n">
-        <v>89</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>81.5</v>
+        <v>79.62</v>
       </c>
       <c r="E53" t="n">
-        <v>87.06</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>4.66</v>
+        <v>-3.66</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0566</v>
+        <v>-0.042</v>
       </c>
       <c r="H53" t="n">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="I53" t="n">
-        <v>70.97</v>
+        <v>74</v>
       </c>
       <c r="J53" t="n">
-        <v>76.18000000000001</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>78.98999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="L53" t="n">
-        <v>81.8</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>85.81</v>
+        <v>90.81</v>
       </c>
       <c r="N53" t="n">
-        <v>89.81999999999999</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="O53" t="n">
-        <v>91.43000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4959,80 +4959,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>86.5</v>
+        <v>84.69</v>
       </c>
       <c r="C54" t="n">
-        <v>86.56999999999999</v>
+        <v>93.14</v>
       </c>
       <c r="D54" t="n">
-        <v>79.62</v>
+        <v>84.11</v>
       </c>
       <c r="E54" t="n">
-        <v>83.40000000000001</v>
+        <v>91.48</v>
       </c>
       <c r="F54" t="n">
-        <v>-3.66</v>
+        <v>8.08</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.042</v>
+        <v>0.0969</v>
       </c>
       <c r="H54" t="n">
-        <v>6.95</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>74</v>
+        <v>72.67</v>
       </c>
       <c r="J54" t="n">
-        <v>80.45999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>83.31</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>86.15000000000001</v>
+        <v>83.25</v>
       </c>
       <c r="M54" t="n">
-        <v>90.81</v>
+        <v>86.88</v>
       </c>
       <c r="N54" t="n">
-        <v>95.45999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="O54" t="n">
-        <v>96.5</v>
+        <v>93.52</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="U54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
@@ -5041,59 +5045,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>84.69</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C55" t="n">
-        <v>93.14</v>
+        <v>104.46</v>
       </c>
       <c r="D55" t="n">
-        <v>84.11</v>
+        <v>90.87</v>
       </c>
       <c r="E55" t="n">
-        <v>91.48</v>
+        <v>100.05</v>
       </c>
       <c r="F55" t="n">
-        <v>8.08</v>
+        <v>8.57</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0969</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>9.029999999999999</v>
+        <v>13.59</v>
       </c>
       <c r="I55" t="n">
-        <v>72.67</v>
+        <v>75.08</v>
       </c>
       <c r="J55" t="n">
-        <v>76.59999999999999</v>
+        <v>83.88</v>
       </c>
       <c r="K55" t="n">
-        <v>79.93000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="L55" t="n">
-        <v>83.25</v>
+        <v>90.05</v>
       </c>
       <c r="M55" t="n">
-        <v>86.88</v>
+        <v>96</v>
       </c>
       <c r="N55" t="n">
-        <v>90.5</v>
+        <v>101.94</v>
       </c>
       <c r="O55" t="n">
-        <v>93.52</v>
+        <v>102.17</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5104,7 +5104,7 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5119,8 +5119,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V55" s="8" t="n">
-        <v/>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
@@ -5132,50 +5134,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>92.26000000000001</v>
+        <v>102.25</v>
       </c>
       <c r="C56" t="n">
-        <v>104.46</v>
+        <v>106.75</v>
       </c>
       <c r="D56" t="n">
-        <v>90.87</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>100.05</v>
+        <v>100.3</v>
       </c>
       <c r="F56" t="n">
-        <v>8.57</v>
+        <v>0.25</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="H56" t="n">
-        <v>13.59</v>
+        <v>7.65</v>
       </c>
       <c r="I56" t="n">
-        <v>75.08</v>
+        <v>77.28</v>
       </c>
       <c r="J56" t="n">
-        <v>83.88</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>86.97</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>90.05</v>
+        <v>98.86</v>
       </c>
       <c r="M56" t="n">
-        <v>96</v>
+        <v>106.85</v>
       </c>
       <c r="N56" t="n">
-        <v>101.94</v>
+        <v>114.83</v>
       </c>
       <c r="O56" t="n">
-        <v>102.17</v>
+        <v>118.05</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5186,25 +5188,19 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
@@ -5216,63 +5212,69 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>102.25</v>
+        <v>101</v>
       </c>
       <c r="C57" t="n">
-        <v>106.75</v>
+        <v>101.08</v>
       </c>
       <c r="D57" t="n">
-        <v>99.09999999999999</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>100.3</v>
+        <v>92.41</v>
       </c>
       <c r="F57" t="n">
-        <v>0.25</v>
+        <v>-7.89</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>7.65</v>
+        <v>12.37</v>
       </c>
       <c r="I57" t="n">
-        <v>77.28</v>
+        <v>91.45</v>
       </c>
       <c r="J57" t="n">
-        <v>87.65000000000001</v>
+        <v>91.34</v>
       </c>
       <c r="K57" t="n">
-        <v>93.26000000000001</v>
+        <v>96.48</v>
       </c>
       <c r="L57" t="n">
-        <v>98.86</v>
+        <v>101.61</v>
       </c>
       <c r="M57" t="n">
-        <v>106.85</v>
+        <v>104.13</v>
       </c>
       <c r="N57" t="n">
-        <v>114.83</v>
+        <v>106.64</v>
       </c>
       <c r="O57" t="n">
-        <v>118.05</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+        <v>114.4</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5289,91 +5291,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>101</v>
-      </c>
-      <c r="C58" t="n">
-        <v>101.08</v>
-      </c>
-      <c r="D58" t="n">
-        <v>88.70999999999999</v>
-      </c>
-      <c r="E58" t="n">
-        <v>94.56999999999999</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-5.73</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0571</v>
-      </c>
-      <c r="H58" t="n">
-        <v>12.37</v>
-      </c>
-      <c r="I58" t="n">
-        <v>91.45</v>
-      </c>
-      <c r="J58" t="n">
-        <v>91.34</v>
-      </c>
-      <c r="K58" t="n">
-        <v>96.48</v>
-      </c>
-      <c r="L58" t="n">
-        <v>101.61</v>
-      </c>
-      <c r="M58" t="n">
-        <v>104.13</v>
-      </c>
-      <c r="N58" t="n">
-        <v>106.64</v>
-      </c>
-      <c r="O58" t="n">
-        <v>114.4</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5297,6 +5297,88 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>93.53</v>
+      </c>
+      <c r="C58" t="n">
+        <v>93.77</v>
+      </c>
+      <c r="D58" t="n">
+        <v>93.39</v>
+      </c>
+      <c r="E58" t="n">
+        <v>93.39</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="I58" t="n">
+        <v>76.34</v>
+      </c>
+      <c r="J58" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="K58" t="n">
+        <v>86.23</v>
+      </c>
+      <c r="L58" t="n">
+        <v>93.65000000000001</v>
+      </c>
+      <c r="M58" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="N58" t="n">
+        <v>103.54</v>
+      </c>
+      <c r="O58" t="n">
+        <v>113.45</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -659,25 +659,25 @@
         <v>4.58</v>
       </c>
       <c r="I2" t="n">
-        <v>60.8</v>
+        <v>61.14</v>
       </c>
       <c r="J2" t="n">
-        <v>61.85</v>
+        <v>62.28</v>
       </c>
       <c r="K2" t="n">
-        <v>62.94</v>
+        <v>63.11</v>
       </c>
       <c r="L2" t="n">
-        <v>64.02</v>
+        <v>63.93</v>
       </c>
       <c r="M2" t="n">
-        <v>65.09</v>
+        <v>64.92</v>
       </c>
       <c r="N2" t="n">
-        <v>66.15000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>67.25</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -702,20 +702,22 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -792,12 +794,12 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -876,12 +878,12 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -960,7 +962,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1046,7 +1048,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1126,7 +1128,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1206,7 +1208,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1288,7 +1290,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1370,7 +1372,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1454,7 +1456,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1540,7 +1542,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1624,7 +1626,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1706,7 +1708,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1790,7 +1792,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1872,7 +1874,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1952,7 +1954,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2032,7 +2034,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2118,7 +2120,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2206,7 +2208,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2290,7 +2292,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2374,7 +2376,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2462,7 +2464,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2542,7 +2544,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2626,7 +2628,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2712,7 +2714,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2796,7 +2798,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2880,7 +2882,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2966,7 +2968,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3044,7 +3046,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3130,7 +3132,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3214,7 +3216,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3296,7 +3298,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3380,7 +3382,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3460,7 +3462,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3548,7 +3550,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3632,7 +3634,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3712,7 +3714,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3798,7 +3800,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3882,7 +3884,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3964,7 +3966,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4050,7 +4052,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4130,7 +4132,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4212,7 +4214,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4290,7 +4292,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4372,7 +4374,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4460,7 +4462,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4542,7 +4544,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4622,7 +4624,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4708,7 +4710,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4792,7 +4794,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4872,7 +4874,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4954,7 +4956,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5040,7 +5042,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5124,7 +5126,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5202,7 +5204,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5286,7 +5288,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5304,25 +5306,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>93.53</v>
+        <v>93.58</v>
       </c>
       <c r="C58" t="n">
-        <v>93.77</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>93.39</v>
+        <v>88.58</v>
       </c>
       <c r="E58" t="n">
-        <v>93.39</v>
+        <v>88.66</v>
       </c>
       <c r="F58" t="n">
-        <v>0.98</v>
+        <v>-3.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0106</v>
+        <v>-0.0406</v>
       </c>
       <c r="H58" t="n">
-        <v>0.38</v>
+        <v>7.96</v>
       </c>
       <c r="I58" t="n">
         <v>76.34</v>
@@ -5351,12 +5353,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5368,14 +5372,14 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>4.58</v>
       </c>
       <c r="I2" t="n">
-        <v>61.14</v>
+        <v>61.2</v>
       </c>
       <c r="J2" t="n">
-        <v>62.28</v>
+        <v>62.35</v>
       </c>
       <c r="K2" t="n">
-        <v>63.11</v>
+        <v>63.14</v>
       </c>
       <c r="L2" t="n">
-        <v>63.93</v>
+        <v>63.92</v>
       </c>
       <c r="M2" t="n">
-        <v>64.92</v>
+        <v>64.89</v>
       </c>
       <c r="N2" t="n">
-        <v>65.90000000000001</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>66.56999999999999</v>
+        <v>66.45</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5312,19 +5312,19 @@
         <v>96.54000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>88.58</v>
+        <v>88.78</v>
       </c>
       <c r="E58" t="n">
-        <v>88.66</v>
+        <v>90.28</v>
       </c>
       <c r="F58" t="n">
-        <v>-3.75</v>
+        <v>-2.13</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0406</v>
+        <v>-0.023</v>
       </c>
       <c r="H58" t="n">
-        <v>7.96</v>
+        <v>7.76</v>
       </c>
       <c r="I58" t="n">
         <v>76.34</v>
@@ -5353,14 +5353,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5379,7 +5377,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -659,32 +659,34 @@
         <v>4.58</v>
       </c>
       <c r="I2" t="n">
-        <v>61.2</v>
+        <v>62</v>
       </c>
       <c r="J2" t="n">
-        <v>62.35</v>
+        <v>62.65</v>
       </c>
       <c r="K2" t="n">
-        <v>63.14</v>
+        <v>63.34</v>
       </c>
       <c r="L2" t="n">
-        <v>63.92</v>
+        <v>64.02</v>
       </c>
       <c r="M2" t="n">
-        <v>64.89</v>
+        <v>64.69</v>
       </c>
       <c r="N2" t="n">
-        <v>65.84999999999999</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>66.45</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>66.05</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -5312,19 +5314,19 @@
         <v>96.54000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>88.78</v>
+        <v>88.58</v>
       </c>
       <c r="E58" t="n">
-        <v>90.28</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.13</v>
+        <v>0.74</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.023</v>
+        <v>0.008</v>
       </c>
       <c r="H58" t="n">
-        <v>7.76</v>
+        <v>7.96</v>
       </c>
       <c r="I58" t="n">
         <v>76.34</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,87 +634,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63.95</v>
+        <v>62</v>
       </c>
       <c r="C2" t="n">
-        <v>66.03</v>
+        <v>64.08</v>
       </c>
       <c r="D2" t="n">
-        <v>61.45</v>
+        <v>61.69</v>
       </c>
       <c r="E2" t="n">
-        <v>61.87</v>
+        <v>62.69</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.14</v>
+        <v>0.82</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0334</v>
+        <v>0.0133</v>
       </c>
       <c r="H2" t="n">
-        <v>4.58</v>
+        <v>2.39</v>
       </c>
       <c r="I2" t="n">
-        <v>62</v>
+        <v>56.87</v>
       </c>
       <c r="J2" t="n">
-        <v>62.65</v>
+        <v>56.36</v>
       </c>
       <c r="K2" t="n">
-        <v>63.34</v>
+        <v>59.58</v>
       </c>
       <c r="L2" t="n">
-        <v>64.02</v>
+        <v>62.8</v>
       </c>
       <c r="M2" t="n">
-        <v>64.69</v>
+        <v>64.16</v>
       </c>
       <c r="N2" t="n">
-        <v>65.34999999999999</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>66.05</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>70.61</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -726,50 +716,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62</v>
+        <v>62.97</v>
       </c>
       <c r="C3" t="n">
-        <v>64.08</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>61.69</v>
+        <v>62.52</v>
       </c>
       <c r="E3" t="n">
-        <v>62.69</v>
+        <v>62.68</v>
       </c>
       <c r="F3" t="n">
-        <v>0.82</v>
+        <v>-0.01</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0002</v>
       </c>
       <c r="H3" t="n">
-        <v>2.39</v>
+        <v>2.24</v>
       </c>
       <c r="I3" t="n">
-        <v>56.87</v>
+        <v>59.3</v>
       </c>
       <c r="J3" t="n">
-        <v>56.36</v>
+        <v>60.2</v>
       </c>
       <c r="K3" t="n">
-        <v>59.58</v>
+        <v>61.49</v>
       </c>
       <c r="L3" t="n">
-        <v>62.8</v>
+        <v>62.79</v>
       </c>
       <c r="M3" t="n">
-        <v>64.16</v>
+        <v>63.89</v>
       </c>
       <c r="N3" t="n">
-        <v>65.51000000000001</v>
+        <v>64.98</v>
       </c>
       <c r="O3" t="n">
-        <v>70.61</v>
+        <v>66.47</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -785,8 +775,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -796,62 +788,62 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62.97</v>
+        <v>62.74</v>
       </c>
       <c r="C4" t="n">
-        <v>64.76000000000001</v>
+        <v>66.42</v>
       </c>
       <c r="D4" t="n">
-        <v>62.52</v>
+        <v>61.85</v>
       </c>
       <c r="E4" t="n">
-        <v>62.68</v>
+        <v>65.72</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.01</v>
+        <v>3.04</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0485</v>
       </c>
       <c r="H4" t="n">
-        <v>2.24</v>
+        <v>4.57</v>
       </c>
       <c r="I4" t="n">
-        <v>59.3</v>
+        <v>60.28</v>
       </c>
       <c r="J4" t="n">
-        <v>60.2</v>
+        <v>59.96</v>
       </c>
       <c r="K4" t="n">
-        <v>61.49</v>
+        <v>61.56</v>
       </c>
       <c r="L4" t="n">
-        <v>62.79</v>
+        <v>63.16</v>
       </c>
       <c r="M4" t="n">
-        <v>63.89</v>
+        <v>63.8</v>
       </c>
       <c r="N4" t="n">
-        <v>64.98</v>
+        <v>64.44</v>
       </c>
       <c r="O4" t="n">
-        <v>66.47</v>
+        <v>67</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -862,9 +854,9 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
@@ -872,170 +864,166 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="n">
-        <v/>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.74</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>66.42</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>61.85</v>
+        <v>60.4</v>
       </c>
       <c r="E5" t="n">
-        <v>65.72</v>
+        <v>60.88</v>
       </c>
       <c r="F5" t="n">
-        <v>3.04</v>
+        <v>-4.84</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0485</v>
+        <v>-0.0736</v>
       </c>
       <c r="H5" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>60.28</v>
+        <v>57.28</v>
       </c>
       <c r="J5" t="n">
-        <v>59.96</v>
+        <v>61.94</v>
       </c>
       <c r="K5" t="n">
-        <v>61.56</v>
+        <v>63.44</v>
       </c>
       <c r="L5" t="n">
-        <v>63.16</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>63.8</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>64.44</v>
+        <v>71.08</v>
       </c>
       <c r="O5" t="n">
-        <v>67</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
       <c r="W5" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65.06999999999999</v>
+        <v>61.14</v>
       </c>
       <c r="C6" t="n">
-        <v>65.40000000000001</v>
+        <v>62.92</v>
       </c>
       <c r="D6" t="n">
-        <v>60.4</v>
+        <v>58.22</v>
       </c>
       <c r="E6" t="n">
-        <v>60.88</v>
+        <v>58.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.84</v>
+        <v>-1.98</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0736</v>
+        <v>-0.0325</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I6" t="n">
-        <v>57.28</v>
+        <v>55.4</v>
       </c>
       <c r="J6" t="n">
-        <v>61.94</v>
+        <v>54.87</v>
       </c>
       <c r="K6" t="n">
-        <v>63.44</v>
+        <v>58.38</v>
       </c>
       <c r="L6" t="n">
-        <v>64.93000000000001</v>
+        <v>61.89</v>
       </c>
       <c r="M6" t="n">
-        <v>68.01000000000001</v>
+        <v>63.38</v>
       </c>
       <c r="N6" t="n">
-        <v>71.08</v>
+        <v>64.87</v>
       </c>
       <c r="O6" t="n">
-        <v>70.98999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1050,7 +1038,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1060,50 +1048,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>61.14</v>
+        <v>59</v>
       </c>
       <c r="C7" t="n">
-        <v>62.92</v>
+        <v>60.17</v>
       </c>
       <c r="D7" t="n">
-        <v>58.22</v>
+        <v>56.6</v>
       </c>
       <c r="E7" t="n">
-        <v>58.9</v>
+        <v>57.54</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.98</v>
+        <v>-1.36</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0325</v>
+        <v>-0.0231</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7</v>
+        <v>3.57</v>
       </c>
       <c r="I7" t="n">
-        <v>55.4</v>
+        <v>53.52</v>
       </c>
       <c r="J7" t="n">
-        <v>54.87</v>
+        <v>53.37</v>
       </c>
       <c r="K7" t="n">
-        <v>58.38</v>
+        <v>56.55</v>
       </c>
       <c r="L7" t="n">
-        <v>61.89</v>
+        <v>59.74</v>
       </c>
       <c r="M7" t="n">
-        <v>63.38</v>
+        <v>61.25</v>
       </c>
       <c r="N7" t="n">
-        <v>64.87</v>
+        <v>62.76</v>
       </c>
       <c r="O7" t="n">
-        <v>70.40000000000001</v>
+        <v>67.62</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1130,7 +1118,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1140,50 +1128,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>57.73</v>
       </c>
       <c r="C8" t="n">
-        <v>60.17</v>
+        <v>62.59</v>
       </c>
       <c r="D8" t="n">
-        <v>56.6</v>
+        <v>56.35</v>
       </c>
       <c r="E8" t="n">
-        <v>57.54</v>
+        <v>61.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.36</v>
+        <v>3.96</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0231</v>
+        <v>0.0688</v>
       </c>
       <c r="H8" t="n">
-        <v>3.57</v>
+        <v>6.24</v>
       </c>
       <c r="I8" t="n">
-        <v>53.52</v>
+        <v>53.03</v>
       </c>
       <c r="J8" t="n">
-        <v>53.37</v>
+        <v>53.55</v>
       </c>
       <c r="K8" t="n">
-        <v>56.55</v>
+        <v>55.76</v>
       </c>
       <c r="L8" t="n">
-        <v>59.74</v>
+        <v>57.96</v>
       </c>
       <c r="M8" t="n">
-        <v>61.25</v>
+        <v>59.33</v>
       </c>
       <c r="N8" t="n">
-        <v>62.76</v>
+        <v>60.69</v>
       </c>
       <c r="O8" t="n">
-        <v>67.62</v>
+        <v>63.74</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,79 +1179,85 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57.73</v>
+        <v>61.82</v>
       </c>
       <c r="C9" t="n">
-        <v>62.59</v>
+        <v>62.17</v>
       </c>
       <c r="D9" t="n">
-        <v>56.35</v>
+        <v>59.64</v>
       </c>
       <c r="E9" t="n">
-        <v>61.5</v>
+        <v>60.98</v>
       </c>
       <c r="F9" t="n">
-        <v>3.96</v>
+        <v>-0.52</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0688</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>6.24</v>
+        <v>2.53</v>
       </c>
       <c r="I9" t="n">
-        <v>53.03</v>
+        <v>50.11</v>
       </c>
       <c r="J9" t="n">
-        <v>53.55</v>
+        <v>56.27</v>
       </c>
       <c r="K9" t="n">
-        <v>55.76</v>
+        <v>58.38</v>
       </c>
       <c r="L9" t="n">
-        <v>57.96</v>
+        <v>60.48</v>
       </c>
       <c r="M9" t="n">
-        <v>59.33</v>
+        <v>64.62</v>
       </c>
       <c r="N9" t="n">
-        <v>60.69</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>63.74</v>
+        <v>68.83</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1276,80 +1270,76 @@
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61.82</v>
+        <v>61.4</v>
       </c>
       <c r="C10" t="n">
-        <v>62.17</v>
+        <v>61.5</v>
       </c>
       <c r="D10" t="n">
-        <v>59.64</v>
+        <v>58.83</v>
       </c>
       <c r="E10" t="n">
-        <v>60.98</v>
+        <v>59.75</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.52</v>
+        <v>-1.23</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0202</v>
       </c>
       <c r="H10" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="I10" t="n">
-        <v>50.11</v>
+        <v>57.11</v>
       </c>
       <c r="J10" t="n">
-        <v>56.27</v>
+        <v>58.49</v>
       </c>
       <c r="K10" t="n">
-        <v>58.38</v>
+        <v>59.72</v>
       </c>
       <c r="L10" t="n">
-        <v>60.48</v>
+        <v>60.94</v>
       </c>
       <c r="M10" t="n">
-        <v>64.62</v>
+        <v>62.24</v>
       </c>
       <c r="N10" t="n">
-        <v>68.76000000000001</v>
+        <v>63.55</v>
       </c>
       <c r="O10" t="n">
-        <v>68.83</v>
+        <v>64.7</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1357,12 +1347,14 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1374,64 +1366,64 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>61.4</v>
+        <v>59.87</v>
       </c>
       <c r="C11" t="n">
-        <v>61.5</v>
+        <v>61.28</v>
       </c>
       <c r="D11" t="n">
-        <v>58.83</v>
+        <v>58.12</v>
       </c>
       <c r="E11" t="n">
-        <v>59.75</v>
+        <v>60.09</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.23</v>
+        <v>0.34</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0202</v>
+        <v>0.0057</v>
       </c>
       <c r="H11" t="n">
-        <v>2.67</v>
+        <v>3.16</v>
       </c>
       <c r="I11" t="n">
-        <v>57.11</v>
+        <v>56.16</v>
       </c>
       <c r="J11" t="n">
-        <v>58.49</v>
+        <v>56.87</v>
       </c>
       <c r="K11" t="n">
-        <v>59.72</v>
+        <v>58.42</v>
       </c>
       <c r="L11" t="n">
-        <v>60.94</v>
+        <v>59.96</v>
       </c>
       <c r="M11" t="n">
-        <v>62.24</v>
+        <v>61.08</v>
       </c>
       <c r="N11" t="n">
-        <v>63.55</v>
+        <v>62.21</v>
       </c>
       <c r="O11" t="n">
-        <v>64.7</v>
+        <v>64.17</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1441,16 +1433,18 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1458,64 +1452,64 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59.87</v>
+        <v>59.8</v>
       </c>
       <c r="C12" t="n">
-        <v>61.28</v>
+        <v>60.93</v>
       </c>
       <c r="D12" t="n">
-        <v>58.12</v>
+        <v>57.38</v>
       </c>
       <c r="E12" t="n">
-        <v>60.09</v>
+        <v>58.06</v>
       </c>
       <c r="F12" t="n">
-        <v>0.34</v>
+        <v>-2.03</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.0338</v>
       </c>
       <c r="H12" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="I12" t="n">
-        <v>56.16</v>
+        <v>54.96</v>
       </c>
       <c r="J12" t="n">
-        <v>56.87</v>
+        <v>57.13</v>
       </c>
       <c r="K12" t="n">
-        <v>58.42</v>
+        <v>58.51</v>
       </c>
       <c r="L12" t="n">
-        <v>59.96</v>
+        <v>59.89</v>
       </c>
       <c r="M12" t="n">
-        <v>61.08</v>
+        <v>61.67</v>
       </c>
       <c r="N12" t="n">
-        <v>62.21</v>
+        <v>63.45</v>
       </c>
       <c r="O12" t="n">
-        <v>64.17</v>
+        <v>64.44</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1525,18 +1519,16 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1544,64 +1536,64 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>59.8</v>
+        <v>58.05</v>
       </c>
       <c r="C13" t="n">
-        <v>60.93</v>
+        <v>59.64</v>
       </c>
       <c r="D13" t="n">
-        <v>57.38</v>
+        <v>57.1</v>
       </c>
       <c r="E13" t="n">
-        <v>58.06</v>
+        <v>58.55</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.03</v>
+        <v>0.49</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>3.55</v>
+        <v>2.54</v>
       </c>
       <c r="I13" t="n">
-        <v>54.96</v>
+        <v>53.83</v>
       </c>
       <c r="J13" t="n">
-        <v>57.13</v>
+        <v>53.96</v>
       </c>
       <c r="K13" t="n">
-        <v>58.51</v>
+        <v>56.29</v>
       </c>
       <c r="L13" t="n">
-        <v>59.89</v>
+        <v>58.61</v>
       </c>
       <c r="M13" t="n">
-        <v>61.67</v>
+        <v>59.84</v>
       </c>
       <c r="N13" t="n">
-        <v>63.45</v>
+        <v>61.06</v>
       </c>
       <c r="O13" t="n">
-        <v>64.44</v>
+        <v>64.48</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1609,14 +1601,12 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1628,64 +1618,64 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>58.05</v>
+        <v>58.96</v>
       </c>
       <c r="C14" t="n">
-        <v>59.64</v>
+        <v>60.5</v>
       </c>
       <c r="D14" t="n">
-        <v>57.1</v>
+        <v>58.28</v>
       </c>
       <c r="E14" t="n">
-        <v>58.55</v>
+        <v>60.08</v>
       </c>
       <c r="F14" t="n">
-        <v>0.49</v>
+        <v>1.53</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0261</v>
       </c>
       <c r="H14" t="n">
-        <v>2.54</v>
+        <v>2.22</v>
       </c>
       <c r="I14" t="n">
-        <v>53.83</v>
+        <v>54.56</v>
       </c>
       <c r="J14" t="n">
-        <v>53.96</v>
+        <v>56.1</v>
       </c>
       <c r="K14" t="n">
-        <v>56.29</v>
+        <v>57.28</v>
       </c>
       <c r="L14" t="n">
-        <v>58.61</v>
+        <v>58.46</v>
       </c>
       <c r="M14" t="n">
-        <v>59.84</v>
+        <v>59.82</v>
       </c>
       <c r="N14" t="n">
-        <v>61.06</v>
+        <v>61.18</v>
       </c>
       <c r="O14" t="n">
-        <v>64.48</v>
+        <v>62.18</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1696,13 +1686,15 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1710,84 +1702,82 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58.96</v>
+        <v>60.15</v>
       </c>
       <c r="C15" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="D15" t="n">
-        <v>58.28</v>
+        <v>57.01</v>
       </c>
       <c r="E15" t="n">
-        <v>60.08</v>
+        <v>57.44</v>
       </c>
       <c r="F15" t="n">
-        <v>1.53</v>
+        <v>-2.64</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0261</v>
+        <v>-0.0439</v>
       </c>
       <c r="H15" t="n">
-        <v>2.22</v>
+        <v>3.29</v>
       </c>
       <c r="I15" t="n">
-        <v>54.56</v>
+        <v>56.06</v>
       </c>
       <c r="J15" t="n">
-        <v>56.1</v>
+        <v>58.21</v>
       </c>
       <c r="K15" t="n">
-        <v>57.28</v>
+        <v>58.97</v>
       </c>
       <c r="L15" t="n">
-        <v>58.46</v>
+        <v>59.74</v>
       </c>
       <c r="M15" t="n">
-        <v>59.82</v>
+        <v>61.19</v>
       </c>
       <c r="N15" t="n">
-        <v>61.18</v>
+        <v>62.65</v>
       </c>
       <c r="O15" t="n">
-        <v>62.18</v>
+        <v>62.72</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+      <c r="Q15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1796,7 +1786,7 @@
       </c>
       <c r="W15" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1804,64 +1794,62 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>60.15</v>
+        <v>57.5</v>
       </c>
       <c r="C16" t="n">
-        <v>60.3</v>
+        <v>57.8</v>
       </c>
       <c r="D16" t="n">
-        <v>57.01</v>
+        <v>54.98</v>
       </c>
       <c r="E16" t="n">
-        <v>57.44</v>
+        <v>56.66</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.64</v>
+        <v>-0.78</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0439</v>
+        <v>-0.0136</v>
       </c>
       <c r="H16" t="n">
-        <v>3.29</v>
+        <v>2.82</v>
       </c>
       <c r="I16" t="n">
-        <v>56.06</v>
+        <v>53.72</v>
       </c>
       <c r="J16" t="n">
-        <v>58.21</v>
+        <v>53.54</v>
       </c>
       <c r="K16" t="n">
-        <v>58.97</v>
+        <v>55.79</v>
       </c>
       <c r="L16" t="n">
-        <v>59.74</v>
+        <v>58.05</v>
       </c>
       <c r="M16" t="n">
-        <v>61.19</v>
+        <v>59.08</v>
       </c>
       <c r="N16" t="n">
-        <v>62.65</v>
+        <v>60.12</v>
       </c>
       <c r="O16" t="n">
-        <v>62.72</v>
+        <v>63.59</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1876,7 +1864,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1886,50 +1874,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>57.5</v>
+        <v>56.63</v>
       </c>
       <c r="C17" t="n">
-        <v>57.8</v>
+        <v>58.88</v>
       </c>
       <c r="D17" t="n">
-        <v>54.98</v>
+        <v>56.6</v>
       </c>
       <c r="E17" t="n">
-        <v>56.66</v>
+        <v>56.74</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.78</v>
+        <v>0.08</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0136</v>
+        <v>0.0014</v>
       </c>
       <c r="H17" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="I17" t="n">
-        <v>53.72</v>
+        <v>52.16</v>
       </c>
       <c r="J17" t="n">
-        <v>53.54</v>
+        <v>53.98</v>
       </c>
       <c r="K17" t="n">
-        <v>55.79</v>
+        <v>55.25</v>
       </c>
       <c r="L17" t="n">
-        <v>58.05</v>
+        <v>56.52</v>
       </c>
       <c r="M17" t="n">
-        <v>59.08</v>
+        <v>58.07</v>
       </c>
       <c r="N17" t="n">
-        <v>60.12</v>
+        <v>59.61</v>
       </c>
       <c r="O17" t="n">
-        <v>63.59</v>
+        <v>60.62</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1937,18 +1925,18 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1956,60 +1944,64 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56.63</v>
+        <v>57.04</v>
       </c>
       <c r="C18" t="n">
-        <v>58.88</v>
+        <v>58.55</v>
       </c>
       <c r="D18" t="n">
         <v>56.6</v>
       </c>
       <c r="E18" t="n">
-        <v>56.74</v>
+        <v>57.32</v>
       </c>
       <c r="F18" t="n">
-        <v>0.08</v>
+        <v>0.58</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0102</v>
       </c>
       <c r="H18" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="I18" t="n">
-        <v>52.16</v>
+        <v>54.32</v>
       </c>
       <c r="J18" t="n">
-        <v>53.98</v>
+        <v>53.96</v>
       </c>
       <c r="K18" t="n">
-        <v>55.25</v>
+        <v>55.6</v>
       </c>
       <c r="L18" t="n">
-        <v>56.52</v>
+        <v>57.24</v>
       </c>
       <c r="M18" t="n">
-        <v>58.07</v>
+        <v>57.88</v>
       </c>
       <c r="N18" t="n">
-        <v>59.61</v>
+        <v>58.52</v>
       </c>
       <c r="O18" t="n">
-        <v>60.62</v>
+        <v>61.16</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2030,70 +2022,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>57.04</v>
+        <v>57.47</v>
       </c>
       <c r="C19" t="n">
-        <v>58.55</v>
+        <v>59.77</v>
       </c>
       <c r="D19" t="n">
-        <v>56.6</v>
+        <v>55.76</v>
       </c>
       <c r="E19" t="n">
-        <v>57.32</v>
+        <v>59.12</v>
       </c>
       <c r="F19" t="n">
-        <v>0.58</v>
+        <v>1.8</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0314</v>
       </c>
       <c r="H19" t="n">
-        <v>1.95</v>
+        <v>4.01</v>
       </c>
       <c r="I19" t="n">
-        <v>54.32</v>
+        <v>54.65</v>
       </c>
       <c r="J19" t="n">
-        <v>53.96</v>
+        <v>55.24</v>
       </c>
       <c r="K19" t="n">
-        <v>55.6</v>
+        <v>56.34</v>
       </c>
       <c r="L19" t="n">
-        <v>57.24</v>
+        <v>57.45</v>
       </c>
       <c r="M19" t="n">
-        <v>57.88</v>
+        <v>58.3</v>
       </c>
       <c r="N19" t="n">
-        <v>58.52</v>
+        <v>59.14</v>
       </c>
       <c r="O19" t="n">
-        <v>61.16</v>
+        <v>60.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2101,12 +2095,14 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2116,70 +2112,70 @@
       </c>
       <c r="U19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>57.47</v>
+        <v>59</v>
       </c>
       <c r="C20" t="n">
-        <v>59.77</v>
+        <v>62.36</v>
       </c>
       <c r="D20" t="n">
-        <v>55.76</v>
+        <v>58.45</v>
       </c>
       <c r="E20" t="n">
-        <v>59.12</v>
+        <v>59.44</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8</v>
+        <v>0.32</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0314</v>
+        <v>0.0054</v>
       </c>
       <c r="H20" t="n">
-        <v>4.01</v>
+        <v>3.91</v>
       </c>
       <c r="I20" t="n">
-        <v>54.65</v>
+        <v>51.75</v>
       </c>
       <c r="J20" t="n">
-        <v>55.24</v>
+        <v>55.79</v>
       </c>
       <c r="K20" t="n">
-        <v>56.34</v>
+        <v>57.11</v>
       </c>
       <c r="L20" t="n">
-        <v>57.45</v>
+        <v>58.44</v>
       </c>
       <c r="M20" t="n">
-        <v>58.3</v>
+        <v>61.12</v>
       </c>
       <c r="N20" t="n">
-        <v>59.14</v>
+        <v>63.81</v>
       </c>
       <c r="O20" t="n">
-        <v>60.5</v>
+        <v>63.78</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2187,87 +2183,83 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>59</v>
+        <v>59.01</v>
       </c>
       <c r="C21" t="n">
-        <v>62.36</v>
+        <v>61.36</v>
       </c>
       <c r="D21" t="n">
-        <v>58.45</v>
+        <v>58.7</v>
       </c>
       <c r="E21" t="n">
-        <v>59.44</v>
+        <v>61.07</v>
       </c>
       <c r="F21" t="n">
-        <v>0.32</v>
+        <v>1.63</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0274</v>
       </c>
       <c r="H21" t="n">
-        <v>3.91</v>
+        <v>2.66</v>
       </c>
       <c r="I21" t="n">
-        <v>51.75</v>
+        <v>54.54</v>
       </c>
       <c r="J21" t="n">
-        <v>55.79</v>
+        <v>55.05</v>
       </c>
       <c r="K21" t="n">
-        <v>57.11</v>
+        <v>57.48</v>
       </c>
       <c r="L21" t="n">
-        <v>58.44</v>
+        <v>59.92</v>
       </c>
       <c r="M21" t="n">
-        <v>61.12</v>
+        <v>61.39</v>
       </c>
       <c r="N21" t="n">
-        <v>63.81</v>
+        <v>62.87</v>
       </c>
       <c r="O21" t="n">
-        <v>63.78</v>
+        <v>66.27</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2280,12 +2272,12 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U21" s="8" t="n">
@@ -2294,64 +2286,64 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>59.01</v>
+        <v>61.22</v>
       </c>
       <c r="C22" t="n">
-        <v>61.36</v>
+        <v>66.48</v>
       </c>
       <c r="D22" t="n">
-        <v>58.7</v>
+        <v>60.14</v>
       </c>
       <c r="E22" t="n">
-        <v>61.07</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>1.63</v>
+        <v>4.14</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0678</v>
       </c>
       <c r="H22" t="n">
-        <v>2.66</v>
+        <v>6.34</v>
       </c>
       <c r="I22" t="n">
-        <v>54.54</v>
+        <v>56.04</v>
       </c>
       <c r="J22" t="n">
-        <v>55.05</v>
+        <v>58.93</v>
       </c>
       <c r="K22" t="n">
-        <v>57.48</v>
+        <v>59.74</v>
       </c>
       <c r="L22" t="n">
-        <v>59.92</v>
+        <v>60.55</v>
       </c>
       <c r="M22" t="n">
-        <v>61.39</v>
+        <v>62.4</v>
       </c>
       <c r="N22" t="n">
-        <v>62.87</v>
+        <v>64.25</v>
       </c>
       <c r="O22" t="n">
-        <v>66.27</v>
+        <v>64.02</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2369,73 +2361,73 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>61.22</v>
+        <v>64.72</v>
       </c>
       <c r="C23" t="n">
-        <v>66.48</v>
+        <v>65.53</v>
       </c>
       <c r="D23" t="n">
-        <v>60.14</v>
+        <v>61.12</v>
       </c>
       <c r="E23" t="n">
-        <v>65.20999999999999</v>
+        <v>63.55</v>
       </c>
       <c r="F23" t="n">
-        <v>4.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0678</v>
+        <v>-0.0255</v>
       </c>
       <c r="H23" t="n">
-        <v>6.34</v>
+        <v>4.41</v>
       </c>
       <c r="I23" t="n">
-        <v>56.04</v>
+        <v>53.8</v>
       </c>
       <c r="J23" t="n">
-        <v>58.93</v>
+        <v>59.82</v>
       </c>
       <c r="K23" t="n">
-        <v>59.74</v>
+        <v>62.04</v>
       </c>
       <c r="L23" t="n">
-        <v>60.55</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>62.4</v>
+        <v>68.38</v>
       </c>
       <c r="N23" t="n">
-        <v>64.25</v>
+        <v>72.5</v>
       </c>
       <c r="O23" t="n">
-        <v>64.02</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2443,83 +2435,83 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>64.72</v>
+        <v>62.99</v>
       </c>
       <c r="C24" t="n">
-        <v>65.53</v>
+        <v>65.83</v>
       </c>
       <c r="D24" t="n">
-        <v>61.12</v>
+        <v>62.14</v>
       </c>
       <c r="E24" t="n">
-        <v>63.55</v>
+        <v>62.89</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.66</v>
+        <v>-0.66</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0255</v>
+        <v>-0.0104</v>
       </c>
       <c r="H24" t="n">
-        <v>4.41</v>
+        <v>3.69</v>
       </c>
       <c r="I24" t="n">
-        <v>53.8</v>
+        <v>56.71</v>
       </c>
       <c r="J24" t="n">
-        <v>59.82</v>
+        <v>59.25</v>
       </c>
       <c r="K24" t="n">
-        <v>62.04</v>
+        <v>61.34</v>
       </c>
       <c r="L24" t="n">
-        <v>64.26000000000001</v>
+        <v>63.44</v>
       </c>
       <c r="M24" t="n">
-        <v>68.38</v>
+        <v>65.75</v>
       </c>
       <c r="N24" t="n">
-        <v>72.5</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>72.81999999999999</v>
+        <v>69.94</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2527,83 +2519,83 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>62.99</v>
+        <v>63.3</v>
       </c>
       <c r="C25" t="n">
-        <v>65.83</v>
+        <v>67.05</v>
       </c>
       <c r="D25" t="n">
-        <v>62.14</v>
+        <v>61.87</v>
       </c>
       <c r="E25" t="n">
-        <v>62.89</v>
+        <v>66.39</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.66</v>
+        <v>3.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0557</v>
       </c>
       <c r="H25" t="n">
-        <v>3.69</v>
+        <v>5.18</v>
       </c>
       <c r="I25" t="n">
-        <v>56.71</v>
+        <v>58.45</v>
       </c>
       <c r="J25" t="n">
-        <v>59.25</v>
+        <v>58.65</v>
       </c>
       <c r="K25" t="n">
-        <v>61.34</v>
+        <v>61.04</v>
       </c>
       <c r="L25" t="n">
         <v>63.44</v>
       </c>
       <c r="M25" t="n">
-        <v>65.75</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>68.06999999999999</v>
+        <v>66.03</v>
       </c>
       <c r="O25" t="n">
-        <v>69.94</v>
+        <v>69.52</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2614,9 +2606,9 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
@@ -2624,13 +2616,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2644,50 +2638,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>63.3</v>
+        <v>65.89</v>
       </c>
       <c r="C26" t="n">
-        <v>67.05</v>
+        <v>67.83</v>
       </c>
       <c r="D26" t="n">
-        <v>61.87</v>
+        <v>63.6</v>
       </c>
       <c r="E26" t="n">
-        <v>66.39</v>
+        <v>67.02</v>
       </c>
       <c r="F26" t="n">
-        <v>3.5</v>
+        <v>0.63</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0557</v>
+        <v>0.0095</v>
       </c>
       <c r="H26" t="n">
-        <v>5.18</v>
+        <v>4.23</v>
       </c>
       <c r="I26" t="n">
-        <v>58.45</v>
+        <v>56.69</v>
       </c>
       <c r="J26" t="n">
-        <v>58.65</v>
+        <v>62.17</v>
       </c>
       <c r="K26" t="n">
-        <v>61.04</v>
+        <v>63.8</v>
       </c>
       <c r="L26" t="n">
-        <v>63.44</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>64.73999999999999</v>
+        <v>68.98</v>
       </c>
       <c r="N26" t="n">
-        <v>66.03</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>69.52</v>
+        <v>72.23</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2695,85 +2689,79 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>65.89</v>
+        <v>75</v>
       </c>
       <c r="C27" t="n">
-        <v>67.83</v>
+        <v>92.61</v>
       </c>
       <c r="D27" t="n">
-        <v>63.6</v>
+        <v>69.2</v>
       </c>
       <c r="E27" t="n">
-        <v>67.02</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.63</v>
+        <v>23.88</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.3563</v>
       </c>
       <c r="H27" t="n">
-        <v>4.23</v>
+        <v>23.41</v>
       </c>
       <c r="I27" t="n">
-        <v>56.69</v>
+        <v>59.37</v>
       </c>
       <c r="J27" t="n">
-        <v>62.17</v>
+        <v>63.44</v>
       </c>
       <c r="K27" t="n">
-        <v>63.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>65.43000000000001</v>
+        <v>66.37</v>
       </c>
       <c r="M27" t="n">
-        <v>68.98</v>
+        <v>69.13</v>
       </c>
       <c r="N27" t="n">
-        <v>72.54000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>72.23</v>
+        <v>72.06</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2781,26 +2769,30 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2810,50 +2802,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>92.61</v>
+        <v>119.48</v>
       </c>
       <c r="D28" t="n">
-        <v>69.2</v>
+        <v>76.73</v>
       </c>
       <c r="E28" t="n">
-        <v>90.90000000000001</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>23.88</v>
+        <v>7.81</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.3563</v>
+        <v>0.0859</v>
       </c>
       <c r="H28" t="n">
-        <v>23.41</v>
+        <v>42.75</v>
       </c>
       <c r="I28" t="n">
-        <v>59.37</v>
+        <v>45.79</v>
       </c>
       <c r="J28" t="n">
-        <v>63.44</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>64.90000000000001</v>
+        <v>79.19</v>
       </c>
       <c r="L28" t="n">
-        <v>66.37</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>69.13</v>
+        <v>102.61</v>
       </c>
       <c r="N28" t="n">
-        <v>71.90000000000001</v>
+        <v>119.31</v>
       </c>
       <c r="O28" t="n">
-        <v>72.06</v>
+        <v>116.02</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2861,8 +2853,10 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
@@ -2871,20 +2865,20 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
+      <c r="V28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2894,50 +2888,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>98</v>
+        <v>100.93</v>
       </c>
       <c r="C29" t="n">
-        <v>119.48</v>
+        <v>102.44</v>
       </c>
       <c r="D29" t="n">
-        <v>76.73</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>98.70999999999999</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>7.81</v>
+        <v>-0.39</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0859</v>
+        <v>-0.004</v>
       </c>
       <c r="H29" t="n">
-        <v>42.75</v>
+        <v>10.48</v>
       </c>
       <c r="I29" t="n">
-        <v>45.79</v>
+        <v>33.98</v>
       </c>
       <c r="J29" t="n">
-        <v>72.48999999999999</v>
+        <v>56.26</v>
       </c>
       <c r="K29" t="n">
-        <v>79.19</v>
+        <v>77.33</v>
       </c>
       <c r="L29" t="n">
-        <v>85.90000000000001</v>
+        <v>98.41</v>
       </c>
       <c r="M29" t="n">
-        <v>102.61</v>
+        <v>120.08</v>
       </c>
       <c r="N29" t="n">
-        <v>119.31</v>
+        <v>141.76</v>
       </c>
       <c r="O29" t="n">
-        <v>116.02</v>
+        <v>162.23</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2945,98 +2939,98 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>100.93</v>
+        <v>100.51</v>
       </c>
       <c r="C30" t="n">
-        <v>102.44</v>
+        <v>101.67</v>
       </c>
       <c r="D30" t="n">
-        <v>91.95999999999999</v>
+        <v>84.37</v>
       </c>
       <c r="E30" t="n">
-        <v>98.31999999999999</v>
+        <v>99.64</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.39</v>
+        <v>1.32</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0134</v>
       </c>
       <c r="H30" t="n">
-        <v>10.48</v>
+        <v>17.3</v>
       </c>
       <c r="I30" t="n">
-        <v>33.98</v>
+        <v>81.48</v>
       </c>
       <c r="J30" t="n">
-        <v>56.26</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>77.33</v>
+        <v>93.08</v>
       </c>
       <c r="L30" t="n">
-        <v>98.41</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>120.08</v>
+        <v>103.56</v>
       </c>
       <c r="N30" t="n">
-        <v>141.76</v>
+        <v>109.36</v>
       </c>
       <c r="O30" t="n">
-        <v>162.23</v>
+        <v>112.92</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3048,7 +3042,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3062,71 +3056,69 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>100.51</v>
+        <v>102.6</v>
       </c>
       <c r="C31" t="n">
-        <v>101.67</v>
+        <v>113.97</v>
       </c>
       <c r="D31" t="n">
-        <v>84.37</v>
+        <v>96.5</v>
       </c>
       <c r="E31" t="n">
-        <v>99.64</v>
+        <v>111.54</v>
       </c>
       <c r="F31" t="n">
-        <v>1.32</v>
+        <v>11.9</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.1194</v>
       </c>
       <c r="H31" t="n">
-        <v>17.3</v>
+        <v>17.47</v>
       </c>
       <c r="I31" t="n">
-        <v>81.48</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>88.40000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>93.08</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>97.76000000000001</v>
+        <v>96.33</v>
       </c>
       <c r="M31" t="n">
-        <v>103.56</v>
+        <v>108.29</v>
       </c>
       <c r="N31" t="n">
-        <v>109.36</v>
+        <v>120.25</v>
       </c>
       <c r="O31" t="n">
-        <v>112.92</v>
+        <v>118.97</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3134,84 +3126,82 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>102.6</v>
+        <v>112.96</v>
       </c>
       <c r="C32" t="n">
-        <v>113.97</v>
+        <v>117.63</v>
       </c>
       <c r="D32" t="n">
-        <v>96.5</v>
+        <v>91.05</v>
       </c>
       <c r="E32" t="n">
-        <v>111.54</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>11.9</v>
+        <v>-14.97</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.1194</v>
+        <v>-0.1342</v>
       </c>
       <c r="H32" t="n">
-        <v>17.47</v>
+        <v>26.58</v>
       </c>
       <c r="I32" t="n">
-        <v>67.06999999999999</v>
+        <v>79.03</v>
       </c>
       <c r="J32" t="n">
-        <v>85.65000000000001</v>
+        <v>97.22</v>
       </c>
       <c r="K32" t="n">
-        <v>90.98999999999999</v>
+        <v>102.81</v>
       </c>
       <c r="L32" t="n">
-        <v>96.33</v>
+        <v>108.39</v>
       </c>
       <c r="M32" t="n">
-        <v>108.29</v>
+        <v>120.28</v>
       </c>
       <c r="N32" t="n">
-        <v>120.25</v>
+        <v>132.16</v>
       </c>
       <c r="O32" t="n">
-        <v>118.97</v>
+        <v>131.44</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="Q32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3220,72 +3210,74 @@
       </c>
       <c r="W32" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>112.96</v>
+        <v>102</v>
       </c>
       <c r="C33" t="n">
-        <v>117.63</v>
+        <v>105.63</v>
       </c>
       <c r="D33" t="n">
-        <v>91.05</v>
+        <v>80.56</v>
       </c>
       <c r="E33" t="n">
-        <v>96.56999999999999</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>-14.97</v>
+        <v>-12.72</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.1342</v>
+        <v>-0.1317</v>
       </c>
       <c r="H33" t="n">
-        <v>26.58</v>
+        <v>25.07</v>
       </c>
       <c r="I33" t="n">
-        <v>79.03</v>
+        <v>64.47</v>
       </c>
       <c r="J33" t="n">
-        <v>97.22</v>
+        <v>66.11</v>
       </c>
       <c r="K33" t="n">
-        <v>102.81</v>
+        <v>83.28</v>
       </c>
       <c r="L33" t="n">
-        <v>108.39</v>
+        <v>100.45</v>
       </c>
       <c r="M33" t="n">
-        <v>120.28</v>
+        <v>109.86</v>
       </c>
       <c r="N33" t="n">
-        <v>132.16</v>
+        <v>119.26</v>
       </c>
       <c r="O33" t="n">
-        <v>131.44</v>
+        <v>144.21</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -3300,64 +3292,60 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C34" t="n">
-        <v>105.63</v>
+        <v>98.39</v>
       </c>
       <c r="D34" t="n">
-        <v>80.56</v>
+        <v>87.02</v>
       </c>
       <c r="E34" t="n">
-        <v>83.84999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-12.72</v>
+        <v>10.55</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.1317</v>
+        <v>0.1258</v>
       </c>
       <c r="H34" t="n">
-        <v>25.07</v>
+        <v>11.37</v>
       </c>
       <c r="I34" t="n">
-        <v>64.47</v>
+        <v>55.49</v>
       </c>
       <c r="J34" t="n">
-        <v>66.11</v>
+        <v>54.16</v>
       </c>
       <c r="K34" t="n">
-        <v>83.28</v>
+        <v>71.31</v>
       </c>
       <c r="L34" t="n">
-        <v>100.45</v>
+        <v>88.47</v>
       </c>
       <c r="M34" t="n">
-        <v>109.86</v>
+        <v>96.38</v>
       </c>
       <c r="N34" t="n">
-        <v>119.26</v>
+        <v>104.3</v>
       </c>
       <c r="O34" t="n">
-        <v>144.21</v>
+        <v>130.7</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3365,79 +3353,83 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>89</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>98.39</v>
+        <v>110.93</v>
       </c>
       <c r="D35" t="n">
-        <v>87.02</v>
+        <v>94.59</v>
       </c>
       <c r="E35" t="n">
-        <v>94.40000000000001</v>
+        <v>101.94</v>
       </c>
       <c r="F35" t="n">
-        <v>10.55</v>
+        <v>7.54</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.1258</v>
+        <v>0.0799</v>
       </c>
       <c r="H35" t="n">
-        <v>11.37</v>
+        <v>16.34</v>
       </c>
       <c r="I35" t="n">
-        <v>55.49</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>54.16</v>
+        <v>83.88</v>
       </c>
       <c r="K35" t="n">
-        <v>71.31</v>
+        <v>88.72</v>
       </c>
       <c r="L35" t="n">
-        <v>88.47</v>
+        <v>93.55</v>
       </c>
       <c r="M35" t="n">
-        <v>96.38</v>
+        <v>100.09</v>
       </c>
       <c r="N35" t="n">
-        <v>104.3</v>
+        <v>106.62</v>
       </c>
       <c r="O35" t="n">
-        <v>130.7</v>
+        <v>109.76</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3458,70 +3450,74 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>95.59999999999999</v>
+        <v>99.73</v>
       </c>
       <c r="C36" t="n">
-        <v>110.93</v>
+        <v>107.46</v>
       </c>
       <c r="D36" t="n">
-        <v>94.59</v>
+        <v>88.66</v>
       </c>
       <c r="E36" t="n">
-        <v>101.94</v>
+        <v>95.42</v>
       </c>
       <c r="F36" t="n">
-        <v>7.54</v>
+        <v>-6.52</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0799</v>
+        <v>-0.064</v>
       </c>
       <c r="H36" t="n">
-        <v>16.34</v>
+        <v>18.8</v>
       </c>
       <c r="I36" t="n">
-        <v>75.65000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="J36" t="n">
-        <v>83.88</v>
+        <v>85.19</v>
       </c>
       <c r="K36" t="n">
-        <v>88.72</v>
+        <v>93.77</v>
       </c>
       <c r="L36" t="n">
-        <v>93.55</v>
+        <v>102.35</v>
       </c>
       <c r="M36" t="n">
-        <v>100.09</v>
+        <v>110.11</v>
       </c>
       <c r="N36" t="n">
-        <v>106.62</v>
+        <v>117.87</v>
       </c>
       <c r="O36" t="n">
-        <v>109.76</v>
+        <v>127.27</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3529,87 +3525,79 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>99.73</v>
+        <v>98.19</v>
       </c>
       <c r="C37" t="n">
-        <v>107.46</v>
+        <v>106</v>
       </c>
       <c r="D37" t="n">
-        <v>88.66</v>
+        <v>96.13</v>
       </c>
       <c r="E37" t="n">
-        <v>95.42</v>
+        <v>105.42</v>
       </c>
       <c r="F37" t="n">
-        <v>-6.52</v>
+        <v>10</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.064</v>
+        <v>0.1048</v>
       </c>
       <c r="H37" t="n">
-        <v>18.8</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>78.25</v>
+        <v>69.86</v>
       </c>
       <c r="J37" t="n">
-        <v>85.19</v>
+        <v>75.3</v>
       </c>
       <c r="K37" t="n">
-        <v>93.77</v>
+        <v>86.02</v>
       </c>
       <c r="L37" t="n">
-        <v>102.35</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>110.11</v>
+        <v>104.82</v>
       </c>
       <c r="N37" t="n">
-        <v>117.87</v>
+        <v>112.9</v>
       </c>
       <c r="O37" t="n">
-        <v>127.27</v>
+        <v>126.26</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3617,177 +3605,181 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>98.19</v>
+        <v>106</v>
       </c>
       <c r="C38" t="n">
-        <v>106</v>
+        <v>109.47</v>
       </c>
       <c r="D38" t="n">
-        <v>96.13</v>
+        <v>94.73</v>
       </c>
       <c r="E38" t="n">
-        <v>105.42</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>10</v>
+        <v>-8.82</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.1048</v>
+        <v>-0.0837</v>
       </c>
       <c r="H38" t="n">
-        <v>9.869999999999999</v>
+        <v>14.74</v>
       </c>
       <c r="I38" t="n">
-        <v>69.86</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>75.3</v>
+        <v>97.73</v>
       </c>
       <c r="K38" t="n">
-        <v>86.02</v>
+        <v>100.48</v>
       </c>
       <c r="L38" t="n">
-        <v>96.73999999999999</v>
+        <v>103.24</v>
       </c>
       <c r="M38" t="n">
-        <v>104.82</v>
+        <v>110.35</v>
       </c>
       <c r="N38" t="n">
-        <v>112.9</v>
+        <v>117.47</v>
       </c>
       <c r="O38" t="n">
-        <v>126.26</v>
+        <v>115.87</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="Q38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>106</v>
+        <v>93.88</v>
       </c>
       <c r="C39" t="n">
-        <v>109.47</v>
+        <v>94.7</v>
       </c>
       <c r="D39" t="n">
-        <v>94.73</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>96.59999999999999</v>
+        <v>87.36</v>
       </c>
       <c r="F39" t="n">
-        <v>-8.82</v>
+        <v>-9.24</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0837</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>14.74</v>
+        <v>8.35</v>
       </c>
       <c r="I39" t="n">
-        <v>86.26000000000001</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>97.73</v>
+        <v>79.11</v>
       </c>
       <c r="K39" t="n">
-        <v>100.48</v>
+        <v>89.23</v>
       </c>
       <c r="L39" t="n">
-        <v>103.24</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>110.35</v>
+        <v>103.97</v>
       </c>
       <c r="N39" t="n">
-        <v>117.47</v>
+        <v>108.59</v>
       </c>
       <c r="O39" t="n">
-        <v>115.87</v>
+        <v>124.21</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -3802,64 +3794,60 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>93.88</v>
+        <v>88.5</v>
       </c>
       <c r="C40" t="n">
-        <v>94.7</v>
+        <v>97</v>
       </c>
       <c r="D40" t="n">
-        <v>86.34999999999999</v>
+        <v>88.45</v>
       </c>
       <c r="E40" t="n">
-        <v>87.36</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>-9.24</v>
+        <v>3.18</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.0364</v>
       </c>
       <c r="H40" t="n">
-        <v>8.35</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>79.98999999999999</v>
+        <v>78</v>
       </c>
       <c r="J40" t="n">
-        <v>79.11</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>89.23</v>
+        <v>83.19</v>
       </c>
       <c r="L40" t="n">
-        <v>99.34999999999999</v>
+        <v>88.94</v>
       </c>
       <c r="M40" t="n">
-        <v>103.97</v>
+        <v>91.53</v>
       </c>
       <c r="N40" t="n">
-        <v>108.59</v>
+        <v>94.13</v>
       </c>
       <c r="O40" t="n">
-        <v>124.21</v>
+        <v>103.05</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3867,79 +3855,85 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>88.5</v>
+        <v>93</v>
       </c>
       <c r="C41" t="n">
-        <v>97</v>
+        <v>95.47</v>
       </c>
       <c r="D41" t="n">
-        <v>88.45</v>
+        <v>83.2</v>
       </c>
       <c r="E41" t="n">
-        <v>90.54000000000001</v>
+        <v>84.88</v>
       </c>
       <c r="F41" t="n">
-        <v>3.18</v>
+        <v>-5.66</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0364</v>
+        <v>-0.0625</v>
       </c>
       <c r="H41" t="n">
-        <v>8.550000000000001</v>
+        <v>12.27</v>
       </c>
       <c r="I41" t="n">
-        <v>78</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>77.43000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>83.19</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>88.94</v>
+        <v>91.63</v>
       </c>
       <c r="M41" t="n">
-        <v>91.53</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>94.13</v>
+        <v>98</v>
       </c>
       <c r="O41" t="n">
-        <v>103.05</v>
+        <v>105.55</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3947,85 +3941,81 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>93</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>95.47</v>
+        <v>82.42</v>
       </c>
       <c r="D42" t="n">
-        <v>83.2</v>
+        <v>73.58</v>
       </c>
       <c r="E42" t="n">
-        <v>84.88</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>-5.66</v>
+        <v>-7.34</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0625</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>12.27</v>
+        <v>8.84</v>
       </c>
       <c r="I42" t="n">
-        <v>79.90000000000001</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>80.90000000000001</v>
+        <v>70.38</v>
       </c>
       <c r="K42" t="n">
-        <v>86.26000000000001</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>91.63</v>
+        <v>87.11</v>
       </c>
       <c r="M42" t="n">
-        <v>94.81999999999999</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>98</v>
+        <v>94.92</v>
       </c>
       <c r="O42" t="n">
-        <v>105.55</v>
+        <v>107.74</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4043,10 +4033,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4054,7 +4042,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4064,60 +4052,62 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>81.40000000000001</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>82.42</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>73.58</v>
+        <v>68.56</v>
       </c>
       <c r="E43" t="n">
-        <v>77.54000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="F43" t="n">
-        <v>-7.34</v>
+        <v>-8.31</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.1072</v>
       </c>
       <c r="H43" t="n">
-        <v>8.84</v>
+        <v>10.4</v>
       </c>
       <c r="I43" t="n">
-        <v>70.93000000000001</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>70.38</v>
+        <v>68.47</v>
       </c>
       <c r="K43" t="n">
-        <v>78.73999999999999</v>
+        <v>73.12</v>
       </c>
       <c r="L43" t="n">
-        <v>87.11</v>
+        <v>77.77</v>
       </c>
       <c r="M43" t="n">
-        <v>91.01000000000001</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="N43" t="n">
-        <v>94.92</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>107.74</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
@@ -4134,7 +4124,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4144,67 +4134,63 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>78.93000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="C44" t="n">
-        <v>78.95999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>68.56</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>69.23</v>
+        <v>68.78</v>
       </c>
       <c r="F44" t="n">
-        <v>-8.31</v>
+        <v>-0.45</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.1072</v>
+        <v>-0.0065</v>
       </c>
       <c r="H44" t="n">
-        <v>10.4</v>
+        <v>4.56</v>
       </c>
       <c r="I44" t="n">
-        <v>64.73999999999999</v>
+        <v>58.16</v>
       </c>
       <c r="J44" t="n">
-        <v>68.47</v>
+        <v>56.57</v>
       </c>
       <c r="K44" t="n">
-        <v>73.12</v>
+        <v>64.03</v>
       </c>
       <c r="L44" t="n">
-        <v>77.77</v>
+        <v>71.5</v>
       </c>
       <c r="M44" t="n">
-        <v>81.95999999999999</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>86.15000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="O44" t="n">
-        <v>91.26000000000001</v>
+        <v>89.36</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4216,7 +4202,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4226,50 +4212,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>70.5</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>71.59999999999999</v>
+        <v>76.08</v>
       </c>
       <c r="D45" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>68.78</v>
+        <v>71.41</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.45</v>
+        <v>2.63</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0382</v>
       </c>
       <c r="H45" t="n">
-        <v>4.56</v>
+        <v>8.26</v>
       </c>
       <c r="I45" t="n">
-        <v>58.16</v>
+        <v>62.48</v>
       </c>
       <c r="J45" t="n">
-        <v>56.57</v>
+        <v>63.95</v>
       </c>
       <c r="K45" t="n">
-        <v>64.03</v>
+        <v>66.5</v>
       </c>
       <c r="L45" t="n">
-        <v>71.5</v>
+        <v>69.05</v>
       </c>
       <c r="M45" t="n">
-        <v>74.43000000000001</v>
+        <v>71.06</v>
       </c>
       <c r="N45" t="n">
-        <v>77.37</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>89.36</v>
+        <v>76.16</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4280,74 +4266,82 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>68.68000000000001</v>
+        <v>73.69</v>
       </c>
       <c r="C46" t="n">
-        <v>76.08</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>67.81999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="E46" t="n">
-        <v>71.41</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>2.63</v>
+        <v>11.08</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0382</v>
+        <v>0.1552</v>
       </c>
       <c r="H46" t="n">
-        <v>8.26</v>
+        <v>10.15</v>
       </c>
       <c r="I46" t="n">
-        <v>62.48</v>
+        <v>59.56</v>
       </c>
       <c r="J46" t="n">
-        <v>63.95</v>
+        <v>62.88</v>
       </c>
       <c r="K46" t="n">
-        <v>66.5</v>
+        <v>67.28</v>
       </c>
       <c r="L46" t="n">
-        <v>69.05</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>71.06</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>73.06999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>76.16</v>
+        <v>84.34</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4365,75 +4359,73 @@
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>73.69</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>82.76000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="D47" t="n">
-        <v>72.61</v>
+        <v>80.27</v>
       </c>
       <c r="E47" t="n">
-        <v>82.48999999999999</v>
+        <v>89.31</v>
       </c>
       <c r="F47" t="n">
-        <v>11.08</v>
+        <v>6.82</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.1552</v>
+        <v>0.0827</v>
       </c>
       <c r="H47" t="n">
-        <v>10.15</v>
+        <v>13.23</v>
       </c>
       <c r="I47" t="n">
-        <v>59.56</v>
+        <v>62.46</v>
       </c>
       <c r="J47" t="n">
-        <v>62.88</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>67.28</v>
+        <v>77.41</v>
       </c>
       <c r="L47" t="n">
-        <v>71.68000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="M47" t="n">
-        <v>75.54000000000001</v>
+        <v>87.56</v>
       </c>
       <c r="N47" t="n">
-        <v>79.40000000000001</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>84.34</v>
+        <v>92.91</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4451,20 +4443,18 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4474,50 +4464,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>83.76000000000001</v>
+        <v>86.12</v>
       </c>
       <c r="C48" t="n">
-        <v>93.5</v>
+        <v>86.87</v>
       </c>
       <c r="D48" t="n">
-        <v>80.27</v>
+        <v>77.78</v>
       </c>
       <c r="E48" t="n">
-        <v>89.31</v>
+        <v>84.67</v>
       </c>
       <c r="F48" t="n">
-        <v>6.82</v>
+        <v>-4.64</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0827</v>
+        <v>-0.052</v>
       </c>
       <c r="H48" t="n">
-        <v>13.23</v>
+        <v>9.09</v>
       </c>
       <c r="I48" t="n">
-        <v>62.46</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>74.73999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>77.41</v>
+        <v>82.69</v>
       </c>
       <c r="L48" t="n">
-        <v>80.09</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>87.56</v>
+        <v>95.92</v>
       </c>
       <c r="N48" t="n">
-        <v>95.04000000000001</v>
+        <v>103.75</v>
       </c>
       <c r="O48" t="n">
-        <v>92.91</v>
+        <v>106.73</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4525,91 +4515,95 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="V48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>86.12</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C49" t="n">
-        <v>86.87</v>
+        <v>82.33</v>
       </c>
       <c r="D49" t="n">
-        <v>77.78</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>84.67</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>-4.64</v>
+        <v>-6.49</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.0767</v>
       </c>
       <c r="H49" t="n">
-        <v>9.09</v>
+        <v>8.09</v>
       </c>
       <c r="I49" t="n">
-        <v>67.04000000000001</v>
+        <v>68.69</v>
       </c>
       <c r="J49" t="n">
-        <v>77.29000000000001</v>
+        <v>76.75</v>
       </c>
       <c r="K49" t="n">
-        <v>82.69</v>
+        <v>80.12</v>
       </c>
       <c r="L49" t="n">
-        <v>88.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="M49" t="n">
-        <v>95.92</v>
+        <v>89.22</v>
       </c>
       <c r="N49" t="n">
-        <v>103.75</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>106.73</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
@@ -4626,7 +4620,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4640,136 +4634,130 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>80.09999999999999</v>
+        <v>78.42</v>
       </c>
       <c r="C50" t="n">
-        <v>82.33</v>
+        <v>84.61</v>
       </c>
       <c r="D50" t="n">
-        <v>74.23999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>78.18000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>-6.49</v>
+        <v>4.22</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0767</v>
+        <v>0.054</v>
       </c>
       <c r="H50" t="n">
-        <v>8.09</v>
+        <v>6.82</v>
       </c>
       <c r="I50" t="n">
-        <v>68.69</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>76.75</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>80.12</v>
+        <v>74.13</v>
       </c>
       <c r="L50" t="n">
-        <v>83.5</v>
+        <v>78.23</v>
       </c>
       <c r="M50" t="n">
-        <v>89.22</v>
+        <v>82.23</v>
       </c>
       <c r="N50" t="n">
-        <v>94.93000000000001</v>
+        <v>86.22</v>
       </c>
       <c r="O50" t="n">
-        <v>95.95999999999999</v>
+        <v>90.42</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>78.42</v>
+        <v>82.53</v>
       </c>
       <c r="C51" t="n">
-        <v>84.61</v>
+        <v>89</v>
       </c>
       <c r="D51" t="n">
-        <v>77.79000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="E51" t="n">
-        <v>82.40000000000001</v>
+        <v>87.06</v>
       </c>
       <c r="F51" t="n">
-        <v>4.22</v>
+        <v>4.66</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.054</v>
+        <v>0.0566</v>
       </c>
       <c r="H51" t="n">
-        <v>6.82</v>
+        <v>7.5</v>
       </c>
       <c r="I51" t="n">
-        <v>66.15000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="J51" t="n">
-        <v>70.04000000000001</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>74.13</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>78.23</v>
+        <v>81.8</v>
       </c>
       <c r="M51" t="n">
-        <v>82.23</v>
+        <v>85.81</v>
       </c>
       <c r="N51" t="n">
-        <v>86.22</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="O51" t="n">
-        <v>90.42</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4796,7 +4784,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4806,216 +4794,218 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>82.53</v>
+        <v>86.5</v>
       </c>
       <c r="C52" t="n">
-        <v>89</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>81.5</v>
+        <v>79.62</v>
       </c>
       <c r="E52" t="n">
-        <v>87.06</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>4.66</v>
+        <v>-3.66</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0566</v>
+        <v>-0.042</v>
       </c>
       <c r="H52" t="n">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="I52" t="n">
-        <v>70.97</v>
+        <v>74</v>
       </c>
       <c r="J52" t="n">
-        <v>76.18000000000001</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>78.98999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="L52" t="n">
-        <v>81.8</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="M52" t="n">
-        <v>85.81</v>
+        <v>90.81</v>
       </c>
       <c r="N52" t="n">
-        <v>89.81999999999999</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="O52" t="n">
-        <v>91.43000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>86.5</v>
+        <v>84.69</v>
       </c>
       <c r="C53" t="n">
-        <v>86.56999999999999</v>
+        <v>93.14</v>
       </c>
       <c r="D53" t="n">
-        <v>79.62</v>
+        <v>84.11</v>
       </c>
       <c r="E53" t="n">
-        <v>83.40000000000001</v>
+        <v>91.48</v>
       </c>
       <c r="F53" t="n">
-        <v>-3.66</v>
+        <v>8.08</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.042</v>
+        <v>0.0969</v>
       </c>
       <c r="H53" t="n">
-        <v>6.95</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>74</v>
+        <v>72.67</v>
       </c>
       <c r="J53" t="n">
-        <v>80.45999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>83.31</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>86.15000000000001</v>
+        <v>83.25</v>
       </c>
       <c r="M53" t="n">
-        <v>90.81</v>
+        <v>86.88</v>
       </c>
       <c r="N53" t="n">
-        <v>95.45999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="O53" t="n">
-        <v>96.5</v>
+        <v>93.52</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="U53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>84.69</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C54" t="n">
-        <v>93.14</v>
+        <v>104.46</v>
       </c>
       <c r="D54" t="n">
-        <v>84.11</v>
+        <v>90.87</v>
       </c>
       <c r="E54" t="n">
-        <v>91.48</v>
+        <v>100.05</v>
       </c>
       <c r="F54" t="n">
-        <v>8.08</v>
+        <v>8.57</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0969</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>9.029999999999999</v>
+        <v>13.59</v>
       </c>
       <c r="I54" t="n">
-        <v>72.67</v>
+        <v>75.08</v>
       </c>
       <c r="J54" t="n">
-        <v>76.59999999999999</v>
+        <v>83.88</v>
       </c>
       <c r="K54" t="n">
-        <v>79.93000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="L54" t="n">
-        <v>83.25</v>
+        <v>90.05</v>
       </c>
       <c r="M54" t="n">
-        <v>86.88</v>
+        <v>96</v>
       </c>
       <c r="N54" t="n">
-        <v>90.5</v>
+        <v>101.94</v>
       </c>
       <c r="O54" t="n">
-        <v>93.52</v>
+        <v>102.17</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5041,10 +5031,12 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5054,50 +5046,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>92.26000000000001</v>
+        <v>102.25</v>
       </c>
       <c r="C55" t="n">
-        <v>104.46</v>
+        <v>106.75</v>
       </c>
       <c r="D55" t="n">
-        <v>90.87</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>100.05</v>
+        <v>100.3</v>
       </c>
       <c r="F55" t="n">
-        <v>8.57</v>
+        <v>0.25</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="H55" t="n">
-        <v>13.59</v>
+        <v>7.65</v>
       </c>
       <c r="I55" t="n">
-        <v>75.08</v>
+        <v>77.28</v>
       </c>
       <c r="J55" t="n">
-        <v>83.88</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="K55" t="n">
-        <v>86.97</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>90.05</v>
+        <v>98.86</v>
       </c>
       <c r="M55" t="n">
-        <v>96</v>
+        <v>106.85</v>
       </c>
       <c r="N55" t="n">
-        <v>101.94</v>
+        <v>114.83</v>
       </c>
       <c r="O55" t="n">
-        <v>102.17</v>
+        <v>118.05</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5110,25 +5102,19 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5138,63 +5124,69 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>102.25</v>
+        <v>101</v>
       </c>
       <c r="C56" t="n">
-        <v>106.75</v>
+        <v>101.08</v>
       </c>
       <c r="D56" t="n">
-        <v>99.09999999999999</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>100.3</v>
+        <v>92.41</v>
       </c>
       <c r="F56" t="n">
-        <v>0.25</v>
+        <v>-7.89</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>7.65</v>
+        <v>12.37</v>
       </c>
       <c r="I56" t="n">
-        <v>77.28</v>
+        <v>91.45</v>
       </c>
       <c r="J56" t="n">
-        <v>87.65000000000001</v>
+        <v>91.34</v>
       </c>
       <c r="K56" t="n">
-        <v>93.26000000000001</v>
+        <v>96.48</v>
       </c>
       <c r="L56" t="n">
-        <v>98.86</v>
+        <v>101.61</v>
       </c>
       <c r="M56" t="n">
-        <v>106.85</v>
+        <v>104.13</v>
       </c>
       <c r="N56" t="n">
-        <v>114.83</v>
+        <v>106.64</v>
       </c>
       <c r="O56" t="n">
-        <v>118.05</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>114.4</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5206,79 +5198,77 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>101</v>
+        <v>93.58</v>
       </c>
       <c r="C57" t="n">
-        <v>101.08</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>88.70999999999999</v>
+        <v>88.06</v>
       </c>
       <c r="E57" t="n">
-        <v>92.41</v>
+        <v>91.11</v>
       </c>
       <c r="F57" t="n">
-        <v>-7.89</v>
+        <v>-1.3</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0141</v>
       </c>
       <c r="H57" t="n">
-        <v>12.37</v>
+        <v>8.48</v>
       </c>
       <c r="I57" t="n">
-        <v>91.45</v>
+        <v>76.34</v>
       </c>
       <c r="J57" t="n">
-        <v>91.34</v>
+        <v>78.8</v>
       </c>
       <c r="K57" t="n">
-        <v>96.48</v>
+        <v>86.23</v>
       </c>
       <c r="L57" t="n">
-        <v>101.61</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>104.13</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>106.64</v>
+        <v>103.54</v>
       </c>
       <c r="O57" t="n">
-        <v>114.4</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>113.45</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5290,7 +5280,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5298,88 +5288,6 @@
       <c r="X57" t="inlineStr">
         <is>
           <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>93.58</v>
-      </c>
-      <c r="C58" t="n">
-        <v>96.54000000000001</v>
-      </c>
-      <c r="D58" t="n">
-        <v>88.58</v>
-      </c>
-      <c r="E58" t="n">
-        <v>93.15000000000001</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="H58" t="n">
-        <v>7.96</v>
-      </c>
-      <c r="I58" t="n">
-        <v>76.34</v>
-      </c>
-      <c r="J58" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="K58" t="n">
-        <v>86.23</v>
-      </c>
-      <c r="L58" t="n">
-        <v>93.65000000000001</v>
-      </c>
-      <c r="M58" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="N58" t="n">
-        <v>103.54</v>
-      </c>
-      <c r="O58" t="n">
-        <v>113.45</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5291,6 +5291,90 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>89.27</v>
+      </c>
+      <c r="C58" t="n">
+        <v>89.36</v>
+      </c>
+      <c r="D58" t="n">
+        <v>89.22</v>
+      </c>
+      <c r="E58" t="n">
+        <v>89.23999999999999</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0205</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I58" t="n">
+        <v>79.58</v>
+      </c>
+      <c r="J58" t="n">
+        <v>82.03</v>
+      </c>
+      <c r="K58" t="n">
+        <v>86.87</v>
+      </c>
+      <c r="L58" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="M58" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="N58" t="n">
+        <v>99</v>
+      </c>
+      <c r="O58" t="n">
+        <v>105.02</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>2.39</v>
       </c>
       <c r="I2" t="n">
-        <v>56.87</v>
+        <v>57.18</v>
       </c>
       <c r="J2" t="n">
-        <v>56.36</v>
+        <v>56.74</v>
       </c>
       <c r="K2" t="n">
-        <v>59.58</v>
+        <v>59.73</v>
       </c>
       <c r="L2" t="n">
-        <v>62.8</v>
+        <v>62.73</v>
       </c>
       <c r="M2" t="n">
-        <v>64.16</v>
+        <v>64</v>
       </c>
       <c r="N2" t="n">
-        <v>65.51000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="O2" t="n">
-        <v>70.61</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -693,8 +693,10 @@
           <t>↓C</t>
         </is>
       </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -5298,25 +5300,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>89.27</v>
+        <v>91.77</v>
       </c>
       <c r="C58" t="n">
-        <v>89.36</v>
+        <v>91.88</v>
       </c>
       <c r="D58" t="n">
-        <v>89.22</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>89.23999999999999</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.87</v>
+        <v>-0.68</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0205</v>
+        <v>-0.0075</v>
       </c>
       <c r="H58" t="n">
-        <v>0.14</v>
+        <v>3.14</v>
       </c>
       <c r="I58" t="n">
         <v>79.58</v>
@@ -5345,14 +5347,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -659,25 +659,25 @@
         <v>2.39</v>
       </c>
       <c r="I2" t="n">
-        <v>57.18</v>
+        <v>59.06</v>
       </c>
       <c r="J2" t="n">
-        <v>56.74</v>
+        <v>59.09</v>
       </c>
       <c r="K2" t="n">
-        <v>59.73</v>
+        <v>60.67</v>
       </c>
       <c r="L2" t="n">
-        <v>62.73</v>
+        <v>62.26</v>
       </c>
       <c r="M2" t="n">
-        <v>64</v>
+        <v>63.06</v>
       </c>
       <c r="N2" t="n">
-        <v>65.28</v>
+        <v>63.87</v>
       </c>
       <c r="O2" t="n">
-        <v>69.98999999999999</v>
+        <v>66.23</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,17 +690,19 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
@@ -709,11 +711,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -772,7 +770,7 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="7" t="inlineStr">
+      <c r="S3" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -856,7 +854,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -946,7 +944,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1026,7 +1024,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1106,7 +1104,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1184,7 +1182,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1270,7 +1268,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1354,7 +1352,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1438,7 +1436,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1524,7 +1522,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1606,7 +1604,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1688,7 +1686,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1772,7 +1770,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1852,7 +1850,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1930,7 +1928,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2014,7 +2012,7 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2102,7 +2100,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2188,7 +2186,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2272,7 +2270,7 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2356,7 +2354,7 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2442,7 +2440,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2524,7 +2522,7 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2608,7 +2606,7 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2696,7 +2694,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2774,7 +2772,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2860,7 +2858,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2944,7 +2942,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3030,7 +3028,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3112,7 +3110,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3196,7 +3194,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3280,7 +3278,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3358,7 +3356,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3442,7 +3440,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3532,7 +3530,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3610,7 +3608,7 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3698,7 +3696,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3782,7 +3780,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3860,7 +3858,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3948,7 +3946,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4030,7 +4028,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4112,7 +4110,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4190,7 +4188,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4268,7 +4266,7 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4354,7 +4352,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4438,7 +4436,7 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4522,7 +4520,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4608,7 +4606,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4690,7 +4688,7 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4770,7 +4768,7 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4854,7 +4852,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4936,7 +4934,7 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5018,7 +5016,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5102,7 +5100,7 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -5186,7 +5184,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5268,7 +5266,7 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5306,19 +5304,19 @@
         <v>91.88</v>
       </c>
       <c r="D58" t="n">
-        <v>88.73999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="E58" t="n">
-        <v>90.43000000000001</v>
+        <v>89</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.68</v>
+        <v>-2.11</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0075</v>
+        <v>-0.0232</v>
       </c>
       <c r="H58" t="n">
-        <v>3.14</v>
+        <v>5.02</v>
       </c>
       <c r="I58" t="n">
         <v>79.58</v>
@@ -5347,12 +5345,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5307,13 +5307,13 @@
         <v>86.86</v>
       </c>
       <c r="E58" t="n">
-        <v>89</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.11</v>
+        <v>-1.82</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0232</v>
+        <v>-0.02</v>
       </c>
       <c r="H58" t="n">
         <v>5.02</v>
@@ -5347,12 +5347,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>2.39</v>
       </c>
       <c r="I2" t="n">
-        <v>59.06</v>
+        <v>59.41</v>
       </c>
       <c r="J2" t="n">
-        <v>59.09</v>
+        <v>59.53</v>
       </c>
       <c r="K2" t="n">
-        <v>60.67</v>
+        <v>60.85</v>
       </c>
       <c r="L2" t="n">
-        <v>62.26</v>
+        <v>62.17</v>
       </c>
       <c r="M2" t="n">
-        <v>63.06</v>
+        <v>62.89</v>
       </c>
       <c r="N2" t="n">
-        <v>63.87</v>
+        <v>63.61</v>
       </c>
       <c r="O2" t="n">
-        <v>66.23</v>
+        <v>65.53</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5307,13 +5307,13 @@
         <v>86.86</v>
       </c>
       <c r="E58" t="n">
-        <v>89.29000000000001</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.82</v>
+        <v>-0.32</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.02</v>
+        <v>-0.0035</v>
       </c>
       <c r="H58" t="n">
         <v>5.02</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62</v>
+        <v>62.97</v>
       </c>
       <c r="C2" t="n">
-        <v>64.08</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>61.69</v>
+        <v>62.52</v>
       </c>
       <c r="E2" t="n">
-        <v>62.69</v>
+        <v>62.68</v>
       </c>
       <c r="F2" t="n">
-        <v>0.82</v>
+        <v>-0.01</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0133</v>
+        <v>-0.0002</v>
       </c>
       <c r="H2" t="n">
-        <v>2.39</v>
+        <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>59.41</v>
+        <v>59.3</v>
       </c>
       <c r="J2" t="n">
-        <v>59.53</v>
+        <v>60.2</v>
       </c>
       <c r="K2" t="n">
-        <v>60.85</v>
+        <v>61.49</v>
       </c>
       <c r="L2" t="n">
-        <v>62.17</v>
+        <v>62.79</v>
       </c>
       <c r="M2" t="n">
-        <v>62.89</v>
+        <v>63.89</v>
       </c>
       <c r="N2" t="n">
-        <v>63.61</v>
+        <v>64.98</v>
       </c>
       <c r="O2" t="n">
-        <v>65.53</v>
+        <v>66.47</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,19 +690,17 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
@@ -711,55 +709,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62.97</v>
+        <v>62.74</v>
       </c>
       <c r="C3" t="n">
-        <v>64.76000000000001</v>
+        <v>66.42</v>
       </c>
       <c r="D3" t="n">
-        <v>62.52</v>
+        <v>61.85</v>
       </c>
       <c r="E3" t="n">
-        <v>62.68</v>
+        <v>65.72</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.01</v>
+        <v>3.04</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0485</v>
       </c>
       <c r="H3" t="n">
-        <v>2.24</v>
+        <v>4.57</v>
       </c>
       <c r="I3" t="n">
-        <v>59.3</v>
+        <v>60.28</v>
       </c>
       <c r="J3" t="n">
-        <v>60.2</v>
+        <v>59.96</v>
       </c>
       <c r="K3" t="n">
-        <v>61.49</v>
+        <v>61.56</v>
       </c>
       <c r="L3" t="n">
-        <v>62.79</v>
+        <v>63.16</v>
       </c>
       <c r="M3" t="n">
-        <v>63.89</v>
+        <v>63.8</v>
       </c>
       <c r="N3" t="n">
-        <v>64.98</v>
+        <v>64.44</v>
       </c>
       <c r="O3" t="n">
-        <v>66.47</v>
+        <v>67</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,7 +774,7 @@
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
@@ -780,8 +782,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="n">
-        <v/>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -800,151 +804,145 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62.74</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>66.42</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>61.85</v>
+        <v>60.4</v>
       </c>
       <c r="E4" t="n">
-        <v>65.72</v>
+        <v>60.88</v>
       </c>
       <c r="F4" t="n">
-        <v>3.04</v>
+        <v>-4.84</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0485</v>
+        <v>-0.0736</v>
       </c>
       <c r="H4" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>60.28</v>
+        <v>57.28</v>
       </c>
       <c r="J4" t="n">
-        <v>59.96</v>
+        <v>61.94</v>
       </c>
       <c r="K4" t="n">
-        <v>61.56</v>
+        <v>63.44</v>
       </c>
       <c r="L4" t="n">
-        <v>63.16</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>63.8</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>64.44</v>
+        <v>71.08</v>
       </c>
       <c r="O4" t="n">
-        <v>67</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.06999999999999</v>
+        <v>61.14</v>
       </c>
       <c r="C5" t="n">
-        <v>65.40000000000001</v>
+        <v>62.92</v>
       </c>
       <c r="D5" t="n">
-        <v>60.4</v>
+        <v>58.22</v>
       </c>
       <c r="E5" t="n">
-        <v>60.88</v>
+        <v>58.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.84</v>
+        <v>-1.98</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0736</v>
+        <v>-0.0325</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
-        <v>57.28</v>
+        <v>55.4</v>
       </c>
       <c r="J5" t="n">
-        <v>61.94</v>
+        <v>54.87</v>
       </c>
       <c r="K5" t="n">
-        <v>63.44</v>
+        <v>58.38</v>
       </c>
       <c r="L5" t="n">
-        <v>64.93000000000001</v>
+        <v>61.89</v>
       </c>
       <c r="M5" t="n">
-        <v>68.01000000000001</v>
+        <v>63.38</v>
       </c>
       <c r="N5" t="n">
-        <v>71.08</v>
+        <v>64.87</v>
       </c>
       <c r="O5" t="n">
-        <v>70.98999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -968,50 +966,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.14</v>
+        <v>59</v>
       </c>
       <c r="C6" t="n">
-        <v>62.92</v>
+        <v>60.17</v>
       </c>
       <c r="D6" t="n">
-        <v>58.22</v>
+        <v>56.6</v>
       </c>
       <c r="E6" t="n">
-        <v>58.9</v>
+        <v>57.54</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.98</v>
+        <v>-1.36</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0325</v>
+        <v>-0.0231</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7</v>
+        <v>3.57</v>
       </c>
       <c r="I6" t="n">
-        <v>55.4</v>
+        <v>53.52</v>
       </c>
       <c r="J6" t="n">
-        <v>54.87</v>
+        <v>53.37</v>
       </c>
       <c r="K6" t="n">
-        <v>58.38</v>
+        <v>56.55</v>
       </c>
       <c r="L6" t="n">
-        <v>61.89</v>
+        <v>59.74</v>
       </c>
       <c r="M6" t="n">
-        <v>63.38</v>
+        <v>61.25</v>
       </c>
       <c r="N6" t="n">
-        <v>64.87</v>
+        <v>62.76</v>
       </c>
       <c r="O6" t="n">
-        <v>70.40000000000001</v>
+        <v>67.62</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1024,7 +1022,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1048,50 +1046,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59</v>
+        <v>57.73</v>
       </c>
       <c r="C7" t="n">
-        <v>60.17</v>
+        <v>62.59</v>
       </c>
       <c r="D7" t="n">
-        <v>56.6</v>
+        <v>56.35</v>
       </c>
       <c r="E7" t="n">
-        <v>57.54</v>
+        <v>61.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.36</v>
+        <v>3.96</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0231</v>
+        <v>0.0688</v>
       </c>
       <c r="H7" t="n">
-        <v>3.57</v>
+        <v>6.24</v>
       </c>
       <c r="I7" t="n">
-        <v>53.52</v>
+        <v>53.03</v>
       </c>
       <c r="J7" t="n">
-        <v>53.37</v>
+        <v>53.55</v>
       </c>
       <c r="K7" t="n">
-        <v>56.55</v>
+        <v>55.76</v>
       </c>
       <c r="L7" t="n">
-        <v>59.74</v>
+        <v>57.96</v>
       </c>
       <c r="M7" t="n">
-        <v>61.25</v>
+        <v>59.33</v>
       </c>
       <c r="N7" t="n">
-        <v>62.76</v>
+        <v>60.69</v>
       </c>
       <c r="O7" t="n">
-        <v>67.62</v>
+        <v>63.74</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1099,79 +1097,85 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="W7" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57.73</v>
+        <v>61.82</v>
       </c>
       <c r="C8" t="n">
-        <v>62.59</v>
+        <v>62.17</v>
       </c>
       <c r="D8" t="n">
-        <v>56.35</v>
+        <v>59.64</v>
       </c>
       <c r="E8" t="n">
-        <v>61.5</v>
+        <v>60.98</v>
       </c>
       <c r="F8" t="n">
-        <v>3.96</v>
+        <v>-0.52</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0688</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>6.24</v>
+        <v>2.53</v>
       </c>
       <c r="I8" t="n">
-        <v>53.03</v>
+        <v>50.11</v>
       </c>
       <c r="J8" t="n">
-        <v>53.55</v>
+        <v>56.27</v>
       </c>
       <c r="K8" t="n">
-        <v>55.76</v>
+        <v>58.38</v>
       </c>
       <c r="L8" t="n">
-        <v>57.96</v>
+        <v>60.48</v>
       </c>
       <c r="M8" t="n">
-        <v>59.33</v>
+        <v>64.62</v>
       </c>
       <c r="N8" t="n">
-        <v>60.69</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>63.74</v>
+        <v>68.83</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1182,20 +1186,16 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1207,57 +1207,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61.82</v>
+        <v>61.4</v>
       </c>
       <c r="C9" t="n">
-        <v>62.17</v>
+        <v>61.5</v>
       </c>
       <c r="D9" t="n">
-        <v>59.64</v>
+        <v>58.83</v>
       </c>
       <c r="E9" t="n">
-        <v>60.98</v>
+        <v>59.75</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.52</v>
+        <v>-1.23</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0202</v>
       </c>
       <c r="H9" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="I9" t="n">
-        <v>50.11</v>
+        <v>57.11</v>
       </c>
       <c r="J9" t="n">
-        <v>56.27</v>
+        <v>58.49</v>
       </c>
       <c r="K9" t="n">
-        <v>58.38</v>
+        <v>59.72</v>
       </c>
       <c r="L9" t="n">
-        <v>60.48</v>
+        <v>60.94</v>
       </c>
       <c r="M9" t="n">
-        <v>64.62</v>
+        <v>62.24</v>
       </c>
       <c r="N9" t="n">
-        <v>68.76000000000001</v>
+        <v>63.55</v>
       </c>
       <c r="O9" t="n">
-        <v>68.83</v>
+        <v>64.7</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1265,12 +1265,14 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1289,57 +1291,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>61.4</v>
+        <v>59.87</v>
       </c>
       <c r="C10" t="n">
-        <v>61.5</v>
+        <v>61.28</v>
       </c>
       <c r="D10" t="n">
-        <v>58.83</v>
+        <v>58.12</v>
       </c>
       <c r="E10" t="n">
-        <v>59.75</v>
+        <v>60.09</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.23</v>
+        <v>0.34</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0202</v>
+        <v>0.0057</v>
       </c>
       <c r="H10" t="n">
-        <v>2.67</v>
+        <v>3.16</v>
       </c>
       <c r="I10" t="n">
-        <v>57.11</v>
+        <v>56.16</v>
       </c>
       <c r="J10" t="n">
-        <v>58.49</v>
+        <v>56.87</v>
       </c>
       <c r="K10" t="n">
-        <v>59.72</v>
+        <v>58.42</v>
       </c>
       <c r="L10" t="n">
-        <v>60.94</v>
+        <v>59.96</v>
       </c>
       <c r="M10" t="n">
-        <v>62.24</v>
+        <v>61.08</v>
       </c>
       <c r="N10" t="n">
-        <v>63.55</v>
+        <v>62.21</v>
       </c>
       <c r="O10" t="n">
-        <v>64.7</v>
+        <v>64.17</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1349,16 +1351,18 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1373,57 +1377,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59.87</v>
+        <v>59.8</v>
       </c>
       <c r="C11" t="n">
-        <v>61.28</v>
+        <v>60.93</v>
       </c>
       <c r="D11" t="n">
-        <v>58.12</v>
+        <v>57.38</v>
       </c>
       <c r="E11" t="n">
-        <v>60.09</v>
+        <v>58.06</v>
       </c>
       <c r="F11" t="n">
-        <v>0.34</v>
+        <v>-2.03</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.0338</v>
       </c>
       <c r="H11" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="I11" t="n">
-        <v>56.16</v>
+        <v>54.96</v>
       </c>
       <c r="J11" t="n">
-        <v>56.87</v>
+        <v>57.13</v>
       </c>
       <c r="K11" t="n">
-        <v>58.42</v>
+        <v>58.51</v>
       </c>
       <c r="L11" t="n">
-        <v>59.96</v>
+        <v>59.89</v>
       </c>
       <c r="M11" t="n">
-        <v>61.08</v>
+        <v>61.67</v>
       </c>
       <c r="N11" t="n">
-        <v>62.21</v>
+        <v>63.45</v>
       </c>
       <c r="O11" t="n">
-        <v>64.17</v>
+        <v>64.44</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1433,18 +1437,16 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1459,57 +1461,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59.8</v>
+        <v>58.05</v>
       </c>
       <c r="C12" t="n">
-        <v>60.93</v>
+        <v>59.64</v>
       </c>
       <c r="D12" t="n">
-        <v>57.38</v>
+        <v>57.1</v>
       </c>
       <c r="E12" t="n">
-        <v>58.06</v>
+        <v>58.55</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.03</v>
+        <v>0.49</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>3.55</v>
+        <v>2.54</v>
       </c>
       <c r="I12" t="n">
-        <v>54.96</v>
+        <v>53.83</v>
       </c>
       <c r="J12" t="n">
-        <v>57.13</v>
+        <v>53.96</v>
       </c>
       <c r="K12" t="n">
-        <v>58.51</v>
+        <v>56.29</v>
       </c>
       <c r="L12" t="n">
-        <v>59.89</v>
+        <v>58.61</v>
       </c>
       <c r="M12" t="n">
-        <v>61.67</v>
+        <v>59.84</v>
       </c>
       <c r="N12" t="n">
-        <v>63.45</v>
+        <v>61.06</v>
       </c>
       <c r="O12" t="n">
-        <v>64.44</v>
+        <v>64.48</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1517,14 +1519,12 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1543,57 +1543,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>58.05</v>
+        <v>58.96</v>
       </c>
       <c r="C13" t="n">
-        <v>59.64</v>
+        <v>60.5</v>
       </c>
       <c r="D13" t="n">
-        <v>57.1</v>
+        <v>58.28</v>
       </c>
       <c r="E13" t="n">
-        <v>58.55</v>
+        <v>60.08</v>
       </c>
       <c r="F13" t="n">
-        <v>0.49</v>
+        <v>1.53</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0261</v>
       </c>
       <c r="H13" t="n">
-        <v>2.54</v>
+        <v>2.22</v>
       </c>
       <c r="I13" t="n">
-        <v>53.83</v>
+        <v>54.56</v>
       </c>
       <c r="J13" t="n">
-        <v>53.96</v>
+        <v>56.1</v>
       </c>
       <c r="K13" t="n">
-        <v>56.29</v>
+        <v>57.28</v>
       </c>
       <c r="L13" t="n">
-        <v>58.61</v>
+        <v>58.46</v>
       </c>
       <c r="M13" t="n">
-        <v>59.84</v>
+        <v>59.82</v>
       </c>
       <c r="N13" t="n">
-        <v>61.06</v>
+        <v>61.18</v>
       </c>
       <c r="O13" t="n">
-        <v>64.48</v>
+        <v>62.18</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1606,11 +1606,13 @@
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1623,78 +1625,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>58.96</v>
+        <v>60.15</v>
       </c>
       <c r="C14" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="D14" t="n">
-        <v>58.28</v>
+        <v>57.01</v>
       </c>
       <c r="E14" t="n">
-        <v>60.08</v>
+        <v>57.44</v>
       </c>
       <c r="F14" t="n">
-        <v>1.53</v>
+        <v>-2.64</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0261</v>
+        <v>-0.0439</v>
       </c>
       <c r="H14" t="n">
-        <v>2.22</v>
+        <v>3.29</v>
       </c>
       <c r="I14" t="n">
-        <v>54.56</v>
+        <v>56.06</v>
       </c>
       <c r="J14" t="n">
-        <v>56.1</v>
+        <v>58.21</v>
       </c>
       <c r="K14" t="n">
-        <v>57.28</v>
+        <v>58.97</v>
       </c>
       <c r="L14" t="n">
-        <v>58.46</v>
+        <v>59.74</v>
       </c>
       <c r="M14" t="n">
-        <v>59.82</v>
+        <v>61.19</v>
       </c>
       <c r="N14" t="n">
-        <v>61.18</v>
+        <v>62.65</v>
       </c>
       <c r="O14" t="n">
-        <v>62.18</v>
+        <v>62.72</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1702,9 +1702,9 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1712,65 +1712,63 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>60.15</v>
+        <v>57.5</v>
       </c>
       <c r="C15" t="n">
-        <v>60.3</v>
+        <v>57.8</v>
       </c>
       <c r="D15" t="n">
-        <v>57.01</v>
+        <v>54.98</v>
       </c>
       <c r="E15" t="n">
-        <v>57.44</v>
+        <v>56.66</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.64</v>
+        <v>-0.78</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0439</v>
+        <v>-0.0136</v>
       </c>
       <c r="H15" t="n">
-        <v>3.29</v>
+        <v>2.82</v>
       </c>
       <c r="I15" t="n">
-        <v>56.06</v>
+        <v>53.72</v>
       </c>
       <c r="J15" t="n">
-        <v>58.21</v>
+        <v>53.54</v>
       </c>
       <c r="K15" t="n">
-        <v>58.97</v>
+        <v>55.79</v>
       </c>
       <c r="L15" t="n">
-        <v>59.74</v>
+        <v>58.05</v>
       </c>
       <c r="M15" t="n">
-        <v>61.19</v>
+        <v>59.08</v>
       </c>
       <c r="N15" t="n">
-        <v>62.65</v>
+        <v>60.12</v>
       </c>
       <c r="O15" t="n">
-        <v>62.72</v>
+        <v>63.59</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1794,50 +1792,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>57.5</v>
+        <v>56.63</v>
       </c>
       <c r="C16" t="n">
-        <v>57.8</v>
+        <v>58.88</v>
       </c>
       <c r="D16" t="n">
-        <v>54.98</v>
+        <v>56.6</v>
       </c>
       <c r="E16" t="n">
-        <v>56.66</v>
+        <v>56.74</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.78</v>
+        <v>0.08</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0136</v>
+        <v>0.0014</v>
       </c>
       <c r="H16" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="I16" t="n">
-        <v>53.72</v>
+        <v>52.16</v>
       </c>
       <c r="J16" t="n">
-        <v>53.54</v>
+        <v>53.98</v>
       </c>
       <c r="K16" t="n">
-        <v>55.79</v>
+        <v>55.25</v>
       </c>
       <c r="L16" t="n">
-        <v>58.05</v>
+        <v>56.52</v>
       </c>
       <c r="M16" t="n">
-        <v>59.08</v>
+        <v>58.07</v>
       </c>
       <c r="N16" t="n">
-        <v>60.12</v>
+        <v>59.61</v>
       </c>
       <c r="O16" t="n">
-        <v>63.59</v>
+        <v>60.62</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1845,18 +1843,18 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1869,55 +1867,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>56.63</v>
+        <v>57.04</v>
       </c>
       <c r="C17" t="n">
-        <v>58.88</v>
+        <v>58.55</v>
       </c>
       <c r="D17" t="n">
         <v>56.6</v>
       </c>
       <c r="E17" t="n">
-        <v>56.74</v>
+        <v>57.32</v>
       </c>
       <c r="F17" t="n">
-        <v>0.08</v>
+        <v>0.58</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0102</v>
       </c>
       <c r="H17" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="I17" t="n">
-        <v>52.16</v>
+        <v>54.32</v>
       </c>
       <c r="J17" t="n">
-        <v>53.98</v>
+        <v>53.96</v>
       </c>
       <c r="K17" t="n">
-        <v>55.25</v>
+        <v>55.6</v>
       </c>
       <c r="L17" t="n">
-        <v>56.52</v>
+        <v>57.24</v>
       </c>
       <c r="M17" t="n">
-        <v>58.07</v>
+        <v>57.88</v>
       </c>
       <c r="N17" t="n">
-        <v>59.61</v>
+        <v>58.52</v>
       </c>
       <c r="O17" t="n">
-        <v>60.62</v>
+        <v>61.16</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1928,7 +1930,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1938,8 +1940,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1951,57 +1955,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57.04</v>
+        <v>57.47</v>
       </c>
       <c r="C18" t="n">
-        <v>58.55</v>
+        <v>59.77</v>
       </c>
       <c r="D18" t="n">
-        <v>56.6</v>
+        <v>55.76</v>
       </c>
       <c r="E18" t="n">
-        <v>57.32</v>
+        <v>59.12</v>
       </c>
       <c r="F18" t="n">
-        <v>0.58</v>
+        <v>1.8</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0314</v>
       </c>
       <c r="H18" t="n">
-        <v>1.95</v>
+        <v>4.01</v>
       </c>
       <c r="I18" t="n">
-        <v>54.32</v>
+        <v>54.65</v>
       </c>
       <c r="J18" t="n">
-        <v>53.96</v>
+        <v>55.24</v>
       </c>
       <c r="K18" t="n">
-        <v>55.6</v>
+        <v>56.34</v>
       </c>
       <c r="L18" t="n">
-        <v>57.24</v>
+        <v>57.45</v>
       </c>
       <c r="M18" t="n">
-        <v>57.88</v>
+        <v>58.3</v>
       </c>
       <c r="N18" t="n">
-        <v>58.52</v>
+        <v>59.14</v>
       </c>
       <c r="O18" t="n">
-        <v>61.16</v>
+        <v>60.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2009,12 +2013,14 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2024,7 +2030,7 @@
       </c>
       <c r="U18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V18" s="8" t="n">
@@ -2037,57 +2043,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>57.47</v>
+        <v>59</v>
       </c>
       <c r="C19" t="n">
-        <v>59.77</v>
+        <v>62.36</v>
       </c>
       <c r="D19" t="n">
-        <v>55.76</v>
+        <v>58.45</v>
       </c>
       <c r="E19" t="n">
-        <v>59.12</v>
+        <v>59.44</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8</v>
+        <v>0.32</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0314</v>
+        <v>0.0054</v>
       </c>
       <c r="H19" t="n">
-        <v>4.01</v>
+        <v>3.91</v>
       </c>
       <c r="I19" t="n">
-        <v>54.65</v>
+        <v>51.75</v>
       </c>
       <c r="J19" t="n">
-        <v>55.24</v>
+        <v>55.79</v>
       </c>
       <c r="K19" t="n">
-        <v>56.34</v>
+        <v>57.11</v>
       </c>
       <c r="L19" t="n">
-        <v>57.45</v>
+        <v>58.44</v>
       </c>
       <c r="M19" t="n">
-        <v>58.3</v>
+        <v>61.12</v>
       </c>
       <c r="N19" t="n">
-        <v>59.14</v>
+        <v>63.81</v>
       </c>
       <c r="O19" t="n">
-        <v>60.5</v>
+        <v>63.78</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2095,25 +2101,21 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2125,57 +2127,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>59</v>
+        <v>59.01</v>
       </c>
       <c r="C20" t="n">
-        <v>62.36</v>
+        <v>61.36</v>
       </c>
       <c r="D20" t="n">
-        <v>58.45</v>
+        <v>58.7</v>
       </c>
       <c r="E20" t="n">
-        <v>59.44</v>
+        <v>61.07</v>
       </c>
       <c r="F20" t="n">
-        <v>0.32</v>
+        <v>1.63</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0274</v>
       </c>
       <c r="H20" t="n">
-        <v>3.91</v>
+        <v>2.66</v>
       </c>
       <c r="I20" t="n">
-        <v>51.75</v>
+        <v>54.54</v>
       </c>
       <c r="J20" t="n">
-        <v>55.79</v>
+        <v>55.05</v>
       </c>
       <c r="K20" t="n">
-        <v>57.11</v>
+        <v>57.48</v>
       </c>
       <c r="L20" t="n">
-        <v>58.44</v>
+        <v>59.92</v>
       </c>
       <c r="M20" t="n">
-        <v>61.12</v>
+        <v>61.39</v>
       </c>
       <c r="N20" t="n">
-        <v>63.81</v>
+        <v>62.87</v>
       </c>
       <c r="O20" t="n">
-        <v>63.78</v>
+        <v>66.27</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2186,14 +2188,14 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U20" s="8" t="n">
@@ -2209,57 +2211,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>59.01</v>
+        <v>61.22</v>
       </c>
       <c r="C21" t="n">
-        <v>61.36</v>
+        <v>66.48</v>
       </c>
       <c r="D21" t="n">
-        <v>58.7</v>
+        <v>60.14</v>
       </c>
       <c r="E21" t="n">
-        <v>61.07</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>1.63</v>
+        <v>4.14</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0678</v>
       </c>
       <c r="H21" t="n">
-        <v>2.66</v>
+        <v>6.34</v>
       </c>
       <c r="I21" t="n">
-        <v>54.54</v>
+        <v>56.04</v>
       </c>
       <c r="J21" t="n">
-        <v>55.05</v>
+        <v>58.93</v>
       </c>
       <c r="K21" t="n">
-        <v>57.48</v>
+        <v>59.74</v>
       </c>
       <c r="L21" t="n">
-        <v>59.92</v>
+        <v>60.55</v>
       </c>
       <c r="M21" t="n">
-        <v>61.39</v>
+        <v>62.4</v>
       </c>
       <c r="N21" t="n">
-        <v>62.87</v>
+        <v>64.25</v>
       </c>
       <c r="O21" t="n">
-        <v>66.27</v>
+        <v>64.02</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2270,80 +2272,80 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>61.22</v>
+        <v>64.72</v>
       </c>
       <c r="C22" t="n">
-        <v>66.48</v>
+        <v>65.53</v>
       </c>
       <c r="D22" t="n">
-        <v>60.14</v>
+        <v>61.12</v>
       </c>
       <c r="E22" t="n">
-        <v>65.20999999999999</v>
+        <v>63.55</v>
       </c>
       <c r="F22" t="n">
-        <v>4.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0678</v>
+        <v>-0.0255</v>
       </c>
       <c r="H22" t="n">
-        <v>6.34</v>
+        <v>4.41</v>
       </c>
       <c r="I22" t="n">
-        <v>56.04</v>
+        <v>53.8</v>
       </c>
       <c r="J22" t="n">
-        <v>58.93</v>
+        <v>59.82</v>
       </c>
       <c r="K22" t="n">
-        <v>59.74</v>
+        <v>62.04</v>
       </c>
       <c r="L22" t="n">
-        <v>60.55</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>62.4</v>
+        <v>68.38</v>
       </c>
       <c r="N22" t="n">
-        <v>64.25</v>
+        <v>72.5</v>
       </c>
       <c r="O22" t="n">
-        <v>64.02</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2351,83 +2353,83 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>64.72</v>
+        <v>62.99</v>
       </c>
       <c r="C23" t="n">
-        <v>65.53</v>
+        <v>65.83</v>
       </c>
       <c r="D23" t="n">
-        <v>61.12</v>
+        <v>62.14</v>
       </c>
       <c r="E23" t="n">
-        <v>63.55</v>
+        <v>62.89</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.66</v>
+        <v>-0.66</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0255</v>
+        <v>-0.0104</v>
       </c>
       <c r="H23" t="n">
-        <v>4.41</v>
+        <v>3.69</v>
       </c>
       <c r="I23" t="n">
-        <v>53.8</v>
+        <v>56.71</v>
       </c>
       <c r="J23" t="n">
-        <v>59.82</v>
+        <v>59.25</v>
       </c>
       <c r="K23" t="n">
-        <v>62.04</v>
+        <v>61.34</v>
       </c>
       <c r="L23" t="n">
-        <v>64.26000000000001</v>
+        <v>63.44</v>
       </c>
       <c r="M23" t="n">
-        <v>68.38</v>
+        <v>65.75</v>
       </c>
       <c r="N23" t="n">
-        <v>72.5</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>72.81999999999999</v>
+        <v>69.94</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2435,19 +2437,19 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2461,57 +2463,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>62.99</v>
+        <v>63.3</v>
       </c>
       <c r="C24" t="n">
-        <v>65.83</v>
+        <v>67.05</v>
       </c>
       <c r="D24" t="n">
-        <v>62.14</v>
+        <v>61.87</v>
       </c>
       <c r="E24" t="n">
-        <v>62.89</v>
+        <v>66.39</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.66</v>
+        <v>3.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0557</v>
       </c>
       <c r="H24" t="n">
-        <v>3.69</v>
+        <v>5.18</v>
       </c>
       <c r="I24" t="n">
-        <v>56.71</v>
+        <v>58.45</v>
       </c>
       <c r="J24" t="n">
-        <v>59.25</v>
+        <v>58.65</v>
       </c>
       <c r="K24" t="n">
-        <v>61.34</v>
+        <v>61.04</v>
       </c>
       <c r="L24" t="n">
         <v>63.44</v>
       </c>
       <c r="M24" t="n">
-        <v>65.75</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>68.06999999999999</v>
+        <v>66.03</v>
       </c>
       <c r="O24" t="n">
-        <v>69.94</v>
+        <v>69.52</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2524,7 +2526,7 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2532,8 +2534,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2552,50 +2556,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63.3</v>
+        <v>65.89</v>
       </c>
       <c r="C25" t="n">
-        <v>67.05</v>
+        <v>67.83</v>
       </c>
       <c r="D25" t="n">
-        <v>61.87</v>
+        <v>63.6</v>
       </c>
       <c r="E25" t="n">
-        <v>66.39</v>
+        <v>67.02</v>
       </c>
       <c r="F25" t="n">
-        <v>3.5</v>
+        <v>0.63</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0557</v>
+        <v>0.0095</v>
       </c>
       <c r="H25" t="n">
-        <v>5.18</v>
+        <v>4.23</v>
       </c>
       <c r="I25" t="n">
-        <v>58.45</v>
+        <v>56.69</v>
       </c>
       <c r="J25" t="n">
-        <v>58.65</v>
+        <v>62.17</v>
       </c>
       <c r="K25" t="n">
-        <v>61.04</v>
+        <v>63.8</v>
       </c>
       <c r="L25" t="n">
-        <v>63.44</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>64.73999999999999</v>
+        <v>68.98</v>
       </c>
       <c r="N25" t="n">
-        <v>66.03</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>69.52</v>
+        <v>72.23</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2603,23 +2607,21 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2629,59 +2631,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>65.89</v>
+        <v>75</v>
       </c>
       <c r="C26" t="n">
-        <v>67.83</v>
+        <v>92.61</v>
       </c>
       <c r="D26" t="n">
-        <v>63.6</v>
+        <v>69.2</v>
       </c>
       <c r="E26" t="n">
-        <v>67.02</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.63</v>
+        <v>23.88</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.3563</v>
       </c>
       <c r="H26" t="n">
-        <v>4.23</v>
+        <v>23.41</v>
       </c>
       <c r="I26" t="n">
-        <v>56.69</v>
+        <v>59.37</v>
       </c>
       <c r="J26" t="n">
-        <v>62.17</v>
+        <v>63.44</v>
       </c>
       <c r="K26" t="n">
-        <v>63.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>65.43000000000001</v>
+        <v>66.37</v>
       </c>
       <c r="M26" t="n">
-        <v>68.98</v>
+        <v>69.13</v>
       </c>
       <c r="N26" t="n">
-        <v>72.54000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>72.23</v>
+        <v>72.06</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2689,24 +2687,28 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
@@ -2718,50 +2720,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C27" t="n">
-        <v>92.61</v>
+        <v>119.48</v>
       </c>
       <c r="D27" t="n">
-        <v>69.2</v>
+        <v>76.73</v>
       </c>
       <c r="E27" t="n">
-        <v>90.90000000000001</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>23.88</v>
+        <v>7.81</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.3563</v>
+        <v>0.0859</v>
       </c>
       <c r="H27" t="n">
-        <v>23.41</v>
+        <v>42.75</v>
       </c>
       <c r="I27" t="n">
-        <v>59.37</v>
+        <v>45.79</v>
       </c>
       <c r="J27" t="n">
-        <v>63.44</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>64.90000000000001</v>
+        <v>79.19</v>
       </c>
       <c r="L27" t="n">
-        <v>66.37</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>69.13</v>
+        <v>102.61</v>
       </c>
       <c r="N27" t="n">
-        <v>71.90000000000001</v>
+        <v>119.31</v>
       </c>
       <c r="O27" t="n">
-        <v>72.06</v>
+        <v>116.02</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2769,27 +2771,29 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
+      <c r="V27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W27" s="9" t="inlineStr">
@@ -2802,50 +2806,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>98</v>
+        <v>100.93</v>
       </c>
       <c r="C28" t="n">
-        <v>119.48</v>
+        <v>102.44</v>
       </c>
       <c r="D28" t="n">
-        <v>76.73</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>98.70999999999999</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>7.81</v>
+        <v>-0.39</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0859</v>
+        <v>-0.004</v>
       </c>
       <c r="H28" t="n">
-        <v>42.75</v>
+        <v>10.48</v>
       </c>
       <c r="I28" t="n">
-        <v>45.79</v>
+        <v>33.98</v>
       </c>
       <c r="J28" t="n">
-        <v>72.48999999999999</v>
+        <v>56.26</v>
       </c>
       <c r="K28" t="n">
-        <v>79.19</v>
+        <v>77.33</v>
       </c>
       <c r="L28" t="n">
-        <v>85.90000000000001</v>
+        <v>98.41</v>
       </c>
       <c r="M28" t="n">
-        <v>102.61</v>
+        <v>120.08</v>
       </c>
       <c r="N28" t="n">
-        <v>119.31</v>
+        <v>141.76</v>
       </c>
       <c r="O28" t="n">
-        <v>116.02</v>
+        <v>162.23</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2853,98 +2857,98 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>100.93</v>
+        <v>100.51</v>
       </c>
       <c r="C29" t="n">
-        <v>102.44</v>
+        <v>101.67</v>
       </c>
       <c r="D29" t="n">
-        <v>91.95999999999999</v>
+        <v>84.37</v>
       </c>
       <c r="E29" t="n">
-        <v>98.31999999999999</v>
+        <v>99.64</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.39</v>
+        <v>1.32</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0134</v>
       </c>
       <c r="H29" t="n">
-        <v>10.48</v>
+        <v>17.3</v>
       </c>
       <c r="I29" t="n">
-        <v>33.98</v>
+        <v>81.48</v>
       </c>
       <c r="J29" t="n">
-        <v>56.26</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>77.33</v>
+        <v>93.08</v>
       </c>
       <c r="L29" t="n">
-        <v>98.41</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>120.08</v>
+        <v>103.56</v>
       </c>
       <c r="N29" t="n">
-        <v>141.76</v>
+        <v>109.36</v>
       </c>
       <c r="O29" t="n">
-        <v>162.23</v>
+        <v>112.92</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2970,71 +2974,69 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>100.51</v>
+        <v>102.6</v>
       </c>
       <c r="C30" t="n">
-        <v>101.67</v>
+        <v>113.97</v>
       </c>
       <c r="D30" t="n">
-        <v>84.37</v>
+        <v>96.5</v>
       </c>
       <c r="E30" t="n">
-        <v>99.64</v>
+        <v>111.54</v>
       </c>
       <c r="F30" t="n">
-        <v>1.32</v>
+        <v>11.9</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.1194</v>
       </c>
       <c r="H30" t="n">
-        <v>17.3</v>
+        <v>17.47</v>
       </c>
       <c r="I30" t="n">
-        <v>81.48</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>88.40000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>93.08</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>97.76000000000001</v>
+        <v>96.33</v>
       </c>
       <c r="M30" t="n">
-        <v>103.56</v>
+        <v>108.29</v>
       </c>
       <c r="N30" t="n">
-        <v>109.36</v>
+        <v>120.25</v>
       </c>
       <c r="O30" t="n">
-        <v>112.92</v>
+        <v>118.97</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3047,78 +3049,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>102.6</v>
+        <v>112.96</v>
       </c>
       <c r="C31" t="n">
-        <v>113.97</v>
+        <v>117.63</v>
       </c>
       <c r="D31" t="n">
-        <v>96.5</v>
+        <v>91.05</v>
       </c>
       <c r="E31" t="n">
-        <v>111.54</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>11.9</v>
+        <v>-14.97</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.1194</v>
+        <v>-0.1342</v>
       </c>
       <c r="H31" t="n">
-        <v>17.47</v>
+        <v>26.58</v>
       </c>
       <c r="I31" t="n">
-        <v>67.06999999999999</v>
+        <v>79.03</v>
       </c>
       <c r="J31" t="n">
-        <v>85.65000000000001</v>
+        <v>97.22</v>
       </c>
       <c r="K31" t="n">
-        <v>90.98999999999999</v>
+        <v>102.81</v>
       </c>
       <c r="L31" t="n">
-        <v>96.33</v>
+        <v>108.39</v>
       </c>
       <c r="M31" t="n">
-        <v>108.29</v>
+        <v>120.28</v>
       </c>
       <c r="N31" t="n">
-        <v>120.25</v>
+        <v>132.16</v>
       </c>
       <c r="O31" t="n">
-        <v>118.97</v>
+        <v>131.44</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3126,75 +3126,77 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="W31" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>112.96</v>
+        <v>102</v>
       </c>
       <c r="C32" t="n">
-        <v>117.63</v>
+        <v>105.63</v>
       </c>
       <c r="D32" t="n">
-        <v>91.05</v>
+        <v>80.56</v>
       </c>
       <c r="E32" t="n">
-        <v>96.56999999999999</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>-14.97</v>
+        <v>-12.72</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.1342</v>
+        <v>-0.1317</v>
       </c>
       <c r="H32" t="n">
-        <v>26.58</v>
+        <v>25.07</v>
       </c>
       <c r="I32" t="n">
-        <v>79.03</v>
+        <v>64.47</v>
       </c>
       <c r="J32" t="n">
-        <v>97.22</v>
+        <v>66.11</v>
       </c>
       <c r="K32" t="n">
-        <v>102.81</v>
+        <v>83.28</v>
       </c>
       <c r="L32" t="n">
-        <v>108.39</v>
+        <v>100.45</v>
       </c>
       <c r="M32" t="n">
-        <v>120.28</v>
+        <v>109.86</v>
       </c>
       <c r="N32" t="n">
-        <v>132.16</v>
+        <v>119.26</v>
       </c>
       <c r="O32" t="n">
-        <v>131.44</v>
+        <v>144.21</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3213,59 +3215,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C33" t="n">
-        <v>105.63</v>
+        <v>98.39</v>
       </c>
       <c r="D33" t="n">
-        <v>80.56</v>
+        <v>87.02</v>
       </c>
       <c r="E33" t="n">
-        <v>83.84999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-12.72</v>
+        <v>10.55</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.1317</v>
+        <v>0.1258</v>
       </c>
       <c r="H33" t="n">
-        <v>25.07</v>
+        <v>11.37</v>
       </c>
       <c r="I33" t="n">
-        <v>64.47</v>
+        <v>55.49</v>
       </c>
       <c r="J33" t="n">
-        <v>66.11</v>
+        <v>54.16</v>
       </c>
       <c r="K33" t="n">
-        <v>83.28</v>
+        <v>71.31</v>
       </c>
       <c r="L33" t="n">
-        <v>100.45</v>
+        <v>88.47</v>
       </c>
       <c r="M33" t="n">
-        <v>109.86</v>
+        <v>96.38</v>
       </c>
       <c r="N33" t="n">
-        <v>119.26</v>
+        <v>104.3</v>
       </c>
       <c r="O33" t="n">
-        <v>144.21</v>
+        <v>130.7</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3273,19 +3271,19 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3297,55 +3295,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>89</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>98.39</v>
+        <v>110.93</v>
       </c>
       <c r="D34" t="n">
-        <v>87.02</v>
+        <v>94.59</v>
       </c>
       <c r="E34" t="n">
-        <v>94.40000000000001</v>
+        <v>101.94</v>
       </c>
       <c r="F34" t="n">
-        <v>10.55</v>
+        <v>7.54</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.1258</v>
+        <v>0.0799</v>
       </c>
       <c r="H34" t="n">
-        <v>11.37</v>
+        <v>16.34</v>
       </c>
       <c r="I34" t="n">
-        <v>55.49</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>54.16</v>
+        <v>83.88</v>
       </c>
       <c r="K34" t="n">
-        <v>71.31</v>
+        <v>88.72</v>
       </c>
       <c r="L34" t="n">
-        <v>88.47</v>
+        <v>93.55</v>
       </c>
       <c r="M34" t="n">
-        <v>96.38</v>
+        <v>100.09</v>
       </c>
       <c r="N34" t="n">
-        <v>104.3</v>
+        <v>106.62</v>
       </c>
       <c r="O34" t="n">
-        <v>130.7</v>
+        <v>109.76</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3356,7 +3358,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3366,11 +3368,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
@@ -3379,57 +3385,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>95.59999999999999</v>
+        <v>99.73</v>
       </c>
       <c r="C35" t="n">
-        <v>110.93</v>
+        <v>107.46</v>
       </c>
       <c r="D35" t="n">
-        <v>94.59</v>
+        <v>88.66</v>
       </c>
       <c r="E35" t="n">
-        <v>101.94</v>
+        <v>95.42</v>
       </c>
       <c r="F35" t="n">
-        <v>7.54</v>
+        <v>-6.52</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0799</v>
+        <v>-0.064</v>
       </c>
       <c r="H35" t="n">
-        <v>16.34</v>
+        <v>18.8</v>
       </c>
       <c r="I35" t="n">
-        <v>75.65000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="J35" t="n">
-        <v>83.88</v>
+        <v>85.19</v>
       </c>
       <c r="K35" t="n">
-        <v>88.72</v>
+        <v>93.77</v>
       </c>
       <c r="L35" t="n">
-        <v>93.55</v>
+        <v>102.35</v>
       </c>
       <c r="M35" t="n">
-        <v>100.09</v>
+        <v>110.11</v>
       </c>
       <c r="N35" t="n">
-        <v>106.62</v>
+        <v>117.87</v>
       </c>
       <c r="O35" t="n">
-        <v>109.76</v>
+        <v>127.27</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3437,87 +3443,79 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>99.73</v>
+        <v>98.19</v>
       </c>
       <c r="C36" t="n">
-        <v>107.46</v>
+        <v>106</v>
       </c>
       <c r="D36" t="n">
-        <v>88.66</v>
+        <v>96.13</v>
       </c>
       <c r="E36" t="n">
-        <v>95.42</v>
+        <v>105.42</v>
       </c>
       <c r="F36" t="n">
-        <v>-6.52</v>
+        <v>10</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.064</v>
+        <v>0.1048</v>
       </c>
       <c r="H36" t="n">
-        <v>18.8</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>78.25</v>
+        <v>69.86</v>
       </c>
       <c r="J36" t="n">
-        <v>85.19</v>
+        <v>75.3</v>
       </c>
       <c r="K36" t="n">
-        <v>93.77</v>
+        <v>86.02</v>
       </c>
       <c r="L36" t="n">
-        <v>102.35</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>110.11</v>
+        <v>104.82</v>
       </c>
       <c r="N36" t="n">
-        <v>117.87</v>
+        <v>112.9</v>
       </c>
       <c r="O36" t="n">
-        <v>127.27</v>
+        <v>126.26</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3525,19 +3523,19 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3549,74 +3547,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>98.19</v>
+        <v>106</v>
       </c>
       <c r="C37" t="n">
-        <v>106</v>
+        <v>109.47</v>
       </c>
       <c r="D37" t="n">
-        <v>96.13</v>
+        <v>94.73</v>
       </c>
       <c r="E37" t="n">
-        <v>105.42</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>-8.82</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.1048</v>
+        <v>-0.0837</v>
       </c>
       <c r="H37" t="n">
-        <v>9.869999999999999</v>
+        <v>14.74</v>
       </c>
       <c r="I37" t="n">
-        <v>69.86</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>75.3</v>
+        <v>97.73</v>
       </c>
       <c r="K37" t="n">
-        <v>86.02</v>
+        <v>100.48</v>
       </c>
       <c r="L37" t="n">
-        <v>96.73999999999999</v>
+        <v>103.24</v>
       </c>
       <c r="M37" t="n">
-        <v>104.82</v>
+        <v>110.35</v>
       </c>
       <c r="N37" t="n">
-        <v>112.9</v>
+        <v>117.47</v>
       </c>
       <c r="O37" t="n">
-        <v>126.26</v>
+        <v>115.87</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3631,72 +3635,70 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>106</v>
+        <v>93.88</v>
       </c>
       <c r="C38" t="n">
-        <v>109.47</v>
+        <v>94.7</v>
       </c>
       <c r="D38" t="n">
-        <v>94.73</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>96.59999999999999</v>
+        <v>87.36</v>
       </c>
       <c r="F38" t="n">
-        <v>-8.82</v>
+        <v>-9.24</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0837</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>14.74</v>
+        <v>8.35</v>
       </c>
       <c r="I38" t="n">
-        <v>86.26000000000001</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>97.73</v>
+        <v>79.11</v>
       </c>
       <c r="K38" t="n">
-        <v>100.48</v>
+        <v>89.23</v>
       </c>
       <c r="L38" t="n">
-        <v>103.24</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>110.35</v>
+        <v>103.97</v>
       </c>
       <c r="N38" t="n">
-        <v>117.47</v>
+        <v>108.59</v>
       </c>
       <c r="O38" t="n">
-        <v>115.87</v>
+        <v>124.21</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3715,59 +3717,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>93.88</v>
+        <v>88.5</v>
       </c>
       <c r="C39" t="n">
-        <v>94.7</v>
+        <v>97</v>
       </c>
       <c r="D39" t="n">
-        <v>86.34999999999999</v>
+        <v>88.45</v>
       </c>
       <c r="E39" t="n">
-        <v>87.36</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>-9.24</v>
+        <v>3.18</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.0364</v>
       </c>
       <c r="H39" t="n">
-        <v>8.35</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>79.98999999999999</v>
+        <v>78</v>
       </c>
       <c r="J39" t="n">
-        <v>79.11</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>89.23</v>
+        <v>83.19</v>
       </c>
       <c r="L39" t="n">
-        <v>99.34999999999999</v>
+        <v>88.94</v>
       </c>
       <c r="M39" t="n">
-        <v>103.97</v>
+        <v>91.53</v>
       </c>
       <c r="N39" t="n">
-        <v>108.59</v>
+        <v>94.13</v>
       </c>
       <c r="O39" t="n">
-        <v>124.21</v>
+        <v>103.05</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3775,21 +3773,23 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3799,55 +3799,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>88.5</v>
+        <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>97</v>
+        <v>95.47</v>
       </c>
       <c r="D40" t="n">
-        <v>88.45</v>
+        <v>83.2</v>
       </c>
       <c r="E40" t="n">
-        <v>90.54000000000001</v>
+        <v>84.88</v>
       </c>
       <c r="F40" t="n">
-        <v>3.18</v>
+        <v>-5.66</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0364</v>
+        <v>-0.0625</v>
       </c>
       <c r="H40" t="n">
-        <v>8.550000000000001</v>
+        <v>12.27</v>
       </c>
       <c r="I40" t="n">
-        <v>78</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>77.43000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>83.19</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>88.94</v>
+        <v>91.63</v>
       </c>
       <c r="M40" t="n">
-        <v>91.53</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>94.13</v>
+        <v>98</v>
       </c>
       <c r="O40" t="n">
-        <v>103.05</v>
+        <v>105.55</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3855,24 +3859,24 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3881,59 +3885,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>93</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>95.47</v>
+        <v>82.42</v>
       </c>
       <c r="D41" t="n">
-        <v>83.2</v>
+        <v>73.58</v>
       </c>
       <c r="E41" t="n">
-        <v>84.88</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>-5.66</v>
+        <v>-7.34</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0625</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>12.27</v>
+        <v>8.84</v>
       </c>
       <c r="I41" t="n">
-        <v>79.90000000000001</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>80.90000000000001</v>
+        <v>70.38</v>
       </c>
       <c r="K41" t="n">
-        <v>86.26000000000001</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>91.63</v>
+        <v>87.11</v>
       </c>
       <c r="M41" t="n">
-        <v>94.81999999999999</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>98</v>
+        <v>94.92</v>
       </c>
       <c r="O41" t="n">
-        <v>105.55</v>
+        <v>107.74</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3946,15 +3946,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3972,63 +3970,65 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>81.40000000000001</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>82.42</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>73.58</v>
+        <v>68.56</v>
       </c>
       <c r="E42" t="n">
-        <v>77.54000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="F42" t="n">
-        <v>-7.34</v>
+        <v>-8.31</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.1072</v>
       </c>
       <c r="H42" t="n">
-        <v>8.84</v>
+        <v>10.4</v>
       </c>
       <c r="I42" t="n">
-        <v>70.93000000000001</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>70.38</v>
+        <v>68.47</v>
       </c>
       <c r="K42" t="n">
-        <v>78.73999999999999</v>
+        <v>73.12</v>
       </c>
       <c r="L42" t="n">
-        <v>87.11</v>
+        <v>77.77</v>
       </c>
       <c r="M42" t="n">
-        <v>91.01000000000001</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>94.92</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>107.74</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4052,67 +4052,63 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>78.93000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="C43" t="n">
-        <v>78.95999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>68.56</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>69.23</v>
+        <v>68.78</v>
       </c>
       <c r="F43" t="n">
-        <v>-8.31</v>
+        <v>-0.45</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.1072</v>
+        <v>-0.0065</v>
       </c>
       <c r="H43" t="n">
-        <v>10.4</v>
+        <v>4.56</v>
       </c>
       <c r="I43" t="n">
-        <v>64.73999999999999</v>
+        <v>58.16</v>
       </c>
       <c r="J43" t="n">
-        <v>68.47</v>
+        <v>56.57</v>
       </c>
       <c r="K43" t="n">
-        <v>73.12</v>
+        <v>64.03</v>
       </c>
       <c r="L43" t="n">
-        <v>77.77</v>
+        <v>71.5</v>
       </c>
       <c r="M43" t="n">
-        <v>81.95999999999999</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>86.15000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="O43" t="n">
-        <v>91.26000000000001</v>
+        <v>89.36</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4134,50 +4130,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>70.5</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>71.59999999999999</v>
+        <v>76.08</v>
       </c>
       <c r="D44" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>68.78</v>
+        <v>71.41</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.45</v>
+        <v>2.63</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0382</v>
       </c>
       <c r="H44" t="n">
-        <v>4.56</v>
+        <v>8.26</v>
       </c>
       <c r="I44" t="n">
-        <v>58.16</v>
+        <v>62.48</v>
       </c>
       <c r="J44" t="n">
-        <v>56.57</v>
+        <v>63.95</v>
       </c>
       <c r="K44" t="n">
-        <v>64.03</v>
+        <v>66.5</v>
       </c>
       <c r="L44" t="n">
-        <v>71.5</v>
+        <v>69.05</v>
       </c>
       <c r="M44" t="n">
-        <v>74.43000000000001</v>
+        <v>71.06</v>
       </c>
       <c r="N44" t="n">
-        <v>77.37</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>89.36</v>
+        <v>76.16</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4190,14 +4186,18 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4207,55 +4207,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>68.68000000000001</v>
+        <v>73.69</v>
       </c>
       <c r="C45" t="n">
-        <v>76.08</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>67.81999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="E45" t="n">
-        <v>71.41</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F45" t="n">
-        <v>2.63</v>
+        <v>11.08</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0382</v>
+        <v>0.1552</v>
       </c>
       <c r="H45" t="n">
-        <v>8.26</v>
+        <v>10.15</v>
       </c>
       <c r="I45" t="n">
-        <v>62.48</v>
+        <v>59.56</v>
       </c>
       <c r="J45" t="n">
-        <v>63.95</v>
+        <v>62.88</v>
       </c>
       <c r="K45" t="n">
-        <v>66.5</v>
+        <v>67.28</v>
       </c>
       <c r="L45" t="n">
-        <v>69.05</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>71.06</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>73.06999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>76.16</v>
+        <v>84.34</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4266,82 +4270,80 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W45" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>73.69</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C46" t="n">
-        <v>82.76000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="D46" t="n">
-        <v>72.61</v>
+        <v>80.27</v>
       </c>
       <c r="E46" t="n">
-        <v>82.48999999999999</v>
+        <v>89.31</v>
       </c>
       <c r="F46" t="n">
-        <v>11.08</v>
+        <v>6.82</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.1552</v>
+        <v>0.0827</v>
       </c>
       <c r="H46" t="n">
-        <v>10.15</v>
+        <v>13.23</v>
       </c>
       <c r="I46" t="n">
-        <v>59.56</v>
+        <v>62.46</v>
       </c>
       <c r="J46" t="n">
-        <v>62.88</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>67.28</v>
+        <v>77.41</v>
       </c>
       <c r="L46" t="n">
-        <v>71.68000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="M46" t="n">
-        <v>75.54000000000001</v>
+        <v>87.56</v>
       </c>
       <c r="N46" t="n">
-        <v>79.40000000000001</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>84.34</v>
+        <v>92.91</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4352,24 +4354,22 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W46" s="9" t="inlineStr">
@@ -4382,50 +4382,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>83.76000000000001</v>
+        <v>86.12</v>
       </c>
       <c r="C47" t="n">
-        <v>93.5</v>
+        <v>86.87</v>
       </c>
       <c r="D47" t="n">
-        <v>80.27</v>
+        <v>77.78</v>
       </c>
       <c r="E47" t="n">
-        <v>89.31</v>
+        <v>84.67</v>
       </c>
       <c r="F47" t="n">
-        <v>6.82</v>
+        <v>-4.64</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0827</v>
+        <v>-0.052</v>
       </c>
       <c r="H47" t="n">
-        <v>13.23</v>
+        <v>9.09</v>
       </c>
       <c r="I47" t="n">
-        <v>62.46</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>74.73999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>77.41</v>
+        <v>82.69</v>
       </c>
       <c r="L47" t="n">
-        <v>80.09</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>87.56</v>
+        <v>95.92</v>
       </c>
       <c r="N47" t="n">
-        <v>95.04000000000001</v>
+        <v>103.75</v>
       </c>
       <c r="O47" t="n">
-        <v>92.91</v>
+        <v>106.73</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4433,94 +4433,98 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>86.12</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C48" t="n">
-        <v>86.87</v>
+        <v>82.33</v>
       </c>
       <c r="D48" t="n">
-        <v>77.78</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>84.67</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>-4.64</v>
+        <v>-6.49</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.0767</v>
       </c>
       <c r="H48" t="n">
-        <v>9.09</v>
+        <v>8.09</v>
       </c>
       <c r="I48" t="n">
-        <v>67.04000000000001</v>
+        <v>68.69</v>
       </c>
       <c r="J48" t="n">
-        <v>77.29000000000001</v>
+        <v>76.75</v>
       </c>
       <c r="K48" t="n">
-        <v>82.69</v>
+        <v>80.12</v>
       </c>
       <c r="L48" t="n">
-        <v>88.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="M48" t="n">
-        <v>95.92</v>
+        <v>89.22</v>
       </c>
       <c r="N48" t="n">
-        <v>103.75</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>106.73</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4548,72 +4552,70 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>80.09999999999999</v>
+        <v>78.42</v>
       </c>
       <c r="C49" t="n">
-        <v>82.33</v>
+        <v>84.61</v>
       </c>
       <c r="D49" t="n">
-        <v>74.23999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>78.18000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>-6.49</v>
+        <v>4.22</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0767</v>
+        <v>0.054</v>
       </c>
       <c r="H49" t="n">
-        <v>8.09</v>
+        <v>6.82</v>
       </c>
       <c r="I49" t="n">
-        <v>68.69</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>76.75</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>80.12</v>
+        <v>74.13</v>
       </c>
       <c r="L49" t="n">
-        <v>83.5</v>
+        <v>78.23</v>
       </c>
       <c r="M49" t="n">
-        <v>89.22</v>
+        <v>82.23</v>
       </c>
       <c r="N49" t="n">
-        <v>94.93000000000001</v>
+        <v>86.22</v>
       </c>
       <c r="O49" t="n">
-        <v>95.95999999999999</v>
+        <v>90.42</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
@@ -4625,59 +4627,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>78.42</v>
+        <v>82.53</v>
       </c>
       <c r="C50" t="n">
-        <v>84.61</v>
+        <v>89</v>
       </c>
       <c r="D50" t="n">
-        <v>77.79000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="E50" t="n">
-        <v>82.40000000000001</v>
+        <v>87.06</v>
       </c>
       <c r="F50" t="n">
-        <v>4.22</v>
+        <v>4.66</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.054</v>
+        <v>0.0566</v>
       </c>
       <c r="H50" t="n">
-        <v>6.82</v>
+        <v>7.5</v>
       </c>
       <c r="I50" t="n">
-        <v>66.15000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="J50" t="n">
-        <v>70.04000000000001</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>74.13</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>78.23</v>
+        <v>81.8</v>
       </c>
       <c r="M50" t="n">
-        <v>82.23</v>
+        <v>85.81</v>
       </c>
       <c r="N50" t="n">
-        <v>86.22</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="O50" t="n">
-        <v>90.42</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4688,7 +4686,7 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4714,69 +4712,71 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>82.53</v>
+        <v>86.5</v>
       </c>
       <c r="C51" t="n">
-        <v>89</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>81.5</v>
+        <v>79.62</v>
       </c>
       <c r="E51" t="n">
-        <v>87.06</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>4.66</v>
+        <v>-3.66</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0566</v>
+        <v>-0.042</v>
       </c>
       <c r="H51" t="n">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="I51" t="n">
-        <v>70.97</v>
+        <v>74</v>
       </c>
       <c r="J51" t="n">
-        <v>76.18000000000001</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>78.98999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="L51" t="n">
-        <v>81.8</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="M51" t="n">
-        <v>85.81</v>
+        <v>90.81</v>
       </c>
       <c r="N51" t="n">
-        <v>89.81999999999999</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="O51" t="n">
-        <v>91.43000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4789,80 +4789,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>86.5</v>
+        <v>84.69</v>
       </c>
       <c r="C52" t="n">
-        <v>86.56999999999999</v>
+        <v>93.14</v>
       </c>
       <c r="D52" t="n">
-        <v>79.62</v>
+        <v>84.11</v>
       </c>
       <c r="E52" t="n">
-        <v>83.40000000000001</v>
+        <v>91.48</v>
       </c>
       <c r="F52" t="n">
-        <v>-3.66</v>
+        <v>8.08</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.042</v>
+        <v>0.0969</v>
       </c>
       <c r="H52" t="n">
-        <v>6.95</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>74</v>
+        <v>72.67</v>
       </c>
       <c r="J52" t="n">
-        <v>80.45999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>83.31</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>86.15000000000001</v>
+        <v>83.25</v>
       </c>
       <c r="M52" t="n">
-        <v>90.81</v>
+        <v>86.88</v>
       </c>
       <c r="N52" t="n">
-        <v>95.45999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="O52" t="n">
-        <v>96.5</v>
+        <v>93.52</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="U52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
@@ -4871,59 +4875,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>84.69</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C53" t="n">
-        <v>93.14</v>
+        <v>104.46</v>
       </c>
       <c r="D53" t="n">
-        <v>84.11</v>
+        <v>90.87</v>
       </c>
       <c r="E53" t="n">
-        <v>91.48</v>
+        <v>100.05</v>
       </c>
       <c r="F53" t="n">
-        <v>8.08</v>
+        <v>8.57</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0969</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>9.029999999999999</v>
+        <v>13.59</v>
       </c>
       <c r="I53" t="n">
-        <v>72.67</v>
+        <v>75.08</v>
       </c>
       <c r="J53" t="n">
-        <v>76.59999999999999</v>
+        <v>83.88</v>
       </c>
       <c r="K53" t="n">
-        <v>79.93000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="L53" t="n">
-        <v>83.25</v>
+        <v>90.05</v>
       </c>
       <c r="M53" t="n">
-        <v>86.88</v>
+        <v>96</v>
       </c>
       <c r="N53" t="n">
-        <v>90.5</v>
+        <v>101.94</v>
       </c>
       <c r="O53" t="n">
-        <v>93.52</v>
+        <v>102.17</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4934,7 +4934,7 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4949,8 +4949,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V53" s="8" t="n">
-        <v/>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
@@ -4962,50 +4964,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>92.26000000000001</v>
+        <v>102.25</v>
       </c>
       <c r="C54" t="n">
-        <v>104.46</v>
+        <v>106.75</v>
       </c>
       <c r="D54" t="n">
-        <v>90.87</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>100.05</v>
+        <v>100.3</v>
       </c>
       <c r="F54" t="n">
-        <v>8.57</v>
+        <v>0.25</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="H54" t="n">
-        <v>13.59</v>
+        <v>7.65</v>
       </c>
       <c r="I54" t="n">
-        <v>75.08</v>
+        <v>77.28</v>
       </c>
       <c r="J54" t="n">
-        <v>83.88</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>86.97</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>90.05</v>
+        <v>98.86</v>
       </c>
       <c r="M54" t="n">
-        <v>96</v>
+        <v>106.85</v>
       </c>
       <c r="N54" t="n">
-        <v>101.94</v>
+        <v>114.83</v>
       </c>
       <c r="O54" t="n">
-        <v>102.17</v>
+        <v>118.05</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5016,25 +5018,19 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
@@ -5046,63 +5042,69 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>102.25</v>
+        <v>101</v>
       </c>
       <c r="C55" t="n">
-        <v>106.75</v>
+        <v>101.08</v>
       </c>
       <c r="D55" t="n">
-        <v>99.09999999999999</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>100.3</v>
+        <v>92.41</v>
       </c>
       <c r="F55" t="n">
-        <v>0.25</v>
+        <v>-7.89</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>7.65</v>
+        <v>12.37</v>
       </c>
       <c r="I55" t="n">
-        <v>77.28</v>
+        <v>91.45</v>
       </c>
       <c r="J55" t="n">
-        <v>87.65000000000001</v>
+        <v>91.34</v>
       </c>
       <c r="K55" t="n">
-        <v>93.26000000000001</v>
+        <v>96.48</v>
       </c>
       <c r="L55" t="n">
-        <v>98.86</v>
+        <v>101.61</v>
       </c>
       <c r="M55" t="n">
-        <v>106.85</v>
+        <v>104.13</v>
       </c>
       <c r="N55" t="n">
-        <v>114.83</v>
+        <v>106.64</v>
       </c>
       <c r="O55" t="n">
-        <v>118.05</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+        <v>114.4</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5119,74 +5121,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>101</v>
+        <v>93.58</v>
       </c>
       <c r="C56" t="n">
-        <v>101.08</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>88.70999999999999</v>
+        <v>88.06</v>
       </c>
       <c r="E56" t="n">
-        <v>92.41</v>
+        <v>91.11</v>
       </c>
       <c r="F56" t="n">
-        <v>-7.89</v>
+        <v>-1.3</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0141</v>
       </c>
       <c r="H56" t="n">
-        <v>12.37</v>
+        <v>8.48</v>
       </c>
       <c r="I56" t="n">
-        <v>91.45</v>
+        <v>76.34</v>
       </c>
       <c r="J56" t="n">
-        <v>91.34</v>
+        <v>78.8</v>
       </c>
       <c r="K56" t="n">
-        <v>96.48</v>
+        <v>86.23</v>
       </c>
       <c r="L56" t="n">
-        <v>101.61</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>104.13</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>106.64</v>
+        <v>103.54</v>
       </c>
       <c r="O56" t="n">
-        <v>114.4</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>113.45</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5212,50 +5212,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>93.58</v>
+        <v>91.77</v>
       </c>
       <c r="C57" t="n">
-        <v>96.54000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="D57" t="n">
-        <v>88.06</v>
+        <v>86.86</v>
       </c>
       <c r="E57" t="n">
-        <v>91.11</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.3</v>
+        <v>0.74</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0141</v>
+        <v>0.0081</v>
       </c>
       <c r="H57" t="n">
-        <v>8.48</v>
+        <v>6.34</v>
       </c>
       <c r="I57" t="n">
-        <v>76.34</v>
+        <v>79.58</v>
       </c>
       <c r="J57" t="n">
-        <v>78.8</v>
+        <v>82.03</v>
       </c>
       <c r="K57" t="n">
-        <v>86.23</v>
+        <v>86.87</v>
       </c>
       <c r="L57" t="n">
-        <v>93.65000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="M57" t="n">
-        <v>98.59999999999999</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>103.54</v>
+        <v>99</v>
       </c>
       <c r="O57" t="n">
-        <v>113.45</v>
+        <v>105.02</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5263,12 +5263,14 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5287,91 +5289,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>91.77</v>
-      </c>
-      <c r="C58" t="n">
-        <v>91.88</v>
-      </c>
-      <c r="D58" t="n">
-        <v>86.86</v>
-      </c>
-      <c r="E58" t="n">
-        <v>90.79000000000001</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0035</v>
-      </c>
-      <c r="H58" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="I58" t="n">
-        <v>79.58</v>
-      </c>
-      <c r="J58" t="n">
-        <v>82.03</v>
-      </c>
-      <c r="K58" t="n">
-        <v>86.87</v>
-      </c>
-      <c r="L58" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="M58" t="n">
-        <v>95.34999999999999</v>
-      </c>
-      <c r="N58" t="n">
-        <v>99</v>
-      </c>
-      <c r="O58" t="n">
-        <v>105.02</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5225,13 +5225,13 @@
         <v>86.86</v>
       </c>
       <c r="E57" t="n">
-        <v>91.84999999999999</v>
+        <v>90.64</v>
       </c>
       <c r="F57" t="n">
-        <v>0.74</v>
+        <v>-0.47</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0081</v>
+        <v>-0.0052</v>
       </c>
       <c r="H57" t="n">
         <v>6.34</v>
@@ -5268,9 +5268,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5225,13 +5225,13 @@
         <v>86.86</v>
       </c>
       <c r="E57" t="n">
-        <v>90.64</v>
+        <v>90.23</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.47</v>
+        <v>-0.88</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0052</v>
+        <v>-0.0097</v>
       </c>
       <c r="H57" t="n">
         <v>6.34</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5225,13 +5225,13 @@
         <v>86.86</v>
       </c>
       <c r="E57" t="n">
-        <v>90.23</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.88</v>
+        <v>0.74</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0081</v>
       </c>
       <c r="H57" t="n">
         <v>6.34</v>
@@ -5268,9 +5268,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5289,9 +5289,89 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>91.83</v>
+      </c>
+      <c r="C58" t="n">
+        <v>94.36</v>
+      </c>
+      <c r="D58" t="n">
+        <v>89.61</v>
+      </c>
+      <c r="E58" t="n">
+        <v>93.73999999999999</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I58" t="n">
+        <v>80.52</v>
+      </c>
+      <c r="J58" t="n">
+        <v>86.42</v>
+      </c>
+      <c r="K58" t="n">
+        <v>88.68000000000001</v>
+      </c>
+      <c r="L58" t="n">
+        <v>90.94</v>
+      </c>
+      <c r="M58" t="n">
+        <v>95.02</v>
+      </c>
+      <c r="N58" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="O58" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5303,22 +5303,22 @@
         <v>91.83</v>
       </c>
       <c r="C58" t="n">
-        <v>94.36</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D58" t="n">
         <v>89.61</v>
       </c>
       <c r="E58" t="n">
-        <v>93.73999999999999</v>
+        <v>95.25</v>
       </c>
       <c r="F58" t="n">
-        <v>1.89</v>
+        <v>3.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0206</v>
+        <v>0.037</v>
       </c>
       <c r="H58" t="n">
-        <v>4.75</v>
+        <v>5.79</v>
       </c>
       <c r="I58" t="n">
         <v>80.52</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>2.24</v>
       </c>
       <c r="I2" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="J2" t="n">
-        <v>60.2</v>
+        <v>60.33</v>
       </c>
       <c r="K2" t="n">
-        <v>61.49</v>
+        <v>61.54</v>
       </c>
       <c r="L2" t="n">
-        <v>62.79</v>
+        <v>62.76</v>
       </c>
       <c r="M2" t="n">
-        <v>63.89</v>
+        <v>63.83</v>
       </c>
       <c r="N2" t="n">
-        <v>64.98</v>
+        <v>64.91</v>
       </c>
       <c r="O2" t="n">
-        <v>66.47</v>
+        <v>66.27</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5303,22 +5303,22 @@
         <v>91.83</v>
       </c>
       <c r="C58" t="n">
-        <v>95.40000000000001</v>
+        <v>95.31</v>
       </c>
       <c r="D58" t="n">
         <v>89.61</v>
       </c>
       <c r="E58" t="n">
-        <v>95.25</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.037</v>
+        <v>0.0293</v>
       </c>
       <c r="H58" t="n">
-        <v>5.79</v>
+        <v>5.7</v>
       </c>
       <c r="I58" t="n">
         <v>80.52</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5309,13 +5309,13 @@
         <v>89.61</v>
       </c>
       <c r="E58" t="n">
-        <v>94.54000000000001</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>2.69</v>
+        <v>2.47</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0293</v>
+        <v>0.0269</v>
       </c>
       <c r="H58" t="n">
         <v>5.7</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5309,13 +5309,13 @@
         <v>89.61</v>
       </c>
       <c r="E58" t="n">
-        <v>94.31999999999999</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0269</v>
+        <v>0.0233</v>
       </c>
       <c r="H58" t="n">
         <v>5.7</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5303,22 +5303,22 @@
         <v>91.83</v>
       </c>
       <c r="C58" t="n">
-        <v>95.31</v>
+        <v>96.39</v>
       </c>
       <c r="D58" t="n">
         <v>89.61</v>
       </c>
       <c r="E58" t="n">
-        <v>93.98999999999999</v>
+        <v>96</v>
       </c>
       <c r="F58" t="n">
-        <v>2.14</v>
+        <v>4.15</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0452</v>
       </c>
       <c r="H58" t="n">
-        <v>5.7</v>
+        <v>6.78</v>
       </c>
       <c r="I58" t="n">
         <v>80.52</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62.97</v>
+        <v>62.74</v>
       </c>
       <c r="C2" t="n">
-        <v>64.76000000000001</v>
+        <v>66.42</v>
       </c>
       <c r="D2" t="n">
-        <v>62.52</v>
+        <v>61.85</v>
       </c>
       <c r="E2" t="n">
-        <v>62.68</v>
+        <v>65.72</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.01</v>
+        <v>3.04</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0485</v>
       </c>
       <c r="H2" t="n">
-        <v>2.24</v>
+        <v>4.57</v>
       </c>
       <c r="I2" t="n">
-        <v>59.4</v>
+        <v>60.28</v>
       </c>
       <c r="J2" t="n">
-        <v>60.33</v>
+        <v>59.96</v>
       </c>
       <c r="K2" t="n">
-        <v>61.54</v>
+        <v>61.56</v>
       </c>
       <c r="L2" t="n">
-        <v>62.76</v>
+        <v>63.16</v>
       </c>
       <c r="M2" t="n">
-        <v>63.83</v>
+        <v>63.8</v>
       </c>
       <c r="N2" t="n">
-        <v>64.91</v>
+        <v>64.44</v>
       </c>
       <c r="O2" t="n">
-        <v>66.27</v>
+        <v>67</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,7 +690,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -698,8 +698,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -718,151 +720,145 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62.74</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>66.42</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>61.85</v>
+        <v>60.4</v>
       </c>
       <c r="E3" t="n">
-        <v>65.72</v>
+        <v>60.88</v>
       </c>
       <c r="F3" t="n">
-        <v>3.04</v>
+        <v>-4.84</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0485</v>
+        <v>-0.0736</v>
       </c>
       <c r="H3" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>60.28</v>
+        <v>57.28</v>
       </c>
       <c r="J3" t="n">
-        <v>59.96</v>
+        <v>61.94</v>
       </c>
       <c r="K3" t="n">
-        <v>61.56</v>
+        <v>63.44</v>
       </c>
       <c r="L3" t="n">
-        <v>63.16</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>63.8</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>64.44</v>
+        <v>71.08</v>
       </c>
       <c r="O3" t="n">
-        <v>67</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65.06999999999999</v>
+        <v>61.14</v>
       </c>
       <c r="C4" t="n">
-        <v>65.40000000000001</v>
+        <v>62.92</v>
       </c>
       <c r="D4" t="n">
-        <v>60.4</v>
+        <v>58.22</v>
       </c>
       <c r="E4" t="n">
-        <v>60.88</v>
+        <v>58.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.84</v>
+        <v>-1.98</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0736</v>
+        <v>-0.0325</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I4" t="n">
-        <v>57.28</v>
+        <v>55.4</v>
       </c>
       <c r="J4" t="n">
-        <v>61.94</v>
+        <v>54.87</v>
       </c>
       <c r="K4" t="n">
-        <v>63.44</v>
+        <v>58.38</v>
       </c>
       <c r="L4" t="n">
-        <v>64.93000000000001</v>
+        <v>61.89</v>
       </c>
       <c r="M4" t="n">
-        <v>68.01000000000001</v>
+        <v>63.38</v>
       </c>
       <c r="N4" t="n">
-        <v>71.08</v>
+        <v>64.87</v>
       </c>
       <c r="O4" t="n">
-        <v>70.98999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -886,50 +882,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.14</v>
+        <v>59</v>
       </c>
       <c r="C5" t="n">
-        <v>62.92</v>
+        <v>60.17</v>
       </c>
       <c r="D5" t="n">
-        <v>58.22</v>
+        <v>56.6</v>
       </c>
       <c r="E5" t="n">
-        <v>58.9</v>
+        <v>57.54</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.98</v>
+        <v>-1.36</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0325</v>
+        <v>-0.0231</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7</v>
+        <v>3.57</v>
       </c>
       <c r="I5" t="n">
-        <v>55.4</v>
+        <v>53.52</v>
       </c>
       <c r="J5" t="n">
-        <v>54.87</v>
+        <v>53.37</v>
       </c>
       <c r="K5" t="n">
-        <v>58.38</v>
+        <v>56.55</v>
       </c>
       <c r="L5" t="n">
-        <v>61.89</v>
+        <v>59.74</v>
       </c>
       <c r="M5" t="n">
-        <v>63.38</v>
+        <v>61.25</v>
       </c>
       <c r="N5" t="n">
-        <v>64.87</v>
+        <v>62.76</v>
       </c>
       <c r="O5" t="n">
-        <v>70.40000000000001</v>
+        <v>67.62</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -942,7 +938,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -966,50 +962,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>57.73</v>
       </c>
       <c r="C6" t="n">
-        <v>60.17</v>
+        <v>62.59</v>
       </c>
       <c r="D6" t="n">
-        <v>56.6</v>
+        <v>56.35</v>
       </c>
       <c r="E6" t="n">
-        <v>57.54</v>
+        <v>61.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.36</v>
+        <v>3.96</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0231</v>
+        <v>0.0688</v>
       </c>
       <c r="H6" t="n">
-        <v>3.57</v>
+        <v>6.24</v>
       </c>
       <c r="I6" t="n">
-        <v>53.52</v>
+        <v>53.03</v>
       </c>
       <c r="J6" t="n">
-        <v>53.37</v>
+        <v>53.55</v>
       </c>
       <c r="K6" t="n">
-        <v>56.55</v>
+        <v>55.76</v>
       </c>
       <c r="L6" t="n">
-        <v>59.74</v>
+        <v>57.96</v>
       </c>
       <c r="M6" t="n">
-        <v>61.25</v>
+        <v>59.33</v>
       </c>
       <c r="N6" t="n">
-        <v>62.76</v>
+        <v>60.69</v>
       </c>
       <c r="O6" t="n">
-        <v>67.62</v>
+        <v>63.74</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1017,79 +1013,85 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="W6" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57.73</v>
+        <v>61.82</v>
       </c>
       <c r="C7" t="n">
-        <v>62.59</v>
+        <v>62.17</v>
       </c>
       <c r="D7" t="n">
-        <v>56.35</v>
+        <v>59.64</v>
       </c>
       <c r="E7" t="n">
-        <v>61.5</v>
+        <v>60.98</v>
       </c>
       <c r="F7" t="n">
-        <v>3.96</v>
+        <v>-0.52</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0688</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>6.24</v>
+        <v>2.53</v>
       </c>
       <c r="I7" t="n">
-        <v>53.03</v>
+        <v>50.11</v>
       </c>
       <c r="J7" t="n">
-        <v>53.55</v>
+        <v>56.27</v>
       </c>
       <c r="K7" t="n">
-        <v>55.76</v>
+        <v>58.38</v>
       </c>
       <c r="L7" t="n">
-        <v>57.96</v>
+        <v>60.48</v>
       </c>
       <c r="M7" t="n">
-        <v>59.33</v>
+        <v>64.62</v>
       </c>
       <c r="N7" t="n">
-        <v>60.69</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>63.74</v>
+        <v>68.83</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1100,20 +1102,16 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1125,57 +1123,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61.82</v>
+        <v>61.4</v>
       </c>
       <c r="C8" t="n">
-        <v>62.17</v>
+        <v>61.5</v>
       </c>
       <c r="D8" t="n">
-        <v>59.64</v>
+        <v>58.83</v>
       </c>
       <c r="E8" t="n">
-        <v>60.98</v>
+        <v>59.75</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.52</v>
+        <v>-1.23</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0202</v>
       </c>
       <c r="H8" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="I8" t="n">
-        <v>50.11</v>
+        <v>57.11</v>
       </c>
       <c r="J8" t="n">
-        <v>56.27</v>
+        <v>58.49</v>
       </c>
       <c r="K8" t="n">
-        <v>58.38</v>
+        <v>59.72</v>
       </c>
       <c r="L8" t="n">
-        <v>60.48</v>
+        <v>60.94</v>
       </c>
       <c r="M8" t="n">
-        <v>64.62</v>
+        <v>62.24</v>
       </c>
       <c r="N8" t="n">
-        <v>68.76000000000001</v>
+        <v>63.55</v>
       </c>
       <c r="O8" t="n">
-        <v>68.83</v>
+        <v>64.7</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1183,12 +1181,14 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1207,57 +1207,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61.4</v>
+        <v>59.87</v>
       </c>
       <c r="C9" t="n">
-        <v>61.5</v>
+        <v>61.28</v>
       </c>
       <c r="D9" t="n">
-        <v>58.83</v>
+        <v>58.12</v>
       </c>
       <c r="E9" t="n">
-        <v>59.75</v>
+        <v>60.09</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.23</v>
+        <v>0.34</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0202</v>
+        <v>0.0057</v>
       </c>
       <c r="H9" t="n">
-        <v>2.67</v>
+        <v>3.16</v>
       </c>
       <c r="I9" t="n">
-        <v>57.11</v>
+        <v>56.16</v>
       </c>
       <c r="J9" t="n">
-        <v>58.49</v>
+        <v>56.87</v>
       </c>
       <c r="K9" t="n">
-        <v>59.72</v>
+        <v>58.42</v>
       </c>
       <c r="L9" t="n">
-        <v>60.94</v>
+        <v>59.96</v>
       </c>
       <c r="M9" t="n">
-        <v>62.24</v>
+        <v>61.08</v>
       </c>
       <c r="N9" t="n">
-        <v>63.55</v>
+        <v>62.21</v>
       </c>
       <c r="O9" t="n">
-        <v>64.7</v>
+        <v>64.17</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1267,16 +1267,18 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1291,57 +1293,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59.87</v>
+        <v>59.8</v>
       </c>
       <c r="C10" t="n">
-        <v>61.28</v>
+        <v>60.93</v>
       </c>
       <c r="D10" t="n">
-        <v>58.12</v>
+        <v>57.38</v>
       </c>
       <c r="E10" t="n">
-        <v>60.09</v>
+        <v>58.06</v>
       </c>
       <c r="F10" t="n">
-        <v>0.34</v>
+        <v>-2.03</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.0338</v>
       </c>
       <c r="H10" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="I10" t="n">
-        <v>56.16</v>
+        <v>54.96</v>
       </c>
       <c r="J10" t="n">
-        <v>56.87</v>
+        <v>57.13</v>
       </c>
       <c r="K10" t="n">
-        <v>58.42</v>
+        <v>58.51</v>
       </c>
       <c r="L10" t="n">
-        <v>59.96</v>
+        <v>59.89</v>
       </c>
       <c r="M10" t="n">
-        <v>61.08</v>
+        <v>61.67</v>
       </c>
       <c r="N10" t="n">
-        <v>62.21</v>
+        <v>63.45</v>
       </c>
       <c r="O10" t="n">
-        <v>64.17</v>
+        <v>64.44</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1351,18 +1353,16 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1377,57 +1377,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59.8</v>
+        <v>58.05</v>
       </c>
       <c r="C11" t="n">
-        <v>60.93</v>
+        <v>59.64</v>
       </c>
       <c r="D11" t="n">
-        <v>57.38</v>
+        <v>57.1</v>
       </c>
       <c r="E11" t="n">
-        <v>58.06</v>
+        <v>58.55</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.03</v>
+        <v>0.49</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>3.55</v>
+        <v>2.54</v>
       </c>
       <c r="I11" t="n">
-        <v>54.96</v>
+        <v>53.83</v>
       </c>
       <c r="J11" t="n">
-        <v>57.13</v>
+        <v>53.96</v>
       </c>
       <c r="K11" t="n">
-        <v>58.51</v>
+        <v>56.29</v>
       </c>
       <c r="L11" t="n">
-        <v>59.89</v>
+        <v>58.61</v>
       </c>
       <c r="M11" t="n">
-        <v>61.67</v>
+        <v>59.84</v>
       </c>
       <c r="N11" t="n">
-        <v>63.45</v>
+        <v>61.06</v>
       </c>
       <c r="O11" t="n">
-        <v>64.44</v>
+        <v>64.48</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1435,14 +1435,12 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1461,57 +1459,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58.05</v>
+        <v>58.96</v>
       </c>
       <c r="C12" t="n">
-        <v>59.64</v>
+        <v>60.5</v>
       </c>
       <c r="D12" t="n">
-        <v>57.1</v>
+        <v>58.28</v>
       </c>
       <c r="E12" t="n">
-        <v>58.55</v>
+        <v>60.08</v>
       </c>
       <c r="F12" t="n">
-        <v>0.49</v>
+        <v>1.53</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0261</v>
       </c>
       <c r="H12" t="n">
-        <v>2.54</v>
+        <v>2.22</v>
       </c>
       <c r="I12" t="n">
-        <v>53.83</v>
+        <v>54.56</v>
       </c>
       <c r="J12" t="n">
-        <v>53.96</v>
+        <v>56.1</v>
       </c>
       <c r="K12" t="n">
-        <v>56.29</v>
+        <v>57.28</v>
       </c>
       <c r="L12" t="n">
-        <v>58.61</v>
+        <v>58.46</v>
       </c>
       <c r="M12" t="n">
-        <v>59.84</v>
+        <v>59.82</v>
       </c>
       <c r="N12" t="n">
-        <v>61.06</v>
+        <v>61.18</v>
       </c>
       <c r="O12" t="n">
-        <v>64.48</v>
+        <v>62.18</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1524,11 +1522,13 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1541,78 +1541,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>58.96</v>
+        <v>60.15</v>
       </c>
       <c r="C13" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="D13" t="n">
-        <v>58.28</v>
+        <v>57.01</v>
       </c>
       <c r="E13" t="n">
-        <v>60.08</v>
+        <v>57.44</v>
       </c>
       <c r="F13" t="n">
-        <v>1.53</v>
+        <v>-2.64</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0261</v>
+        <v>-0.0439</v>
       </c>
       <c r="H13" t="n">
-        <v>2.22</v>
+        <v>3.29</v>
       </c>
       <c r="I13" t="n">
-        <v>54.56</v>
+        <v>56.06</v>
       </c>
       <c r="J13" t="n">
-        <v>56.1</v>
+        <v>58.21</v>
       </c>
       <c r="K13" t="n">
-        <v>57.28</v>
+        <v>58.97</v>
       </c>
       <c r="L13" t="n">
-        <v>58.46</v>
+        <v>59.74</v>
       </c>
       <c r="M13" t="n">
-        <v>59.82</v>
+        <v>61.19</v>
       </c>
       <c r="N13" t="n">
-        <v>61.18</v>
+        <v>62.65</v>
       </c>
       <c r="O13" t="n">
-        <v>62.18</v>
+        <v>62.72</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1620,9 +1618,9 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -1630,65 +1628,63 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60.15</v>
+        <v>57.5</v>
       </c>
       <c r="C14" t="n">
-        <v>60.3</v>
+        <v>57.8</v>
       </c>
       <c r="D14" t="n">
-        <v>57.01</v>
+        <v>54.98</v>
       </c>
       <c r="E14" t="n">
-        <v>57.44</v>
+        <v>56.66</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.64</v>
+        <v>-0.78</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0439</v>
+        <v>-0.0136</v>
       </c>
       <c r="H14" t="n">
-        <v>3.29</v>
+        <v>2.82</v>
       </c>
       <c r="I14" t="n">
-        <v>56.06</v>
+        <v>53.72</v>
       </c>
       <c r="J14" t="n">
-        <v>58.21</v>
+        <v>53.54</v>
       </c>
       <c r="K14" t="n">
-        <v>58.97</v>
+        <v>55.79</v>
       </c>
       <c r="L14" t="n">
-        <v>59.74</v>
+        <v>58.05</v>
       </c>
       <c r="M14" t="n">
-        <v>61.19</v>
+        <v>59.08</v>
       </c>
       <c r="N14" t="n">
-        <v>62.65</v>
+        <v>60.12</v>
       </c>
       <c r="O14" t="n">
-        <v>62.72</v>
+        <v>63.59</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1712,50 +1708,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>57.5</v>
+        <v>56.63</v>
       </c>
       <c r="C15" t="n">
-        <v>57.8</v>
+        <v>58.88</v>
       </c>
       <c r="D15" t="n">
-        <v>54.98</v>
+        <v>56.6</v>
       </c>
       <c r="E15" t="n">
-        <v>56.66</v>
+        <v>56.74</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.78</v>
+        <v>0.08</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0136</v>
+        <v>0.0014</v>
       </c>
       <c r="H15" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="I15" t="n">
-        <v>53.72</v>
+        <v>52.16</v>
       </c>
       <c r="J15" t="n">
-        <v>53.54</v>
+        <v>53.98</v>
       </c>
       <c r="K15" t="n">
-        <v>55.79</v>
+        <v>55.25</v>
       </c>
       <c r="L15" t="n">
-        <v>58.05</v>
+        <v>56.52</v>
       </c>
       <c r="M15" t="n">
-        <v>59.08</v>
+        <v>58.07</v>
       </c>
       <c r="N15" t="n">
-        <v>60.12</v>
+        <v>59.61</v>
       </c>
       <c r="O15" t="n">
-        <v>63.59</v>
+        <v>60.62</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1763,18 +1759,18 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1787,55 +1783,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>56.63</v>
+        <v>57.04</v>
       </c>
       <c r="C16" t="n">
-        <v>58.88</v>
+        <v>58.55</v>
       </c>
       <c r="D16" t="n">
         <v>56.6</v>
       </c>
       <c r="E16" t="n">
-        <v>56.74</v>
+        <v>57.32</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08</v>
+        <v>0.58</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0102</v>
       </c>
       <c r="H16" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="I16" t="n">
-        <v>52.16</v>
+        <v>54.32</v>
       </c>
       <c r="J16" t="n">
-        <v>53.98</v>
+        <v>53.96</v>
       </c>
       <c r="K16" t="n">
-        <v>55.25</v>
+        <v>55.6</v>
       </c>
       <c r="L16" t="n">
-        <v>56.52</v>
+        <v>57.24</v>
       </c>
       <c r="M16" t="n">
-        <v>58.07</v>
+        <v>57.88</v>
       </c>
       <c r="N16" t="n">
-        <v>59.61</v>
+        <v>58.52</v>
       </c>
       <c r="O16" t="n">
-        <v>60.62</v>
+        <v>61.16</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1846,7 +1846,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1856,8 +1856,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1869,57 +1871,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>57.04</v>
+        <v>57.47</v>
       </c>
       <c r="C17" t="n">
-        <v>58.55</v>
+        <v>59.77</v>
       </c>
       <c r="D17" t="n">
-        <v>56.6</v>
+        <v>55.76</v>
       </c>
       <c r="E17" t="n">
-        <v>57.32</v>
+        <v>59.12</v>
       </c>
       <c r="F17" t="n">
-        <v>0.58</v>
+        <v>1.8</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0314</v>
       </c>
       <c r="H17" t="n">
-        <v>1.95</v>
+        <v>4.01</v>
       </c>
       <c r="I17" t="n">
-        <v>54.32</v>
+        <v>54.65</v>
       </c>
       <c r="J17" t="n">
-        <v>53.96</v>
+        <v>55.24</v>
       </c>
       <c r="K17" t="n">
-        <v>55.6</v>
+        <v>56.34</v>
       </c>
       <c r="L17" t="n">
-        <v>57.24</v>
+        <v>57.45</v>
       </c>
       <c r="M17" t="n">
-        <v>57.88</v>
+        <v>58.3</v>
       </c>
       <c r="N17" t="n">
-        <v>58.52</v>
+        <v>59.14</v>
       </c>
       <c r="O17" t="n">
-        <v>61.16</v>
+        <v>60.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1927,12 +1929,14 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
@@ -1942,7 +1946,7 @@
       </c>
       <c r="U17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V17" s="8" t="n">
@@ -1955,57 +1959,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>57.47</v>
+        <v>59</v>
       </c>
       <c r="C18" t="n">
-        <v>59.77</v>
+        <v>62.36</v>
       </c>
       <c r="D18" t="n">
-        <v>55.76</v>
+        <v>58.45</v>
       </c>
       <c r="E18" t="n">
-        <v>59.12</v>
+        <v>59.44</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8</v>
+        <v>0.32</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0314</v>
+        <v>0.0054</v>
       </c>
       <c r="H18" t="n">
-        <v>4.01</v>
+        <v>3.91</v>
       </c>
       <c r="I18" t="n">
-        <v>54.65</v>
+        <v>51.75</v>
       </c>
       <c r="J18" t="n">
-        <v>55.24</v>
+        <v>55.79</v>
       </c>
       <c r="K18" t="n">
-        <v>56.34</v>
+        <v>57.11</v>
       </c>
       <c r="L18" t="n">
-        <v>57.45</v>
+        <v>58.44</v>
       </c>
       <c r="M18" t="n">
-        <v>58.3</v>
+        <v>61.12</v>
       </c>
       <c r="N18" t="n">
-        <v>59.14</v>
+        <v>63.81</v>
       </c>
       <c r="O18" t="n">
-        <v>60.5</v>
+        <v>63.78</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2013,25 +2017,21 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2043,57 +2043,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>59</v>
+        <v>59.01</v>
       </c>
       <c r="C19" t="n">
-        <v>62.36</v>
+        <v>61.36</v>
       </c>
       <c r="D19" t="n">
-        <v>58.45</v>
+        <v>58.7</v>
       </c>
       <c r="E19" t="n">
-        <v>59.44</v>
+        <v>61.07</v>
       </c>
       <c r="F19" t="n">
-        <v>0.32</v>
+        <v>1.63</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0274</v>
       </c>
       <c r="H19" t="n">
-        <v>3.91</v>
+        <v>2.66</v>
       </c>
       <c r="I19" t="n">
-        <v>51.75</v>
+        <v>54.54</v>
       </c>
       <c r="J19" t="n">
-        <v>55.79</v>
+        <v>55.05</v>
       </c>
       <c r="K19" t="n">
-        <v>57.11</v>
+        <v>57.48</v>
       </c>
       <c r="L19" t="n">
-        <v>58.44</v>
+        <v>59.92</v>
       </c>
       <c r="M19" t="n">
-        <v>61.12</v>
+        <v>61.39</v>
       </c>
       <c r="N19" t="n">
-        <v>63.81</v>
+        <v>62.87</v>
       </c>
       <c r="O19" t="n">
-        <v>63.78</v>
+        <v>66.27</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2104,14 +2104,14 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U19" s="8" t="n">
@@ -2127,57 +2127,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>59.01</v>
+        <v>61.22</v>
       </c>
       <c r="C20" t="n">
-        <v>61.36</v>
+        <v>66.48</v>
       </c>
       <c r="D20" t="n">
-        <v>58.7</v>
+        <v>60.14</v>
       </c>
       <c r="E20" t="n">
-        <v>61.07</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>1.63</v>
+        <v>4.14</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0678</v>
       </c>
       <c r="H20" t="n">
-        <v>2.66</v>
+        <v>6.34</v>
       </c>
       <c r="I20" t="n">
-        <v>54.54</v>
+        <v>56.04</v>
       </c>
       <c r="J20" t="n">
-        <v>55.05</v>
+        <v>58.93</v>
       </c>
       <c r="K20" t="n">
-        <v>57.48</v>
+        <v>59.74</v>
       </c>
       <c r="L20" t="n">
-        <v>59.92</v>
+        <v>60.55</v>
       </c>
       <c r="M20" t="n">
-        <v>61.39</v>
+        <v>62.4</v>
       </c>
       <c r="N20" t="n">
-        <v>62.87</v>
+        <v>64.25</v>
       </c>
       <c r="O20" t="n">
-        <v>66.27</v>
+        <v>64.02</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2188,80 +2188,80 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>61.22</v>
+        <v>64.72</v>
       </c>
       <c r="C21" t="n">
-        <v>66.48</v>
+        <v>65.53</v>
       </c>
       <c r="D21" t="n">
-        <v>60.14</v>
+        <v>61.12</v>
       </c>
       <c r="E21" t="n">
-        <v>65.20999999999999</v>
+        <v>63.55</v>
       </c>
       <c r="F21" t="n">
-        <v>4.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0678</v>
+        <v>-0.0255</v>
       </c>
       <c r="H21" t="n">
-        <v>6.34</v>
+        <v>4.41</v>
       </c>
       <c r="I21" t="n">
-        <v>56.04</v>
+        <v>53.8</v>
       </c>
       <c r="J21" t="n">
-        <v>58.93</v>
+        <v>59.82</v>
       </c>
       <c r="K21" t="n">
-        <v>59.74</v>
+        <v>62.04</v>
       </c>
       <c r="L21" t="n">
-        <v>60.55</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>62.4</v>
+        <v>68.38</v>
       </c>
       <c r="N21" t="n">
-        <v>64.25</v>
+        <v>72.5</v>
       </c>
       <c r="O21" t="n">
-        <v>64.02</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2269,83 +2269,83 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>64.72</v>
+        <v>62.99</v>
       </c>
       <c r="C22" t="n">
-        <v>65.53</v>
+        <v>65.83</v>
       </c>
       <c r="D22" t="n">
-        <v>61.12</v>
+        <v>62.14</v>
       </c>
       <c r="E22" t="n">
-        <v>63.55</v>
+        <v>62.89</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.66</v>
+        <v>-0.66</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0255</v>
+        <v>-0.0104</v>
       </c>
       <c r="H22" t="n">
-        <v>4.41</v>
+        <v>3.69</v>
       </c>
       <c r="I22" t="n">
-        <v>53.8</v>
+        <v>56.71</v>
       </c>
       <c r="J22" t="n">
-        <v>59.82</v>
+        <v>59.25</v>
       </c>
       <c r="K22" t="n">
-        <v>62.04</v>
+        <v>61.34</v>
       </c>
       <c r="L22" t="n">
-        <v>64.26000000000001</v>
+        <v>63.44</v>
       </c>
       <c r="M22" t="n">
-        <v>68.38</v>
+        <v>65.75</v>
       </c>
       <c r="N22" t="n">
-        <v>72.5</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>72.81999999999999</v>
+        <v>69.94</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2353,19 +2353,19 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2379,57 +2379,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>62.99</v>
+        <v>63.3</v>
       </c>
       <c r="C23" t="n">
-        <v>65.83</v>
+        <v>67.05</v>
       </c>
       <c r="D23" t="n">
-        <v>62.14</v>
+        <v>61.87</v>
       </c>
       <c r="E23" t="n">
-        <v>62.89</v>
+        <v>66.39</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.66</v>
+        <v>3.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0557</v>
       </c>
       <c r="H23" t="n">
-        <v>3.69</v>
+        <v>5.18</v>
       </c>
       <c r="I23" t="n">
-        <v>56.71</v>
+        <v>58.45</v>
       </c>
       <c r="J23" t="n">
-        <v>59.25</v>
+        <v>58.65</v>
       </c>
       <c r="K23" t="n">
-        <v>61.34</v>
+        <v>61.04</v>
       </c>
       <c r="L23" t="n">
         <v>63.44</v>
       </c>
       <c r="M23" t="n">
-        <v>65.75</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>68.06999999999999</v>
+        <v>66.03</v>
       </c>
       <c r="O23" t="n">
-        <v>69.94</v>
+        <v>69.52</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2450,8 +2450,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2470,50 +2472,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>63.3</v>
+        <v>65.89</v>
       </c>
       <c r="C24" t="n">
-        <v>67.05</v>
+        <v>67.83</v>
       </c>
       <c r="D24" t="n">
-        <v>61.87</v>
+        <v>63.6</v>
       </c>
       <c r="E24" t="n">
-        <v>66.39</v>
+        <v>67.02</v>
       </c>
       <c r="F24" t="n">
-        <v>3.5</v>
+        <v>0.63</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0557</v>
+        <v>0.0095</v>
       </c>
       <c r="H24" t="n">
-        <v>5.18</v>
+        <v>4.23</v>
       </c>
       <c r="I24" t="n">
-        <v>58.45</v>
+        <v>56.69</v>
       </c>
       <c r="J24" t="n">
-        <v>58.65</v>
+        <v>62.17</v>
       </c>
       <c r="K24" t="n">
-        <v>61.04</v>
+        <v>63.8</v>
       </c>
       <c r="L24" t="n">
-        <v>63.44</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>64.73999999999999</v>
+        <v>68.98</v>
       </c>
       <c r="N24" t="n">
-        <v>66.03</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>69.52</v>
+        <v>72.23</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2521,23 +2523,21 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2547,59 +2547,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65.89</v>
+        <v>75</v>
       </c>
       <c r="C25" t="n">
-        <v>67.83</v>
+        <v>92.61</v>
       </c>
       <c r="D25" t="n">
-        <v>63.6</v>
+        <v>69.2</v>
       </c>
       <c r="E25" t="n">
-        <v>67.02</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.63</v>
+        <v>23.88</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.3563</v>
       </c>
       <c r="H25" t="n">
-        <v>4.23</v>
+        <v>23.41</v>
       </c>
       <c r="I25" t="n">
-        <v>56.69</v>
+        <v>59.37</v>
       </c>
       <c r="J25" t="n">
-        <v>62.17</v>
+        <v>63.44</v>
       </c>
       <c r="K25" t="n">
-        <v>63.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>65.43000000000001</v>
+        <v>66.37</v>
       </c>
       <c r="M25" t="n">
-        <v>68.98</v>
+        <v>69.13</v>
       </c>
       <c r="N25" t="n">
-        <v>72.54000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>72.23</v>
+        <v>72.06</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2607,24 +2603,28 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
@@ -2636,50 +2636,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C26" t="n">
-        <v>92.61</v>
+        <v>119.48</v>
       </c>
       <c r="D26" t="n">
-        <v>69.2</v>
+        <v>76.73</v>
       </c>
       <c r="E26" t="n">
-        <v>90.90000000000001</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>23.88</v>
+        <v>7.81</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.3563</v>
+        <v>0.0859</v>
       </c>
       <c r="H26" t="n">
-        <v>23.41</v>
+        <v>42.75</v>
       </c>
       <c r="I26" t="n">
-        <v>59.37</v>
+        <v>45.79</v>
       </c>
       <c r="J26" t="n">
-        <v>63.44</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>64.90000000000001</v>
+        <v>79.19</v>
       </c>
       <c r="L26" t="n">
-        <v>66.37</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>69.13</v>
+        <v>102.61</v>
       </c>
       <c r="N26" t="n">
-        <v>71.90000000000001</v>
+        <v>119.31</v>
       </c>
       <c r="O26" t="n">
-        <v>72.06</v>
+        <v>116.02</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2687,27 +2687,29 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
+      <c r="V26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W26" s="9" t="inlineStr">
@@ -2720,50 +2722,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>98</v>
+        <v>100.93</v>
       </c>
       <c r="C27" t="n">
-        <v>119.48</v>
+        <v>102.44</v>
       </c>
       <c r="D27" t="n">
-        <v>76.73</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>98.70999999999999</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>7.81</v>
+        <v>-0.39</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0859</v>
+        <v>-0.004</v>
       </c>
       <c r="H27" t="n">
-        <v>42.75</v>
+        <v>10.48</v>
       </c>
       <c r="I27" t="n">
-        <v>45.79</v>
+        <v>33.98</v>
       </c>
       <c r="J27" t="n">
-        <v>72.48999999999999</v>
+        <v>56.26</v>
       </c>
       <c r="K27" t="n">
-        <v>79.19</v>
+        <v>77.33</v>
       </c>
       <c r="L27" t="n">
-        <v>85.90000000000001</v>
+        <v>98.41</v>
       </c>
       <c r="M27" t="n">
-        <v>102.61</v>
+        <v>120.08</v>
       </c>
       <c r="N27" t="n">
-        <v>119.31</v>
+        <v>141.76</v>
       </c>
       <c r="O27" t="n">
-        <v>116.02</v>
+        <v>162.23</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2771,98 +2773,98 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>100.93</v>
+        <v>100.51</v>
       </c>
       <c r="C28" t="n">
-        <v>102.44</v>
+        <v>101.67</v>
       </c>
       <c r="D28" t="n">
-        <v>91.95999999999999</v>
+        <v>84.37</v>
       </c>
       <c r="E28" t="n">
-        <v>98.31999999999999</v>
+        <v>99.64</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.39</v>
+        <v>1.32</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0134</v>
       </c>
       <c r="H28" t="n">
-        <v>10.48</v>
+        <v>17.3</v>
       </c>
       <c r="I28" t="n">
-        <v>33.98</v>
+        <v>81.48</v>
       </c>
       <c r="J28" t="n">
-        <v>56.26</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>77.33</v>
+        <v>93.08</v>
       </c>
       <c r="L28" t="n">
-        <v>98.41</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>120.08</v>
+        <v>103.56</v>
       </c>
       <c r="N28" t="n">
-        <v>141.76</v>
+        <v>109.36</v>
       </c>
       <c r="O28" t="n">
-        <v>162.23</v>
+        <v>112.92</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2888,71 +2890,69 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>100.51</v>
+        <v>102.6</v>
       </c>
       <c r="C29" t="n">
-        <v>101.67</v>
+        <v>113.97</v>
       </c>
       <c r="D29" t="n">
-        <v>84.37</v>
+        <v>96.5</v>
       </c>
       <c r="E29" t="n">
-        <v>99.64</v>
+        <v>111.54</v>
       </c>
       <c r="F29" t="n">
-        <v>1.32</v>
+        <v>11.9</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.1194</v>
       </c>
       <c r="H29" t="n">
-        <v>17.3</v>
+        <v>17.47</v>
       </c>
       <c r="I29" t="n">
-        <v>81.48</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>88.40000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>93.08</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>97.76000000000001</v>
+        <v>96.33</v>
       </c>
       <c r="M29" t="n">
-        <v>103.56</v>
+        <v>108.29</v>
       </c>
       <c r="N29" t="n">
-        <v>109.36</v>
+        <v>120.25</v>
       </c>
       <c r="O29" t="n">
-        <v>112.92</v>
+        <v>118.97</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2965,78 +2965,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>102.6</v>
+        <v>112.96</v>
       </c>
       <c r="C30" t="n">
-        <v>113.97</v>
+        <v>117.63</v>
       </c>
       <c r="D30" t="n">
-        <v>96.5</v>
+        <v>91.05</v>
       </c>
       <c r="E30" t="n">
-        <v>111.54</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>11.9</v>
+        <v>-14.97</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.1194</v>
+        <v>-0.1342</v>
       </c>
       <c r="H30" t="n">
-        <v>17.47</v>
+        <v>26.58</v>
       </c>
       <c r="I30" t="n">
-        <v>67.06999999999999</v>
+        <v>79.03</v>
       </c>
       <c r="J30" t="n">
-        <v>85.65000000000001</v>
+        <v>97.22</v>
       </c>
       <c r="K30" t="n">
-        <v>90.98999999999999</v>
+        <v>102.81</v>
       </c>
       <c r="L30" t="n">
-        <v>96.33</v>
+        <v>108.39</v>
       </c>
       <c r="M30" t="n">
-        <v>108.29</v>
+        <v>120.28</v>
       </c>
       <c r="N30" t="n">
-        <v>120.25</v>
+        <v>132.16</v>
       </c>
       <c r="O30" t="n">
-        <v>118.97</v>
+        <v>131.44</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3044,75 +3042,77 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>112.96</v>
+        <v>102</v>
       </c>
       <c r="C31" t="n">
-        <v>117.63</v>
+        <v>105.63</v>
       </c>
       <c r="D31" t="n">
-        <v>91.05</v>
+        <v>80.56</v>
       </c>
       <c r="E31" t="n">
-        <v>96.56999999999999</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>-14.97</v>
+        <v>-12.72</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.1342</v>
+        <v>-0.1317</v>
       </c>
       <c r="H31" t="n">
-        <v>26.58</v>
+        <v>25.07</v>
       </c>
       <c r="I31" t="n">
-        <v>79.03</v>
+        <v>64.47</v>
       </c>
       <c r="J31" t="n">
-        <v>97.22</v>
+        <v>66.11</v>
       </c>
       <c r="K31" t="n">
-        <v>102.81</v>
+        <v>83.28</v>
       </c>
       <c r="L31" t="n">
-        <v>108.39</v>
+        <v>100.45</v>
       </c>
       <c r="M31" t="n">
-        <v>120.28</v>
+        <v>109.86</v>
       </c>
       <c r="N31" t="n">
-        <v>132.16</v>
+        <v>119.26</v>
       </c>
       <c r="O31" t="n">
-        <v>131.44</v>
+        <v>144.21</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3131,59 +3131,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C32" t="n">
-        <v>105.63</v>
+        <v>98.39</v>
       </c>
       <c r="D32" t="n">
-        <v>80.56</v>
+        <v>87.02</v>
       </c>
       <c r="E32" t="n">
-        <v>83.84999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>-12.72</v>
+        <v>10.55</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.1317</v>
+        <v>0.1258</v>
       </c>
       <c r="H32" t="n">
-        <v>25.07</v>
+        <v>11.37</v>
       </c>
       <c r="I32" t="n">
-        <v>64.47</v>
+        <v>55.49</v>
       </c>
       <c r="J32" t="n">
-        <v>66.11</v>
+        <v>54.16</v>
       </c>
       <c r="K32" t="n">
-        <v>83.28</v>
+        <v>71.31</v>
       </c>
       <c r="L32" t="n">
-        <v>100.45</v>
+        <v>88.47</v>
       </c>
       <c r="M32" t="n">
-        <v>109.86</v>
+        <v>96.38</v>
       </c>
       <c r="N32" t="n">
-        <v>119.26</v>
+        <v>104.3</v>
       </c>
       <c r="O32" t="n">
-        <v>144.21</v>
+        <v>130.7</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3191,19 +3187,19 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3215,55 +3211,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>89</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>98.39</v>
+        <v>110.93</v>
       </c>
       <c r="D33" t="n">
-        <v>87.02</v>
+        <v>94.59</v>
       </c>
       <c r="E33" t="n">
-        <v>94.40000000000001</v>
+        <v>101.94</v>
       </c>
       <c r="F33" t="n">
-        <v>10.55</v>
+        <v>7.54</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.1258</v>
+        <v>0.0799</v>
       </c>
       <c r="H33" t="n">
-        <v>11.37</v>
+        <v>16.34</v>
       </c>
       <c r="I33" t="n">
-        <v>55.49</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>54.16</v>
+        <v>83.88</v>
       </c>
       <c r="K33" t="n">
-        <v>71.31</v>
+        <v>88.72</v>
       </c>
       <c r="L33" t="n">
-        <v>88.47</v>
+        <v>93.55</v>
       </c>
       <c r="M33" t="n">
-        <v>96.38</v>
+        <v>100.09</v>
       </c>
       <c r="N33" t="n">
-        <v>104.3</v>
+        <v>106.62</v>
       </c>
       <c r="O33" t="n">
-        <v>130.7</v>
+        <v>109.76</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3274,7 +3274,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3284,11 +3284,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W33" s="11" t="inlineStr">
         <is>
@@ -3297,57 +3301,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>95.59999999999999</v>
+        <v>99.73</v>
       </c>
       <c r="C34" t="n">
-        <v>110.93</v>
+        <v>107.46</v>
       </c>
       <c r="D34" t="n">
-        <v>94.59</v>
+        <v>88.66</v>
       </c>
       <c r="E34" t="n">
-        <v>101.94</v>
+        <v>95.42</v>
       </c>
       <c r="F34" t="n">
-        <v>7.54</v>
+        <v>-6.52</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0799</v>
+        <v>-0.064</v>
       </c>
       <c r="H34" t="n">
-        <v>16.34</v>
+        <v>18.8</v>
       </c>
       <c r="I34" t="n">
-        <v>75.65000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="J34" t="n">
-        <v>83.88</v>
+        <v>85.19</v>
       </c>
       <c r="K34" t="n">
-        <v>88.72</v>
+        <v>93.77</v>
       </c>
       <c r="L34" t="n">
-        <v>93.55</v>
+        <v>102.35</v>
       </c>
       <c r="M34" t="n">
-        <v>100.09</v>
+        <v>110.11</v>
       </c>
       <c r="N34" t="n">
-        <v>106.62</v>
+        <v>117.87</v>
       </c>
       <c r="O34" t="n">
-        <v>109.76</v>
+        <v>127.27</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3355,87 +3359,79 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>99.73</v>
+        <v>98.19</v>
       </c>
       <c r="C35" t="n">
-        <v>107.46</v>
+        <v>106</v>
       </c>
       <c r="D35" t="n">
-        <v>88.66</v>
+        <v>96.13</v>
       </c>
       <c r="E35" t="n">
-        <v>95.42</v>
+        <v>105.42</v>
       </c>
       <c r="F35" t="n">
-        <v>-6.52</v>
+        <v>10</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.064</v>
+        <v>0.1048</v>
       </c>
       <c r="H35" t="n">
-        <v>18.8</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>78.25</v>
+        <v>69.86</v>
       </c>
       <c r="J35" t="n">
-        <v>85.19</v>
+        <v>75.3</v>
       </c>
       <c r="K35" t="n">
-        <v>93.77</v>
+        <v>86.02</v>
       </c>
       <c r="L35" t="n">
-        <v>102.35</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>110.11</v>
+        <v>104.82</v>
       </c>
       <c r="N35" t="n">
-        <v>117.87</v>
+        <v>112.9</v>
       </c>
       <c r="O35" t="n">
-        <v>127.27</v>
+        <v>126.26</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3443,19 +3439,19 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3467,74 +3463,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>98.19</v>
+        <v>106</v>
       </c>
       <c r="C36" t="n">
-        <v>106</v>
+        <v>109.47</v>
       </c>
       <c r="D36" t="n">
-        <v>96.13</v>
+        <v>94.73</v>
       </c>
       <c r="E36" t="n">
-        <v>105.42</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>-8.82</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.1048</v>
+        <v>-0.0837</v>
       </c>
       <c r="H36" t="n">
-        <v>9.869999999999999</v>
+        <v>14.74</v>
       </c>
       <c r="I36" t="n">
-        <v>69.86</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>75.3</v>
+        <v>97.73</v>
       </c>
       <c r="K36" t="n">
-        <v>86.02</v>
+        <v>100.48</v>
       </c>
       <c r="L36" t="n">
-        <v>96.73999999999999</v>
+        <v>103.24</v>
       </c>
       <c r="M36" t="n">
-        <v>104.82</v>
+        <v>110.35</v>
       </c>
       <c r="N36" t="n">
-        <v>112.9</v>
+        <v>117.47</v>
       </c>
       <c r="O36" t="n">
-        <v>126.26</v>
+        <v>115.87</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3549,72 +3551,70 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>106</v>
+        <v>93.88</v>
       </c>
       <c r="C37" t="n">
-        <v>109.47</v>
+        <v>94.7</v>
       </c>
       <c r="D37" t="n">
-        <v>94.73</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>96.59999999999999</v>
+        <v>87.36</v>
       </c>
       <c r="F37" t="n">
-        <v>-8.82</v>
+        <v>-9.24</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0837</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>14.74</v>
+        <v>8.35</v>
       </c>
       <c r="I37" t="n">
-        <v>86.26000000000001</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>97.73</v>
+        <v>79.11</v>
       </c>
       <c r="K37" t="n">
-        <v>100.48</v>
+        <v>89.23</v>
       </c>
       <c r="L37" t="n">
-        <v>103.24</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>110.35</v>
+        <v>103.97</v>
       </c>
       <c r="N37" t="n">
-        <v>117.47</v>
+        <v>108.59</v>
       </c>
       <c r="O37" t="n">
-        <v>115.87</v>
+        <v>124.21</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3633,59 +3633,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>93.88</v>
+        <v>88.5</v>
       </c>
       <c r="C38" t="n">
-        <v>94.7</v>
+        <v>97</v>
       </c>
       <c r="D38" t="n">
-        <v>86.34999999999999</v>
+        <v>88.45</v>
       </c>
       <c r="E38" t="n">
-        <v>87.36</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-9.24</v>
+        <v>3.18</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.0364</v>
       </c>
       <c r="H38" t="n">
-        <v>8.35</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>79.98999999999999</v>
+        <v>78</v>
       </c>
       <c r="J38" t="n">
-        <v>79.11</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>89.23</v>
+        <v>83.19</v>
       </c>
       <c r="L38" t="n">
-        <v>99.34999999999999</v>
+        <v>88.94</v>
       </c>
       <c r="M38" t="n">
-        <v>103.97</v>
+        <v>91.53</v>
       </c>
       <c r="N38" t="n">
-        <v>108.59</v>
+        <v>94.13</v>
       </c>
       <c r="O38" t="n">
-        <v>124.21</v>
+        <v>103.05</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3693,21 +3689,23 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3717,55 +3715,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>88.5</v>
+        <v>93</v>
       </c>
       <c r="C39" t="n">
-        <v>97</v>
+        <v>95.47</v>
       </c>
       <c r="D39" t="n">
-        <v>88.45</v>
+        <v>83.2</v>
       </c>
       <c r="E39" t="n">
-        <v>90.54000000000001</v>
+        <v>84.88</v>
       </c>
       <c r="F39" t="n">
-        <v>3.18</v>
+        <v>-5.66</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0364</v>
+        <v>-0.0625</v>
       </c>
       <c r="H39" t="n">
-        <v>8.550000000000001</v>
+        <v>12.27</v>
       </c>
       <c r="I39" t="n">
-        <v>78</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>77.43000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>83.19</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>88.94</v>
+        <v>91.63</v>
       </c>
       <c r="M39" t="n">
-        <v>91.53</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>94.13</v>
+        <v>98</v>
       </c>
       <c r="O39" t="n">
-        <v>103.05</v>
+        <v>105.55</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3773,24 +3775,24 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3799,59 +3801,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>93</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>95.47</v>
+        <v>82.42</v>
       </c>
       <c r="D40" t="n">
-        <v>83.2</v>
+        <v>73.58</v>
       </c>
       <c r="E40" t="n">
-        <v>84.88</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>-5.66</v>
+        <v>-7.34</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0625</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>12.27</v>
+        <v>8.84</v>
       </c>
       <c r="I40" t="n">
-        <v>79.90000000000001</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>80.90000000000001</v>
+        <v>70.38</v>
       </c>
       <c r="K40" t="n">
-        <v>86.26000000000001</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>91.63</v>
+        <v>87.11</v>
       </c>
       <c r="M40" t="n">
-        <v>94.81999999999999</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>98</v>
+        <v>94.92</v>
       </c>
       <c r="O40" t="n">
-        <v>105.55</v>
+        <v>107.74</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3864,15 +3862,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3890,63 +3886,65 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>81.40000000000001</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>82.42</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>73.58</v>
+        <v>68.56</v>
       </c>
       <c r="E41" t="n">
-        <v>77.54000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="F41" t="n">
-        <v>-7.34</v>
+        <v>-8.31</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.1072</v>
       </c>
       <c r="H41" t="n">
-        <v>8.84</v>
+        <v>10.4</v>
       </c>
       <c r="I41" t="n">
-        <v>70.93000000000001</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>70.38</v>
+        <v>68.47</v>
       </c>
       <c r="K41" t="n">
-        <v>78.73999999999999</v>
+        <v>73.12</v>
       </c>
       <c r="L41" t="n">
-        <v>87.11</v>
+        <v>77.77</v>
       </c>
       <c r="M41" t="n">
-        <v>91.01000000000001</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>94.92</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>107.74</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3970,67 +3968,63 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>78.93000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="C42" t="n">
-        <v>78.95999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>68.56</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>69.23</v>
+        <v>68.78</v>
       </c>
       <c r="F42" t="n">
-        <v>-8.31</v>
+        <v>-0.45</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.1072</v>
+        <v>-0.0065</v>
       </c>
       <c r="H42" t="n">
-        <v>10.4</v>
+        <v>4.56</v>
       </c>
       <c r="I42" t="n">
-        <v>64.73999999999999</v>
+        <v>58.16</v>
       </c>
       <c r="J42" t="n">
-        <v>68.47</v>
+        <v>56.57</v>
       </c>
       <c r="K42" t="n">
-        <v>73.12</v>
+        <v>64.03</v>
       </c>
       <c r="L42" t="n">
-        <v>77.77</v>
+        <v>71.5</v>
       </c>
       <c r="M42" t="n">
-        <v>81.95999999999999</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>86.15000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="O42" t="n">
-        <v>91.26000000000001</v>
+        <v>89.36</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4052,50 +4046,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>70.5</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>71.59999999999999</v>
+        <v>76.08</v>
       </c>
       <c r="D43" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>68.78</v>
+        <v>71.41</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.45</v>
+        <v>2.63</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0382</v>
       </c>
       <c r="H43" t="n">
-        <v>4.56</v>
+        <v>8.26</v>
       </c>
       <c r="I43" t="n">
-        <v>58.16</v>
+        <v>62.48</v>
       </c>
       <c r="J43" t="n">
-        <v>56.57</v>
+        <v>63.95</v>
       </c>
       <c r="K43" t="n">
-        <v>64.03</v>
+        <v>66.5</v>
       </c>
       <c r="L43" t="n">
-        <v>71.5</v>
+        <v>69.05</v>
       </c>
       <c r="M43" t="n">
-        <v>74.43000000000001</v>
+        <v>71.06</v>
       </c>
       <c r="N43" t="n">
-        <v>77.37</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O43" t="n">
-        <v>89.36</v>
+        <v>76.16</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4108,14 +4102,18 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4125,55 +4123,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>68.68000000000001</v>
+        <v>73.69</v>
       </c>
       <c r="C44" t="n">
-        <v>76.08</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>67.81999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="E44" t="n">
-        <v>71.41</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>2.63</v>
+        <v>11.08</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0382</v>
+        <v>0.1552</v>
       </c>
       <c r="H44" t="n">
-        <v>8.26</v>
+        <v>10.15</v>
       </c>
       <c r="I44" t="n">
-        <v>62.48</v>
+        <v>59.56</v>
       </c>
       <c r="J44" t="n">
-        <v>63.95</v>
+        <v>62.88</v>
       </c>
       <c r="K44" t="n">
-        <v>66.5</v>
+        <v>67.28</v>
       </c>
       <c r="L44" t="n">
-        <v>69.05</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>71.06</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>73.06999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>76.16</v>
+        <v>84.34</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4184,82 +4186,80 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W44" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>73.69</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>82.76000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="D45" t="n">
-        <v>72.61</v>
+        <v>80.27</v>
       </c>
       <c r="E45" t="n">
-        <v>82.48999999999999</v>
+        <v>89.31</v>
       </c>
       <c r="F45" t="n">
-        <v>11.08</v>
+        <v>6.82</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.1552</v>
+        <v>0.0827</v>
       </c>
       <c r="H45" t="n">
-        <v>10.15</v>
+        <v>13.23</v>
       </c>
       <c r="I45" t="n">
-        <v>59.56</v>
+        <v>62.46</v>
       </c>
       <c r="J45" t="n">
-        <v>62.88</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>67.28</v>
+        <v>77.41</v>
       </c>
       <c r="L45" t="n">
-        <v>71.68000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="M45" t="n">
-        <v>75.54000000000001</v>
+        <v>87.56</v>
       </c>
       <c r="N45" t="n">
-        <v>79.40000000000001</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>84.34</v>
+        <v>92.91</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4270,24 +4270,22 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="W45" s="9" t="inlineStr">
@@ -4300,50 +4298,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>83.76000000000001</v>
+        <v>86.12</v>
       </c>
       <c r="C46" t="n">
-        <v>93.5</v>
+        <v>86.87</v>
       </c>
       <c r="D46" t="n">
-        <v>80.27</v>
+        <v>77.78</v>
       </c>
       <c r="E46" t="n">
-        <v>89.31</v>
+        <v>84.67</v>
       </c>
       <c r="F46" t="n">
-        <v>6.82</v>
+        <v>-4.64</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0827</v>
+        <v>-0.052</v>
       </c>
       <c r="H46" t="n">
-        <v>13.23</v>
+        <v>9.09</v>
       </c>
       <c r="I46" t="n">
-        <v>62.46</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>74.73999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>77.41</v>
+        <v>82.69</v>
       </c>
       <c r="L46" t="n">
-        <v>80.09</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>87.56</v>
+        <v>95.92</v>
       </c>
       <c r="N46" t="n">
-        <v>95.04000000000001</v>
+        <v>103.75</v>
       </c>
       <c r="O46" t="n">
-        <v>92.91</v>
+        <v>106.73</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4351,94 +4349,98 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V46" s="8" t="n">
+        <v/>
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>86.12</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>86.87</v>
+        <v>82.33</v>
       </c>
       <c r="D47" t="n">
-        <v>77.78</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>84.67</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>-4.64</v>
+        <v>-6.49</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.0767</v>
       </c>
       <c r="H47" t="n">
-        <v>9.09</v>
+        <v>8.09</v>
       </c>
       <c r="I47" t="n">
-        <v>67.04000000000001</v>
+        <v>68.69</v>
       </c>
       <c r="J47" t="n">
-        <v>77.29000000000001</v>
+        <v>76.75</v>
       </c>
       <c r="K47" t="n">
-        <v>82.69</v>
+        <v>80.12</v>
       </c>
       <c r="L47" t="n">
-        <v>88.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="M47" t="n">
-        <v>95.92</v>
+        <v>89.22</v>
       </c>
       <c r="N47" t="n">
-        <v>103.75</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>106.73</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4466,72 +4468,70 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>80.09999999999999</v>
+        <v>78.42</v>
       </c>
       <c r="C48" t="n">
-        <v>82.33</v>
+        <v>84.61</v>
       </c>
       <c r="D48" t="n">
-        <v>74.23999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>78.18000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>-6.49</v>
+        <v>4.22</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0767</v>
+        <v>0.054</v>
       </c>
       <c r="H48" t="n">
-        <v>8.09</v>
+        <v>6.82</v>
       </c>
       <c r="I48" t="n">
-        <v>68.69</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>76.75</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>80.12</v>
+        <v>74.13</v>
       </c>
       <c r="L48" t="n">
-        <v>83.5</v>
+        <v>78.23</v>
       </c>
       <c r="M48" t="n">
-        <v>89.22</v>
+        <v>82.23</v>
       </c>
       <c r="N48" t="n">
-        <v>94.93000000000001</v>
+        <v>86.22</v>
       </c>
       <c r="O48" t="n">
-        <v>95.95999999999999</v>
+        <v>90.42</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4543,59 +4543,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>78.42</v>
+        <v>82.53</v>
       </c>
       <c r="C49" t="n">
-        <v>84.61</v>
+        <v>89</v>
       </c>
       <c r="D49" t="n">
-        <v>77.79000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="E49" t="n">
-        <v>82.40000000000001</v>
+        <v>87.06</v>
       </c>
       <c r="F49" t="n">
-        <v>4.22</v>
+        <v>4.66</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.054</v>
+        <v>0.0566</v>
       </c>
       <c r="H49" t="n">
-        <v>6.82</v>
+        <v>7.5</v>
       </c>
       <c r="I49" t="n">
-        <v>66.15000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="J49" t="n">
-        <v>70.04000000000001</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>74.13</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>78.23</v>
+        <v>81.8</v>
       </c>
       <c r="M49" t="n">
-        <v>82.23</v>
+        <v>85.81</v>
       </c>
       <c r="N49" t="n">
-        <v>86.22</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="O49" t="n">
-        <v>90.42</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4606,7 +4602,7 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4632,69 +4628,71 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>82.53</v>
+        <v>86.5</v>
       </c>
       <c r="C50" t="n">
-        <v>89</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>81.5</v>
+        <v>79.62</v>
       </c>
       <c r="E50" t="n">
-        <v>87.06</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>4.66</v>
+        <v>-3.66</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0566</v>
+        <v>-0.042</v>
       </c>
       <c r="H50" t="n">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="I50" t="n">
-        <v>70.97</v>
+        <v>74</v>
       </c>
       <c r="J50" t="n">
-        <v>76.18000000000001</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>78.98999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="L50" t="n">
-        <v>81.8</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="M50" t="n">
-        <v>85.81</v>
+        <v>90.81</v>
       </c>
       <c r="N50" t="n">
-        <v>89.81999999999999</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="O50" t="n">
-        <v>91.43000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4707,80 +4705,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>86.5</v>
+        <v>84.69</v>
       </c>
       <c r="C51" t="n">
-        <v>86.56999999999999</v>
+        <v>93.14</v>
       </c>
       <c r="D51" t="n">
-        <v>79.62</v>
+        <v>84.11</v>
       </c>
       <c r="E51" t="n">
-        <v>83.40000000000001</v>
+        <v>91.48</v>
       </c>
       <c r="F51" t="n">
-        <v>-3.66</v>
+        <v>8.08</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.042</v>
+        <v>0.0969</v>
       </c>
       <c r="H51" t="n">
-        <v>6.95</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>74</v>
+        <v>72.67</v>
       </c>
       <c r="J51" t="n">
-        <v>80.45999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>83.31</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>86.15000000000001</v>
+        <v>83.25</v>
       </c>
       <c r="M51" t="n">
-        <v>90.81</v>
+        <v>86.88</v>
       </c>
       <c r="N51" t="n">
-        <v>95.45999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="O51" t="n">
-        <v>96.5</v>
+        <v>93.52</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
@@ -4789,59 +4791,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>84.69</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>93.14</v>
+        <v>104.46</v>
       </c>
       <c r="D52" t="n">
-        <v>84.11</v>
+        <v>90.87</v>
       </c>
       <c r="E52" t="n">
-        <v>91.48</v>
+        <v>100.05</v>
       </c>
       <c r="F52" t="n">
-        <v>8.08</v>
+        <v>8.57</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0969</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>9.029999999999999</v>
+        <v>13.59</v>
       </c>
       <c r="I52" t="n">
-        <v>72.67</v>
+        <v>75.08</v>
       </c>
       <c r="J52" t="n">
-        <v>76.59999999999999</v>
+        <v>83.88</v>
       </c>
       <c r="K52" t="n">
-        <v>79.93000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="L52" t="n">
-        <v>83.25</v>
+        <v>90.05</v>
       </c>
       <c r="M52" t="n">
-        <v>86.88</v>
+        <v>96</v>
       </c>
       <c r="N52" t="n">
-        <v>90.5</v>
+        <v>101.94</v>
       </c>
       <c r="O52" t="n">
-        <v>93.52</v>
+        <v>102.17</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4852,7 +4850,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4867,8 +4865,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V52" s="8" t="n">
-        <v/>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
@@ -4880,50 +4880,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>92.26000000000001</v>
+        <v>102.25</v>
       </c>
       <c r="C53" t="n">
-        <v>104.46</v>
+        <v>106.75</v>
       </c>
       <c r="D53" t="n">
-        <v>90.87</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>100.05</v>
+        <v>100.3</v>
       </c>
       <c r="F53" t="n">
-        <v>8.57</v>
+        <v>0.25</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="H53" t="n">
-        <v>13.59</v>
+        <v>7.65</v>
       </c>
       <c r="I53" t="n">
-        <v>75.08</v>
+        <v>77.28</v>
       </c>
       <c r="J53" t="n">
-        <v>83.88</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>86.97</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>90.05</v>
+        <v>98.86</v>
       </c>
       <c r="M53" t="n">
-        <v>96</v>
+        <v>106.85</v>
       </c>
       <c r="N53" t="n">
-        <v>101.94</v>
+        <v>114.83</v>
       </c>
       <c r="O53" t="n">
-        <v>102.17</v>
+        <v>118.05</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4934,25 +4934,19 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
       </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
@@ -4964,63 +4958,69 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>102.25</v>
+        <v>101</v>
       </c>
       <c r="C54" t="n">
-        <v>106.75</v>
+        <v>101.08</v>
       </c>
       <c r="D54" t="n">
-        <v>99.09999999999999</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>100.3</v>
+        <v>92.41</v>
       </c>
       <c r="F54" t="n">
-        <v>0.25</v>
+        <v>-7.89</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>7.65</v>
+        <v>12.37</v>
       </c>
       <c r="I54" t="n">
-        <v>77.28</v>
+        <v>91.45</v>
       </c>
       <c r="J54" t="n">
-        <v>87.65000000000001</v>
+        <v>91.34</v>
       </c>
       <c r="K54" t="n">
-        <v>93.26000000000001</v>
+        <v>96.48</v>
       </c>
       <c r="L54" t="n">
-        <v>98.86</v>
+        <v>101.61</v>
       </c>
       <c r="M54" t="n">
-        <v>106.85</v>
+        <v>104.13</v>
       </c>
       <c r="N54" t="n">
-        <v>114.83</v>
+        <v>106.64</v>
       </c>
       <c r="O54" t="n">
-        <v>118.05</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+        <v>114.4</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5037,74 +5037,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>101</v>
+        <v>93.58</v>
       </c>
       <c r="C55" t="n">
-        <v>101.08</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>88.70999999999999</v>
+        <v>88.06</v>
       </c>
       <c r="E55" t="n">
-        <v>92.41</v>
+        <v>91.11</v>
       </c>
       <c r="F55" t="n">
-        <v>-7.89</v>
+        <v>-1.3</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0141</v>
       </c>
       <c r="H55" t="n">
-        <v>12.37</v>
+        <v>8.48</v>
       </c>
       <c r="I55" t="n">
-        <v>91.45</v>
+        <v>76.34</v>
       </c>
       <c r="J55" t="n">
-        <v>91.34</v>
+        <v>78.8</v>
       </c>
       <c r="K55" t="n">
-        <v>96.48</v>
+        <v>86.23</v>
       </c>
       <c r="L55" t="n">
-        <v>101.61</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>104.13</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>106.64</v>
+        <v>103.54</v>
       </c>
       <c r="O55" t="n">
-        <v>114.4</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>113.45</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5130,50 +5128,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>93.58</v>
+        <v>91.77</v>
       </c>
       <c r="C56" t="n">
-        <v>96.54000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="D56" t="n">
-        <v>88.06</v>
+        <v>86.86</v>
       </c>
       <c r="E56" t="n">
-        <v>91.11</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.3</v>
+        <v>0.74</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0141</v>
+        <v>0.0081</v>
       </c>
       <c r="H56" t="n">
-        <v>8.48</v>
+        <v>6.34</v>
       </c>
       <c r="I56" t="n">
-        <v>76.34</v>
+        <v>79.58</v>
       </c>
       <c r="J56" t="n">
-        <v>78.8</v>
+        <v>82.03</v>
       </c>
       <c r="K56" t="n">
-        <v>86.23</v>
+        <v>86.87</v>
       </c>
       <c r="L56" t="n">
-        <v>93.65000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="M56" t="n">
-        <v>98.59999999999999</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>103.54</v>
+        <v>99</v>
       </c>
       <c r="O56" t="n">
-        <v>113.45</v>
+        <v>105.02</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5181,12 +5179,14 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5205,57 +5205,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>91.77</v>
+        <v>91.83</v>
       </c>
       <c r="C57" t="n">
-        <v>93.2</v>
+        <v>101.9</v>
       </c>
       <c r="D57" t="n">
-        <v>86.86</v>
+        <v>89.61</v>
       </c>
       <c r="E57" t="n">
-        <v>91.84999999999999</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>0.74</v>
+        <v>7.19</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0081</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>6.34</v>
+        <v>12.29</v>
       </c>
       <c r="I57" t="n">
-        <v>79.58</v>
+        <v>80.52</v>
       </c>
       <c r="J57" t="n">
-        <v>82.03</v>
+        <v>86.42</v>
       </c>
       <c r="K57" t="n">
-        <v>86.87</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>91.7</v>
+        <v>90.94</v>
       </c>
       <c r="M57" t="n">
-        <v>95.34999999999999</v>
+        <v>95.02</v>
       </c>
       <c r="N57" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O57" t="n">
-        <v>105.02</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5263,115 +5263,35 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>91.83</v>
-      </c>
-      <c r="C58" t="n">
-        <v>96.39</v>
-      </c>
-      <c r="D58" t="n">
-        <v>89.61</v>
-      </c>
-      <c r="E58" t="n">
-        <v>96</v>
-      </c>
-      <c r="F58" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0452</v>
-      </c>
-      <c r="H58" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="I58" t="n">
-        <v>80.52</v>
-      </c>
-      <c r="J58" t="n">
-        <v>86.42</v>
-      </c>
-      <c r="K58" t="n">
-        <v>88.68000000000001</v>
-      </c>
-      <c r="L58" t="n">
-        <v>90.94</v>
-      </c>
-      <c r="M58" t="n">
-        <v>95.02</v>
-      </c>
-      <c r="N58" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="O58" t="n">
-        <v>99.54000000000001</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5225,13 +5225,13 @@
         <v>89.61</v>
       </c>
       <c r="E57" t="n">
-        <v>99.04000000000001</v>
+        <v>99.02</v>
       </c>
       <c r="F57" t="n">
-        <v>7.19</v>
+        <v>7.17</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0781</v>
       </c>
       <c r="H57" t="n">
         <v>12.29</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5225,13 +5225,13 @@
         <v>89.61</v>
       </c>
       <c r="E57" t="n">
-        <v>99.02</v>
+        <v>98.06</v>
       </c>
       <c r="F57" t="n">
-        <v>7.17</v>
+        <v>6.21</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0781</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="H57" t="n">
         <v>12.29</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5225,13 +5225,13 @@
         <v>89.61</v>
       </c>
       <c r="E57" t="n">
-        <v>98.06</v>
+        <v>97.56</v>
       </c>
       <c r="F57" t="n">
-        <v>6.21</v>
+        <v>5.71</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0622</v>
       </c>
       <c r="H57" t="n">
         <v>12.29</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -659,25 +662,25 @@
         <v>4.57</v>
       </c>
       <c r="I2" t="n">
-        <v>60.28</v>
+        <v>60.44</v>
       </c>
       <c r="J2" t="n">
-        <v>59.96</v>
+        <v>60.02</v>
       </c>
       <c r="K2" t="n">
-        <v>61.56</v>
+        <v>61.6</v>
       </c>
       <c r="L2" t="n">
-        <v>63.16</v>
+        <v>63.18</v>
       </c>
       <c r="M2" t="n">
-        <v>63.8</v>
+        <v>63.76</v>
       </c>
       <c r="N2" t="n">
-        <v>64.44</v>
+        <v>64.34</v>
       </c>
       <c r="O2" t="n">
-        <v>67</v>
+        <v>66.92</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,11 +703,13 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5225,13 +5230,13 @@
         <v>89.61</v>
       </c>
       <c r="E57" t="n">
-        <v>97.56</v>
+        <v>101.41</v>
       </c>
       <c r="F57" t="n">
-        <v>5.71</v>
+        <v>9.56</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0622</v>
+        <v>0.1041</v>
       </c>
       <c r="H57" t="n">
         <v>12.29</v>
@@ -5278,20 +5283,104 @@
       </c>
       <c r="U57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>98.23999999999999</v>
+      </c>
+      <c r="C58" t="n">
+        <v>98.59</v>
+      </c>
+      <c r="D58" t="n">
+        <v>98.04000000000001</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I58" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="J58" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="K58" t="n">
+        <v>95.27</v>
+      </c>
+      <c r="L58" t="n">
+        <v>98.58</v>
+      </c>
+      <c r="M58" t="n">
+        <v>107.56</v>
+      </c>
+      <c r="N58" t="n">
+        <v>116.53</v>
+      </c>
+      <c r="O58" t="n">
+        <v>114.19</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5308,7 +5308,7 @@
         <v>98.23999999999999</v>
       </c>
       <c r="C58" t="n">
-        <v>98.59</v>
+        <v>98.97</v>
       </c>
       <c r="D58" t="n">
         <v>98.04000000000001</v>
@@ -5323,7 +5323,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>0.55</v>
+        <v>0.93</v>
       </c>
       <c r="I58" t="n">
         <v>77.31999999999999</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>4.57</v>
       </c>
       <c r="I2" t="n">
-        <v>60.44</v>
+        <v>60.53</v>
       </c>
       <c r="J2" t="n">
-        <v>60.02</v>
+        <v>60.13</v>
       </c>
       <c r="K2" t="n">
-        <v>61.6</v>
+        <v>61.65</v>
       </c>
       <c r="L2" t="n">
-        <v>63.18</v>
+        <v>63.16</v>
       </c>
       <c r="M2" t="n">
-        <v>63.76</v>
+        <v>63.72</v>
       </c>
       <c r="N2" t="n">
-        <v>64.34</v>
+        <v>64.27</v>
       </c>
       <c r="O2" t="n">
-        <v>66.92</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5305,25 +5302,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>98.23999999999999</v>
+        <v>101.75</v>
       </c>
       <c r="C58" t="n">
-        <v>98.97</v>
+        <v>104.18</v>
       </c>
       <c r="D58" t="n">
-        <v>98.04000000000001</v>
+        <v>97.91</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>98.88</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-2.53</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0249</v>
       </c>
       <c r="H58" t="n">
-        <v>0.93</v>
+        <v>6.27</v>
       </c>
       <c r="I58" t="n">
         <v>77.31999999999999</v>
@@ -5346,10 +5343,8 @@
       <c r="O58" t="n">
         <v>114.19</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5357,9 +5352,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>4.57</v>
       </c>
       <c r="I2" t="n">
-        <v>60.53</v>
+        <v>60.65</v>
       </c>
       <c r="J2" t="n">
-        <v>60.13</v>
+        <v>60.28</v>
       </c>
       <c r="K2" t="n">
-        <v>61.65</v>
+        <v>61.7</v>
       </c>
       <c r="L2" t="n">
-        <v>63.16</v>
+        <v>63.13</v>
       </c>
       <c r="M2" t="n">
-        <v>63.72</v>
+        <v>63.66</v>
       </c>
       <c r="N2" t="n">
-        <v>64.27</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>66.73999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5305,22 +5305,22 @@
         <v>101.75</v>
       </c>
       <c r="C58" t="n">
-        <v>104.18</v>
+        <v>110.48</v>
       </c>
       <c r="D58" t="n">
-        <v>97.91</v>
+        <v>97.72</v>
       </c>
       <c r="E58" t="n">
-        <v>98.88</v>
+        <v>98.11</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.53</v>
+        <v>-3.3</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0249</v>
+        <v>-0.0325</v>
       </c>
       <c r="H58" t="n">
-        <v>6.27</v>
+        <v>12.76</v>
       </c>
       <c r="I58" t="n">
         <v>77.31999999999999</v>
@@ -5352,13 +5352,15 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5308,19 +5308,19 @@
         <v>110.48</v>
       </c>
       <c r="D58" t="n">
-        <v>97.72</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>98.11</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-3.3</v>
+        <v>-3.01</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0325</v>
+        <v>-0.0297</v>
       </c>
       <c r="H58" t="n">
-        <v>12.76</v>
+        <v>14.22</v>
       </c>
       <c r="I58" t="n">
         <v>77.31999999999999</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>4.57</v>
       </c>
       <c r="I2" t="n">
-        <v>60.65</v>
+        <v>61.55</v>
       </c>
       <c r="J2" t="n">
-        <v>60.28</v>
+        <v>61.41</v>
       </c>
       <c r="K2" t="n">
-        <v>61.7</v>
+        <v>62.15</v>
       </c>
       <c r="L2" t="n">
-        <v>63.13</v>
+        <v>62.9</v>
       </c>
       <c r="M2" t="n">
-        <v>63.66</v>
+        <v>63.21</v>
       </c>
       <c r="N2" t="n">
-        <v>64.18000000000001</v>
+        <v>63.51</v>
       </c>
       <c r="O2" t="n">
-        <v>66.5</v>
+        <v>64.7</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -5311,13 +5313,13 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>98.40000000000001</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>-3.01</v>
+        <v>-1.45</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0297</v>
+        <v>-0.0143</v>
       </c>
       <c r="H58" t="n">
         <v>14.22</v>
@@ -5352,9 +5354,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,56 +634,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62.74</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>66.42</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>61.85</v>
+        <v>60.4</v>
       </c>
       <c r="E2" t="n">
-        <v>65.72</v>
+        <v>60.88</v>
       </c>
       <c r="F2" t="n">
-        <v>3.04</v>
+        <v>-4.84</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0485</v>
+        <v>-0.0736</v>
       </c>
       <c r="H2" t="n">
-        <v>4.57</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>61.55</v>
+        <v>57.28</v>
       </c>
       <c r="J2" t="n">
-        <v>61.41</v>
+        <v>61.94</v>
       </c>
       <c r="K2" t="n">
-        <v>62.15</v>
+        <v>63.44</v>
       </c>
       <c r="L2" t="n">
-        <v>62.9</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>63.21</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>63.51</v>
+        <v>71.08</v>
       </c>
       <c r="O2" t="n">
-        <v>64.7</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -692,97 +694,85 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.06999999999999</v>
+        <v>61.14</v>
       </c>
       <c r="C3" t="n">
-        <v>65.40000000000001</v>
+        <v>62.92</v>
       </c>
       <c r="D3" t="n">
-        <v>60.4</v>
+        <v>58.22</v>
       </c>
       <c r="E3" t="n">
-        <v>60.88</v>
+        <v>58.9</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.84</v>
+        <v>-1.98</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0736</v>
+        <v>-0.0325</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I3" t="n">
-        <v>57.28</v>
+        <v>55.4</v>
       </c>
       <c r="J3" t="n">
-        <v>61.94</v>
+        <v>54.87</v>
       </c>
       <c r="K3" t="n">
-        <v>63.44</v>
+        <v>58.38</v>
       </c>
       <c r="L3" t="n">
-        <v>64.93000000000001</v>
+        <v>61.89</v>
       </c>
       <c r="M3" t="n">
-        <v>68.01000000000001</v>
+        <v>63.38</v>
       </c>
       <c r="N3" t="n">
-        <v>71.08</v>
+        <v>64.87</v>
       </c>
       <c r="O3" t="n">
-        <v>70.98999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -796,7 +786,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -806,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61.14</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
-        <v>62.92</v>
+        <v>60.17</v>
       </c>
       <c r="D4" t="n">
-        <v>58.22</v>
+        <v>56.6</v>
       </c>
       <c r="E4" t="n">
-        <v>58.9</v>
+        <v>57.54</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.98</v>
+        <v>-1.36</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0325</v>
+        <v>-0.0231</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7</v>
+        <v>3.57</v>
       </c>
       <c r="I4" t="n">
-        <v>55.4</v>
+        <v>53.52</v>
       </c>
       <c r="J4" t="n">
-        <v>54.87</v>
+        <v>53.37</v>
       </c>
       <c r="K4" t="n">
-        <v>58.38</v>
+        <v>56.55</v>
       </c>
       <c r="L4" t="n">
-        <v>61.89</v>
+        <v>59.74</v>
       </c>
       <c r="M4" t="n">
-        <v>63.38</v>
+        <v>61.25</v>
       </c>
       <c r="N4" t="n">
-        <v>64.87</v>
+        <v>62.76</v>
       </c>
       <c r="O4" t="n">
-        <v>70.40000000000001</v>
+        <v>67.62</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -862,7 +852,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -876,7 +866,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -886,50 +876,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>57.73</v>
       </c>
       <c r="C5" t="n">
-        <v>60.17</v>
+        <v>62.59</v>
       </c>
       <c r="D5" t="n">
-        <v>56.6</v>
+        <v>56.35</v>
       </c>
       <c r="E5" t="n">
-        <v>57.54</v>
+        <v>61.5</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.36</v>
+        <v>3.96</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0231</v>
+        <v>0.0688</v>
       </c>
       <c r="H5" t="n">
-        <v>3.57</v>
+        <v>6.24</v>
       </c>
       <c r="I5" t="n">
-        <v>53.52</v>
+        <v>53.03</v>
       </c>
       <c r="J5" t="n">
-        <v>53.37</v>
+        <v>53.55</v>
       </c>
       <c r="K5" t="n">
-        <v>56.55</v>
+        <v>55.76</v>
       </c>
       <c r="L5" t="n">
-        <v>59.74</v>
+        <v>57.96</v>
       </c>
       <c r="M5" t="n">
-        <v>61.25</v>
+        <v>59.33</v>
       </c>
       <c r="N5" t="n">
-        <v>62.76</v>
+        <v>60.69</v>
       </c>
       <c r="O5" t="n">
-        <v>67.62</v>
+        <v>63.74</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -937,79 +927,85 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
       <c r="W5" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57.73</v>
+        <v>61.82</v>
       </c>
       <c r="C6" t="n">
-        <v>62.59</v>
+        <v>62.17</v>
       </c>
       <c r="D6" t="n">
-        <v>56.35</v>
+        <v>59.64</v>
       </c>
       <c r="E6" t="n">
-        <v>61.5</v>
+        <v>60.98</v>
       </c>
       <c r="F6" t="n">
-        <v>3.96</v>
+        <v>-0.52</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0688</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>6.24</v>
+        <v>2.53</v>
       </c>
       <c r="I6" t="n">
-        <v>53.03</v>
+        <v>50.11</v>
       </c>
       <c r="J6" t="n">
-        <v>53.55</v>
+        <v>56.27</v>
       </c>
       <c r="K6" t="n">
-        <v>55.76</v>
+        <v>58.38</v>
       </c>
       <c r="L6" t="n">
-        <v>57.96</v>
+        <v>60.48</v>
       </c>
       <c r="M6" t="n">
-        <v>59.33</v>
+        <v>64.62</v>
       </c>
       <c r="N6" t="n">
-        <v>60.69</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>63.74</v>
+        <v>68.83</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,82 +1016,78 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>61.82</v>
+        <v>61.4</v>
       </c>
       <c r="C7" t="n">
-        <v>62.17</v>
+        <v>61.5</v>
       </c>
       <c r="D7" t="n">
-        <v>59.64</v>
+        <v>58.83</v>
       </c>
       <c r="E7" t="n">
-        <v>60.98</v>
+        <v>59.75</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.52</v>
+        <v>-1.23</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0202</v>
       </c>
       <c r="H7" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="I7" t="n">
-        <v>50.11</v>
+        <v>57.11</v>
       </c>
       <c r="J7" t="n">
-        <v>56.27</v>
+        <v>58.49</v>
       </c>
       <c r="K7" t="n">
-        <v>58.38</v>
+        <v>59.72</v>
       </c>
       <c r="L7" t="n">
-        <v>60.48</v>
+        <v>60.94</v>
       </c>
       <c r="M7" t="n">
-        <v>64.62</v>
+        <v>62.24</v>
       </c>
       <c r="N7" t="n">
-        <v>68.76000000000001</v>
+        <v>63.55</v>
       </c>
       <c r="O7" t="n">
-        <v>68.83</v>
+        <v>64.7</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1103,12 +1095,14 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1120,64 +1114,64 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61.4</v>
+        <v>59.87</v>
       </c>
       <c r="C8" t="n">
-        <v>61.5</v>
+        <v>61.28</v>
       </c>
       <c r="D8" t="n">
-        <v>58.83</v>
+        <v>58.12</v>
       </c>
       <c r="E8" t="n">
-        <v>59.75</v>
+        <v>60.09</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.23</v>
+        <v>0.34</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0202</v>
+        <v>0.0057</v>
       </c>
       <c r="H8" t="n">
-        <v>2.67</v>
+        <v>3.16</v>
       </c>
       <c r="I8" t="n">
-        <v>57.11</v>
+        <v>56.16</v>
       </c>
       <c r="J8" t="n">
-        <v>58.49</v>
+        <v>56.87</v>
       </c>
       <c r="K8" t="n">
-        <v>59.72</v>
+        <v>58.42</v>
       </c>
       <c r="L8" t="n">
-        <v>60.94</v>
+        <v>59.96</v>
       </c>
       <c r="M8" t="n">
-        <v>62.24</v>
+        <v>61.08</v>
       </c>
       <c r="N8" t="n">
-        <v>63.55</v>
+        <v>62.21</v>
       </c>
       <c r="O8" t="n">
-        <v>64.7</v>
+        <v>64.17</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1187,16 +1181,18 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1204,64 +1200,64 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59.87</v>
+        <v>59.8</v>
       </c>
       <c r="C9" t="n">
-        <v>61.28</v>
+        <v>60.93</v>
       </c>
       <c r="D9" t="n">
-        <v>58.12</v>
+        <v>57.38</v>
       </c>
       <c r="E9" t="n">
-        <v>60.09</v>
+        <v>58.06</v>
       </c>
       <c r="F9" t="n">
-        <v>0.34</v>
+        <v>-2.03</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.0338</v>
       </c>
       <c r="H9" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="I9" t="n">
-        <v>56.16</v>
+        <v>54.96</v>
       </c>
       <c r="J9" t="n">
-        <v>56.87</v>
+        <v>57.13</v>
       </c>
       <c r="K9" t="n">
-        <v>58.42</v>
+        <v>58.51</v>
       </c>
       <c r="L9" t="n">
-        <v>59.96</v>
+        <v>59.89</v>
       </c>
       <c r="M9" t="n">
-        <v>61.08</v>
+        <v>61.67</v>
       </c>
       <c r="N9" t="n">
-        <v>62.21</v>
+        <v>63.45</v>
       </c>
       <c r="O9" t="n">
-        <v>64.17</v>
+        <v>64.44</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,18 +1267,16 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1290,64 +1284,64 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59.8</v>
+        <v>58.05</v>
       </c>
       <c r="C10" t="n">
-        <v>60.93</v>
+        <v>59.64</v>
       </c>
       <c r="D10" t="n">
-        <v>57.38</v>
+        <v>57.1</v>
       </c>
       <c r="E10" t="n">
-        <v>58.06</v>
+        <v>58.55</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.03</v>
+        <v>0.49</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>3.55</v>
+        <v>2.54</v>
       </c>
       <c r="I10" t="n">
-        <v>54.96</v>
+        <v>53.83</v>
       </c>
       <c r="J10" t="n">
-        <v>57.13</v>
+        <v>53.96</v>
       </c>
       <c r="K10" t="n">
-        <v>58.51</v>
+        <v>56.29</v>
       </c>
       <c r="L10" t="n">
-        <v>59.89</v>
+        <v>58.61</v>
       </c>
       <c r="M10" t="n">
-        <v>61.67</v>
+        <v>59.84</v>
       </c>
       <c r="N10" t="n">
-        <v>63.45</v>
+        <v>61.06</v>
       </c>
       <c r="O10" t="n">
-        <v>64.44</v>
+        <v>64.48</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1355,14 +1349,12 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1374,64 +1366,64 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58.05</v>
+        <v>58.96</v>
       </c>
       <c r="C11" t="n">
-        <v>59.64</v>
+        <v>60.5</v>
       </c>
       <c r="D11" t="n">
-        <v>57.1</v>
+        <v>58.28</v>
       </c>
       <c r="E11" t="n">
-        <v>58.55</v>
+        <v>60.08</v>
       </c>
       <c r="F11" t="n">
-        <v>0.49</v>
+        <v>1.53</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0261</v>
       </c>
       <c r="H11" t="n">
-        <v>2.54</v>
+        <v>2.22</v>
       </c>
       <c r="I11" t="n">
-        <v>53.83</v>
+        <v>54.56</v>
       </c>
       <c r="J11" t="n">
-        <v>53.96</v>
+        <v>56.1</v>
       </c>
       <c r="K11" t="n">
-        <v>56.29</v>
+        <v>57.28</v>
       </c>
       <c r="L11" t="n">
-        <v>58.61</v>
+        <v>58.46</v>
       </c>
       <c r="M11" t="n">
-        <v>59.84</v>
+        <v>59.82</v>
       </c>
       <c r="N11" t="n">
-        <v>61.06</v>
+        <v>61.18</v>
       </c>
       <c r="O11" t="n">
-        <v>64.48</v>
+        <v>62.18</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1444,11 +1436,13 @@
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1456,83 +1450,81 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58.96</v>
+        <v>60.15</v>
       </c>
       <c r="C12" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="D12" t="n">
-        <v>58.28</v>
+        <v>57.01</v>
       </c>
       <c r="E12" t="n">
-        <v>60.08</v>
+        <v>57.44</v>
       </c>
       <c r="F12" t="n">
-        <v>1.53</v>
+        <v>-2.64</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0261</v>
+        <v>-0.0439</v>
       </c>
       <c r="H12" t="n">
-        <v>2.22</v>
+        <v>3.29</v>
       </c>
       <c r="I12" t="n">
-        <v>54.56</v>
+        <v>56.06</v>
       </c>
       <c r="J12" t="n">
-        <v>56.1</v>
+        <v>58.21</v>
       </c>
       <c r="K12" t="n">
-        <v>57.28</v>
+        <v>58.97</v>
       </c>
       <c r="L12" t="n">
-        <v>58.46</v>
+        <v>59.74</v>
       </c>
       <c r="M12" t="n">
-        <v>59.82</v>
+        <v>61.19</v>
       </c>
       <c r="N12" t="n">
-        <v>61.18</v>
+        <v>62.65</v>
       </c>
       <c r="O12" t="n">
-        <v>62.18</v>
+        <v>62.72</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1542,7 +1534,7 @@
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -1550,65 +1542,63 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60.15</v>
+        <v>57.5</v>
       </c>
       <c r="C13" t="n">
-        <v>60.3</v>
+        <v>57.8</v>
       </c>
       <c r="D13" t="n">
-        <v>57.01</v>
+        <v>54.98</v>
       </c>
       <c r="E13" t="n">
-        <v>57.44</v>
+        <v>56.66</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.64</v>
+        <v>-0.78</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0439</v>
+        <v>-0.0136</v>
       </c>
       <c r="H13" t="n">
-        <v>3.29</v>
+        <v>2.82</v>
       </c>
       <c r="I13" t="n">
-        <v>56.06</v>
+        <v>53.72</v>
       </c>
       <c r="J13" t="n">
-        <v>58.21</v>
+        <v>53.54</v>
       </c>
       <c r="K13" t="n">
-        <v>58.97</v>
+        <v>55.79</v>
       </c>
       <c r="L13" t="n">
-        <v>59.74</v>
+        <v>58.05</v>
       </c>
       <c r="M13" t="n">
-        <v>61.19</v>
+        <v>59.08</v>
       </c>
       <c r="N13" t="n">
-        <v>62.65</v>
+        <v>60.12</v>
       </c>
       <c r="O13" t="n">
-        <v>62.72</v>
+        <v>63.59</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1622,7 +1612,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1632,50 +1622,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>57.5</v>
+        <v>56.63</v>
       </c>
       <c r="C14" t="n">
-        <v>57.8</v>
+        <v>58.88</v>
       </c>
       <c r="D14" t="n">
-        <v>54.98</v>
+        <v>56.6</v>
       </c>
       <c r="E14" t="n">
-        <v>56.66</v>
+        <v>56.74</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.78</v>
+        <v>0.08</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0136</v>
+        <v>0.0014</v>
       </c>
       <c r="H14" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="I14" t="n">
-        <v>53.72</v>
+        <v>52.16</v>
       </c>
       <c r="J14" t="n">
-        <v>53.54</v>
+        <v>53.98</v>
       </c>
       <c r="K14" t="n">
-        <v>55.79</v>
+        <v>55.25</v>
       </c>
       <c r="L14" t="n">
-        <v>58.05</v>
+        <v>56.52</v>
       </c>
       <c r="M14" t="n">
-        <v>59.08</v>
+        <v>58.07</v>
       </c>
       <c r="N14" t="n">
-        <v>60.12</v>
+        <v>59.61</v>
       </c>
       <c r="O14" t="n">
-        <v>63.59</v>
+        <v>60.62</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1683,18 +1673,18 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1702,60 +1692,64 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>56.63</v>
+        <v>57.04</v>
       </c>
       <c r="C15" t="n">
-        <v>58.88</v>
+        <v>58.55</v>
       </c>
       <c r="D15" t="n">
         <v>56.6</v>
       </c>
       <c r="E15" t="n">
-        <v>56.74</v>
+        <v>57.32</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08</v>
+        <v>0.58</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0102</v>
       </c>
       <c r="H15" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="I15" t="n">
-        <v>52.16</v>
+        <v>54.32</v>
       </c>
       <c r="J15" t="n">
-        <v>53.98</v>
+        <v>53.96</v>
       </c>
       <c r="K15" t="n">
-        <v>55.25</v>
+        <v>55.6</v>
       </c>
       <c r="L15" t="n">
-        <v>56.52</v>
+        <v>57.24</v>
       </c>
       <c r="M15" t="n">
-        <v>58.07</v>
+        <v>57.88</v>
       </c>
       <c r="N15" t="n">
-        <v>59.61</v>
+        <v>58.52</v>
       </c>
       <c r="O15" t="n">
-        <v>60.62</v>
+        <v>61.16</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1766,7 +1760,7 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1776,70 +1770,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>57.04</v>
+        <v>57.47</v>
       </c>
       <c r="C16" t="n">
-        <v>58.55</v>
+        <v>59.77</v>
       </c>
       <c r="D16" t="n">
-        <v>56.6</v>
+        <v>55.76</v>
       </c>
       <c r="E16" t="n">
-        <v>57.32</v>
+        <v>59.12</v>
       </c>
       <c r="F16" t="n">
-        <v>0.58</v>
+        <v>1.8</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0314</v>
       </c>
       <c r="H16" t="n">
-        <v>1.95</v>
+        <v>4.01</v>
       </c>
       <c r="I16" t="n">
-        <v>54.32</v>
+        <v>54.65</v>
       </c>
       <c r="J16" t="n">
-        <v>53.96</v>
+        <v>55.24</v>
       </c>
       <c r="K16" t="n">
-        <v>55.6</v>
+        <v>56.34</v>
       </c>
       <c r="L16" t="n">
-        <v>57.24</v>
+        <v>57.45</v>
       </c>
       <c r="M16" t="n">
-        <v>57.88</v>
+        <v>58.3</v>
       </c>
       <c r="N16" t="n">
-        <v>58.52</v>
+        <v>59.14</v>
       </c>
       <c r="O16" t="n">
-        <v>61.16</v>
+        <v>60.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1847,12 +1843,14 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -1862,70 +1860,70 @@
       </c>
       <c r="U16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>57.47</v>
+        <v>59</v>
       </c>
       <c r="C17" t="n">
-        <v>59.77</v>
+        <v>62.36</v>
       </c>
       <c r="D17" t="n">
-        <v>55.76</v>
+        <v>58.45</v>
       </c>
       <c r="E17" t="n">
-        <v>59.12</v>
+        <v>59.44</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8</v>
+        <v>0.32</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0314</v>
+        <v>0.0054</v>
       </c>
       <c r="H17" t="n">
-        <v>4.01</v>
+        <v>3.91</v>
       </c>
       <c r="I17" t="n">
-        <v>54.65</v>
+        <v>51.75</v>
       </c>
       <c r="J17" t="n">
-        <v>55.24</v>
+        <v>55.79</v>
       </c>
       <c r="K17" t="n">
-        <v>56.34</v>
+        <v>57.11</v>
       </c>
       <c r="L17" t="n">
-        <v>57.45</v>
+        <v>58.44</v>
       </c>
       <c r="M17" t="n">
-        <v>58.3</v>
+        <v>61.12</v>
       </c>
       <c r="N17" t="n">
-        <v>59.14</v>
+        <v>63.81</v>
       </c>
       <c r="O17" t="n">
-        <v>60.5</v>
+        <v>63.78</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1933,87 +1931,83 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>59</v>
+        <v>59.01</v>
       </c>
       <c r="C18" t="n">
-        <v>62.36</v>
+        <v>61.36</v>
       </c>
       <c r="D18" t="n">
-        <v>58.45</v>
+        <v>58.7</v>
       </c>
       <c r="E18" t="n">
-        <v>59.44</v>
+        <v>61.07</v>
       </c>
       <c r="F18" t="n">
-        <v>0.32</v>
+        <v>1.63</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0274</v>
       </c>
       <c r="H18" t="n">
-        <v>3.91</v>
+        <v>2.66</v>
       </c>
       <c r="I18" t="n">
-        <v>51.75</v>
+        <v>54.54</v>
       </c>
       <c r="J18" t="n">
-        <v>55.79</v>
+        <v>55.05</v>
       </c>
       <c r="K18" t="n">
-        <v>57.11</v>
+        <v>57.48</v>
       </c>
       <c r="L18" t="n">
-        <v>58.44</v>
+        <v>59.92</v>
       </c>
       <c r="M18" t="n">
-        <v>61.12</v>
+        <v>61.39</v>
       </c>
       <c r="N18" t="n">
-        <v>63.81</v>
+        <v>62.87</v>
       </c>
       <c r="O18" t="n">
-        <v>63.78</v>
+        <v>66.27</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2024,14 +2018,14 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U18" s="8" t="n">
@@ -2040,64 +2034,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>59.01</v>
+        <v>61.22</v>
       </c>
       <c r="C19" t="n">
-        <v>61.36</v>
+        <v>66.48</v>
       </c>
       <c r="D19" t="n">
-        <v>58.7</v>
+        <v>60.14</v>
       </c>
       <c r="E19" t="n">
-        <v>61.07</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>1.63</v>
+        <v>4.14</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0678</v>
       </c>
       <c r="H19" t="n">
-        <v>2.66</v>
+        <v>6.34</v>
       </c>
       <c r="I19" t="n">
-        <v>54.54</v>
+        <v>56.04</v>
       </c>
       <c r="J19" t="n">
-        <v>55.05</v>
+        <v>58.93</v>
       </c>
       <c r="K19" t="n">
-        <v>57.48</v>
+        <v>59.74</v>
       </c>
       <c r="L19" t="n">
-        <v>59.92</v>
+        <v>60.55</v>
       </c>
       <c r="M19" t="n">
-        <v>61.39</v>
+        <v>62.4</v>
       </c>
       <c r="N19" t="n">
-        <v>62.87</v>
+        <v>64.25</v>
       </c>
       <c r="O19" t="n">
-        <v>66.27</v>
+        <v>64.02</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2108,80 +2102,80 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W19" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>61.22</v>
+        <v>64.72</v>
       </c>
       <c r="C20" t="n">
-        <v>66.48</v>
+        <v>65.53</v>
       </c>
       <c r="D20" t="n">
-        <v>60.14</v>
+        <v>61.12</v>
       </c>
       <c r="E20" t="n">
-        <v>65.20999999999999</v>
+        <v>63.55</v>
       </c>
       <c r="F20" t="n">
-        <v>4.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0678</v>
+        <v>-0.0255</v>
       </c>
       <c r="H20" t="n">
-        <v>6.34</v>
+        <v>4.41</v>
       </c>
       <c r="I20" t="n">
-        <v>56.04</v>
+        <v>53.8</v>
       </c>
       <c r="J20" t="n">
-        <v>58.93</v>
+        <v>59.82</v>
       </c>
       <c r="K20" t="n">
-        <v>59.74</v>
+        <v>62.04</v>
       </c>
       <c r="L20" t="n">
-        <v>60.55</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>62.4</v>
+        <v>68.38</v>
       </c>
       <c r="N20" t="n">
-        <v>64.25</v>
+        <v>72.5</v>
       </c>
       <c r="O20" t="n">
-        <v>64.02</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2189,83 +2183,83 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W20" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>64.72</v>
+        <v>62.99</v>
       </c>
       <c r="C21" t="n">
-        <v>65.53</v>
+        <v>65.83</v>
       </c>
       <c r="D21" t="n">
-        <v>61.12</v>
+        <v>62.14</v>
       </c>
       <c r="E21" t="n">
-        <v>63.55</v>
+        <v>62.89</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.66</v>
+        <v>-0.66</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0255</v>
+        <v>-0.0104</v>
       </c>
       <c r="H21" t="n">
-        <v>4.41</v>
+        <v>3.69</v>
       </c>
       <c r="I21" t="n">
-        <v>53.8</v>
+        <v>56.71</v>
       </c>
       <c r="J21" t="n">
-        <v>59.82</v>
+        <v>59.25</v>
       </c>
       <c r="K21" t="n">
-        <v>62.04</v>
+        <v>61.34</v>
       </c>
       <c r="L21" t="n">
-        <v>64.26000000000001</v>
+        <v>63.44</v>
       </c>
       <c r="M21" t="n">
-        <v>68.38</v>
+        <v>65.75</v>
       </c>
       <c r="N21" t="n">
-        <v>72.5</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>72.81999999999999</v>
+        <v>69.94</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2273,83 +2267,83 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>62.99</v>
+        <v>63.3</v>
       </c>
       <c r="C22" t="n">
-        <v>65.83</v>
+        <v>67.05</v>
       </c>
       <c r="D22" t="n">
-        <v>62.14</v>
+        <v>61.87</v>
       </c>
       <c r="E22" t="n">
-        <v>62.89</v>
+        <v>66.39</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.66</v>
+        <v>3.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0557</v>
       </c>
       <c r="H22" t="n">
-        <v>3.69</v>
+        <v>5.18</v>
       </c>
       <c r="I22" t="n">
-        <v>56.71</v>
+        <v>58.45</v>
       </c>
       <c r="J22" t="n">
-        <v>59.25</v>
+        <v>58.65</v>
       </c>
       <c r="K22" t="n">
-        <v>61.34</v>
+        <v>61.04</v>
       </c>
       <c r="L22" t="n">
         <v>63.44</v>
       </c>
       <c r="M22" t="n">
-        <v>65.75</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>68.06999999999999</v>
+        <v>66.03</v>
       </c>
       <c r="O22" t="n">
-        <v>69.94</v>
+        <v>69.52</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2362,7 +2356,7 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2370,13 +2364,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2390,50 +2386,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>63.3</v>
+        <v>65.89</v>
       </c>
       <c r="C23" t="n">
-        <v>67.05</v>
+        <v>67.83</v>
       </c>
       <c r="D23" t="n">
-        <v>61.87</v>
+        <v>63.6</v>
       </c>
       <c r="E23" t="n">
-        <v>66.39</v>
+        <v>67.02</v>
       </c>
       <c r="F23" t="n">
-        <v>3.5</v>
+        <v>0.63</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0557</v>
+        <v>0.0095</v>
       </c>
       <c r="H23" t="n">
-        <v>5.18</v>
+        <v>4.23</v>
       </c>
       <c r="I23" t="n">
-        <v>58.45</v>
+        <v>56.69</v>
       </c>
       <c r="J23" t="n">
-        <v>58.65</v>
+        <v>62.17</v>
       </c>
       <c r="K23" t="n">
-        <v>61.04</v>
+        <v>63.8</v>
       </c>
       <c r="L23" t="n">
-        <v>63.44</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>64.73999999999999</v>
+        <v>68.98</v>
       </c>
       <c r="N23" t="n">
-        <v>66.03</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>69.52</v>
+        <v>72.23</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2441,85 +2437,79 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>65.89</v>
+        <v>75</v>
       </c>
       <c r="C24" t="n">
-        <v>67.83</v>
+        <v>92.61</v>
       </c>
       <c r="D24" t="n">
-        <v>63.6</v>
+        <v>69.2</v>
       </c>
       <c r="E24" t="n">
-        <v>67.02</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.63</v>
+        <v>23.88</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.3563</v>
       </c>
       <c r="H24" t="n">
-        <v>4.23</v>
+        <v>23.41</v>
       </c>
       <c r="I24" t="n">
-        <v>56.69</v>
+        <v>59.37</v>
       </c>
       <c r="J24" t="n">
-        <v>62.17</v>
+        <v>63.44</v>
       </c>
       <c r="K24" t="n">
-        <v>63.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>65.43000000000001</v>
+        <v>66.37</v>
       </c>
       <c r="M24" t="n">
-        <v>68.98</v>
+        <v>69.13</v>
       </c>
       <c r="N24" t="n">
-        <v>72.54000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>72.23</v>
+        <v>72.06</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2527,26 +2517,30 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2556,50 +2550,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C25" t="n">
-        <v>92.61</v>
+        <v>119.48</v>
       </c>
       <c r="D25" t="n">
-        <v>69.2</v>
+        <v>76.73</v>
       </c>
       <c r="E25" t="n">
-        <v>90.90000000000001</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>23.88</v>
+        <v>7.81</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.3563</v>
+        <v>0.0859</v>
       </c>
       <c r="H25" t="n">
-        <v>23.41</v>
+        <v>42.75</v>
       </c>
       <c r="I25" t="n">
-        <v>59.37</v>
+        <v>45.79</v>
       </c>
       <c r="J25" t="n">
-        <v>63.44</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>64.90000000000001</v>
+        <v>79.19</v>
       </c>
       <c r="L25" t="n">
-        <v>66.37</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>69.13</v>
+        <v>102.61</v>
       </c>
       <c r="N25" t="n">
-        <v>71.90000000000001</v>
+        <v>119.31</v>
       </c>
       <c r="O25" t="n">
-        <v>72.06</v>
+        <v>116.02</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2607,30 +2601,32 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
+      <c r="V25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2640,50 +2636,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>98</v>
+        <v>100.93</v>
       </c>
       <c r="C26" t="n">
-        <v>119.48</v>
+        <v>102.44</v>
       </c>
       <c r="D26" t="n">
-        <v>76.73</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>98.70999999999999</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>7.81</v>
+        <v>-0.39</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0859</v>
+        <v>-0.004</v>
       </c>
       <c r="H26" t="n">
-        <v>42.75</v>
+        <v>10.48</v>
       </c>
       <c r="I26" t="n">
-        <v>45.79</v>
+        <v>33.98</v>
       </c>
       <c r="J26" t="n">
-        <v>72.48999999999999</v>
+        <v>56.26</v>
       </c>
       <c r="K26" t="n">
-        <v>79.19</v>
+        <v>77.33</v>
       </c>
       <c r="L26" t="n">
-        <v>85.90000000000001</v>
+        <v>98.41</v>
       </c>
       <c r="M26" t="n">
-        <v>102.61</v>
+        <v>120.08</v>
       </c>
       <c r="N26" t="n">
-        <v>119.31</v>
+        <v>141.76</v>
       </c>
       <c r="O26" t="n">
-        <v>116.02</v>
+        <v>162.23</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2691,98 +2687,98 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W26" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>100.93</v>
+        <v>100.51</v>
       </c>
       <c r="C27" t="n">
-        <v>102.44</v>
+        <v>101.67</v>
       </c>
       <c r="D27" t="n">
-        <v>91.95999999999999</v>
+        <v>84.37</v>
       </c>
       <c r="E27" t="n">
-        <v>98.31999999999999</v>
+        <v>99.64</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.39</v>
+        <v>1.32</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0134</v>
       </c>
       <c r="H27" t="n">
-        <v>10.48</v>
+        <v>17.3</v>
       </c>
       <c r="I27" t="n">
-        <v>33.98</v>
+        <v>81.48</v>
       </c>
       <c r="J27" t="n">
-        <v>56.26</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>77.33</v>
+        <v>93.08</v>
       </c>
       <c r="L27" t="n">
-        <v>98.41</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>120.08</v>
+        <v>103.56</v>
       </c>
       <c r="N27" t="n">
-        <v>141.76</v>
+        <v>109.36</v>
       </c>
       <c r="O27" t="n">
-        <v>162.23</v>
+        <v>112.92</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2794,7 +2790,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2808,71 +2804,69 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>100.51</v>
+        <v>102.6</v>
       </c>
       <c r="C28" t="n">
-        <v>101.67</v>
+        <v>113.97</v>
       </c>
       <c r="D28" t="n">
-        <v>84.37</v>
+        <v>96.5</v>
       </c>
       <c r="E28" t="n">
-        <v>99.64</v>
+        <v>111.54</v>
       </c>
       <c r="F28" t="n">
-        <v>1.32</v>
+        <v>11.9</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.1194</v>
       </c>
       <c r="H28" t="n">
-        <v>17.3</v>
+        <v>17.47</v>
       </c>
       <c r="I28" t="n">
-        <v>81.48</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>88.40000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>93.08</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>97.76000000000001</v>
+        <v>96.33</v>
       </c>
       <c r="M28" t="n">
-        <v>103.56</v>
+        <v>108.29</v>
       </c>
       <c r="N28" t="n">
-        <v>109.36</v>
+        <v>120.25</v>
       </c>
       <c r="O28" t="n">
-        <v>112.92</v>
+        <v>118.97</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2880,83 +2874,81 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>102.6</v>
+        <v>112.96</v>
       </c>
       <c r="C29" t="n">
-        <v>113.97</v>
+        <v>117.63</v>
       </c>
       <c r="D29" t="n">
-        <v>96.5</v>
+        <v>91.05</v>
       </c>
       <c r="E29" t="n">
-        <v>111.54</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>11.9</v>
+        <v>-14.97</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.1194</v>
+        <v>-0.1342</v>
       </c>
       <c r="H29" t="n">
-        <v>17.47</v>
+        <v>26.58</v>
       </c>
       <c r="I29" t="n">
-        <v>67.06999999999999</v>
+        <v>79.03</v>
       </c>
       <c r="J29" t="n">
-        <v>85.65000000000001</v>
+        <v>97.22</v>
       </c>
       <c r="K29" t="n">
-        <v>90.98999999999999</v>
+        <v>102.81</v>
       </c>
       <c r="L29" t="n">
-        <v>96.33</v>
+        <v>108.39</v>
       </c>
       <c r="M29" t="n">
-        <v>108.29</v>
+        <v>120.28</v>
       </c>
       <c r="N29" t="n">
-        <v>120.25</v>
+        <v>132.16</v>
       </c>
       <c r="O29" t="n">
-        <v>118.97</v>
+        <v>131.44</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2966,73 +2958,75 @@
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>112.96</v>
+        <v>102</v>
       </c>
       <c r="C30" t="n">
-        <v>117.63</v>
+        <v>105.63</v>
       </c>
       <c r="D30" t="n">
-        <v>91.05</v>
+        <v>80.56</v>
       </c>
       <c r="E30" t="n">
-        <v>96.56999999999999</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-14.97</v>
+        <v>-12.72</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.1342</v>
+        <v>-0.1317</v>
       </c>
       <c r="H30" t="n">
-        <v>26.58</v>
+        <v>25.07</v>
       </c>
       <c r="I30" t="n">
-        <v>79.03</v>
+        <v>64.47</v>
       </c>
       <c r="J30" t="n">
-        <v>97.22</v>
+        <v>66.11</v>
       </c>
       <c r="K30" t="n">
-        <v>102.81</v>
+        <v>83.28</v>
       </c>
       <c r="L30" t="n">
-        <v>108.39</v>
+        <v>100.45</v>
       </c>
       <c r="M30" t="n">
-        <v>120.28</v>
+        <v>109.86</v>
       </c>
       <c r="N30" t="n">
-        <v>132.16</v>
+        <v>119.26</v>
       </c>
       <c r="O30" t="n">
-        <v>131.44</v>
+        <v>144.21</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3046,64 +3040,60 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C31" t="n">
-        <v>105.63</v>
+        <v>98.39</v>
       </c>
       <c r="D31" t="n">
-        <v>80.56</v>
+        <v>87.02</v>
       </c>
       <c r="E31" t="n">
-        <v>83.84999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>-12.72</v>
+        <v>10.55</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.1317</v>
+        <v>0.1258</v>
       </c>
       <c r="H31" t="n">
-        <v>25.07</v>
+        <v>11.37</v>
       </c>
       <c r="I31" t="n">
-        <v>64.47</v>
+        <v>55.49</v>
       </c>
       <c r="J31" t="n">
-        <v>66.11</v>
+        <v>54.16</v>
       </c>
       <c r="K31" t="n">
-        <v>83.28</v>
+        <v>71.31</v>
       </c>
       <c r="L31" t="n">
-        <v>100.45</v>
+        <v>88.47</v>
       </c>
       <c r="M31" t="n">
-        <v>109.86</v>
+        <v>96.38</v>
       </c>
       <c r="N31" t="n">
-        <v>119.26</v>
+        <v>104.3</v>
       </c>
       <c r="O31" t="n">
-        <v>144.21</v>
+        <v>130.7</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3111,79 +3101,83 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>89</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>98.39</v>
+        <v>110.93</v>
       </c>
       <c r="D32" t="n">
-        <v>87.02</v>
+        <v>94.59</v>
       </c>
       <c r="E32" t="n">
-        <v>94.40000000000001</v>
+        <v>101.94</v>
       </c>
       <c r="F32" t="n">
-        <v>10.55</v>
+        <v>7.54</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.1258</v>
+        <v>0.0799</v>
       </c>
       <c r="H32" t="n">
-        <v>11.37</v>
+        <v>16.34</v>
       </c>
       <c r="I32" t="n">
-        <v>55.49</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>54.16</v>
+        <v>83.88</v>
       </c>
       <c r="K32" t="n">
-        <v>71.31</v>
+        <v>88.72</v>
       </c>
       <c r="L32" t="n">
-        <v>88.47</v>
+        <v>93.55</v>
       </c>
       <c r="M32" t="n">
-        <v>96.38</v>
+        <v>100.09</v>
       </c>
       <c r="N32" t="n">
-        <v>104.3</v>
+        <v>106.62</v>
       </c>
       <c r="O32" t="n">
-        <v>130.7</v>
+        <v>109.76</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3194,7 +3188,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3204,70 +3198,74 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>95.59999999999999</v>
+        <v>99.73</v>
       </c>
       <c r="C33" t="n">
-        <v>110.93</v>
+        <v>107.46</v>
       </c>
       <c r="D33" t="n">
-        <v>94.59</v>
+        <v>88.66</v>
       </c>
       <c r="E33" t="n">
-        <v>101.94</v>
+        <v>95.42</v>
       </c>
       <c r="F33" t="n">
-        <v>7.54</v>
+        <v>-6.52</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0799</v>
+        <v>-0.064</v>
       </c>
       <c r="H33" t="n">
-        <v>16.34</v>
+        <v>18.8</v>
       </c>
       <c r="I33" t="n">
-        <v>75.65000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="J33" t="n">
-        <v>83.88</v>
+        <v>85.19</v>
       </c>
       <c r="K33" t="n">
-        <v>88.72</v>
+        <v>93.77</v>
       </c>
       <c r="L33" t="n">
-        <v>93.55</v>
+        <v>102.35</v>
       </c>
       <c r="M33" t="n">
-        <v>100.09</v>
+        <v>110.11</v>
       </c>
       <c r="N33" t="n">
-        <v>106.62</v>
+        <v>117.87</v>
       </c>
       <c r="O33" t="n">
-        <v>109.76</v>
+        <v>127.27</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3275,87 +3273,79 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W33" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>99.73</v>
+        <v>98.19</v>
       </c>
       <c r="C34" t="n">
-        <v>107.46</v>
+        <v>106</v>
       </c>
       <c r="D34" t="n">
-        <v>88.66</v>
+        <v>96.13</v>
       </c>
       <c r="E34" t="n">
-        <v>95.42</v>
+        <v>105.42</v>
       </c>
       <c r="F34" t="n">
-        <v>-6.52</v>
+        <v>10</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.064</v>
+        <v>0.1048</v>
       </c>
       <c r="H34" t="n">
-        <v>18.8</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>78.25</v>
+        <v>69.86</v>
       </c>
       <c r="J34" t="n">
-        <v>85.19</v>
+        <v>75.3</v>
       </c>
       <c r="K34" t="n">
-        <v>93.77</v>
+        <v>86.02</v>
       </c>
       <c r="L34" t="n">
-        <v>102.35</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>110.11</v>
+        <v>104.82</v>
       </c>
       <c r="N34" t="n">
-        <v>117.87</v>
+        <v>112.9</v>
       </c>
       <c r="O34" t="n">
-        <v>127.27</v>
+        <v>126.26</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3363,98 +3353,104 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>98.19</v>
+        <v>106</v>
       </c>
       <c r="C35" t="n">
-        <v>106</v>
+        <v>109.47</v>
       </c>
       <c r="D35" t="n">
-        <v>96.13</v>
+        <v>94.73</v>
       </c>
       <c r="E35" t="n">
-        <v>105.42</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>-8.82</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.1048</v>
+        <v>-0.0837</v>
       </c>
       <c r="H35" t="n">
-        <v>9.869999999999999</v>
+        <v>14.74</v>
       </c>
       <c r="I35" t="n">
-        <v>69.86</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>75.3</v>
+        <v>97.73</v>
       </c>
       <c r="K35" t="n">
-        <v>86.02</v>
+        <v>100.48</v>
       </c>
       <c r="L35" t="n">
-        <v>96.73999999999999</v>
+        <v>103.24</v>
       </c>
       <c r="M35" t="n">
-        <v>104.82</v>
+        <v>110.35</v>
       </c>
       <c r="N35" t="n">
-        <v>112.9</v>
+        <v>117.47</v>
       </c>
       <c r="O35" t="n">
-        <v>126.26</v>
+        <v>115.87</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3462,79 +3458,77 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>106</v>
+        <v>93.88</v>
       </c>
       <c r="C36" t="n">
-        <v>109.47</v>
+        <v>94.7</v>
       </c>
       <c r="D36" t="n">
-        <v>94.73</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>96.59999999999999</v>
+        <v>87.36</v>
       </c>
       <c r="F36" t="n">
-        <v>-8.82</v>
+        <v>-9.24</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0837</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>14.74</v>
+        <v>8.35</v>
       </c>
       <c r="I36" t="n">
-        <v>86.26000000000001</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>97.73</v>
+        <v>79.11</v>
       </c>
       <c r="K36" t="n">
-        <v>100.48</v>
+        <v>89.23</v>
       </c>
       <c r="L36" t="n">
-        <v>103.24</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>110.35</v>
+        <v>103.97</v>
       </c>
       <c r="N36" t="n">
-        <v>117.47</v>
+        <v>108.59</v>
       </c>
       <c r="O36" t="n">
-        <v>115.87</v>
+        <v>124.21</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3548,64 +3542,60 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>93.88</v>
+        <v>88.5</v>
       </c>
       <c r="C37" t="n">
-        <v>94.7</v>
+        <v>97</v>
       </c>
       <c r="D37" t="n">
-        <v>86.34999999999999</v>
+        <v>88.45</v>
       </c>
       <c r="E37" t="n">
-        <v>87.36</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-9.24</v>
+        <v>3.18</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.0364</v>
       </c>
       <c r="H37" t="n">
-        <v>8.35</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>79.98999999999999</v>
+        <v>78</v>
       </c>
       <c r="J37" t="n">
-        <v>79.11</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>89.23</v>
+        <v>83.19</v>
       </c>
       <c r="L37" t="n">
-        <v>99.34999999999999</v>
+        <v>88.94</v>
       </c>
       <c r="M37" t="n">
-        <v>103.97</v>
+        <v>91.53</v>
       </c>
       <c r="N37" t="n">
-        <v>108.59</v>
+        <v>94.13</v>
       </c>
       <c r="O37" t="n">
-        <v>124.21</v>
+        <v>103.05</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3613,79 +3603,85 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>88.5</v>
+        <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>97</v>
+        <v>95.47</v>
       </c>
       <c r="D38" t="n">
-        <v>88.45</v>
+        <v>83.2</v>
       </c>
       <c r="E38" t="n">
-        <v>90.54000000000001</v>
+        <v>84.88</v>
       </c>
       <c r="F38" t="n">
-        <v>3.18</v>
+        <v>-5.66</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0364</v>
+        <v>-0.0625</v>
       </c>
       <c r="H38" t="n">
-        <v>8.550000000000001</v>
+        <v>12.27</v>
       </c>
       <c r="I38" t="n">
-        <v>78</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>77.43000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>83.19</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>88.94</v>
+        <v>91.63</v>
       </c>
       <c r="M38" t="n">
-        <v>91.53</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>94.13</v>
+        <v>98</v>
       </c>
       <c r="O38" t="n">
-        <v>103.05</v>
+        <v>105.55</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3693,85 +3689,81 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>93</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>95.47</v>
+        <v>82.42</v>
       </c>
       <c r="D39" t="n">
-        <v>83.2</v>
+        <v>73.58</v>
       </c>
       <c r="E39" t="n">
-        <v>84.88</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>-5.66</v>
+        <v>-7.34</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0625</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>12.27</v>
+        <v>8.84</v>
       </c>
       <c r="I39" t="n">
-        <v>79.90000000000001</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>80.90000000000001</v>
+        <v>70.38</v>
       </c>
       <c r="K39" t="n">
-        <v>86.26000000000001</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>91.63</v>
+        <v>87.11</v>
       </c>
       <c r="M39" t="n">
-        <v>94.81999999999999</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>98</v>
+        <v>94.92</v>
       </c>
       <c r="O39" t="n">
-        <v>105.55</v>
+        <v>107.74</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3784,15 +3776,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3800,7 +3790,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3810,63 +3800,65 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>81.40000000000001</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>82.42</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>73.58</v>
+        <v>68.56</v>
       </c>
       <c r="E40" t="n">
-        <v>77.54000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="F40" t="n">
-        <v>-7.34</v>
+        <v>-8.31</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.1072</v>
       </c>
       <c r="H40" t="n">
-        <v>8.84</v>
+        <v>10.4</v>
       </c>
       <c r="I40" t="n">
-        <v>70.93000000000001</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>70.38</v>
+        <v>68.47</v>
       </c>
       <c r="K40" t="n">
-        <v>78.73999999999999</v>
+        <v>73.12</v>
       </c>
       <c r="L40" t="n">
-        <v>87.11</v>
+        <v>77.77</v>
       </c>
       <c r="M40" t="n">
-        <v>91.01000000000001</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>94.92</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>107.74</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3880,7 +3872,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3890,67 +3882,63 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>78.93000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="C41" t="n">
-        <v>78.95999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>68.56</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>69.23</v>
+        <v>68.78</v>
       </c>
       <c r="F41" t="n">
-        <v>-8.31</v>
+        <v>-0.45</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.1072</v>
+        <v>-0.0065</v>
       </c>
       <c r="H41" t="n">
-        <v>10.4</v>
+        <v>4.56</v>
       </c>
       <c r="I41" t="n">
-        <v>64.73999999999999</v>
+        <v>58.16</v>
       </c>
       <c r="J41" t="n">
-        <v>68.47</v>
+        <v>56.57</v>
       </c>
       <c r="K41" t="n">
-        <v>73.12</v>
+        <v>64.03</v>
       </c>
       <c r="L41" t="n">
-        <v>77.77</v>
+        <v>71.5</v>
       </c>
       <c r="M41" t="n">
-        <v>81.95999999999999</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>86.15000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="O41" t="n">
-        <v>91.26000000000001</v>
+        <v>89.36</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3962,7 +3950,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3972,50 +3960,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>70.5</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>71.59999999999999</v>
+        <v>76.08</v>
       </c>
       <c r="D42" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>68.78</v>
+        <v>71.41</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.45</v>
+        <v>2.63</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0382</v>
       </c>
       <c r="H42" t="n">
-        <v>4.56</v>
+        <v>8.26</v>
       </c>
       <c r="I42" t="n">
-        <v>58.16</v>
+        <v>62.48</v>
       </c>
       <c r="J42" t="n">
-        <v>56.57</v>
+        <v>63.95</v>
       </c>
       <c r="K42" t="n">
-        <v>64.03</v>
+        <v>66.5</v>
       </c>
       <c r="L42" t="n">
-        <v>71.5</v>
+        <v>69.05</v>
       </c>
       <c r="M42" t="n">
-        <v>74.43000000000001</v>
+        <v>71.06</v>
       </c>
       <c r="N42" t="n">
-        <v>77.37</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O42" t="n">
-        <v>89.36</v>
+        <v>76.16</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4028,72 +4016,80 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>68.68000000000001</v>
+        <v>73.69</v>
       </c>
       <c r="C43" t="n">
-        <v>76.08</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>67.81999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="E43" t="n">
-        <v>71.41</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>2.63</v>
+        <v>11.08</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0382</v>
+        <v>0.1552</v>
       </c>
       <c r="H43" t="n">
-        <v>8.26</v>
+        <v>10.15</v>
       </c>
       <c r="I43" t="n">
-        <v>62.48</v>
+        <v>59.56</v>
       </c>
       <c r="J43" t="n">
-        <v>63.95</v>
+        <v>62.88</v>
       </c>
       <c r="K43" t="n">
-        <v>66.5</v>
+        <v>67.28</v>
       </c>
       <c r="L43" t="n">
-        <v>69.05</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>71.06</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>73.06999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>76.16</v>
+        <v>84.34</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4104,82 +4100,80 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
-      </c>
       <c r="W43" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>73.69</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>82.76000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="D44" t="n">
-        <v>72.61</v>
+        <v>80.27</v>
       </c>
       <c r="E44" t="n">
-        <v>82.48999999999999</v>
+        <v>89.31</v>
       </c>
       <c r="F44" t="n">
-        <v>11.08</v>
+        <v>6.82</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.1552</v>
+        <v>0.0827</v>
       </c>
       <c r="H44" t="n">
-        <v>10.15</v>
+        <v>13.23</v>
       </c>
       <c r="I44" t="n">
-        <v>59.56</v>
+        <v>62.46</v>
       </c>
       <c r="J44" t="n">
-        <v>62.88</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>67.28</v>
+        <v>77.41</v>
       </c>
       <c r="L44" t="n">
-        <v>71.68000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="M44" t="n">
-        <v>75.54000000000001</v>
+        <v>87.56</v>
       </c>
       <c r="N44" t="n">
-        <v>79.40000000000001</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>84.34</v>
+        <v>92.91</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4190,27 +4184,25 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4220,50 +4212,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>83.76000000000001</v>
+        <v>86.12</v>
       </c>
       <c r="C45" t="n">
-        <v>93.5</v>
+        <v>86.87</v>
       </c>
       <c r="D45" t="n">
-        <v>80.27</v>
+        <v>77.78</v>
       </c>
       <c r="E45" t="n">
-        <v>89.31</v>
+        <v>84.67</v>
       </c>
       <c r="F45" t="n">
-        <v>6.82</v>
+        <v>-4.64</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0827</v>
+        <v>-0.052</v>
       </c>
       <c r="H45" t="n">
-        <v>13.23</v>
+        <v>9.09</v>
       </c>
       <c r="I45" t="n">
-        <v>62.46</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>74.73999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>77.41</v>
+        <v>82.69</v>
       </c>
       <c r="L45" t="n">
-        <v>80.09</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>87.56</v>
+        <v>95.92</v>
       </c>
       <c r="N45" t="n">
-        <v>95.04000000000001</v>
+        <v>103.75</v>
       </c>
       <c r="O45" t="n">
-        <v>92.91</v>
+        <v>106.73</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4271,94 +4263,98 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="V45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>86.12</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C46" t="n">
-        <v>86.87</v>
+        <v>82.33</v>
       </c>
       <c r="D46" t="n">
-        <v>77.78</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>84.67</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>-4.64</v>
+        <v>-6.49</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.0767</v>
       </c>
       <c r="H46" t="n">
-        <v>9.09</v>
+        <v>8.09</v>
       </c>
       <c r="I46" t="n">
-        <v>67.04000000000001</v>
+        <v>68.69</v>
       </c>
       <c r="J46" t="n">
-        <v>77.29000000000001</v>
+        <v>76.75</v>
       </c>
       <c r="K46" t="n">
-        <v>82.69</v>
+        <v>80.12</v>
       </c>
       <c r="L46" t="n">
-        <v>88.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="M46" t="n">
-        <v>95.92</v>
+        <v>89.22</v>
       </c>
       <c r="N46" t="n">
-        <v>103.75</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>106.73</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4372,7 +4368,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4386,136 +4382,130 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>80.09999999999999</v>
+        <v>78.42</v>
       </c>
       <c r="C47" t="n">
-        <v>82.33</v>
+        <v>84.61</v>
       </c>
       <c r="D47" t="n">
-        <v>74.23999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>78.18000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>-6.49</v>
+        <v>4.22</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0767</v>
+        <v>0.054</v>
       </c>
       <c r="H47" t="n">
-        <v>8.09</v>
+        <v>6.82</v>
       </c>
       <c r="I47" t="n">
-        <v>68.69</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>76.75</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>80.12</v>
+        <v>74.13</v>
       </c>
       <c r="L47" t="n">
-        <v>83.5</v>
+        <v>78.23</v>
       </c>
       <c r="M47" t="n">
-        <v>89.22</v>
+        <v>82.23</v>
       </c>
       <c r="N47" t="n">
-        <v>94.93000000000001</v>
+        <v>86.22</v>
       </c>
       <c r="O47" t="n">
-        <v>95.95999999999999</v>
+        <v>90.42</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>78.42</v>
+        <v>82.53</v>
       </c>
       <c r="C48" t="n">
-        <v>84.61</v>
+        <v>89</v>
       </c>
       <c r="D48" t="n">
-        <v>77.79000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="E48" t="n">
-        <v>82.40000000000001</v>
+        <v>87.06</v>
       </c>
       <c r="F48" t="n">
-        <v>4.22</v>
+        <v>4.66</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.054</v>
+        <v>0.0566</v>
       </c>
       <c r="H48" t="n">
-        <v>6.82</v>
+        <v>7.5</v>
       </c>
       <c r="I48" t="n">
-        <v>66.15000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="J48" t="n">
-        <v>70.04000000000001</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>74.13</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>78.23</v>
+        <v>81.8</v>
       </c>
       <c r="M48" t="n">
-        <v>82.23</v>
+        <v>85.81</v>
       </c>
       <c r="N48" t="n">
-        <v>86.22</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="O48" t="n">
-        <v>90.42</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4526,7 +4516,7 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4542,7 +4532,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4552,69 +4542,71 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>82.53</v>
+        <v>86.5</v>
       </c>
       <c r="C49" t="n">
-        <v>89</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>81.5</v>
+        <v>79.62</v>
       </c>
       <c r="E49" t="n">
-        <v>87.06</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>4.66</v>
+        <v>-3.66</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0566</v>
+        <v>-0.042</v>
       </c>
       <c r="H49" t="n">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="I49" t="n">
-        <v>70.97</v>
+        <v>74</v>
       </c>
       <c r="J49" t="n">
-        <v>76.18000000000001</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>78.98999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="L49" t="n">
-        <v>81.8</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>85.81</v>
+        <v>90.81</v>
       </c>
       <c r="N49" t="n">
-        <v>89.81999999999999</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="O49" t="n">
-        <v>91.43000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4622,146 +4614,146 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>86.5</v>
+        <v>84.69</v>
       </c>
       <c r="C50" t="n">
-        <v>86.56999999999999</v>
+        <v>93.14</v>
       </c>
       <c r="D50" t="n">
-        <v>79.62</v>
+        <v>84.11</v>
       </c>
       <c r="E50" t="n">
-        <v>83.40000000000001</v>
+        <v>91.48</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.66</v>
+        <v>8.08</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.042</v>
+        <v>0.0969</v>
       </c>
       <c r="H50" t="n">
-        <v>6.95</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I50" t="n">
-        <v>74</v>
+        <v>72.67</v>
       </c>
       <c r="J50" t="n">
-        <v>80.45999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>83.31</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>86.15000000000001</v>
+        <v>83.25</v>
       </c>
       <c r="M50" t="n">
-        <v>90.81</v>
+        <v>86.88</v>
       </c>
       <c r="N50" t="n">
-        <v>95.45999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="O50" t="n">
-        <v>96.5</v>
+        <v>93.52</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="U50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>84.69</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>93.14</v>
+        <v>104.46</v>
       </c>
       <c r="D51" t="n">
-        <v>84.11</v>
+        <v>90.87</v>
       </c>
       <c r="E51" t="n">
-        <v>91.48</v>
+        <v>100.05</v>
       </c>
       <c r="F51" t="n">
-        <v>8.08</v>
+        <v>8.57</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0969</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>9.029999999999999</v>
+        <v>13.59</v>
       </c>
       <c r="I51" t="n">
-        <v>72.67</v>
+        <v>75.08</v>
       </c>
       <c r="J51" t="n">
-        <v>76.59999999999999</v>
+        <v>83.88</v>
       </c>
       <c r="K51" t="n">
-        <v>79.93000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="L51" t="n">
-        <v>83.25</v>
+        <v>90.05</v>
       </c>
       <c r="M51" t="n">
-        <v>86.88</v>
+        <v>96</v>
       </c>
       <c r="N51" t="n">
-        <v>90.5</v>
+        <v>101.94</v>
       </c>
       <c r="O51" t="n">
-        <v>93.52</v>
+        <v>102.17</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4772,7 +4764,7 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4787,10 +4779,12 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4800,50 +4794,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>92.26000000000001</v>
+        <v>102.25</v>
       </c>
       <c r="C52" t="n">
-        <v>104.46</v>
+        <v>106.75</v>
       </c>
       <c r="D52" t="n">
-        <v>90.87</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>100.05</v>
+        <v>100.3</v>
       </c>
       <c r="F52" t="n">
-        <v>8.57</v>
+        <v>0.25</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="H52" t="n">
-        <v>13.59</v>
+        <v>7.65</v>
       </c>
       <c r="I52" t="n">
-        <v>75.08</v>
+        <v>77.28</v>
       </c>
       <c r="J52" t="n">
-        <v>83.88</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>86.97</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>90.05</v>
+        <v>98.86</v>
       </c>
       <c r="M52" t="n">
-        <v>96</v>
+        <v>106.85</v>
       </c>
       <c r="N52" t="n">
-        <v>101.94</v>
+        <v>114.83</v>
       </c>
       <c r="O52" t="n">
-        <v>102.17</v>
+        <v>118.05</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4854,27 +4848,21 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4884,63 +4872,69 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>102.25</v>
+        <v>101</v>
       </c>
       <c r="C53" t="n">
-        <v>106.75</v>
+        <v>101.08</v>
       </c>
       <c r="D53" t="n">
-        <v>99.09999999999999</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>100.3</v>
+        <v>92.41</v>
       </c>
       <c r="F53" t="n">
-        <v>0.25</v>
+        <v>-7.89</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>7.65</v>
+        <v>12.37</v>
       </c>
       <c r="I53" t="n">
-        <v>77.28</v>
+        <v>91.45</v>
       </c>
       <c r="J53" t="n">
-        <v>87.65000000000001</v>
+        <v>91.34</v>
       </c>
       <c r="K53" t="n">
-        <v>93.26000000000001</v>
+        <v>96.48</v>
       </c>
       <c r="L53" t="n">
-        <v>98.86</v>
+        <v>101.61</v>
       </c>
       <c r="M53" t="n">
-        <v>106.85</v>
+        <v>104.13</v>
       </c>
       <c r="N53" t="n">
-        <v>114.83</v>
+        <v>106.64</v>
       </c>
       <c r="O53" t="n">
-        <v>118.05</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+        <v>114.4</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4952,79 +4946,77 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>101</v>
+        <v>93.58</v>
       </c>
       <c r="C54" t="n">
-        <v>101.08</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>88.70999999999999</v>
+        <v>88.06</v>
       </c>
       <c r="E54" t="n">
-        <v>92.41</v>
+        <v>91.11</v>
       </c>
       <c r="F54" t="n">
-        <v>-7.89</v>
+        <v>-1.3</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0141</v>
       </c>
       <c r="H54" t="n">
-        <v>12.37</v>
+        <v>8.48</v>
       </c>
       <c r="I54" t="n">
-        <v>91.45</v>
+        <v>76.34</v>
       </c>
       <c r="J54" t="n">
-        <v>91.34</v>
+        <v>78.8</v>
       </c>
       <c r="K54" t="n">
-        <v>96.48</v>
+        <v>86.23</v>
       </c>
       <c r="L54" t="n">
-        <v>101.61</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>104.13</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>106.64</v>
+        <v>103.54</v>
       </c>
       <c r="O54" t="n">
-        <v>114.4</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>113.45</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5036,7 +5028,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5050,50 +5042,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>93.58</v>
+        <v>91.77</v>
       </c>
       <c r="C55" t="n">
-        <v>96.54000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="D55" t="n">
-        <v>88.06</v>
+        <v>86.86</v>
       </c>
       <c r="E55" t="n">
-        <v>91.11</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.3</v>
+        <v>0.74</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0141</v>
+        <v>0.0081</v>
       </c>
       <c r="H55" t="n">
-        <v>8.48</v>
+        <v>6.34</v>
       </c>
       <c r="I55" t="n">
-        <v>76.34</v>
+        <v>79.58</v>
       </c>
       <c r="J55" t="n">
-        <v>78.8</v>
+        <v>82.03</v>
       </c>
       <c r="K55" t="n">
-        <v>86.23</v>
+        <v>86.87</v>
       </c>
       <c r="L55" t="n">
-        <v>93.65000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="M55" t="n">
-        <v>98.59999999999999</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>103.54</v>
+        <v>99</v>
       </c>
       <c r="O55" t="n">
-        <v>113.45</v>
+        <v>105.02</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5101,12 +5093,14 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5118,64 +5112,64 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>91.77</v>
+        <v>91.83</v>
       </c>
       <c r="C56" t="n">
-        <v>93.2</v>
+        <v>101.9</v>
       </c>
       <c r="D56" t="n">
-        <v>86.86</v>
+        <v>89.61</v>
       </c>
       <c r="E56" t="n">
-        <v>91.84999999999999</v>
+        <v>101.41</v>
       </c>
       <c r="F56" t="n">
-        <v>0.74</v>
+        <v>9.56</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0081</v>
+        <v>0.1041</v>
       </c>
       <c r="H56" t="n">
-        <v>6.34</v>
+        <v>12.29</v>
       </c>
       <c r="I56" t="n">
-        <v>79.58</v>
+        <v>80.52</v>
       </c>
       <c r="J56" t="n">
-        <v>82.03</v>
+        <v>86.42</v>
       </c>
       <c r="K56" t="n">
-        <v>86.87</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>91.7</v>
+        <v>90.94</v>
       </c>
       <c r="M56" t="n">
-        <v>95.34999999999999</v>
+        <v>95.02</v>
       </c>
       <c r="N56" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O56" t="n">
-        <v>105.02</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5183,83 +5177,83 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>91.83</v>
+        <v>101.75</v>
       </c>
       <c r="C57" t="n">
-        <v>101.9</v>
+        <v>110.48</v>
       </c>
       <c r="D57" t="n">
-        <v>89.61</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>101.41</v>
+        <v>103.44</v>
       </c>
       <c r="F57" t="n">
-        <v>9.56</v>
+        <v>2.03</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.1041</v>
+        <v>0.02</v>
       </c>
       <c r="H57" t="n">
-        <v>12.29</v>
+        <v>14.22</v>
       </c>
       <c r="I57" t="n">
-        <v>80.52</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>86.42</v>
+        <v>91.95</v>
       </c>
       <c r="K57" t="n">
-        <v>88.68000000000001</v>
+        <v>95.27</v>
       </c>
       <c r="L57" t="n">
-        <v>90.94</v>
+        <v>98.58</v>
       </c>
       <c r="M57" t="n">
-        <v>95.02</v>
+        <v>107.56</v>
       </c>
       <c r="N57" t="n">
-        <v>99.09999999999999</v>
+        <v>116.53</v>
       </c>
       <c r="O57" t="n">
-        <v>99.54000000000001</v>
+        <v>114.19</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5270,116 +5264,28 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>101.75</v>
-      </c>
-      <c r="C58" t="n">
-        <v>110.48</v>
-      </c>
-      <c r="D58" t="n">
-        <v>96.26000000000001</v>
-      </c>
-      <c r="E58" t="n">
-        <v>99.95999999999999</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0143</v>
-      </c>
-      <c r="H58" t="n">
-        <v>14.22</v>
-      </c>
-      <c r="I58" t="n">
-        <v>77.31999999999999</v>
-      </c>
-      <c r="J58" t="n">
-        <v>91.95</v>
-      </c>
-      <c r="K58" t="n">
-        <v>95.27</v>
-      </c>
-      <c r="L58" t="n">
-        <v>98.58</v>
-      </c>
-      <c r="M58" t="n">
-        <v>107.56</v>
-      </c>
-      <c r="N58" t="n">
-        <v>116.53</v>
-      </c>
-      <c r="O58" t="n">
-        <v>114.19</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -5223,13 +5223,13 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>103.44</v>
+        <v>101.88</v>
       </c>
       <c r="F57" t="n">
-        <v>2.03</v>
+        <v>0.47</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.02</v>
+        <v>0.0046</v>
       </c>
       <c r="H57" t="n">
         <v>14.22</v>
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U57" s="8" t="n">

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5223,13 +5226,13 @@
         <v>96.26000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>101.88</v>
+        <v>103.27</v>
       </c>
       <c r="F57" t="n">
-        <v>0.47</v>
+        <v>1.86</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.0183</v>
       </c>
       <c r="H57" t="n">
         <v>14.22</v>
@@ -5266,12 +5269,12 @@
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U57" s="8" t="n">
@@ -5286,6 +5289,90 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>101.29</v>
+      </c>
+      <c r="C58" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="D58" t="n">
+        <v>100.71</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I58" t="n">
+        <v>82.04000000000001</v>
+      </c>
+      <c r="J58" t="n">
+        <v>89</v>
+      </c>
+      <c r="K58" t="n">
+        <v>96.16</v>
+      </c>
+      <c r="L58" t="n">
+        <v>103.32</v>
+      </c>
+      <c r="M58" t="n">
+        <v>110.38</v>
+      </c>
+      <c r="N58" t="n">
+        <v>117.44</v>
+      </c>
+      <c r="O58" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,32 +659,34 @@
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>57.28</v>
+        <v>60.08</v>
       </c>
       <c r="J2" t="n">
-        <v>61.94</v>
+        <v>62.99</v>
       </c>
       <c r="K2" t="n">
-        <v>63.44</v>
+        <v>64.14</v>
       </c>
       <c r="L2" t="n">
-        <v>64.93000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="M2" t="n">
-        <v>68.01000000000001</v>
+        <v>67.31</v>
       </c>
       <c r="N2" t="n">
-        <v>71.08</v>
+        <v>69.33</v>
       </c>
       <c r="O2" t="n">
-        <v>70.98999999999999</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>69.59</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
@@ -5297,25 +5296,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>101.29</v>
+        <v>102.61</v>
       </c>
       <c r="C58" t="n">
-        <v>101.6</v>
+        <v>103.13</v>
       </c>
       <c r="D58" t="n">
-        <v>100.71</v>
+        <v>99.44</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>101.15</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-2.12</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0205</v>
       </c>
       <c r="H58" t="n">
-        <v>0.89</v>
+        <v>3.69</v>
       </c>
       <c r="I58" t="n">
         <v>82.04000000000001</v>
@@ -5338,10 +5337,8 @@
       <c r="O58" t="n">
         <v>124.7</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5349,9 +5346,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5370,7 +5367,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>60.08</v>
+        <v>61.7</v>
       </c>
       <c r="J2" t="n">
-        <v>62.99</v>
+        <v>63.6</v>
       </c>
       <c r="K2" t="n">
-        <v>64.14</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>65.28</v>
+        <v>65.48</v>
       </c>
       <c r="M2" t="n">
-        <v>67.31</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>69.33</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>69.59</v>
+        <v>68.78</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -5299,22 +5299,22 @@
         <v>102.61</v>
       </c>
       <c r="C58" t="n">
-        <v>103.13</v>
+        <v>103.55</v>
       </c>
       <c r="D58" t="n">
         <v>99.44</v>
       </c>
       <c r="E58" t="n">
-        <v>101.15</v>
+        <v>101.84</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.12</v>
+        <v>-1.43</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0205</v>
+        <v>-0.0138</v>
       </c>
       <c r="H58" t="n">
-        <v>3.69</v>
+        <v>4.11</v>
       </c>
       <c r="I58" t="n">
         <v>82.04000000000001</v>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>61.7</v>
+        <v>62.9</v>
       </c>
       <c r="J2" t="n">
-        <v>63.6</v>
+        <v>64.05</v>
       </c>
       <c r="K2" t="n">
-        <v>64.54000000000001</v>
+        <v>64.84</v>
       </c>
       <c r="L2" t="n">
-        <v>65.48</v>
+        <v>65.63</v>
       </c>
       <c r="M2" t="n">
-        <v>66.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>68.31999999999999</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>68.78</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -5299,22 +5299,22 @@
         <v>102.61</v>
       </c>
       <c r="C58" t="n">
-        <v>103.55</v>
+        <v>104.99</v>
       </c>
       <c r="D58" t="n">
         <v>99.44</v>
       </c>
       <c r="E58" t="n">
-        <v>101.84</v>
+        <v>104.12</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.43</v>
+        <v>0.85</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>4.11</v>
+        <v>5.55</v>
       </c>
       <c r="I58" t="n">
         <v>82.04000000000001</v>
@@ -5346,9 +5346,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/CL_weekly.xlsx
+++ b/three_gate/analysis/CL_weekly.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,66 +634,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>65.06999999999999</v>
+        <v>61.14</v>
       </c>
       <c r="C2" t="n">
-        <v>65.40000000000001</v>
+        <v>62.92</v>
       </c>
       <c r="D2" t="n">
-        <v>60.4</v>
+        <v>58.22</v>
       </c>
       <c r="E2" t="n">
-        <v>60.88</v>
+        <v>58.9</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.84</v>
+        <v>-1.98</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0736</v>
+        <v>-0.0325</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I2" t="n">
-        <v>62.9</v>
+        <v>55.4</v>
       </c>
       <c r="J2" t="n">
-        <v>64.05</v>
+        <v>54.87</v>
       </c>
       <c r="K2" t="n">
-        <v>64.84</v>
+        <v>58.38</v>
       </c>
       <c r="L2" t="n">
-        <v>65.63</v>
+        <v>61.89</v>
       </c>
       <c r="M2" t="n">
-        <v>66.59999999999999</v>
+        <v>63.38</v>
       </c>
       <c r="N2" t="n">
-        <v>67.56999999999999</v>
+        <v>64.87</v>
       </c>
       <c r="O2" t="n">
-        <v>68.18000000000001</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -710,58 +706,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.14</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>62.92</v>
+        <v>60.17</v>
       </c>
       <c r="D3" t="n">
-        <v>58.22</v>
+        <v>56.6</v>
       </c>
       <c r="E3" t="n">
-        <v>58.9</v>
+        <v>57.54</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.98</v>
+        <v>-1.36</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0325</v>
+        <v>-0.0231</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7</v>
+        <v>3.57</v>
       </c>
       <c r="I3" t="n">
-        <v>55.4</v>
+        <v>53.52</v>
       </c>
       <c r="J3" t="n">
-        <v>54.87</v>
+        <v>53.37</v>
       </c>
       <c r="K3" t="n">
-        <v>58.38</v>
+        <v>56.55</v>
       </c>
       <c r="L3" t="n">
-        <v>61.89</v>
+        <v>59.74</v>
       </c>
       <c r="M3" t="n">
-        <v>63.38</v>
+        <v>61.25</v>
       </c>
       <c r="N3" t="n">
-        <v>64.87</v>
+        <v>62.76</v>
       </c>
       <c r="O3" t="n">
-        <v>70.40000000000001</v>
+        <v>67.62</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -790,58 +790,62 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>57.73</v>
       </c>
       <c r="C4" t="n">
-        <v>60.17</v>
+        <v>62.59</v>
       </c>
       <c r="D4" t="n">
-        <v>56.6</v>
+        <v>56.35</v>
       </c>
       <c r="E4" t="n">
-        <v>57.54</v>
+        <v>61.5</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.36</v>
+        <v>3.96</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0231</v>
+        <v>0.0688</v>
       </c>
       <c r="H4" t="n">
-        <v>3.57</v>
+        <v>6.24</v>
       </c>
       <c r="I4" t="n">
-        <v>53.52</v>
+        <v>53.03</v>
       </c>
       <c r="J4" t="n">
-        <v>53.37</v>
+        <v>53.55</v>
       </c>
       <c r="K4" t="n">
-        <v>56.55</v>
+        <v>55.76</v>
       </c>
       <c r="L4" t="n">
-        <v>59.74</v>
+        <v>57.96</v>
       </c>
       <c r="M4" t="n">
-        <v>61.25</v>
+        <v>59.33</v>
       </c>
       <c r="N4" t="n">
-        <v>62.76</v>
+        <v>60.69</v>
       </c>
       <c r="O4" t="n">
-        <v>67.62</v>
+        <v>63.74</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -849,79 +853,85 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57.73</v>
+        <v>61.82</v>
       </c>
       <c r="C5" t="n">
-        <v>62.59</v>
+        <v>62.17</v>
       </c>
       <c r="D5" t="n">
-        <v>56.35</v>
+        <v>59.64</v>
       </c>
       <c r="E5" t="n">
-        <v>61.5</v>
+        <v>60.98</v>
       </c>
       <c r="F5" t="n">
-        <v>3.96</v>
+        <v>-0.52</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0688</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>6.24</v>
+        <v>2.53</v>
       </c>
       <c r="I5" t="n">
-        <v>53.03</v>
+        <v>50.11</v>
       </c>
       <c r="J5" t="n">
-        <v>53.55</v>
+        <v>56.27</v>
       </c>
       <c r="K5" t="n">
-        <v>55.76</v>
+        <v>58.38</v>
       </c>
       <c r="L5" t="n">
-        <v>57.96</v>
+        <v>60.48</v>
       </c>
       <c r="M5" t="n">
-        <v>59.33</v>
+        <v>64.62</v>
       </c>
       <c r="N5" t="n">
-        <v>60.69</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>63.74</v>
+        <v>68.83</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -934,80 +944,76 @@
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61.82</v>
+        <v>61.4</v>
       </c>
       <c r="C6" t="n">
-        <v>62.17</v>
+        <v>61.5</v>
       </c>
       <c r="D6" t="n">
-        <v>59.64</v>
+        <v>58.83</v>
       </c>
       <c r="E6" t="n">
-        <v>60.98</v>
+        <v>59.75</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.52</v>
+        <v>-1.23</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0202</v>
       </c>
       <c r="H6" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="I6" t="n">
-        <v>50.11</v>
+        <v>57.11</v>
       </c>
       <c r="J6" t="n">
-        <v>56.27</v>
+        <v>58.49</v>
       </c>
       <c r="K6" t="n">
-        <v>58.38</v>
+        <v>59.72</v>
       </c>
       <c r="L6" t="n">
-        <v>60.48</v>
+        <v>60.94</v>
       </c>
       <c r="M6" t="n">
-        <v>64.62</v>
+        <v>62.24</v>
       </c>
       <c r="N6" t="n">
-        <v>68.76000000000001</v>
+        <v>63.55</v>
       </c>
       <c r="O6" t="n">
-        <v>68.83</v>
+        <v>64.7</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1015,12 +1021,14 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1032,64 +1040,64 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>61.4</v>
+        <v>59.87</v>
       </c>
       <c r="C7" t="n">
-        <v>61.5</v>
+        <v>61.28</v>
       </c>
       <c r="D7" t="n">
-        <v>58.83</v>
+        <v>58.12</v>
       </c>
       <c r="E7" t="n">
-        <v>59.75</v>
+        <v>60.09</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.23</v>
+        <v>0.34</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0202</v>
+        <v>0.0057</v>
       </c>
       <c r="H7" t="n">
-        <v>2.67</v>
+        <v>3.16</v>
       </c>
       <c r="I7" t="n">
-        <v>57.11</v>
+        <v>56.16</v>
       </c>
       <c r="J7" t="n">
-        <v>58.49</v>
+        <v>56.87</v>
       </c>
       <c r="K7" t="n">
-        <v>59.72</v>
+        <v>58.42</v>
       </c>
       <c r="L7" t="n">
-        <v>60.94</v>
+        <v>59.96</v>
       </c>
       <c r="M7" t="n">
-        <v>62.24</v>
+        <v>61.08</v>
       </c>
       <c r="N7" t="n">
-        <v>63.55</v>
+        <v>62.21</v>
       </c>
       <c r="O7" t="n">
-        <v>64.7</v>
+        <v>64.17</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1099,16 +1107,18 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1116,64 +1126,64 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59.87</v>
+        <v>59.8</v>
       </c>
       <c r="C8" t="n">
-        <v>61.28</v>
+        <v>60.93</v>
       </c>
       <c r="D8" t="n">
-        <v>58.12</v>
+        <v>57.38</v>
       </c>
       <c r="E8" t="n">
-        <v>60.09</v>
+        <v>58.06</v>
       </c>
       <c r="F8" t="n">
-        <v>0.34</v>
+        <v>-2.03</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.0338</v>
       </c>
       <c r="H8" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="I8" t="n">
-        <v>56.16</v>
+        <v>54.96</v>
       </c>
       <c r="J8" t="n">
-        <v>56.87</v>
+        <v>57.13</v>
       </c>
       <c r="K8" t="n">
-        <v>58.42</v>
+        <v>58.51</v>
       </c>
       <c r="L8" t="n">
-        <v>59.96</v>
+        <v>59.89</v>
       </c>
       <c r="M8" t="n">
-        <v>61.08</v>
+        <v>61.67</v>
       </c>
       <c r="N8" t="n">
-        <v>62.21</v>
+        <v>63.45</v>
       </c>
       <c r="O8" t="n">
-        <v>64.17</v>
+        <v>64.44</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1183,18 +1193,16 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1202,64 +1210,64 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59.8</v>
+        <v>58.05</v>
       </c>
       <c r="C9" t="n">
-        <v>60.93</v>
+        <v>59.64</v>
       </c>
       <c r="D9" t="n">
-        <v>57.38</v>
+        <v>57.1</v>
       </c>
       <c r="E9" t="n">
-        <v>58.06</v>
+        <v>58.55</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.03</v>
+        <v>0.49</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>3.55</v>
+        <v>2.54</v>
       </c>
       <c r="I9" t="n">
-        <v>54.96</v>
+        <v>53.83</v>
       </c>
       <c r="J9" t="n">
-        <v>57.13</v>
+        <v>53.96</v>
       </c>
       <c r="K9" t="n">
-        <v>58.51</v>
+        <v>56.29</v>
       </c>
       <c r="L9" t="n">
-        <v>59.89</v>
+        <v>58.61</v>
       </c>
       <c r="M9" t="n">
-        <v>61.67</v>
+        <v>59.84</v>
       </c>
       <c r="N9" t="n">
-        <v>63.45</v>
+        <v>61.06</v>
       </c>
       <c r="O9" t="n">
-        <v>64.44</v>
+        <v>64.48</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1267,14 +1275,12 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1286,64 +1292,64 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58.05</v>
+        <v>58.96</v>
       </c>
       <c r="C10" t="n">
-        <v>59.64</v>
+        <v>60.5</v>
       </c>
       <c r="D10" t="n">
-        <v>57.1</v>
+        <v>58.28</v>
       </c>
       <c r="E10" t="n">
-        <v>58.55</v>
+        <v>60.08</v>
       </c>
       <c r="F10" t="n">
-        <v>0.49</v>
+        <v>1.53</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0261</v>
       </c>
       <c r="H10" t="n">
-        <v>2.54</v>
+        <v>2.22</v>
       </c>
       <c r="I10" t="n">
-        <v>53.83</v>
+        <v>54.56</v>
       </c>
       <c r="J10" t="n">
-        <v>53.96</v>
+        <v>56.1</v>
       </c>
       <c r="K10" t="n">
-        <v>56.29</v>
+        <v>57.28</v>
       </c>
       <c r="L10" t="n">
-        <v>58.61</v>
+        <v>58.46</v>
       </c>
       <c r="M10" t="n">
-        <v>59.84</v>
+        <v>59.82</v>
       </c>
       <c r="N10" t="n">
-        <v>61.06</v>
+        <v>61.18</v>
       </c>
       <c r="O10" t="n">
-        <v>64.48</v>
+        <v>62.18</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1354,13 +1360,15 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1368,84 +1376,82 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58.96</v>
+        <v>60.15</v>
       </c>
       <c r="C11" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="D11" t="n">
-        <v>58.28</v>
+        <v>57.01</v>
       </c>
       <c r="E11" t="n">
-        <v>60.08</v>
+        <v>57.44</v>
       </c>
       <c r="F11" t="n">
-        <v>1.53</v>
+        <v>-2.64</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0261</v>
+        <v>-0.0439</v>
       </c>
       <c r="H11" t="n">
-        <v>2.22</v>
+        <v>3.29</v>
       </c>
       <c r="I11" t="n">
-        <v>54.56</v>
+        <v>56.06</v>
       </c>
       <c r="J11" t="n">
-        <v>56.1</v>
+        <v>58.21</v>
       </c>
       <c r="K11" t="n">
-        <v>57.28</v>
+        <v>58.97</v>
       </c>
       <c r="L11" t="n">
-        <v>58.46</v>
+        <v>59.74</v>
       </c>
       <c r="M11" t="n">
-        <v>59.82</v>
+        <v>61.19</v>
       </c>
       <c r="N11" t="n">
-        <v>61.18</v>
+        <v>62.65</v>
       </c>
       <c r="O11" t="n">
-        <v>62.18</v>
+        <v>62.72</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1454,7 +1460,7 @@
       </c>
       <c r="W11" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -1462,64 +1468,62 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60.15</v>
+        <v>57.5</v>
       </c>
       <c r="C12" t="n">
-        <v>60.3</v>
+        <v>57.8</v>
       </c>
       <c r="D12" t="n">
-        <v>57.01</v>
+        <v>54.98</v>
       </c>
       <c r="E12" t="n">
-        <v>57.44</v>
+        <v>56.66</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.64</v>
+        <v>-0.78</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0439</v>
+        <v>-0.0136</v>
       </c>
       <c r="H12" t="n">
-        <v>3.29</v>
+        <v>2.82</v>
       </c>
       <c r="I12" t="n">
-        <v>56.06</v>
+        <v>53.72</v>
       </c>
       <c r="J12" t="n">
-        <v>58.21</v>
+        <v>53.54</v>
       </c>
       <c r="K12" t="n">
-        <v>58.97</v>
+        <v>55.79</v>
       </c>
       <c r="L12" t="n">
-        <v>59.74</v>
+        <v>58.05</v>
       </c>
       <c r="M12" t="n">
-        <v>61.19</v>
+        <v>59.08</v>
       </c>
       <c r="N12" t="n">
-        <v>62.65</v>
+        <v>60.12</v>
       </c>
       <c r="O12" t="n">
-        <v>62.72</v>
+        <v>63.59</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1534,7 +1538,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1544,50 +1548,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>57.5</v>
+        <v>56.63</v>
       </c>
       <c r="C13" t="n">
-        <v>57.8</v>
+        <v>58.88</v>
       </c>
       <c r="D13" t="n">
-        <v>54.98</v>
+        <v>56.6</v>
       </c>
       <c r="E13" t="n">
-        <v>56.66</v>
+        <v>56.74</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.78</v>
+        <v>0.08</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0136</v>
+        <v>0.0014</v>
       </c>
       <c r="H13" t="n">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="I13" t="n">
-        <v>53.72</v>
+        <v>52.16</v>
       </c>
       <c r="J13" t="n">
-        <v>53.54</v>
+        <v>53.98</v>
       </c>
       <c r="K13" t="n">
-        <v>55.79</v>
+        <v>55.25</v>
       </c>
       <c r="L13" t="n">
-        <v>58.05</v>
+        <v>56.52</v>
       </c>
       <c r="M13" t="n">
-        <v>59.08</v>
+        <v>58.07</v>
       </c>
       <c r="N13" t="n">
-        <v>60.12</v>
+        <v>59.61</v>
       </c>
       <c r="O13" t="n">
-        <v>63.59</v>
+        <v>60.62</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1595,18 +1599,18 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1614,60 +1618,64 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>56.63</v>
+        <v>57.04</v>
       </c>
       <c r="C14" t="n">
-        <v>58.88</v>
+        <v>58.55</v>
       </c>
       <c r="D14" t="n">
         <v>56.6</v>
       </c>
       <c r="E14" t="n">
-        <v>56.74</v>
+        <v>57.32</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08</v>
+        <v>0.58</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0014</v>
+        <v>0.0102</v>
       </c>
       <c r="H14" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="I14" t="n">
-        <v>52.16</v>
+        <v>54.32</v>
       </c>
       <c r="J14" t="n">
-        <v>53.98</v>
+        <v>53.96</v>
       </c>
       <c r="K14" t="n">
-        <v>55.25</v>
+        <v>55.6</v>
       </c>
       <c r="L14" t="n">
-        <v>56.52</v>
+        <v>57.24</v>
       </c>
       <c r="M14" t="n">
-        <v>58.07</v>
+        <v>57.88</v>
       </c>
       <c r="N14" t="n">
-        <v>59.61</v>
+        <v>58.52</v>
       </c>
       <c r="O14" t="n">
-        <v>60.62</v>
+        <v>61.16</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1688,70 +1696,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>57.04</v>
+        <v>57.47</v>
       </c>
       <c r="C15" t="n">
-        <v>58.55</v>
+        <v>59.77</v>
       </c>
       <c r="D15" t="n">
-        <v>56.6</v>
+        <v>55.76</v>
       </c>
       <c r="E15" t="n">
-        <v>57.32</v>
+        <v>59.12</v>
       </c>
       <c r="F15" t="n">
-        <v>0.58</v>
+        <v>1.8</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0314</v>
       </c>
       <c r="H15" t="n">
-        <v>1.95</v>
+        <v>4.01</v>
       </c>
       <c r="I15" t="n">
-        <v>54.32</v>
+        <v>54.65</v>
       </c>
       <c r="J15" t="n">
-        <v>53.96</v>
+        <v>55.24</v>
       </c>
       <c r="K15" t="n">
-        <v>55.6</v>
+        <v>56.34</v>
       </c>
       <c r="L15" t="n">
-        <v>57.24</v>
+        <v>57.45</v>
       </c>
       <c r="M15" t="n">
-        <v>57.88</v>
+        <v>58.3</v>
       </c>
       <c r="N15" t="n">
-        <v>58.52</v>
+        <v>59.14</v>
       </c>
       <c r="O15" t="n">
-        <v>61.16</v>
+        <v>60.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1759,12 +1769,14 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
@@ -1774,70 +1786,70 @@
       </c>
       <c r="U15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>57.47</v>
+        <v>59</v>
       </c>
       <c r="C16" t="n">
-        <v>59.77</v>
+        <v>62.36</v>
       </c>
       <c r="D16" t="n">
-        <v>55.76</v>
+        <v>58.45</v>
       </c>
       <c r="E16" t="n">
-        <v>59.12</v>
+        <v>59.44</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8</v>
+        <v>0.32</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0314</v>
+        <v>0.0054</v>
       </c>
       <c r="H16" t="n">
-        <v>4.01</v>
+        <v>3.91</v>
       </c>
       <c r="I16" t="n">
-        <v>54.65</v>
+        <v>51.75</v>
       </c>
       <c r="J16" t="n">
-        <v>55.24</v>
+        <v>55.79</v>
       </c>
       <c r="K16" t="n">
-        <v>56.34</v>
+        <v>57.11</v>
       </c>
       <c r="L16" t="n">
-        <v>57.45</v>
+        <v>58.44</v>
       </c>
       <c r="M16" t="n">
-        <v>58.3</v>
+        <v>61.12</v>
       </c>
       <c r="N16" t="n">
-        <v>59.14</v>
+        <v>63.81</v>
       </c>
       <c r="O16" t="n">
-        <v>60.5</v>
+        <v>63.78</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1845,87 +1857,83 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>59</v>
+        <v>59.01</v>
       </c>
       <c r="C17" t="n">
-        <v>62.36</v>
+        <v>61.36</v>
       </c>
       <c r="D17" t="n">
-        <v>58.45</v>
+        <v>58.7</v>
       </c>
       <c r="E17" t="n">
-        <v>59.44</v>
+        <v>61.07</v>
       </c>
       <c r="F17" t="n">
-        <v>0.32</v>
+        <v>1.63</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0054</v>
+        <v>0.0274</v>
       </c>
       <c r="H17" t="n">
-        <v>3.91</v>
+        <v>2.66</v>
       </c>
       <c r="I17" t="n">
-        <v>51.75</v>
+        <v>54.54</v>
       </c>
       <c r="J17" t="n">
-        <v>55.79</v>
+        <v>55.05</v>
       </c>
       <c r="K17" t="n">
-        <v>57.11</v>
+        <v>57.48</v>
       </c>
       <c r="L17" t="n">
-        <v>58.44</v>
+        <v>59.92</v>
       </c>
       <c r="M17" t="n">
-        <v>61.12</v>
+        <v>61.39</v>
       </c>
       <c r="N17" t="n">
-        <v>63.81</v>
+        <v>62.87</v>
       </c>
       <c r="O17" t="n">
-        <v>63.78</v>
+        <v>66.27</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1938,12 +1946,12 @@
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U17" s="8" t="n">
@@ -1952,64 +1960,64 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>59.01</v>
+        <v>61.22</v>
       </c>
       <c r="C18" t="n">
-        <v>61.36</v>
+        <v>66.48</v>
       </c>
       <c r="D18" t="n">
-        <v>58.7</v>
+        <v>60.14</v>
       </c>
       <c r="E18" t="n">
-        <v>61.07</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1.63</v>
+        <v>4.14</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0274</v>
+        <v>0.0678</v>
       </c>
       <c r="H18" t="n">
-        <v>2.66</v>
+        <v>6.34</v>
       </c>
       <c r="I18" t="n">
-        <v>54.54</v>
+        <v>56.04</v>
       </c>
       <c r="J18" t="n">
-        <v>55.05</v>
+        <v>58.93</v>
       </c>
       <c r="K18" t="n">
-        <v>57.48</v>
+        <v>59.74</v>
       </c>
       <c r="L18" t="n">
-        <v>59.92</v>
+        <v>60.55</v>
       </c>
       <c r="M18" t="n">
-        <v>61.39</v>
+        <v>62.4</v>
       </c>
       <c r="N18" t="n">
-        <v>62.87</v>
+        <v>64.25</v>
       </c>
       <c r="O18" t="n">
-        <v>66.27</v>
+        <v>64.02</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2027,73 +2035,73 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>61.22</v>
+        <v>64.72</v>
       </c>
       <c r="C19" t="n">
-        <v>66.48</v>
+        <v>65.53</v>
       </c>
       <c r="D19" t="n">
-        <v>60.14</v>
+        <v>61.12</v>
       </c>
       <c r="E19" t="n">
-        <v>65.20999999999999</v>
+        <v>63.55</v>
       </c>
       <c r="F19" t="n">
-        <v>4.14</v>
+        <v>-1.66</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0678</v>
+        <v>-0.0255</v>
       </c>
       <c r="H19" t="n">
-        <v>6.34</v>
+        <v>4.41</v>
       </c>
       <c r="I19" t="n">
-        <v>56.04</v>
+        <v>53.8</v>
       </c>
       <c r="J19" t="n">
-        <v>58.93</v>
+        <v>59.82</v>
       </c>
       <c r="K19" t="n">
-        <v>59.74</v>
+        <v>62.04</v>
       </c>
       <c r="L19" t="n">
-        <v>60.55</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>62.4</v>
+        <v>68.38</v>
       </c>
       <c r="N19" t="n">
-        <v>64.25</v>
+        <v>72.5</v>
       </c>
       <c r="O19" t="n">
-        <v>64.02</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2101,83 +2109,83 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>64.72</v>
+        <v>62.99</v>
       </c>
       <c r="C20" t="n">
-        <v>65.53</v>
+        <v>65.83</v>
       </c>
       <c r="D20" t="n">
-        <v>61.12</v>
+        <v>62.14</v>
       </c>
       <c r="E20" t="n">
-        <v>63.55</v>
+        <v>62.89</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.66</v>
+        <v>-0.66</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0255</v>
+        <v>-0.0104</v>
       </c>
       <c r="H20" t="n">
-        <v>4.41</v>
+        <v>3.69</v>
       </c>
       <c r="I20" t="n">
-        <v>53.8</v>
+        <v>56.71</v>
       </c>
       <c r="J20" t="n">
-        <v>59.82</v>
+        <v>59.25</v>
       </c>
       <c r="K20" t="n">
-        <v>62.04</v>
+        <v>61.34</v>
       </c>
       <c r="L20" t="n">
-        <v>64.26000000000001</v>
+        <v>63.44</v>
       </c>
       <c r="M20" t="n">
-        <v>68.38</v>
+        <v>65.75</v>
       </c>
       <c r="N20" t="n">
-        <v>72.5</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>72.81999999999999</v>
+        <v>69.94</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2185,83 +2193,83 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>62.99</v>
+        <v>63.3</v>
       </c>
       <c r="C21" t="n">
-        <v>65.83</v>
+        <v>67.05</v>
       </c>
       <c r="D21" t="n">
-        <v>62.14</v>
+        <v>61.87</v>
       </c>
       <c r="E21" t="n">
-        <v>62.89</v>
+        <v>66.39</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.66</v>
+        <v>3.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0104</v>
+        <v>0.0557</v>
       </c>
       <c r="H21" t="n">
-        <v>3.69</v>
+        <v>5.18</v>
       </c>
       <c r="I21" t="n">
-        <v>56.71</v>
+        <v>58.45</v>
       </c>
       <c r="J21" t="n">
-        <v>59.25</v>
+        <v>58.65</v>
       </c>
       <c r="K21" t="n">
-        <v>61.34</v>
+        <v>61.04</v>
       </c>
       <c r="L21" t="n">
         <v>63.44</v>
       </c>
       <c r="M21" t="n">
-        <v>65.75</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>68.06999999999999</v>
+        <v>66.03</v>
       </c>
       <c r="O21" t="n">
-        <v>69.94</v>
+        <v>69.52</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2272,9 +2280,9 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2282,13 +2290,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2302,50 +2312,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63.3</v>
+        <v>65.89</v>
       </c>
       <c r="C22" t="n">
-        <v>67.05</v>
+        <v>67.83</v>
       </c>
       <c r="D22" t="n">
-        <v>61.87</v>
+        <v>63.6</v>
       </c>
       <c r="E22" t="n">
-        <v>66.39</v>
+        <v>67.02</v>
       </c>
       <c r="F22" t="n">
-        <v>3.5</v>
+        <v>0.63</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0557</v>
+        <v>0.0095</v>
       </c>
       <c r="H22" t="n">
-        <v>5.18</v>
+        <v>4.23</v>
       </c>
       <c r="I22" t="n">
-        <v>58.45</v>
+        <v>56.69</v>
       </c>
       <c r="J22" t="n">
-        <v>58.65</v>
+        <v>62.17</v>
       </c>
       <c r="K22" t="n">
-        <v>61.04</v>
+        <v>63.8</v>
       </c>
       <c r="L22" t="n">
-        <v>63.44</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>64.73999999999999</v>
+        <v>68.98</v>
       </c>
       <c r="N22" t="n">
-        <v>66.03</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>69.52</v>
+        <v>72.23</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2353,85 +2363,79 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>65.89</v>
+        <v>75</v>
       </c>
       <c r="C23" t="n">
-        <v>67.83</v>
+        <v>92.61</v>
       </c>
       <c r="D23" t="n">
-        <v>63.6</v>
+        <v>69.2</v>
       </c>
       <c r="E23" t="n">
-        <v>67.02</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.63</v>
+        <v>23.88</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.3563</v>
       </c>
       <c r="H23" t="n">
-        <v>4.23</v>
+        <v>23.41</v>
       </c>
       <c r="I23" t="n">
-        <v>56.69</v>
+        <v>59.37</v>
       </c>
       <c r="J23" t="n">
-        <v>62.17</v>
+        <v>63.44</v>
       </c>
       <c r="K23" t="n">
-        <v>63.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>65.43000000000001</v>
+        <v>66.37</v>
       </c>
       <c r="M23" t="n">
-        <v>68.98</v>
+        <v>69.13</v>
       </c>
       <c r="N23" t="n">
-        <v>72.54000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>72.23</v>
+        <v>72.06</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2439,26 +2443,30 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2468,50 +2476,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C24" t="n">
-        <v>92.61</v>
+        <v>119.48</v>
       </c>
       <c r="D24" t="n">
-        <v>69.2</v>
+        <v>76.73</v>
       </c>
       <c r="E24" t="n">
-        <v>90.90000000000001</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>23.88</v>
+        <v>7.81</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.3563</v>
+        <v>0.0859</v>
       </c>
       <c r="H24" t="n">
-        <v>23.41</v>
+        <v>42.75</v>
       </c>
       <c r="I24" t="n">
-        <v>59.37</v>
+        <v>45.79</v>
       </c>
       <c r="J24" t="n">
-        <v>63.44</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>64.90000000000001</v>
+        <v>79.19</v>
       </c>
       <c r="L24" t="n">
-        <v>66.37</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>69.13</v>
+        <v>102.61</v>
       </c>
       <c r="N24" t="n">
-        <v>71.90000000000001</v>
+        <v>119.31</v>
       </c>
       <c r="O24" t="n">
-        <v>72.06</v>
+        <v>116.02</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2519,8 +2527,10 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
@@ -2529,20 +2539,20 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
+      <c r="V24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2552,50 +2562,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>98</v>
+        <v>100.93</v>
       </c>
       <c r="C25" t="n">
-        <v>119.48</v>
+        <v>102.44</v>
       </c>
       <c r="D25" t="n">
-        <v>76.73</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>98.70999999999999</v>
+        <v>98.31999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>7.81</v>
+        <v>-0.39</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0859</v>
+        <v>-0.004</v>
       </c>
       <c r="H25" t="n">
-        <v>42.75</v>
+        <v>10.48</v>
       </c>
       <c r="I25" t="n">
-        <v>45.79</v>
+        <v>33.98</v>
       </c>
       <c r="J25" t="n">
-        <v>72.48999999999999</v>
+        <v>56.26</v>
       </c>
       <c r="K25" t="n">
-        <v>79.19</v>
+        <v>77.33</v>
       </c>
       <c r="L25" t="n">
-        <v>85.90000000000001</v>
+        <v>98.41</v>
       </c>
       <c r="M25" t="n">
-        <v>102.61</v>
+        <v>120.08</v>
       </c>
       <c r="N25" t="n">
-        <v>119.31</v>
+        <v>141.76</v>
       </c>
       <c r="O25" t="n">
-        <v>116.02</v>
+        <v>162.23</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2603,98 +2613,98 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>100.93</v>
+        <v>100.51</v>
       </c>
       <c r="C26" t="n">
-        <v>102.44</v>
+        <v>101.67</v>
       </c>
       <c r="D26" t="n">
-        <v>91.95999999999999</v>
+        <v>84.37</v>
       </c>
       <c r="E26" t="n">
-        <v>98.31999999999999</v>
+        <v>99.64</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.39</v>
+        <v>1.32</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0134</v>
       </c>
       <c r="H26" t="n">
-        <v>10.48</v>
+        <v>17.3</v>
       </c>
       <c r="I26" t="n">
-        <v>33.98</v>
+        <v>81.48</v>
       </c>
       <c r="J26" t="n">
-        <v>56.26</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>77.33</v>
+        <v>93.08</v>
       </c>
       <c r="L26" t="n">
-        <v>98.41</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>120.08</v>
+        <v>103.56</v>
       </c>
       <c r="N26" t="n">
-        <v>141.76</v>
+        <v>109.36</v>
       </c>
       <c r="O26" t="n">
-        <v>162.23</v>
+        <v>112.92</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2706,7 +2716,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2720,71 +2730,69 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>100.51</v>
+        <v>102.6</v>
       </c>
       <c r="C27" t="n">
-        <v>101.67</v>
+        <v>113.97</v>
       </c>
       <c r="D27" t="n">
-        <v>84.37</v>
+        <v>96.5</v>
       </c>
       <c r="E27" t="n">
-        <v>99.64</v>
+        <v>111.54</v>
       </c>
       <c r="F27" t="n">
-        <v>1.32</v>
+        <v>11.9</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.1194</v>
       </c>
       <c r="H27" t="n">
-        <v>17.3</v>
+        <v>17.47</v>
       </c>
       <c r="I27" t="n">
-        <v>81.48</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>88.40000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>93.08</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>97.76000000000001</v>
+        <v>96.33</v>
       </c>
       <c r="M27" t="n">
-        <v>103.56</v>
+        <v>108.29</v>
       </c>
       <c r="N27" t="n">
-        <v>109.36</v>
+        <v>120.25</v>
       </c>
       <c r="O27" t="n">
-        <v>112.92</v>
+        <v>118.97</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2792,84 +2800,82 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>102.6</v>
+        <v>112.96</v>
       </c>
       <c r="C28" t="n">
-        <v>113.97</v>
+        <v>117.63</v>
       </c>
       <c r="D28" t="n">
-        <v>96.5</v>
+        <v>91.05</v>
       </c>
       <c r="E28" t="n">
-        <v>111.54</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>11.9</v>
+        <v>-14.97</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.1194</v>
+        <v>-0.1342</v>
       </c>
       <c r="H28" t="n">
-        <v>17.47</v>
+        <v>26.58</v>
       </c>
       <c r="I28" t="n">
-        <v>67.06999999999999</v>
+        <v>79.03</v>
       </c>
       <c r="J28" t="n">
-        <v>85.65000000000001</v>
+        <v>97.22</v>
       </c>
       <c r="K28" t="n">
-        <v>90.98999999999999</v>
+        <v>102.81</v>
       </c>
       <c r="L28" t="n">
-        <v>96.33</v>
+        <v>108.39</v>
       </c>
       <c r="M28" t="n">
-        <v>108.29</v>
+        <v>120.28</v>
       </c>
       <c r="N28" t="n">
-        <v>120.25</v>
+        <v>132.16</v>
       </c>
       <c r="O28" t="n">
-        <v>118.97</v>
+        <v>131.44</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
+      <c r="Q28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2878,72 +2884,74 @@
       </c>
       <c r="W28" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>112.96</v>
+        <v>102</v>
       </c>
       <c r="C29" t="n">
-        <v>117.63</v>
+        <v>105.63</v>
       </c>
       <c r="D29" t="n">
-        <v>91.05</v>
+        <v>80.56</v>
       </c>
       <c r="E29" t="n">
-        <v>96.56999999999999</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>-14.97</v>
+        <v>-12.72</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.1342</v>
+        <v>-0.1317</v>
       </c>
       <c r="H29" t="n">
-        <v>26.58</v>
+        <v>25.07</v>
       </c>
       <c r="I29" t="n">
-        <v>79.03</v>
+        <v>64.47</v>
       </c>
       <c r="J29" t="n">
-        <v>97.22</v>
+        <v>66.11</v>
       </c>
       <c r="K29" t="n">
-        <v>102.81</v>
+        <v>83.28</v>
       </c>
       <c r="L29" t="n">
-        <v>108.39</v>
+        <v>100.45</v>
       </c>
       <c r="M29" t="n">
-        <v>120.28</v>
+        <v>109.86</v>
       </c>
       <c r="N29" t="n">
-        <v>132.16</v>
+        <v>119.26</v>
       </c>
       <c r="O29" t="n">
-        <v>131.44</v>
+        <v>144.21</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -2958,64 +2966,60 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C30" t="n">
-        <v>105.63</v>
+        <v>98.39</v>
       </c>
       <c r="D30" t="n">
-        <v>80.56</v>
+        <v>87.02</v>
       </c>
       <c r="E30" t="n">
-        <v>83.84999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>-12.72</v>
+        <v>10.55</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.1317</v>
+        <v>0.1258</v>
       </c>
       <c r="H30" t="n">
-        <v>25.07</v>
+        <v>11.37</v>
       </c>
       <c r="I30" t="n">
-        <v>64.47</v>
+        <v>55.49</v>
       </c>
       <c r="J30" t="n">
-        <v>66.11</v>
+        <v>54.16</v>
       </c>
       <c r="K30" t="n">
-        <v>83.28</v>
+        <v>71.31</v>
       </c>
       <c r="L30" t="n">
-        <v>100.45</v>
+        <v>88.47</v>
       </c>
       <c r="M30" t="n">
-        <v>109.86</v>
+        <v>96.38</v>
       </c>
       <c r="N30" t="n">
-        <v>119.26</v>
+        <v>104.3</v>
       </c>
       <c r="O30" t="n">
-        <v>144.21</v>
+        <v>130.7</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3023,79 +3027,83 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>89</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>98.39</v>
+        <v>110.93</v>
       </c>
       <c r="D31" t="n">
-        <v>87.02</v>
+        <v>94.59</v>
       </c>
       <c r="E31" t="n">
-        <v>94.40000000000001</v>
+        <v>101.94</v>
       </c>
       <c r="F31" t="n">
-        <v>10.55</v>
+        <v>7.54</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.1258</v>
+        <v>0.0799</v>
       </c>
       <c r="H31" t="n">
-        <v>11.37</v>
+        <v>16.34</v>
       </c>
       <c r="I31" t="n">
-        <v>55.49</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>54.16</v>
+        <v>83.88</v>
       </c>
       <c r="K31" t="n">
-        <v>71.31</v>
+        <v>88.72</v>
       </c>
       <c r="L31" t="n">
-        <v>88.47</v>
+        <v>93.55</v>
       </c>
       <c r="M31" t="n">
-        <v>96.38</v>
+        <v>100.09</v>
       </c>
       <c r="N31" t="n">
-        <v>104.3</v>
+        <v>106.62</v>
       </c>
       <c r="O31" t="n">
-        <v>130.7</v>
+        <v>109.76</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3116,70 +3124,74 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>95.59999999999999</v>
+        <v>99.73</v>
       </c>
       <c r="C32" t="n">
-        <v>110.93</v>
+        <v>107.46</v>
       </c>
       <c r="D32" t="n">
-        <v>94.59</v>
+        <v>88.66</v>
       </c>
       <c r="E32" t="n">
-        <v>101.94</v>
+        <v>95.42</v>
       </c>
       <c r="F32" t="n">
-        <v>7.54</v>
+        <v>-6.52</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0799</v>
+        <v>-0.064</v>
       </c>
       <c r="H32" t="n">
-        <v>16.34</v>
+        <v>18.8</v>
       </c>
       <c r="I32" t="n">
-        <v>75.65000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="J32" t="n">
-        <v>83.88</v>
+        <v>85.19</v>
       </c>
       <c r="K32" t="n">
-        <v>88.72</v>
+        <v>93.77</v>
       </c>
       <c r="L32" t="n">
-        <v>93.55</v>
+        <v>102.35</v>
       </c>
       <c r="M32" t="n">
-        <v>100.09</v>
+        <v>110.11</v>
       </c>
       <c r="N32" t="n">
-        <v>106.62</v>
+        <v>117.87</v>
       </c>
       <c r="O32" t="n">
-        <v>109.76</v>
+        <v>127.27</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3187,87 +3199,79 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>99.73</v>
+        <v>98.19</v>
       </c>
       <c r="C33" t="n">
-        <v>107.46</v>
+        <v>106</v>
       </c>
       <c r="D33" t="n">
-        <v>88.66</v>
+        <v>96.13</v>
       </c>
       <c r="E33" t="n">
-        <v>95.42</v>
+        <v>105.42</v>
       </c>
       <c r="F33" t="n">
-        <v>-6.52</v>
+        <v>10</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.064</v>
+        <v>0.1048</v>
       </c>
       <c r="H33" t="n">
-        <v>18.8</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>78.25</v>
+        <v>69.86</v>
       </c>
       <c r="J33" t="n">
-        <v>85.19</v>
+        <v>75.3</v>
       </c>
       <c r="K33" t="n">
-        <v>93.77</v>
+        <v>86.02</v>
       </c>
       <c r="L33" t="n">
-        <v>102.35</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>110.11</v>
+        <v>104.82</v>
       </c>
       <c r="N33" t="n">
-        <v>117.87</v>
+        <v>112.9</v>
       </c>
       <c r="O33" t="n">
-        <v>127.27</v>
+        <v>126.26</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3275,177 +3279,181 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>98.19</v>
+        <v>106</v>
       </c>
       <c r="C34" t="n">
-        <v>106</v>
+        <v>109.47</v>
       </c>
       <c r="D34" t="n">
-        <v>96.13</v>
+        <v>94.73</v>
       </c>
       <c r="E34" t="n">
-        <v>105.42</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>-8.82</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.1048</v>
+        <v>-0.0837</v>
       </c>
       <c r="H34" t="n">
-        <v>9.869999999999999</v>
+        <v>14.74</v>
       </c>
       <c r="I34" t="n">
-        <v>69.86</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>75.3</v>
+        <v>97.73</v>
       </c>
       <c r="K34" t="n">
-        <v>86.02</v>
+        <v>100.48</v>
       </c>
       <c r="L34" t="n">
-        <v>96.73999999999999</v>
+        <v>103.24</v>
       </c>
       <c r="M34" t="n">
-        <v>104.82</v>
+        <v>110.35</v>
       </c>
       <c r="N34" t="n">
-        <v>112.9</v>
+        <v>117.47</v>
       </c>
       <c r="O34" t="n">
-        <v>126.26</v>
+        <v>115.87</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
+      <c r="Q34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>106</v>
+        <v>93.88</v>
       </c>
       <c r="C35" t="n">
-        <v>109.47</v>
+        <v>94.7</v>
       </c>
       <c r="D35" t="n">
-        <v>94.73</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>96.59999999999999</v>
+        <v>87.36</v>
       </c>
       <c r="F35" t="n">
-        <v>-8.82</v>
+        <v>-9.24</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0837</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>14.74</v>
+        <v>8.35</v>
       </c>
       <c r="I35" t="n">
-        <v>86.26000000000001</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>97.73</v>
+        <v>79.11</v>
       </c>
       <c r="K35" t="n">
-        <v>100.48</v>
+        <v>89.23</v>
       </c>
       <c r="L35" t="n">
-        <v>103.24</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>110.35</v>
+        <v>103.97</v>
       </c>
       <c r="N35" t="n">
-        <v>117.47</v>
+        <v>108.59</v>
       </c>
       <c r="O35" t="n">
-        <v>115.87</v>
+        <v>124.21</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -3460,64 +3468,60 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>93.88</v>
+        <v>88.5</v>
       </c>
       <c r="C36" t="n">
-        <v>94.7</v>
+        <v>97</v>
       </c>
       <c r="D36" t="n">
-        <v>86.34999999999999</v>
+        <v>88.45</v>
       </c>
       <c r="E36" t="n">
-        <v>87.36</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-9.24</v>
+        <v>3.18</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.09569999999999999</v>
+        <v>0.0364</v>
       </c>
       <c r="H36" t="n">
-        <v>8.35</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>79.98999999999999</v>
+        <v>78</v>
       </c>
       <c r="J36" t="n">
-        <v>79.11</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>89.23</v>
+        <v>83.19</v>
       </c>
       <c r="L36" t="n">
-        <v>99.34999999999999</v>
+        <v>88.94</v>
       </c>
       <c r="M36" t="n">
-        <v>103.97</v>
+        <v>91.53</v>
       </c>
       <c r="N36" t="n">
-        <v>108.59</v>
+        <v>94.13</v>
       </c>
       <c r="O36" t="n">
-        <v>124.21</v>
+        <v>103.05</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3525,79 +3529,85 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>88.5</v>
+        <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>97</v>
+        <v>95.47</v>
       </c>
       <c r="D37" t="n">
-        <v>88.45</v>
+        <v>83.2</v>
       </c>
       <c r="E37" t="n">
-        <v>90.54000000000001</v>
+        <v>84.88</v>
       </c>
       <c r="F37" t="n">
-        <v>3.18</v>
+        <v>-5.66</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0364</v>
+        <v>-0.0625</v>
       </c>
       <c r="H37" t="n">
-        <v>8.550000000000001</v>
+        <v>12.27</v>
       </c>
       <c r="I37" t="n">
-        <v>78</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>77.43000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>83.19</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>88.94</v>
+        <v>91.63</v>
       </c>
       <c r="M37" t="n">
-        <v>91.53</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>94.13</v>
+        <v>98</v>
       </c>
       <c r="O37" t="n">
-        <v>103.05</v>
+        <v>105.55</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3605,85 +3615,81 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>93</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>95.47</v>
+        <v>82.42</v>
       </c>
       <c r="D38" t="n">
-        <v>83.2</v>
+        <v>73.58</v>
       </c>
       <c r="E38" t="n">
-        <v>84.88</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-5.66</v>
+        <v>-7.34</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0625</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>12.27</v>
+        <v>8.84</v>
       </c>
       <c r="I38" t="n">
-        <v>79.90000000000001</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>80.90000000000001</v>
+        <v>70.38</v>
       </c>
       <c r="K38" t="n">
-        <v>86.26000000000001</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>91.63</v>
+        <v>87.11</v>
       </c>
       <c r="M38" t="n">
-        <v>94.81999999999999</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>98</v>
+        <v>94.92</v>
       </c>
       <c r="O38" t="n">
-        <v>105.55</v>
+        <v>107.74</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3701,10 +3707,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3712,7 +3716,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3722,60 +3726,62 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>81.40000000000001</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>82.42</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>73.58</v>
+        <v>68.56</v>
       </c>
       <c r="E39" t="n">
-        <v>77.54000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="F39" t="n">
-        <v>-7.34</v>
+        <v>-8.31</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.08649999999999999</v>
+        <v>-0.1072</v>
       </c>
       <c r="H39" t="n">
-        <v>8.84</v>
+        <v>10.4</v>
       </c>
       <c r="I39" t="n">
-        <v>70.93000000000001</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>70.38</v>
+        <v>68.47</v>
       </c>
       <c r="K39" t="n">
-        <v>78.73999999999999</v>
+        <v>73.12</v>
       </c>
       <c r="L39" t="n">
-        <v>87.11</v>
+        <v>77.77</v>
       </c>
       <c r="M39" t="n">
-        <v>91.01000000000001</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>94.92</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>107.74</v>
+        <v>91.26000000000001</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
@@ -3792,7 +3798,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3802,67 +3808,63 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>78.93000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="C40" t="n">
-        <v>78.95999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>68.56</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>69.23</v>
+        <v>68.78</v>
       </c>
       <c r="F40" t="n">
-        <v>-8.31</v>
+        <v>-0.45</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.1072</v>
+        <v>-0.0065</v>
       </c>
       <c r="H40" t="n">
-        <v>10.4</v>
+        <v>4.56</v>
       </c>
       <c r="I40" t="n">
-        <v>64.73999999999999</v>
+        <v>58.16</v>
       </c>
       <c r="J40" t="n">
-        <v>68.47</v>
+        <v>56.57</v>
       </c>
       <c r="K40" t="n">
-        <v>73.12</v>
+        <v>64.03</v>
       </c>
       <c r="L40" t="n">
-        <v>77.77</v>
+        <v>71.5</v>
       </c>
       <c r="M40" t="n">
-        <v>81.95999999999999</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>86.15000000000001</v>
+        <v>77.37</v>
       </c>
       <c r="O40" t="n">
-        <v>91.26000000000001</v>
+        <v>89.36</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3874,7 +3876,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3884,50 +3886,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>70.5</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>71.59999999999999</v>
+        <v>76.08</v>
       </c>
       <c r="D41" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>68.78</v>
+        <v>71.41</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.45</v>
+        <v>2.63</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0065</v>
+        <v>0.0382</v>
       </c>
       <c r="H41" t="n">
-        <v>4.56</v>
+        <v>8.26</v>
       </c>
       <c r="I41" t="n">
-        <v>58.16</v>
+        <v>62.48</v>
       </c>
       <c r="J41" t="n">
-        <v>56.57</v>
+        <v>63.95</v>
       </c>
       <c r="K41" t="n">
-        <v>64.03</v>
+        <v>66.5</v>
       </c>
       <c r="L41" t="n">
-        <v>71.5</v>
+        <v>69.05</v>
       </c>
       <c r="M41" t="n">
-        <v>74.43000000000001</v>
+        <v>71.06</v>
       </c>
       <c r="N41" t="n">
-        <v>77.37</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="O41" t="n">
-        <v>89.36</v>
+        <v>76.16</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3938,74 +3940,82 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>68.68000000000001</v>
+        <v>73.69</v>
       </c>
       <c r="C42" t="n">
-        <v>76.08</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>67.81999999999999</v>
+        <v>72.61</v>
       </c>
       <c r="E42" t="n">
-        <v>71.41</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>2.63</v>
+        <v>11.08</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0382</v>
+        <v>0.1552</v>
       </c>
       <c r="H42" t="n">
-        <v>8.26</v>
+        <v>10.15</v>
       </c>
       <c r="I42" t="n">
-        <v>62.48</v>
+        <v>59.56</v>
       </c>
       <c r="J42" t="n">
-        <v>63.95</v>
+        <v>62.88</v>
       </c>
       <c r="K42" t="n">
-        <v>66.5</v>
+        <v>67.28</v>
       </c>
       <c r="L42" t="n">
-        <v>69.05</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>71.06</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>73.06999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>76.16</v>
+        <v>84.34</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4023,75 +4033,73 @@
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
-      </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>73.69</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>82.76000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="D43" t="n">
-        <v>72.61</v>
+        <v>80.27</v>
       </c>
       <c r="E43" t="n">
-        <v>82.48999999999999</v>
+        <v>89.31</v>
       </c>
       <c r="F43" t="n">
-        <v>11.08</v>
+        <v>6.82</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.1552</v>
+        <v>0.0827</v>
       </c>
       <c r="H43" t="n">
-        <v>10.15</v>
+        <v>13.23</v>
       </c>
       <c r="I43" t="n">
-        <v>59.56</v>
+        <v>62.46</v>
       </c>
       <c r="J43" t="n">
-        <v>62.88</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>67.28</v>
+        <v>77.41</v>
       </c>
       <c r="L43" t="n">
-        <v>71.68000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="M43" t="n">
-        <v>75.54000000000001</v>
+        <v>87.56</v>
       </c>
       <c r="N43" t="n">
-        <v>79.40000000000001</v>
+        <v>95.04000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>84.34</v>
+        <v>92.91</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4109,20 +4117,18 @@
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4132,50 +4138,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>83.76000000000001</v>
+        <v>86.12</v>
       </c>
       <c r="C44" t="n">
-        <v>93.5</v>
+        <v>86.87</v>
       </c>
       <c r="D44" t="n">
-        <v>80.27</v>
+        <v>77.78</v>
       </c>
       <c r="E44" t="n">
-        <v>89.31</v>
+        <v>84.67</v>
       </c>
       <c r="F44" t="n">
-        <v>6.82</v>
+        <v>-4.64</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0827</v>
+        <v>-0.052</v>
       </c>
       <c r="H44" t="n">
-        <v>13.23</v>
+        <v>9.09</v>
       </c>
       <c r="I44" t="n">
-        <v>62.46</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>74.73999999999999</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>77.41</v>
+        <v>82.69</v>
       </c>
       <c r="L44" t="n">
-        <v>80.09</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>87.56</v>
+        <v>95.92</v>
       </c>
       <c r="N44" t="n">
-        <v>95.04000000000001</v>
+        <v>103.75</v>
       </c>
       <c r="O44" t="n">
-        <v>92.91</v>
+        <v>106.73</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4183,91 +4189,95 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="V44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>86.12</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C45" t="n">
-        <v>86.87</v>
+        <v>82.33</v>
       </c>
       <c r="D45" t="n">
-        <v>77.78</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>84.67</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>-4.64</v>
+        <v>-6.49</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.052</v>
+        <v>-0.0767</v>
       </c>
       <c r="H45" t="n">
-        <v>9.09</v>
+        <v>8.09</v>
       </c>
       <c r="I45" t="n">
-        <v>67.04000000000001</v>
+        <v>68.69</v>
       </c>
       <c r="J45" t="n">
-        <v>77.29000000000001</v>
+        <v>76.75</v>
       </c>
       <c r="K45" t="n">
-        <v>82.69</v>
+        <v>80.12</v>
       </c>
       <c r="L45" t="n">
-        <v>88.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="M45" t="n">
-        <v>95.92</v>
+        <v>89.22</v>
       </c>
       <c r="N45" t="n">
-        <v>103.75</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>106.73</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
@@ -4284,7 +4294,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4298,136 +4308,130 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>80.09999999999999</v>
+        <v>78.42</v>
       </c>
       <c r="C46" t="n">
-        <v>82.33</v>
+        <v>84.61</v>
       </c>
       <c r="D46" t="n">
-        <v>74.23999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>78.18000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>-6.49</v>
+        <v>4.22</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0767</v>
+        <v>0.054</v>
       </c>
       <c r="H46" t="n">
-        <v>8.09</v>
+        <v>6.82</v>
       </c>
       <c r="I46" t="n">
-        <v>68.69</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>76.75</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>80.12</v>
+        <v>74.13</v>
       </c>
       <c r="L46" t="n">
-        <v>83.5</v>
+        <v>78.23</v>
       </c>
       <c r="M46" t="n">
-        <v>89.22</v>
+        <v>82.23</v>
       </c>
       <c r="N46" t="n">
-        <v>94.93000000000001</v>
+        <v>86.22</v>
       </c>
       <c r="O46" t="n">
-        <v>95.95999999999999</v>
+        <v>90.42</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>78.42</v>
+        <v>82.53</v>
       </c>
       <c r="C47" t="n">
-        <v>84.61</v>
+        <v>89</v>
       </c>
       <c r="D47" t="n">
-        <v>77.79000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="E47" t="n">
-        <v>82.40000000000001</v>
+        <v>87.06</v>
       </c>
       <c r="F47" t="n">
-        <v>4.22</v>
+        <v>4.66</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.054</v>
+        <v>0.0566</v>
       </c>
       <c r="H47" t="n">
-        <v>6.82</v>
+        <v>7.5</v>
       </c>
       <c r="I47" t="n">
-        <v>66.15000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="J47" t="n">
-        <v>70.04000000000001</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>74.13</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>78.23</v>
+        <v>81.8</v>
       </c>
       <c r="M47" t="n">
-        <v>82.23</v>
+        <v>85.81</v>
       </c>
       <c r="N47" t="n">
-        <v>86.22</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="O47" t="n">
-        <v>90.42</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4454,7 +4458,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4464,216 +4468,218 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>82.53</v>
+        <v>86.5</v>
       </c>
       <c r="C48" t="n">
-        <v>89</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>81.5</v>
+        <v>79.62</v>
       </c>
       <c r="E48" t="n">
-        <v>87.06</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>4.66</v>
+        <v>-3.66</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0566</v>
+        <v>-0.042</v>
       </c>
       <c r="H48" t="n">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="I48" t="n">
-        <v>70.97</v>
+        <v>74</v>
       </c>
       <c r="J48" t="n">
-        <v>76.18000000000001</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>78.98999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="L48" t="n">
-        <v>81.8</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>85.81</v>
+        <v>90.81</v>
       </c>
       <c r="N48" t="n">
-        <v>89.81999999999999</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="O48" t="n">
-        <v>91.43000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>86.5</v>
+        <v>84.69</v>
       </c>
       <c r="C49" t="n">
-        <v>86.56999999999999</v>
+        <v>93.14</v>
       </c>
       <c r="D49" t="n">
-        <v>79.62</v>
+        <v>84.11</v>
       </c>
       <c r="E49" t="n">
-        <v>83.40000000000001</v>
+        <v>91.48</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.66</v>
+        <v>8.08</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.042</v>
+        <v>0.0969</v>
       </c>
       <c r="H49" t="n">
-        <v>6.95</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>74</v>
+        <v>72.67</v>
       </c>
       <c r="J49" t="n">
-        <v>80.45999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>83.31</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>86.15000000000001</v>
+        <v>83.25</v>
       </c>
       <c r="M49" t="n">
-        <v>90.81</v>
+        <v>86.88</v>
       </c>
       <c r="N49" t="n">
-        <v>95.45999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="O49" t="n">
-        <v>96.5</v>
+        <v>93.52</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>84.69</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>93.14</v>
+        <v>104.46</v>
       </c>
       <c r="D50" t="n">
-        <v>84.11</v>
+        <v>90.87</v>
       </c>
       <c r="E50" t="n">
-        <v>91.48</v>
+        <v>100.05</v>
       </c>
       <c r="F50" t="n">
-        <v>8.08</v>
+        <v>8.57</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0969</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>9.029999999999999</v>
+        <v>13.59</v>
       </c>
       <c r="I50" t="n">
-        <v>72.67</v>
+        <v>75.08</v>
       </c>
       <c r="J50" t="n">
-        <v>76.59999999999999</v>
+        <v>83.88</v>
       </c>
       <c r="K50" t="n">
-        <v>79.93000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="L50" t="n">
-        <v>83.25</v>
+        <v>90.05</v>
       </c>
       <c r="M50" t="n">
-        <v>86.88</v>
+        <v>96</v>
       </c>
       <c r="N50" t="n">
-        <v>90.5</v>
+        <v>101.94</v>
       </c>
       <c r="O50" t="n">
-        <v>93.52</v>
+        <v>102.17</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4699,10 +4705,12 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4712,50 +4720,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>92.26000000000001</v>
+        <v>102.25</v>
       </c>
       <c r="C51" t="n">
-        <v>104.46</v>
+        <v>106.75</v>
       </c>
       <c r="D51" t="n">
-        <v>90.87</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>100.05</v>
+        <v>100.3</v>
       </c>
       <c r="F51" t="n">
-        <v>8.57</v>
+        <v>0.25</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="H51" t="n">
-        <v>13.59</v>
+        <v>7.65</v>
       </c>
       <c r="I51" t="n">
-        <v>75.08</v>
+        <v>77.28</v>
       </c>
       <c r="J51" t="n">
-        <v>83.88</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>86.97</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>90.05</v>
+        <v>98.86</v>
       </c>
       <c r="M51" t="n">
-        <v>96</v>
+        <v>106.85</v>
       </c>
       <c r="N51" t="n">
-        <v>101.94</v>
+        <v>114.83</v>
       </c>
       <c r="O51" t="n">
-        <v>102.17</v>
+        <v>118.05</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4768,25 +4776,19 @@
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W51" s="11" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4796,63 +4798,69 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>102.25</v>
+        <v>101</v>
       </c>
       <c r="C52" t="n">
-        <v>106.75</v>
+        <v>101.08</v>
       </c>
       <c r="D52" t="n">
-        <v>99.09999999999999</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>100.3</v>
+        <v>92.41</v>
       </c>
       <c r="F52" t="n">
-        <v>0.25</v>
+        <v>-7.89</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>7.65</v>
+        <v>12.37</v>
       </c>
       <c r="I52" t="n">
-        <v>77.28</v>
+        <v>91.45</v>
       </c>
       <c r="J52" t="n">
-        <v>87.65000000000001</v>
+        <v>91.34</v>
       </c>
       <c r="K52" t="n">
-        <v>93.26000000000001</v>
+        <v>96.48</v>
       </c>
       <c r="L52" t="n">
-        <v>98.86</v>
+        <v>101.61</v>
       </c>
       <c r="M52" t="n">
-        <v>106.85</v>
+        <v>104.13</v>
       </c>
       <c r="N52" t="n">
-        <v>114.83</v>
+        <v>106.64</v>
       </c>
       <c r="O52" t="n">
-        <v>118.05</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>114.4</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4864,79 +4872,77 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>101</v>
+        <v>93.58</v>
       </c>
       <c r="C53" t="n">
-        <v>101.08</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>88.70999999999999</v>
+        <v>88.06</v>
       </c>
       <c r="E53" t="n">
-        <v>92.41</v>
+        <v>91.11</v>
       </c>
       <c r="F53" t="n">
-        <v>-7.89</v>
+        <v>-1.3</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0141</v>
       </c>
       <c r="H53" t="n">
-        <v>12.37</v>
+        <v>8.48</v>
       </c>
       <c r="I53" t="n">
-        <v>91.45</v>
+        <v>76.34</v>
       </c>
       <c r="J53" t="n">
-        <v>91.34</v>
+        <v>78.8</v>
       </c>
       <c r="K53" t="n">
-        <v>96.48</v>
+        <v>86.23</v>
       </c>
       <c r="L53" t="n">
-        <v>101.61</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>104.13</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>106.64</v>
+        <v>103.54</v>
       </c>
       <c r="O53" t="n">
-        <v>114.4</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>113.45</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4948,7 +4954,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4962,50 +4968,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>93.58</v>
+        <v>91.77</v>
       </c>
       <c r="C54" t="n">
-        <v>96.54000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="D54" t="n">
-        <v>88.06</v>
+        <v>86.86</v>
       </c>
       <c r="E54" t="n">
-        <v>91.11</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.3</v>
+        <v>0.74</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0141</v>
+        <v>0.0081</v>
       </c>
       <c r="H54" t="n">
-        <v>8.48</v>
+        <v>6.34</v>
       </c>
       <c r="I54" t="n">
-        <v>76.34</v>
+        <v>79.58</v>
       </c>
       <c r="J54" t="n">
-        <v>78.8</v>
+        <v>82.03</v>
       </c>
       <c r="K54" t="n">
-        <v>86.23</v>
+        <v>86.87</v>
       </c>
       <c r="L54" t="n">
-        <v>93.65000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="M54" t="n">
-        <v>98.59999999999999</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>103.54</v>
+        <v>99</v>
       </c>
       <c r="O54" t="n">
-        <v>113.45</v>
+        <v>105.02</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5013,12 +5019,14 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5030,64 +5038,64 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>91.77</v>
+        <v>91.83</v>
       </c>
       <c r="C55" t="n">
-        <v>93.2</v>
+        <v>101.9</v>
       </c>
       <c r="D55" t="n">
-        <v>86.86</v>
+        <v>89.61</v>
       </c>
       <c r="E55" t="n">
-        <v>91.84999999999999</v>
+        <v>101.41</v>
       </c>
       <c r="F55" t="n">
-        <v>0.74</v>
+        <v>9.56</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0081</v>
+        <v>0.1041</v>
       </c>
       <c r="H55" t="n">
-        <v>6.34</v>
+        <v>12.29</v>
       </c>
       <c r="I55" t="n">
-        <v>79.58</v>
+        <v>80.52</v>
       </c>
       <c r="J55" t="n">
-        <v>82.03</v>
+        <v>86.42</v>
       </c>
       <c r="K55" t="n">
-        <v>86.87</v>
+        <v>88.68000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>91.7</v>
+        <v>90.94</v>
       </c>
       <c r="M55" t="n">
-        <v>95.34999999999999</v>
+        <v>95.02</v>
       </c>
       <c r="N55" t="n">
-        <v>99</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O55" t="n">
-        <v>105.02</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5095,83 +5103,83 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>91.83</v>
+        <v>101.75</v>
       </c>
       <c r="C56" t="n">
-        <v>101.9</v>
+        <v>110.48</v>
       </c>
       <c r="D56" t="n">
-        <v>89.61</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>101.41</v>
+        <v>103.27</v>
       </c>
       <c r="F56" t="n">
-        <v>9.56</v>
+        <v>1.86</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.1041</v>
+        <v>0.0183</v>
       </c>
       <c r="H56" t="n">
-        <v>12.29</v>
+        <v>14.22</v>
       </c>
       <c r="I56" t="n">
-        <v>80.52</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>86.42</v>
+        <v>91.95</v>
       </c>
       <c r="K56" t="n">
-        <v>88.68000000000001</v>
+        <v>95.27</v>
       </c>
       <c r="L56" t="n">
-        <v>90.94</v>
+        <v>98.58</v>
       </c>
       <c r="M56" t="n">
-        <v>95.02</v>
+        <v>107.56</v>
       </c>
       <c r="N56" t="n">
-        <v>99.09999999999999</v>
+        <v>116.53</v>
       </c>
       <c r="O56" t="n">
-        <v>99.54000000000001</v>
+        <v>114.19</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5189,20 +5197,16 @@
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5212,50 +5216,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>101.75</v>
+        <v>102.61</v>
       </c>
       <c r="C57" t="n">
-        <v>110.48</v>
+        <v>104.99</v>
       </c>
       <c r="D57" t="n">
-        <v>96.26000000000001</v>
+        <v>99.44</v>
       </c>
       <c r="E57" t="n">
-        <v>103.27</v>
+        <v>102.95</v>
       </c>
       <c r="F57" t="n">
-        <v>1.86</v>
+        <v>-0.32</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0183</v>
+        <v>-0.0031</v>
       </c>
       <c r="H57" t="n">
-        <v>14.22</v>
+        <v>5.55</v>
       </c>
       <c r="I57" t="n">
-        <v>77.31999999999999</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>91.95</v>
+        <v>89</v>
       </c>
       <c r="K57" t="n">
-        <v>95.27</v>
+        <v>96.16</v>
       </c>
       <c r="L57" t="n">
-        <v>98.58</v>
+        <v>103.32</v>
       </c>
       <c r="M57" t="n">
-        <v>107.56</v>
+        <v>110.38</v>
       </c>
       <c r="N57" t="n">
-        <v>116.53</v>
+        <v>117.44</v>
       </c>
       <c r="O57" t="n">
-        <v>114.19</v>
+        <v>124.7</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5266,15 +5270,13 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5282,92 +5284,14 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>102.61</v>
-      </c>
-      <c r="C58" t="n">
-        <v>104.99</v>
-      </c>
-      <c r="D58" t="n">
-        <v>99.44</v>
-      </c>
-      <c r="E58" t="n">
-        <v>104.12</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.008200000000000001</v>
-      </c>
-      <c r="H58" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="I58" t="n">
-        <v>82.04000000000001</v>
-      </c>
-      <c r="J58" t="n">
-        <v>89</v>
-      </c>
-      <c r="K58" t="n">
-        <v>96.16</v>
-      </c>
-      <c r="L58" t="n">
-        <v>103.32</v>
-      </c>
-      <c r="M58" t="n">
-        <v>110.38</v>
-      </c>
-      <c r="N58" t="n">
-        <v>117.44</v>
-      </c>
-      <c r="O58" t="n">
-        <v>124.7</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
